--- a/feed_converted.xlsx
+++ b/feed_converted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E420"/>
+  <dimension ref="A1:E446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6900</v>
+        <v>6500</v>
       </c>
       <c r="C6" t="n">
         <v>9600</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7800</v>
+        <v>6800</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3850</v>
+        <v>3250</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4050</v>
+        <v>3550</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5350</v>
+        <v>4300</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5650</v>
+        <v>4500</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7750</v>
+        <v>6250</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8150</v>
+        <v>6650</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15250</v>
+        <v>11500</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15650</v>
+        <v>11950</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>15900</v>
+        <v>11950</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>7990</v>
+        <v>6650</v>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
@@ -3997,656 +3997,656 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>25 Роз Премиум в оформлении - 60 см</t>
+          <t>101 красно-белая роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C163" t="n">
-        <v>7800</v>
-      </c>
+        <v>24590</v>
+      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3736-6232-4930-b438-303165643933/38373375.jpg</t>
+          <t>https://static.tildacdn.com/stor3831-3066-4439-b961-663663623165/29975434.jpg</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-472980179331-25-roz-premium-v-oformlenii?editionuid=120293941621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=478488702861</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>25 красно-белых роз в оформлении - 60 см</t>
+          <t>101 красно-белая роза - 60 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C164" t="n">
-        <v>7800</v>
-      </c>
+        <v>24990</v>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3964-6438-4238-a635-313134306536/28552846.jpg</t>
+          <t>https://static.tildacdn.com/stor6362-3662-4063-a164-636263353730/41852469.jpg</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-710052950101-25-krasno-belih-roz-v-oformlenii?editionuid=111716594231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=658675482971</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>21 красная роза - 60 см - Атласная лента</t>
+          <t>25 Роз Премиум в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>5600</v>
+        <v>6800</v>
       </c>
       <c r="C165" t="n">
         <v>7800</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
+          <t>https://static.tildacdn.com/stor3736-6232-4930-b438-303165643933/38373375.jpg</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=679979674191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-472980179331-25-roz-premium-v-oformlenii?editionuid=120293941621</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>21 красная роза - 45 см - Атласная лента</t>
+          <t>25 красно-белых роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>3500</v>
+        <v>6800</v>
       </c>
       <c r="C166" t="n">
-        <v>6300</v>
+        <v>7800</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
+          <t>https://static.tildacdn.com/stor3964-6438-4238-a635-313134306536/28552846.jpg</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=688291434032</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-710052950101-25-krasno-belih-roz-v-oformlenii?editionuid=111716594231</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>51 розовая роза - 60 см</t>
+          <t>21 красная роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>12590</v>
+        <v>5600</v>
       </c>
       <c r="C167" t="n">
-        <v>16500</v>
+        <v>7800</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3434-6137-4538-b861-386430633162/A14C231B-75DB-4B7B-B.JPG</t>
+          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-289807833441-51-rozovaya-roza?editionuid=895253955391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=679979674191</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>15 Розовых роз Премиум в упаковке - 60 см</t>
+          <t>21 красная роза - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>4300</v>
+        <v>3500</v>
       </c>
       <c r="C168" t="n">
-        <v>5700</v>
+        <v>6300</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3562-6666-4866-a631-386530363233/69119634.jpg</t>
+          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=688291434032</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>51 роза микс в крафте - 60 см</t>
+          <t>51 розовая роза - 60 см</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>12990</v>
-      </c>
-      <c r="C169" t="inlineStr"/>
+        <v>12590</v>
+      </c>
+      <c r="C169" t="n">
+        <v>16500</v>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6136-3162-4138-b562-653731633664/FullSizeRender_4.jpg</t>
+          <t>https://static.tildacdn.com/tild3434-6137-4538-b861-386430633162/A14C231B-75DB-4B7B-B.JPG</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-289807833441-51-rozovaya-roza?editionuid=895253955391</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>25 красных роз с оформлением - 45 см - Матовая бумага</t>
+          <t>15 Розовых роз Премиум в упаковке - 60 см</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>4300</v>
       </c>
-      <c r="C170" t="inlineStr"/>
+      <c r="C170" t="n">
+        <v>5700</v>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
+          <t>https://static.tildacdn.com/stor3562-6666-4866-a631-386530363233/69119634.jpg</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>25 красных роз с оформлением - 60 см - Матовая бумага</t>
+          <t>151 роза в корзине - 60 см</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C171" t="inlineStr"/>
+        <v>45500</v>
+      </c>
+      <c r="C171" t="n">
+        <v>49000</v>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
+          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>301 роза в корзине - 60 см</t>
+          <t>151 роза в корзине - 45 см</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>65500</v>
-      </c>
-      <c r="C172" t="inlineStr"/>
+        <v>18990</v>
+      </c>
+      <c r="C172" t="n">
+        <v>39000</v>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
+          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=502662350182</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>301 роза в корзине - 45 см</t>
+          <t>51 роза микс в крафте - 60 см</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>32500</v>
+        <v>12990</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
+          <t>https://static.tildacdn.com/tild6136-3162-4138-b562-653731633664/FullSizeRender_4.jpg</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>11 красных роз в крафте - 60 см</t>
+          <t>25 красных роз с оформлением - 45 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>3300</v>
+        <v>4300</v>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>11 красных роз в крафте - 45 см</t>
+          <t>25 красных роз с оформлением - 60 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2200</v>
+        <v>6800</v>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>15 красных роз в оформлении - 60 см</t>
+          <t>301 роза в корзине - 60 см</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>4800</v>
-      </c>
-      <c r="C176" t="n">
-        <v>5900</v>
-      </c>
+        <v>65500</v>
+      </c>
+      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
+          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>15 красных роз в оформлении - 45 см</t>
+          <t>301 роза в корзине - 45 см</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2350</v>
-      </c>
-      <c r="C177" t="n">
-        <v>3500</v>
-      </c>
+        <v>32500</v>
+      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
+          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>25 кремовых роз в упаковке - 60 см</t>
+          <t>11 красных роз в крафте - 60 см</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>6800</v>
+        <v>3300</v>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3437-4165-b166-393339663536/27441782.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Букет КЛАССИКА</t>
+          <t>11 красных роз в крафте - 45 см</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>3500</v>
+        <v>2200</v>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6362-3466-4262-b537-646161643436/11667921.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759586080041-buket-klassika</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>25 красных роз в крафте - 60 см</t>
+          <t>15 красных роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C180" t="inlineStr"/>
+        <v>4800</v>
+      </c>
+      <c r="C180" t="n">
+        <v>5900</v>
+      </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>25 красных роз в крафте - 45 см</t>
+          <t>15 красных роз в оформлении - 45 см</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C181" t="inlineStr"/>
+        <v>2350</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3500</v>
+      </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>21 красная роза в цветной коробке</t>
+          <t>25 кремовых роз в упаковке - 60 см</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>7300</v>
-      </c>
-      <c r="C182" t="n">
-        <v>8700</v>
-      </c>
+        <v>6800</v>
+      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6661-3763-4866-a530-333563333863/60558C1C-4284-4D41-A.JPG</t>
+          <t>https://static.tildacdn.com/stor3530-3437-4165-b166-393339663536/27441782.jpg</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-887039306391-21-krasnaya-roza-v-tsvetnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>25 красных роз в коробке</t>
+          <t>Букет КЛАССИКА с красными розами и хризантемами</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>8800</v>
-      </c>
-      <c r="C183" t="n">
-        <v>11000</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6163-3466-4231-b833-303730383136/FCA8C57F-F641-4EA7-8.JPG</t>
+          <t>https://static.tildacdn.com/stor6362-3466-4262-b537-646161643436/11667921.jpg</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-395916445391-25-krasnih-roz-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Атласная лента</t>
+          <t>25 красных роз в крафте - 60 см</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>24590</v>
-      </c>
-      <c r="C184" t="n">
-        <v>35500</v>
-      </c>
+        <v>6800</v>
+      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
+          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Матова бумага</t>
+          <t>25 красных роз в крафте - 45 см</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>24990</v>
-      </c>
-      <c r="C185" t="n">
-        <v>35500</v>
-      </c>
+        <v>4300</v>
+      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Атласная лента</t>
+          <t>21 красная роза в цветной коробке</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>15500</v>
+        <v>7300</v>
       </c>
       <c r="C186" t="n">
-        <v>15300</v>
+        <v>8700</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/tild6661-3763-4866-a530-333563333863/60558C1C-4284-4D41-A.JPG</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-887039306391-21-krasnaya-roza-v-tsvetnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Матова бумага</t>
+          <t>25 красных роз в коробке</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>15900</v>
+        <v>8800</v>
       </c>
       <c r="C187" t="n">
-        <v>15500</v>
+        <v>11000</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
+          <t>https://static.tildacdn.com/tild6163-3466-4231-b833-303730383136/FCA8C57F-F641-4EA7-8.JPG</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-395916445391-25-krasnih-roz-v-korobke</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
+          <t>101 красная роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>3850</v>
+        <v>24590</v>
       </c>
       <c r="C188" t="n">
-        <v>4200</v>
+        <v>35500</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
+          <t>101 красная роза - 60 см - Матова бумага</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>3850</v>
+        <v>24990</v>
       </c>
       <c r="C189" t="n">
-        <v>4200</v>
+        <v>35500</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
+          <t>101 красная роза - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>5100</v>
+        <v>11500</v>
       </c>
       <c r="C190" t="n">
-        <v>6900</v>
+        <v>15300</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
+          <t>101 красная роза - 45 см - Матова бумага</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>5100</v>
-      </c>
-      <c r="C191" t="inlineStr"/>
+        <v>11950</v>
+      </c>
+      <c r="C191" t="n">
+        <v>15500</v>
+      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>6950</v>
-      </c>
-      <c r="C192" t="inlineStr"/>
+        <v>3850</v>
+      </c>
+      <c r="C192" t="n">
+        <v>4200</v>
+      </c>
       <c r="D192" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
@@ -4654,41 +4654,45 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>6950</v>
-      </c>
-      <c r="C193" t="inlineStr"/>
+        <v>3850</v>
+      </c>
+      <c r="C193" t="n">
+        <v>4200</v>
+      </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>8150</v>
-      </c>
-      <c r="C194" t="inlineStr"/>
+        <v>5100</v>
+      </c>
+      <c r="C194" t="n">
+        <v>6900</v>
+      </c>
       <c r="D194" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
@@ -4696,18 +4700,18 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>8150</v>
+        <v>5100</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
@@ -4717,18 +4721,18 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>9950</v>
+        <v>6950</v>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
@@ -4738,18 +4742,18 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>9950</v>
+        <v>6950</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
@@ -4759,274 +4763,274 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>11150</v>
+        <v>8150</v>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
+          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>11150</v>
-      </c>
-      <c r="C199" t="n">
-        <v>11300</v>
-      </c>
+        <v>8150</v>
+      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
+          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>15990</v>
+        <v>9950</v>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
+          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>15990</v>
+        <v>9950</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
+          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>2900</v>
+        <v>11150</v>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>3700</v>
-      </c>
-      <c r="C203" t="inlineStr"/>
+        <v>11150</v>
+      </c>
+      <c r="C203" t="n">
+        <v>11300</v>
+      </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
+          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>15 красно белых роз в оформлении</t>
+          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C204" t="n">
-        <v>6800</v>
-      </c>
+        <v>15990</v>
+      </c>
+      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
+          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Raffaello</t>
+          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>690</v>
+        <v>15990</v>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
+          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
+          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
+          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
+          <t>15 красно белых роз в оформлении</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C208" t="inlineStr"/>
+        <v>4300</v>
+      </c>
+      <c r="C208" t="n">
+        <v>6800</v>
+      </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
+          <t>Raffaello</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1800</v>
+        <v>690</v>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1400</v>
+        <v>3000</v>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
@@ -5036,18 +5040,18 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1000</v>
+        <v>3800</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
@@ -5057,102 +5061,102 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>3800</v>
+        <v>1800</v>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>6200</v>
+        <v>1000</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
@@ -5162,18 +5166,18 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>1800</v>
+        <v>3800</v>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
@@ -5183,18 +5187,18 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1400</v>
+        <v>5000</v>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
@@ -5204,18 +5208,18 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1000</v>
+        <v>6200</v>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
@@ -5225,102 +5229,102 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 15</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>3750</v>
+        <v>7000</v>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 19</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>4750</v>
+        <v>1800</v>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 25</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>6350</v>
+        <v>1400</v>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 31</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>7750</v>
+        <v>1000</v>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 35</t>
+          <t>Набор из гелиевых шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>8750</v>
+        <v>3750</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
@@ -5330,18 +5334,18 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 9</t>
+          <t>Набор из гелиевых шаров "Сердце" - 19</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>2250</v>
+        <v>4750</v>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
@@ -5351,18 +5355,18 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 7</t>
+          <t>Набор из гелиевых шаров "Сердце" - 25</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>1750</v>
+        <v>6350</v>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
@@ -5372,18 +5376,18 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 5</t>
+          <t>Набор из гелиевых шаров "Сердце" - 31</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1250</v>
+        <v>7750</v>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
@@ -5393,18 +5397,18 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 11</t>
+          <t>Набор из гелиевых шаров "Сердце" - 35</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>2750</v>
+        <v>8750</v>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
@@ -5414,102 +5418,102 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 15</t>
+          <t>Набор из гелиевых шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>6750</v>
+        <v>2250</v>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 11</t>
+          <t>Набор из гелиевых шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>4950</v>
+        <v>1750</v>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 9</t>
+          <t>Набор из гелиевых шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>4050</v>
+        <v>1250</v>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 7</t>
+          <t>Набор из гелиевых шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>3150</v>
+        <v>2750</v>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 5</t>
+          <t>Набор из фольгированных шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2250</v>
+        <v>6750</v>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
@@ -5519,113 +5523,105 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
+          <t>Набор из фольгированных шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C234" t="n">
-        <v>4500</v>
-      </c>
+        <v>4950</v>
+      </c>
+      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
+          <t>Набор из фольгированных шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>5600</v>
-      </c>
-      <c r="C235" t="n">
-        <v>6100</v>
-      </c>
+        <v>4050</v>
+      </c>
+      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
+          <t>Набор из фольгированных шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>7700</v>
-      </c>
-      <c r="C236" t="n">
-        <v>8500</v>
-      </c>
+        <v>3150</v>
+      </c>
+      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
+          <t>Набор из фольгированных шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>9100</v>
-      </c>
-      <c r="C237" t="n">
-        <v>10100</v>
-      </c>
+        <v>2250</v>
+      </c>
+      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>12600</v>
+        <v>4200</v>
       </c>
       <c r="C238" t="n">
-        <v>14100</v>
+        <v>4500</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -5634,20 +5630,22 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>3700</v>
-      </c>
-      <c r="C239" t="inlineStr"/>
+        <v>5600</v>
+      </c>
+      <c r="C239" t="n">
+        <v>6100</v>
+      </c>
       <c r="D239" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5655,20 +5653,22 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C240" t="inlineStr"/>
+        <v>7700</v>
+      </c>
+      <c r="C240" t="n">
+        <v>8500</v>
+      </c>
       <c r="D240" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5676,21 +5676,21 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>17690</v>
+        <v>9100</v>
       </c>
       <c r="C241" t="n">
-        <v>18690</v>
+        <v>10100</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -5699,21 +5699,21 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>34690</v>
+        <v>12600</v>
       </c>
       <c r="C242" t="n">
-        <v>38690</v>
+        <v>14100</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -5722,123 +5722,129 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ - Посмотреть...</t>
+          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>4990</v>
+        <v>3700</v>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ - Raffaello (+690 руб)</t>
+          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>5680</v>
+        <v>2900</v>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ - 5 шаров микс (+1000руб)</t>
+          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>5990</v>
-      </c>
-      <c r="C245" t="inlineStr"/>
+        <v>17690</v>
+      </c>
+      <c r="C245" t="n">
+        <v>18690</v>
+      </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>5990</v>
-      </c>
-      <c r="C246" t="inlineStr"/>
+        <v>34690</v>
+      </c>
+      <c r="C246" t="n">
+        <v>38690</v>
+      </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Стильный букет в крафтовой сумочке</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>6240</v>
-      </c>
-      <c r="C247" t="inlineStr"/>
+        <v>4200</v>
+      </c>
+      <c r="C247" t="n">
+        <v>5200</v>
+      </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ - Игрушка-медведь (+1300 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>6290</v>
+        <v>4990</v>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
@@ -5848,18 +5854,18 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ - Игрушка мишка 110см (+5500руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>10490</v>
+        <v>5680</v>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
@@ -5869,179 +5875,169 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ДОРОГУША</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C250" t="n">
-        <v>8500</v>
-      </c>
+        <v>5990</v>
+      </c>
+      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Коробка гигант с радужной гипсофилой</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>9999</v>
-      </c>
-      <c r="C251" t="n">
-        <v>10990</v>
-      </c>
+        <v>5990</v>
+      </c>
+      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Посмотреть...</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>4650</v>
-      </c>
-      <c r="C252" t="n">
-        <v>5200</v>
-      </c>
+        <v>6240</v>
+      </c>
+      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>5340</v>
-      </c>
-      <c r="C253" t="n">
-        <v>5200</v>
-      </c>
+        <v>6290</v>
+      </c>
+      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>5650</v>
-      </c>
-      <c r="C254" t="n">
-        <v>5200</v>
-      </c>
+        <v>10490</v>
+      </c>
+      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
+          <t>ДОРОГУША из красных роз с орхидеями</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>5650</v>
+        <v>7500</v>
       </c>
       <c r="C255" t="n">
-        <v>5200</v>
+        <v>8500</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Коробка гигант с радужной гипсофилой</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>5900</v>
+        <v>9999</v>
       </c>
       <c r="C256" t="n">
-        <v>5200</v>
+        <v>10990</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
+          <t>Букет Малиновое вино - Посмотреть...</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>5950</v>
+        <v>4650</v>
       </c>
       <c r="C257" t="n">
         <v>5200</v>
@@ -6060,11 +6056,11 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
+          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>10150</v>
+        <v>5340</v>
       </c>
       <c r="C258" t="n">
         <v>5200</v>
@@ -6083,126 +6079,126 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Посмотреть...</t>
+          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>2500</v>
+        <v>5650</v>
       </c>
       <c r="C259" t="n">
-        <v>2380</v>
+        <v>5200</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
+          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>3190</v>
+        <v>5650</v>
       </c>
       <c r="C260" t="n">
-        <v>2380</v>
+        <v>5200</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
+          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>3500</v>
+        <v>5900</v>
       </c>
       <c r="C261" t="n">
-        <v>2380</v>
+        <v>5200</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>3500</v>
+        <v>5950</v>
       </c>
       <c r="C262" t="n">
-        <v>2380</v>
+        <v>5200</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>3750</v>
+        <v>10150</v>
       </c>
       <c r="C263" t="n">
-        <v>2380</v>
+        <v>5200</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
+          <t>11альстромерий в оформлении - Посмотреть...</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>3800</v>
+        <v>2500</v>
       </c>
       <c r="C264" t="n">
         <v>2380</v>
@@ -6221,11 +6217,11 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
+          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>8000</v>
+        <v>3190</v>
       </c>
       <c r="C265" t="n">
         <v>2380</v>
@@ -6244,105 +6240,115 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>900</v>
-      </c>
-      <c r="C266" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="C266" t="n">
+        <v>2380</v>
+      </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>900</v>
-      </c>
-      <c r="C267" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="C267" t="n">
+        <v>2380</v>
+      </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>900</v>
-      </c>
-      <c r="C268" t="inlineStr"/>
+        <v>3750</v>
+      </c>
+      <c r="C268" t="n">
+        <v>2380</v>
+      </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>900</v>
-      </c>
-      <c r="C269" t="inlineStr"/>
+        <v>3800</v>
+      </c>
+      <c r="C269" t="n">
+        <v>2380</v>
+      </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>900</v>
-      </c>
-      <c r="C270" t="inlineStr"/>
+        <v>8000</v>
+      </c>
+      <c r="C270" t="n">
+        <v>2380</v>
+      </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
@@ -6358,12 +6364,12 @@
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
         </is>
       </c>
     </row>
@@ -6379,12 +6385,12 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
         </is>
       </c>
     </row>
@@ -6400,12 +6406,12 @@
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6427,12 @@
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
         </is>
       </c>
     </row>
@@ -6442,348 +6448,342 @@
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Комплимент "Куколка"</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>3000</v>
+        <v>900</v>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
+          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-332537387381-kompliment-kukolka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Букет НАСТРОЕНИЕ</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>3690</v>
+        <v>900</v>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
+          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Зефирный - Белые</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C278" t="n">
-        <v>3500</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
+          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Зефирный - Микс</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C279" t="n">
-        <v>3500</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
+          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ - Нежный</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>3450</v>
-      </c>
-      <c r="C280" t="n">
-        <v>3800</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3061-4535-b035-306430303965/35298752.jpg</t>
+          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit?editionuid=430145379292</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ - Яркие</t>
+          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>3550</v>
-      </c>
-      <c r="C281" t="n">
-        <v>3900</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-3031-4331-b733-356664626131/31576954.jpg</t>
+          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit?editionuid=628386621972</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>КРЕМ ДЖЕМ С ЭВКАЛИПТОМ</t>
+          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>3950</v>
+        <v>3690</v>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6637-6164-4634-b466-333164313039/56875072.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-krem-dzhem-s-evkaliptom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Летающий Единорожка</t>
+          <t>Зефирный - Белые</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>1400</v>
-      </c>
-      <c r="C283" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="C283" t="n">
+        <v>3500</v>
+      </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-3961-4366-b766-326639646432/18447615.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-letayuschii-edinorozhka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Мягкий медведь Мишаня</t>
+          <t>Зефирный - Микс</t>
         </is>
       </c>
       <c r="B284" t="n">
         <v>3500</v>
       </c>
-      <c r="C284" t="inlineStr"/>
+      <c r="C284" t="n">
+        <v>3500</v>
+      </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
+          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-myagkii-medved-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Зайка милашка</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Нежный</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C285" t="inlineStr"/>
+        <v>3450</v>
+      </c>
+      <c r="C285" t="n">
+        <v>3800</v>
+      </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3061-4535-b035-306430303965/35298752.jpg</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-zaika-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=430145379292</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>LOVE IS....</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Яркие</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>10990</v>
-      </c>
-      <c r="C286" t="inlineStr"/>
+        <v>3550</v>
+      </c>
+      <c r="C286" t="n">
+        <v>3900</v>
+      </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-3031-4331-b733-356664626131/31576954.jpg</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-is</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=628386621972</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Букет Красотуля</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-3531-4231-b735-333535643938/12128252.jpg</t>
+          <t>https://static.tildacdn.com/stor3037-3037-4331-b032-653532393265/10296532.jpg</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>25 белых роз с эвкалиптом</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C288" t="n">
-        <v>9750</v>
-      </c>
+        <v>5800</v>
+      </c>
+      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
+          <t>https://static.tildacdn.com/stor6630-3762-4363-b331-323964366539/21633765.jpg</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Букет орхидей БАБОЧКА</t>
+          <t>КРЕМ ДЖЕМ С ЭВКАЛИПТОМ из кустовых роз</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>3750</v>
-      </c>
-      <c r="C289" t="n">
-        <v>4300</v>
-      </c>
+        <v>3950</v>
+      </c>
+      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
+          <t>https://static.tildacdn.com/stor6637-6164-4634-b466-333164313039/56875072.jpg</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-krem-dzhem-s-evkaliptom-iz-kustovih-roz</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Букет ромашек "Модный"</t>
+          <t>Игрушка Летающий Единорожка</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C290" t="n">
-        <v>3200</v>
-      </c>
+        <v>1400</v>
+      </c>
+      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-3961-4366-b766-326639646432/18447615.jpg</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-letayuschii-edinorozhka</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ЛАЙК с красными розами</t>
+          <t>Игрушка Мякий медведь Мишаня</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -6792,2471 +6792,2477 @@
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-laik-s-krasnimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
+          <t>Игрушкп Зайка милашка</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>2650</v>
+        <v>1100</v>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
+          <t>Букет Солнечный из хризантем</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>3250</v>
+        <v>2800</v>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
+          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
+          <t>LOVE IS....из кустовых роз с ромашками</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>3850</v>
+        <v>10990</v>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
+          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
+          <t>БУКЕТ ПРОВАНС с хризантемамми и розами</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>5050</v>
-      </c>
-      <c r="C295" t="inlineStr"/>
+        <v>4990</v>
+      </c>
+      <c r="C295" t="n">
+        <v>5500</v>
+      </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
+          <t>https://static.tildacdn.com/stor6331-3465-4438-a461-636562623633/78518381.jpg</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-provans-s-hrizantemammi-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
+          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>8250</v>
-      </c>
-      <c r="C296" t="inlineStr"/>
+        <v>16290</v>
+      </c>
+      <c r="C296" t="n">
+        <v>175550</v>
+      </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
+          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
+          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>11250</v>
-      </c>
-      <c r="C297" t="inlineStr"/>
+        <v>8500</v>
+      </c>
+      <c r="C297" t="n">
+        <v>9200</v>
+      </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
+          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
+          <t>Букет Красотуля с орхидеями</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>15550</v>
+        <v>3300</v>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-3531-4231-b735-333535643938/12128252.jpg</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
+          <t>25 белых роз с эвкалиптом</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>28990</v>
-      </c>
-      <c r="C299" t="inlineStr"/>
+        <v>7800</v>
+      </c>
+      <c r="C299" t="n">
+        <v>9750</v>
+      </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Микс "Нежный " - 25 - Матовая бумага</t>
+          <t>Букет орхидей БАБОЧКА</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>6700</v>
-      </c>
-      <c r="C300" t="inlineStr"/>
+        <v>3750</v>
+      </c>
+      <c r="C300" t="n">
+        <v>4300</v>
+      </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
+          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-?editionuid=144808655921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Микс "Нежный " - 35 - Матовая бумага</t>
+          <t>Букет ромашек "Модный"</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>9300</v>
-      </c>
-      <c r="C301" t="inlineStr"/>
+        <v>2800</v>
+      </c>
+      <c r="C301" t="n">
+        <v>3200</v>
+      </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-?editionuid=682095661901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Микс "Нежный " - 51 - Матовая бумага</t>
+          <t>Букет ЛАЙК с красными розами</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>12300</v>
+        <v>3500</v>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
+          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-?editionuid=818421126901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Микс "Нежный " - 101 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>22999</v>
+        <v>2650</v>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-?editionuid=339758706201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Микс "Нежный " - 11 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>3300</v>
+        <v>3250</v>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-?editionuid=231105875691</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Микс "Нежный " - 15 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>4100</v>
+        <v>3850</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
+          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-?editionuid=759439311541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Букет Белый шоколад</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C306" t="n">
-        <v>5900</v>
-      </c>
+        <v>5050</v>
+      </c>
+      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Ажурные розы в коробке</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>3800</v>
+        <v>8250</v>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3638-6166-4062-a634-363361633538/95787248.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-706637499731-azhurnie-rozi-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Комплимент ВАНИЛЬ с ромашками</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>2690</v>
+        <v>11250</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Коробка с кустовыми розами</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>3500</v>
+        <v>15550</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6561-6635-4566-b836-393737636261/47533235.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Дивная Орхидея</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>5600</v>
+        <v>28990</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Коробка "Орхидея "</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>5700</v>
+        <v>6700</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Розовый дым</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>13500</v>
+        <v>9300</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Комплимент ПУШ - M</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>1800</v>
+        <v>12300</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-kompliment-push?editionuid=217256802002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Комплимент ПУШ - L</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>2150</v>
+        <v>22999</v>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-kompliment-push?editionuid=989656423962</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Комплимент МАРМЕЛАД</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>2650</v>
+        <v>3300</v>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
+          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-kompliment-marmelad</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Шикарная корзина с кустовыми розами</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>18990</v>
-      </c>
-      <c r="C316" t="n">
-        <v>21500</v>
-      </c>
+        <v>4100</v>
+      </c>
+      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3938-6432-4138-a266-633765366335/95496298.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
+          <t>Букет Белый шоколад из белых роз</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>2350</v>
-      </c>
-      <c r="C317" t="inlineStr"/>
+        <v>5800</v>
+      </c>
+      <c r="C317" t="n">
+        <v>5900</v>
+      </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
+          <t>Ажурные розы в коробке</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>3850</v>
+        <v>3800</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
+          <t>https://static.tildacdn.com/stor3638-6166-4062-a634-363361633538/95787248.jpg</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-706637499731-azhurnie-rozi-v-korobke</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
+          <t>Комплимент ВАНИЛЬ с ромашками</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>5350</v>
+        <v>2690</v>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
+          <t>Коробка с кустовыми розами</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>2550</v>
+        <v>3500</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
+          <t>https://static.tildacdn.com/stor6561-6635-4566-b836-393737636261/47533235.jpg</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
+          <t>Дивная Орхидея</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>4250</v>
+        <v>5600</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
+          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
+          <t>Коробка "Орхидея "</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>5900</v>
+        <v>5700</v>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
+          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>8600</v>
+        <v>6999</v>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
+          <t>https://static.tildacdn.com/stor3366-3065-4265-b239-376235653964/39754072.jpg</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
+          <t>Розовый дым</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>8990</v>
+        <v>13500</v>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
+          <t>Букет Комплимент ПУШ с хризантемами - M</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>11990</v>
+        <v>1800</v>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Мечта</t>
+          <t>Букет Комплимент ПУШ с хризантемами - L</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>6500</v>
-      </c>
-      <c r="C326" t="n">
-        <v>6500</v>
-      </c>
+        <v>2150</v>
+      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6538-3533-4866-b134-646334653462/14245314.jpg</t>
+          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-mechta</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Корзина кустовых роз 1</t>
+          <t>Букет Комплимент МАРМЕЛАД</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>13990</v>
-      </c>
-      <c r="C327" t="n">
-        <v>14990</v>
-      </c>
+        <v>2650</v>
+      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 15</t>
+          <t>Коробка с цветами ЛЮКС</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>6400</v>
+        <v>9990</v>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-3036-4663-b030-666130666261/13712242.jpg</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-146373087581-korobka-s-tsvetami-lyuks</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 25</t>
+          <t>Шикарная корзина с кустовыми розами</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>10800</v>
-      </c>
-      <c r="C329" t="inlineStr"/>
+        <v>18990</v>
+      </c>
+      <c r="C329" t="n">
+        <v>21500</v>
+      </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3938-6432-4138-a266-633765366335/95496298.jpg</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 35</t>
+          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>16500</v>
+        <v>2350</v>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 11</t>
+          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>5200</v>
+        <v>3850</v>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 9</t>
+          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>4400</v>
+        <v>5350</v>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
+          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>5050</v>
-      </c>
-      <c r="C333" t="n">
-        <v>5500</v>
-      </c>
+        <v>2550</v>
+      </c>
+      <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
+          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
+          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>8250</v>
-      </c>
-      <c r="C334" t="n">
-        <v>9500</v>
-      </c>
+        <v>4250</v>
+      </c>
+      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
+          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>11250</v>
-      </c>
-      <c r="C335" t="n">
-        <v>15500</v>
-      </c>
+        <v>5900</v>
+      </c>
+      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
+          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
+          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>15550</v>
-      </c>
-      <c r="C336" t="n">
-        <v>18200</v>
-      </c>
+        <v>8600</v>
+      </c>
+      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
+          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
+          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>27999</v>
-      </c>
-      <c r="C337" t="n">
-        <v>35500</v>
-      </c>
+        <v>8990</v>
+      </c>
+      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
+          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>3250</v>
-      </c>
-      <c r="C338" t="n">
-        <v>3500</v>
-      </c>
+        <v>11990</v>
+      </c>
+      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Вау-букет 151 роза и Большой медведь</t>
+          <t>Букет МЕЧТА с кустовыми розами и розами крем</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>39990</v>
+        <v>6500</v>
       </c>
       <c r="C339" t="n">
-        <v>49999</v>
+        <v>6500</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
+          <t>https://static.tildacdn.com/stor6538-3533-4866-b134-646334653462/14245314.jpg</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-mechta-s-kustovimi-rozami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
+          <t>Корзина кустовых роз 1</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C340" t="inlineStr"/>
+        <v>13990</v>
+      </c>
+      <c r="C340" t="n">
+        <v>14990</v>
+      </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
+          <t>Ажурные французские розы - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>4100</v>
+        <v>3250</v>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
+          <t>Ажурные французские розы - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>9100</v>
+        <v>3950</v>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
+          <t>Ажурные французские розы - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>14900</v>
+        <v>5350</v>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
+          <t>Ажурные французские розы - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>23990</v>
+        <v>8850</v>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
+          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>5750</v>
+        <v>12350</v>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Корзина люкс</t>
+          <t>Ажурные французские розы - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>39000</v>
-      </c>
-      <c r="C346" t="n">
-        <v>49990</v>
-      </c>
+        <v>16990</v>
+      </c>
+      <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3665-3335-4462-b738-363535393066/72943061.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-832446607671-korzina-lyuks</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Букет "Улыбка "</t>
+          <t>Ажурные французские розы - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>4450</v>
+        <v>9100</v>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
+          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Букет "Свидание"</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>6250</v>
-      </c>
-      <c r="C348" t="n">
-        <v>7500</v>
-      </c>
+        <v>12650</v>
+      </c>
+      <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
+          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Букет "Милашка"</t>
+          <t>Ажурные французские розы - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>8950</v>
-      </c>
-      <c r="C349" t="n">
-        <v>9990</v>
-      </c>
+        <v>17500</v>
+      </c>
+      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3033-6433-4637-b666-346533306135/93848240.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
+          <t>Ажурные французские розы - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>12999</v>
-      </c>
-      <c r="C350" t="n">
-        <v>15590</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Комплимент "НЕЖНОСТЬ"</t>
+          <t>Ажурные французские розы - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>3650</v>
+        <v>4200</v>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3639-3537-4637-b334-343835343030/44921274.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-kompliment-nezhnost</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Комплимент "Дюшес"</t>
+          <t>Букет пионовидных роз с эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>2450</v>
-      </c>
-      <c r="C352" t="n">
-        <v>2600</v>
-      </c>
+        <v>6400</v>
+      </c>
+      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-kompliment-dyushes</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ИГРУШКА) - Нет</t>
+          <t>Букет пионовидных роз с эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>3300</v>
+        <v>10800</v>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-igrushka?editionuid=223863406172</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ИГРУШКА) - Да</t>
+          <t>Букет пионовидных роз с эвкалиптом - 35</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>3550</v>
+        <v>16500</v>
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-igrushka?editionuid=119690417772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Букет ПЛОМБИР</t>
+          <t>Букет пионовидных роз с эвкалиптом - 11</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>4100</v>
+        <v>5200</v>
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Комплимент "КРЕМ"</t>
+          <t>Букет пионовидных роз с эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>3650</v>
+        <v>4400</v>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-kompliment-krem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Мишка-плюш с бантом "M"</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C357" t="inlineStr"/>
+        <v>5050</v>
+      </c>
+      <c r="C357" t="n">
+        <v>5500</v>
+      </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
+          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-mishka-plyush-s-bantom-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Медведь большой Ягодка</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>5500</v>
-      </c>
-      <c r="C358" t="inlineStr"/>
+        <v>8250</v>
+      </c>
+      <c r="C358" t="n">
+        <v>9500</v>
+      </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
+          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-medved-bolshoi-yagodka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Мишка-плюш "S" беж.</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C359" t="inlineStr"/>
+        <v>11250</v>
+      </c>
+      <c r="C359" t="n">
+        <v>15500</v>
+      </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-mishka-plyush-s-bezh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Мишка-плюш "S" белый</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C360" t="inlineStr"/>
+        <v>15550</v>
+      </c>
+      <c r="C360" t="n">
+        <v>18200</v>
+      </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-mishka-plyush-s-belii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Букет ГИПНОЗ</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>6700</v>
+        <v>27999</v>
       </c>
       <c r="C361" t="n">
-        <v>7200</v>
+        <v>35500</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3763-3431-4736-b439-363632386633/37134397.jpg</t>
+          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Коробка "Ангажемент "</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C362" t="inlineStr"/>
+        <v>3250</v>
+      </c>
+      <c r="C362" t="n">
+        <v>3500</v>
+      </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6363-3963-4364-a238-633236333363/13028423.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-359890373941-korobka-angazhement-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Коробка "Ангажемент Лайт"</t>
+          <t>Вау-букет 151 роза и Большой медведь</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C363" t="inlineStr"/>
+        <v>39990</v>
+      </c>
+      <c r="C363" t="n">
+        <v>49999</v>
+      </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6537-6664-4833-b033-343662313561/26722422.jpg</t>
+          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522766706011-korobka-angazhement-lait</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>51 роза нежный микс в корзине</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>15750</v>
-      </c>
-      <c r="C364" t="n">
-        <v>18990</v>
-      </c>
+        <v>3650</v>
+      </c>
+      <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Микс "Нежный "в шляпной коробке</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C365" t="n">
-        <v>4600</v>
-      </c>
+        <v>4100</v>
+      </c>
+      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>3890</v>
-      </c>
-      <c r="C366" t="n">
-        <v>4500</v>
-      </c>
+        <v>9100</v>
+      </c>
+      <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>4999</v>
+        <v>14900</v>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>"Мерилин "</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C368" t="n">
-        <v>3999</v>
-      </c>
+        <v>23990</v>
+      </c>
+      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Мон Амур - 25</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>6800</v>
+        <v>5750</v>
       </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Мон Амур - 35</t>
+          <t>Корзина люкс</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>9300</v>
-      </c>
-      <c r="C370" t="inlineStr"/>
+        <v>39000</v>
+      </c>
+      <c r="C370" t="n">
+        <v>49990</v>
+      </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3665-3335-4462-b738-363535393066/72943061.jpg</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-832446607671-korzina-lyuks</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Мон Амур - 51</t>
+          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>12990</v>
-      </c>
-      <c r="C371" t="n">
-        <v>17750</v>
-      </c>
+        <v>4450</v>
+      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Мон Амур - 101</t>
+          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>24990</v>
+        <v>6250</v>
       </c>
       <c r="C372" t="n">
-        <v>35600</v>
+        <v>7500</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Коробка L с радужной гипсофилой для мамы</t>
+          <t>Букет "Милашка"</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>3799</v>
-      </c>
-      <c r="C373" t="inlineStr"/>
+        <v>8950</v>
+      </c>
+      <c r="C373" t="n">
+        <v>9990</v>
+      </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
+          <t>https://static.tildacdn.com/stor3033-6433-4637-b666-346533306135/93848240.jpg</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-milashka</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Коробка для мамы с гипсофилой M</t>
+          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>2999</v>
-      </c>
-      <c r="C374" t="inlineStr"/>
+        <v>12999</v>
+      </c>
+      <c r="C374" t="n">
+        <v>15590</v>
+      </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>101 роза нежный микс в корзине</t>
+          <t>Букет Комплимент "НЕЖНОСТЬ" с хризантемами и белыми розами</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>27990</v>
-      </c>
-      <c r="C375" t="n">
-        <v>33500</v>
-      </c>
+        <v>3650</v>
+      </c>
+      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
+          <t>https://static.tildacdn.com/stor3639-3537-4637-b334-343835343030/44921274.jpg</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-hrizantemami</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Букет ЛЕТО с хризантемами и ромашками</t>
+          <t>Букет Комплимент "Дюшес" с альстромериями</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>3100</v>
-      </c>
-      <c r="C376" t="inlineStr"/>
+        <v>2450</v>
+      </c>
+      <c r="C376" t="n">
+        <v>2600</v>
+      </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
+          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Букет АРОМАТ</t>
+          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Нет</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>2700</v>
+        <v>3300</v>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3837-6639-4439-b637-613064363466/87696411.jpg</t>
+          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-aromat</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=223863406172</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Вставка сердце в букет</t>
+          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Да</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>250</v>
+        <v>3550</v>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=119690417772</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Букет ФЕЯ</t>
+          <t>Букет ПЛОМБИР</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>3890</v>
-      </c>
-      <c r="C379" t="n">
-        <v>4000</v>
-      </c>
+        <v>4100</v>
+      </c>
+      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
+          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720813660271-buket-feya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Букет "Стильный микс" с орхидеями</t>
+          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>5300</v>
-      </c>
-      <c r="C380" t="n">
-        <v>5900</v>
-      </c>
+        <v>3650</v>
+      </c>
+      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-704877065131-buket-stilnii-miks-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
+          <t>Игрушка Мишка-плюш с бантом "M"</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>7200</v>
+        <v>1850</v>
       </c>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-6636-4435-b631-343863306433/59411787.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ - Xl</t>
+          <t>Игрушкп Медведь большой Ягодка</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>4690</v>
+        <v>5500</v>
       </c>
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov?editionuid=958551503321</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ - L</t>
+          <t>Игрушка Мишка-плюш "S" беж.</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>3500</v>
+        <v>1300</v>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
+          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov?editionuid=138048727071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Комплимент из пионовидных роз в оформлении - 7</t>
+          <t>Игрушка Мишка-плюш "S" белый</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>2650</v>
+        <v>1300</v>
       </c>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-kompliment-iz-pionovidnih-roz-v-oformlen?editionuid=308194824921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Комплимент из пионовидных роз в оформлении - 9</t>
+          <t>Букет ГИПНОЗ с лилиями и розами</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>3250</v>
-      </c>
-      <c r="C385" t="inlineStr"/>
+        <v>6700</v>
+      </c>
+      <c r="C385" t="n">
+        <v>7200</v>
+      </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
+          <t>https://static.tildacdn.com/stor3763-3431-4736-b439-363632386633/37134397.jpg</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-kompliment-iz-pionovidnih-roz-v-oformlen?editionuid=302968644811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Комплимент из пионовидных роз в оформлении - 11</t>
+          <t>Коробка "Ангажемент Лайт"</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>3850</v>
+        <v>4500</v>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
+          <t>https://static.tildacdn.com/stor6537-6664-4833-b033-343662313561/26722422.jpg</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-kompliment-iz-pionovidnih-roz-v-oformlen?editionuid=266242456331</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522766706011-korobka-angazhement-lait</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Букет ТВОЙ ДЕНЬ</t>
+          <t>51 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>3590</v>
-      </c>
-      <c r="C387" t="inlineStr"/>
+        <v>15750</v>
+      </c>
+      <c r="C387" t="n">
+        <v>18990</v>
+      </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>ВАУ КОРЗИНА ОРХИДЕЙ</t>
+          <t>Микс "Нежный "в шляпной коробке</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>32990</v>
-      </c>
-      <c r="C388" t="inlineStr"/>
+        <v>4500</v>
+      </c>
+      <c r="C388" t="n">
+        <v>4600</v>
+      </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6232-6239-4333-b864-323133363433/21466466.jpg</t>
+          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-orhidei</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>КОМПЛИМЕНТ "НЕЖЕНКА"</t>
+          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>2250</v>
-      </c>
-      <c r="C389" t="inlineStr"/>
+        <v>3890</v>
+      </c>
+      <c r="C389" t="n">
+        <v>4500</v>
+      </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3734-3730-4135-a565-386666386134/91097418.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-kompliment-nezhenka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Букет РАДУЖНЫЙ</t>
+          <t>"Ванильное небо "в шляпной коробке</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>2700</v>
-      </c>
-      <c r="C390" t="n">
-        <v>3450</v>
-      </c>
+        <v>4999</v>
+      </c>
+      <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
+          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Гипсофила от всего сердца</t>
+          <t>"Мерилин "</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C391" t="inlineStr"/>
+        <v>3650</v>
+      </c>
+      <c r="C391" t="n">
+        <v>3999</v>
+      </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6530-4836-a565-643263303762/33953573.jpg</t>
+          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-398838219472-gipsofila-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
+          <t>Мон Амур - 25</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>3600</v>
+        <v>6800</v>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Букет МАЛИНОВОЕ СУФЛЕ</t>
+          <t>Мон Амур - 35</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>3600</v>
+        <v>9300</v>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-910512563562-buket-malinovoe-sufle</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
+          <t>Мон Амур - 51</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>5650</v>
-      </c>
-      <c r="C394" t="inlineStr"/>
+        <v>12990</v>
+      </c>
+      <c r="C394" t="n">
+        <v>17750</v>
+      </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-3435-4736-b964-373535626539/31455574.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>51 пионовидная кустовая роза в нежном оформлении</t>
+          <t>Мон Амур - 101</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>15500</v>
+        <v>24990</v>
       </c>
       <c r="C395" t="n">
-        <v>18000</v>
+        <v>35600</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Букет РОМАНТИКА</t>
+          <t>Коробка L с радужной гипсофилой для мамы</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>4150</v>
-      </c>
-      <c r="C396" t="n">
-        <v>5790</v>
-      </c>
+        <v>3799</v>
+      </c>
+      <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6236-3638-4164-b265-643862396434/56613877.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-359890420482-buket-romantika</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Комплимент с маттиолой</t>
+          <t>Коробка для мамы с гипсофилой M</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>1800</v>
+        <v>2999</v>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-kompliment-s-mattioloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 9</t>
+          <t>101 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C398" t="inlineStr"/>
+        <v>27990</v>
+      </c>
+      <c r="C398" t="n">
+        <v>33500</v>
+      </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
+          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 11</t>
+          <t>Букет ЛЕТО с хризантемами и ромашками</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>4400</v>
+        <v>3100</v>
       </c>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
+          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 15</t>
+          <t>Букет АРОМАТ с диантусами</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
+          <t>https://static.tildacdn.com/stor3837-6639-4439-b637-613064363466/87696411.jpg</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-aromat-s-diantusami</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 25</t>
+          <t>Вставка сердце в букет</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>9500</v>
+        <v>250</v>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 35</t>
+          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>12900</v>
-      </c>
-      <c r="C402" t="inlineStr"/>
+        <v>3890</v>
+      </c>
+      <c r="C402" t="n">
+        <v>4000</v>
+      </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 51</t>
+          <t>Букет "Стильный микс" с орхидеями</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>15900</v>
-      </c>
-      <c r="C403" t="inlineStr"/>
+        <v>5300</v>
+      </c>
+      <c r="C403" t="n">
+        <v>5900</v>
+      </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-704877065131-buket-stilnii-miks-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 101</t>
+          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>31100</v>
+        <v>7200</v>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-6636-4435-b631-343863306433/59411787.jpg</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>2800</v>
+        <v>4690</v>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -9265,306 +9271,860 @@
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
+          <t>Букет БОМБИТА</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>5500</v>
-      </c>
-      <c r="C407" t="inlineStr"/>
+        <v>4050</v>
+      </c>
+      <c r="C407" t="n">
+        <v>5400</v>
+      </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-6363-4130-a535-336236616236/99256221.jpg</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-bombita</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
+          <t>Букет из пионовидных роз в оформлении - 7</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>8700</v>
+        <v>2650</v>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
+          <t>Букет из пионовидных роз в оформлении - 9</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>15900</v>
+        <v>3250</v>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Подарочный набор для мамы 1</t>
+          <t>Букет из пионовидных роз в оформлении - 11</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>3990</v>
+        <v>3850</v>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Подарок для мамы 2</t>
+          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>4990</v>
+        <v>3590</v>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Подарок для мамы 3 селебрити</t>
+          <t>Ромашкина любовь</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>5199</v>
+        <v>10990</v>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Подарочный бокс Рафаэлло</t>
+          <t>ВАУ КОРЗИНА ОРХИДЕЙ</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>2300</v>
+        <v>32990</v>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3132-3163-4362-b936-303066363765/67414703.jpg</t>
+          <t>https://static.tildacdn.com/stor6232-6239-4333-b864-323133363433/21466466.jpg</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-291016517802-podarochnii-boks-rafaello</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-orhidei</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Мишка "Валентин"</t>
+          <t>Букет "НЕЖЕНКА" с гортензией</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>1300</v>
+        <v>2200</v>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
+          <t>https://static.tildacdn.com/stor6532-3462-4639-b135-666433323866/31702549.jpg</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-mishka-valentin</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Котик - 25см</t>
+          <t>Букет РАДУЖНЫЙ с альстромериями</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C415" t="inlineStr"/>
+        <v>2700</v>
+      </c>
+      <c r="C415" t="n">
+        <v>3450</v>
+      </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-kotik?editionuid=707456987082</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Котик - 35см</t>
+          <t>Гипсофила от всего сердца</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>1850</v>
+        <v>3200</v>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6530-4836-a565-643263303762/33953573.jpg</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-kotik?editionuid=932117895852</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-398838219472-gipsofila-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Мишка Милые глазки - 25см</t>
+          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>1100</v>
+        <v>3600</v>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-mishka-milie-glazki?editionuid=689680733112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Мишка Милые глазки - 35см</t>
+          <t>Букет МАЛИНОВОЕ СУФЛЕ с кустовыми розами</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>1850</v>
+        <v>3600</v>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-mishka-milie-glazki?editionuid=511053776132</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-910512563562-buket-malinovoe-sufle-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Гипсофила от всего сердца</t>
+          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>4550</v>
+        <v>5650</v>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-3435-4736-b964-373535626539/31455574.jpg</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Букет ЭКСЛЮЗИВ</t>
+          <t>51 пионовидная кустовая роза в нежном оформлении</t>
         </is>
       </c>
       <c r="B420" t="n">
+        <v>15500</v>
+      </c>
+      <c r="C420" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Букет РОМАНТИКА</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>4150</v>
+      </c>
+      <c r="C421" t="n">
+        <v>5790</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6236-3638-4164-b265-643862396434/56613877.jpg</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-359890420482-buket-romantika</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Букет Комплимент с маттиолой</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Пионовидные кустовые розы в оформлении - 9</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>3650</v>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Пионовидные кустовые розы в оформлении - 11</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Пионовидные кустовые розы в оформлении - 15</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Пионовидные кустовые розы в оформлении - 25</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Пионовидные кустовые розы в оформлении - 35</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>12900</v>
+      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Пионовидные кустовые розы в оформлении - 51</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>15900</v>
+      </c>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Пионовидные кустовые розы в оформлении - 101</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>31100</v>
+      </c>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>2800</v>
+      </c>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>8700</v>
+      </c>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>15900</v>
+      </c>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Подарочный набор для мамы 1</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>3990</v>
+      </c>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Подарок для мамы 2</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>4990</v>
+      </c>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Подарок для мамы 3 селебрити</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>5199</v>
+      </c>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Букет ЛЕДИ РЕД с пион розами</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>2450</v>
+      </c>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6430-6634-4338-a635-316164643339/52783953.jpg</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-341373252172-buket-ledi-red-s-pion-rozami</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Подарочный бокс Рафаэлло</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>2300</v>
+      </c>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3132-3163-4362-b936-303066363765/67414703.jpg</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-291016517802-podarochnii-boks-rafaello</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Игрушка Мишка "Валентин"</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Игрушка Котик - 25см</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Игрушка Котик - 35см</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Игрушка Мишка Милые глазки - 25см</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Игрушка Мишка Милые глазки - 35см</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Гипсофила от всего сердца</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>4550</v>
+      </c>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Букет ЭКСЛЮЗИВ с ажурными розами</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
         <v>7200</v>
       </c>
-      <c r="C420" t="inlineStr"/>
-      <c r="D420" t="inlineStr">
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3465-6139-4161-b636-326631643031/80766082.jpg</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-655606921272-buket-ekslyuziv</t>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-655606921272-buket-ekslyuziv-s-azhurnimi-rozami</t>
         </is>
       </c>
     </row>

--- a/feed_converted.xlsx
+++ b/feed_converted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E446"/>
+  <dimension ref="A1:E441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="C2" t="n">
         <v>6550</v>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4300</v>
+        <v>4800</v>
       </c>
       <c r="C3" t="n">
         <v>5650</v>
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5350</v>
+        <v>6400</v>
       </c>
       <c r="C4" t="n">
         <v>6800</v>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5800</v>
+        <v>6600</v>
       </c>
       <c r="C5" t="n">
         <v>8350</v>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6500</v>
+        <v>7800</v>
       </c>
       <c r="C6" t="n">
         <v>9600</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9400</v>
+        <v>10800</v>
       </c>
       <c r="C7" t="n">
         <v>13400</v>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12600</v>
+        <v>14600</v>
       </c>
       <c r="C8" t="n">
         <v>15600</v>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12990</v>
+        <v>14990</v>
       </c>
       <c r="C9" t="n">
         <v>15700</v>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18350</v>
+        <v>21100</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18750</v>
+        <v>21600</v>
       </c>
       <c r="C11" t="n">
         <v>25200</v>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24590</v>
+        <v>28400</v>
       </c>
       <c r="C12" t="n">
         <v>35300</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24990</v>
+        <v>28900</v>
       </c>
       <c r="C13" t="n">
         <v>35400</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24990</v>
+        <v>28900</v>
       </c>
       <c r="C14" t="n">
         <v>35500</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6800</v>
+        <v>7600</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8850</v>
+        <v>10600</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4300</v>
+        <v>5350</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4500</v>
+        <v>5550</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6250</v>
+        <v>6350</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6650</v>
+        <v>6550</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>11500</v>
+        <v>12250</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11950</v>
+        <v>12550</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>24990</v>
+        <v>28990</v>
       </c>
       <c r="C82" t="n">
         <v>30550</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>11950</v>
+        <v>12550</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>16690</v>
+        <v>13690</v>
       </c>
       <c r="C151" t="n">
         <v>19000</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>27990</v>
+        <v>29990</v>
       </c>
       <c r="C152" t="n">
         <v>35000</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>12590</v>
+        <v>14600</v>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>4100</v>
+        <v>4800</v>
       </c>
       <c r="C159" t="n">
         <v>5500</v>
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>6800</v>
+        <v>7800</v>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>6800</v>
+        <v>7800</v>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
@@ -4523,60 +4523,60 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>25 красных роз в коробке</t>
+          <t>101 красная роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>8800</v>
+        <v>28590</v>
       </c>
       <c r="C187" t="n">
-        <v>11000</v>
+        <v>35500</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6163-3466-4231-b833-303730383136/FCA8C57F-F641-4EA7-8.JPG</t>
+          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-395916445391-25-krasnih-roz-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Атласная лента</t>
+          <t>101 красная роза - 60 см - Матова бумага</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>24590</v>
+        <v>28990</v>
       </c>
       <c r="C188" t="n">
         <v>35500</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Матова бумага</t>
+          <t>101 красная роза - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>24990</v>
+        <v>12250</v>
       </c>
       <c r="C189" t="n">
-        <v>35500</v>
+        <v>15300</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -4585,60 +4585,60 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Атласная лента</t>
+          <t>101 красная роза - 45 см - Матова бумага</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>11500</v>
+        <v>12550</v>
       </c>
       <c r="C190" t="n">
-        <v>15300</v>
+        <v>15500</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Матова бумага</t>
+          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>11950</v>
+        <v>3850</v>
       </c>
       <c r="C191" t="n">
-        <v>15500</v>
+        <v>4200</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
+          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4649,50 +4649,48 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>3850</v>
+        <v>5100</v>
       </c>
       <c r="C193" t="n">
-        <v>4200</v>
+        <v>6900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
+          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B194" t="n">
         <v>5100</v>
       </c>
-      <c r="C194" t="n">
-        <v>6900</v>
-      </c>
+      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
@@ -4700,18 +4698,18 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>5100</v>
+        <v>6950</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
@@ -4721,14 +4719,14 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4742,18 +4740,18 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>6950</v>
+        <v>8150</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
@@ -4763,14 +4761,14 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4784,18 +4782,18 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>8150</v>
+        <v>9950</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
@@ -4805,14 +4803,14 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -4826,64 +4824,64 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>9950</v>
+        <v>11150</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B202" t="n">
         <v>11150</v>
       </c>
-      <c r="C202" t="inlineStr"/>
+      <c r="C202" t="n">
+        <v>11300</v>
+      </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
+          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>11150</v>
-      </c>
-      <c r="C203" t="n">
-        <v>11300</v>
-      </c>
+        <v>15990</v>
+      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
@@ -4891,14 +4889,14 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -4912,125 +4910,125 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>15990</v>
+        <v>2900</v>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
+          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>2900</v>
+        <v>3700</v>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
+          <t>15 красно белых роз в оформлении</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>3700</v>
-      </c>
-      <c r="C207" t="inlineStr"/>
+        <v>4300</v>
+      </c>
+      <c r="C207" t="n">
+        <v>6800</v>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
+          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>15 красно белых роз в оформлении</t>
+          <t>Raffaello</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C208" t="n">
-        <v>6800</v>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
+          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Raffaello</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>690</v>
+        <v>3000</v>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>3000</v>
+        <v>3800</v>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
@@ -5040,18 +5038,18 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>3800</v>
+        <v>5000</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
@@ -5061,18 +5059,18 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>5000</v>
+        <v>1800</v>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
@@ -5082,18 +5080,18 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
@@ -5103,18 +5101,18 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
@@ -5124,39 +5122,39 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>3000</v>
+        <v>3800</v>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
@@ -5166,18 +5164,18 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>3800</v>
+        <v>5000</v>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
@@ -5187,18 +5185,18 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>5000</v>
+        <v>6200</v>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
@@ -5208,18 +5206,18 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>6200</v>
+        <v>7000</v>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
@@ -5229,18 +5227,18 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>7000</v>
+        <v>1800</v>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
@@ -5250,18 +5248,18 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
@@ -5271,18 +5269,18 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
@@ -5292,39 +5290,39 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
+          <t>Набор из гелиевых шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1000</v>
+        <v>3750</v>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 15</t>
+          <t>Набор из гелиевых шаров "Сердце" - 19</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>3750</v>
+        <v>4750</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
@@ -5334,18 +5332,18 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 19</t>
+          <t>Набор из гелиевых шаров "Сердце" - 25</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>4750</v>
+        <v>6350</v>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
@@ -5355,18 +5353,18 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 25</t>
+          <t>Набор из гелиевых шаров "Сердце" - 31</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>6350</v>
+        <v>7750</v>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
@@ -5376,18 +5374,18 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 31</t>
+          <t>Набор из гелиевых шаров "Сердце" - 35</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>7750</v>
+        <v>8750</v>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
@@ -5397,18 +5395,18 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 35</t>
+          <t>Набор из гелиевых шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>8750</v>
+        <v>2250</v>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
@@ -5418,18 +5416,18 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 9</t>
+          <t>Набор из гелиевых шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2250</v>
+        <v>1750</v>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
@@ -5439,18 +5437,18 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 7</t>
+          <t>Набор из гелиевых шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1750</v>
+        <v>1250</v>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
@@ -5460,18 +5458,18 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 5</t>
+          <t>Набор из гелиевых шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1250</v>
+        <v>2750</v>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
@@ -5481,39 +5479,39 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 11</t>
+          <t>Набор из фольгированных шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>2750</v>
+        <v>6750</v>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 15</t>
+          <t>Набор из фольгированных шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>6750</v>
+        <v>4950</v>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
@@ -5523,18 +5521,18 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 11</t>
+          <t>Набор из фольгированных шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>4950</v>
+        <v>4050</v>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
@@ -5544,18 +5542,18 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 9</t>
+          <t>Набор из фольгированных шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>4050</v>
+        <v>3150</v>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
@@ -5565,18 +5563,18 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 7</t>
+          <t>Набор из фольгированных шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
@@ -5586,42 +5584,44 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 5</t>
+          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>2250</v>
-      </c>
-      <c r="C237" t="inlineStr"/>
+        <v>4200</v>
+      </c>
+      <c r="C237" t="n">
+        <v>4500</v>
+      </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>4200</v>
+        <v>5600</v>
       </c>
       <c r="C238" t="n">
-        <v>4500</v>
+        <v>6100</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -5630,21 +5630,21 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>5600</v>
+        <v>7700</v>
       </c>
       <c r="C239" t="n">
-        <v>6100</v>
+        <v>8500</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>7700</v>
+        <v>9100</v>
       </c>
       <c r="C240" t="n">
-        <v>8500</v>
+        <v>10100</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -5676,21 +5676,21 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>9100</v>
+        <v>12600</v>
       </c>
       <c r="C241" t="n">
-        <v>10100</v>
+        <v>14100</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -5699,22 +5699,20 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>12600</v>
-      </c>
-      <c r="C242" t="n">
-        <v>14100</v>
-      </c>
+        <v>3700</v>
+      </c>
+      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5722,18 +5720,18 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>3700</v>
+        <v>2900</v>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
@@ -5743,20 +5741,22 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C244" t="inlineStr"/>
+        <v>17690</v>
+      </c>
+      <c r="C244" t="n">
+        <v>18690</v>
+      </c>
       <c r="D244" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5764,21 +5764,21 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>17690</v>
+        <v>34690</v>
       </c>
       <c r="C245" t="n">
-        <v>18690</v>
+        <v>38690</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -5787,64 +5787,62 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
+          <t>Стильный букет в крафтовой сумочке</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>34690</v>
+        <v>4200</v>
       </c>
       <c r="C246" t="n">
-        <v>38690</v>
+        <v>5200</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Стильный букет в крафтовой сумочке</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C247" t="n">
-        <v>5200</v>
-      </c>
+        <v>4990</v>
+      </c>
+      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>4990</v>
+        <v>5680</v>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
@@ -5861,11 +5859,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>5680</v>
+        <v>5990</v>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
@@ -5882,7 +5880,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -5903,11 +5901,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>5990</v>
+        <v>6240</v>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
@@ -5924,11 +5922,11 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>6240</v>
+        <v>6290</v>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
@@ -5945,11 +5943,11 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>6290</v>
+        <v>10490</v>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
@@ -5966,78 +5964,80 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
+          <t>ДОРОГУША из красных роз с орхидеями</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>10490</v>
-      </c>
-      <c r="C254" t="inlineStr"/>
+        <v>7500</v>
+      </c>
+      <c r="C254" t="n">
+        <v>8500</v>
+      </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ДОРОГУША из красных роз с орхидеями</t>
+          <t>Коробка гигант с радужной гипсофилой</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>7500</v>
+        <v>9999</v>
       </c>
       <c r="C255" t="n">
-        <v>8500</v>
+        <v>10990</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
+          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Коробка гигант с радужной гипсофилой</t>
+          <t>Букет Малиновое вино - Посмотреть...</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>9999</v>
+        <v>4650</v>
       </c>
       <c r="C256" t="n">
-        <v>10990</v>
+        <v>5200</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Посмотреть...</t>
+          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>4650</v>
+        <v>5340</v>
       </c>
       <c r="C257" t="n">
         <v>5200</v>
@@ -6056,11 +6056,11 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
+          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>5340</v>
+        <v>5650</v>
       </c>
       <c r="C258" t="n">
         <v>5200</v>
@@ -6079,7 +6079,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
+          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6102,11 +6102,11 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>5650</v>
+        <v>5900</v>
       </c>
       <c r="C260" t="n">
         <v>5200</v>
@@ -6125,11 +6125,11 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>5900</v>
+        <v>5950</v>
       </c>
       <c r="C261" t="n">
         <v>5200</v>
@@ -6148,11 +6148,11 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
+          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>5950</v>
+        <v>10150</v>
       </c>
       <c r="C262" t="n">
         <v>5200</v>
@@ -6171,34 +6171,34 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
+          <t>11альстромерий в оформлении - Посмотреть...</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>10150</v>
+        <v>2500</v>
       </c>
       <c r="C263" t="n">
-        <v>5200</v>
+        <v>2380</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Посмотреть...</t>
+          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>2500</v>
+        <v>3190</v>
       </c>
       <c r="C264" t="n">
         <v>2380</v>
@@ -6217,11 +6217,11 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>3190</v>
+        <v>3500</v>
       </c>
       <c r="C265" t="n">
         <v>2380</v>
@@ -6240,7 +6240,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -6263,11 +6263,11 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>3500</v>
+        <v>3750</v>
       </c>
       <c r="C267" t="n">
         <v>2380</v>
@@ -6286,11 +6286,11 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>3750</v>
+        <v>3800</v>
       </c>
       <c r="C268" t="n">
         <v>2380</v>
@@ -6309,11 +6309,11 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
+          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>3800</v>
+        <v>8000</v>
       </c>
       <c r="C269" t="n">
         <v>2380</v>
@@ -6332,23 +6332,21 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C270" t="n">
-        <v>2380</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
         </is>
       </c>
     </row>
@@ -6364,12 +6362,12 @@
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
         </is>
       </c>
     </row>
@@ -6385,12 +6383,12 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
         </is>
       </c>
     </row>
@@ -6406,12 +6404,12 @@
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6425,12 @@
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
         </is>
       </c>
     </row>
@@ -6448,12 +6446,12 @@
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
         </is>
       </c>
     </row>
@@ -6469,12 +6467,12 @@
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
         </is>
       </c>
     </row>
@@ -6490,12 +6488,12 @@
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
         </is>
       </c>
     </row>
@@ -6511,12 +6509,12 @@
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
         </is>
       </c>
     </row>
@@ -6532,1405 +6530,1405 @@
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>900</v>
+        <v>3690</v>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
+          <t>Зефирный - Белые</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C281" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="C281" t="n">
+        <v>3500</v>
+      </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
+          <t>Зефирный - Микс</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>3690</v>
-      </c>
-      <c r="C282" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="C282" t="n">
+        <v>3500</v>
+      </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
+          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Зефирный - Белые</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Нежный</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="C283" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3061-4535-b035-306430303965/35298752.jpg</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=430145379292</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Зефирный - Микс</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Яркие</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>3500</v>
+        <v>3550</v>
       </c>
       <c r="C284" t="n">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-3031-4331-b733-356664626131/31576954.jpg</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=628386621972</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Нежный</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>3450</v>
-      </c>
-      <c r="C285" t="n">
-        <v>3800</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3061-4535-b035-306430303965/35298752.jpg</t>
+          <t>https://static.tildacdn.com/stor3037-3037-4331-b032-653532393265/10296532.jpg</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=430145379292</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Яркие</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>3550</v>
-      </c>
-      <c r="C286" t="n">
-        <v>3900</v>
-      </c>
+        <v>5800</v>
+      </c>
+      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-3031-4331-b733-356664626131/31576954.jpg</t>
+          <t>https://static.tildacdn.com/stor6630-3762-4363-b331-323964366539/21633765.jpg</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=628386621972</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
+          <t>КРЕМ ДЖЕМ С ЭВКАЛИПТОМ из кустовых роз</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>3500</v>
+        <v>3950</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3037-3037-4331-b032-653532393265/10296532.jpg</t>
+          <t>https://static.tildacdn.com/stor6637-6164-4634-b466-333164313039/56875072.jpg</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-krem-dzhem-s-evkaliptom-iz-kustovih-roz</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
+          <t>Игрушка Летающий Единорожка</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>5800</v>
+        <v>1400</v>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6630-3762-4363-b331-323964366539/21633765.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-3961-4366-b766-326639646432/18447615.jpg</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-letayuschii-edinorozhka</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>КРЕМ ДЖЕМ С ЭВКАЛИПТОМ из кустовых роз</t>
+          <t>Игрушка Мякий медведь Мишаня</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>3950</v>
+        <v>3500</v>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6637-6164-4634-b466-333164313039/56875072.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-krem-dzhem-s-evkaliptom-iz-kustovih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Игрушка Летающий Единорожка</t>
+          <t>Игрушкп Зайка милашка</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-3961-4366-b766-326639646432/18447615.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-letayuschii-edinorozhka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Игрушка Мякий медведь Мишаня</t>
+          <t>Букет Солнечный из хризантем</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
+          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Игрушкп Зайка милашка</t>
+          <t>LOVE IS....из кустовых роз с ромашками</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>1100</v>
+        <v>10990</v>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
+          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Букет Солнечный из хризантем</t>
+          <t>БУКЕТ ПРОВАНС с хризантемамми и розами</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C293" t="inlineStr"/>
+        <v>4990</v>
+      </c>
+      <c r="C293" t="n">
+        <v>5500</v>
+      </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
+          <t>https://static.tildacdn.com/stor6331-3465-4438-a461-636562623633/78518381.jpg</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-provans-s-hrizantemammi-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>LOVE IS....из кустовых роз с ромашками</t>
+          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>10990</v>
-      </c>
-      <c r="C294" t="inlineStr"/>
+        <v>16290</v>
+      </c>
+      <c r="C294" t="n">
+        <v>175550</v>
+      </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
+          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>БУКЕТ ПРОВАНС с хризантемамми и розами</t>
+          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>4990</v>
+        <v>8500</v>
       </c>
       <c r="C295" t="n">
-        <v>5500</v>
+        <v>9200</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6331-3465-4438-a461-636562623633/78518381.jpg</t>
+          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-provans-s-hrizantemammi-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
+          <t>25 белых роз с эвкалиптом</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>16290</v>
+        <v>7800</v>
       </c>
       <c r="C296" t="n">
-        <v>175550</v>
+        <v>9750</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
+          <t>Букет орхидей БАБОЧКА</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>8500</v>
+        <v>3750</v>
       </c>
       <c r="C297" t="n">
-        <v>9200</v>
+        <v>4300</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
+          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Букет Красотуля с орхидеями</t>
+          <t>Букет ромашек "Модный"</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C298" t="inlineStr"/>
+        <v>2800</v>
+      </c>
+      <c r="C298" t="n">
+        <v>3200</v>
+      </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-3531-4231-b735-333535643938/12128252.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>25 белых роз с эвкалиптом</t>
+          <t>Букет ЛАЙК с красными розами</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C299" t="n">
-        <v>9750</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
+          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Букет орхидей БАБОЧКА</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>3750</v>
-      </c>
-      <c r="C300" t="n">
-        <v>4300</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
+          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Букет ромашек "Модный"</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C301" t="n">
-        <v>3200</v>
-      </c>
+        <v>3700</v>
+      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Букет ЛАЙК с красными розами</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>3500</v>
+        <v>4400</v>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
+          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>2650</v>
+        <v>5800</v>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>3250</v>
+        <v>9300</v>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>3850</v>
+        <v>11250</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>5050</v>
+        <v>15990</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>8250</v>
+        <v>29990</v>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>11250</v>
+        <v>6700</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>15550</v>
+        <v>9300</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>28990</v>
+        <v>12300</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>6700</v>
+        <v>22999</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>9300</v>
+        <v>3300</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>12300</v>
+        <v>4100</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
+          <t>Букет Белый шоколад из белых роз</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>22999</v>
-      </c>
-      <c r="C314" t="inlineStr"/>
+        <v>5800</v>
+      </c>
+      <c r="C314" t="n">
+        <v>5900</v>
+      </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
+          <t>Ажурные розы в коробке</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>3300</v>
+        <v>3800</v>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
+          <t>https://static.tildacdn.com/stor3638-6166-4062-a634-363361633538/95787248.jpg</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-706637499731-azhurnie-rozi-v-korobke</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
+          <t>Комплимент ВАНИЛЬ с ромашками</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>4100</v>
+        <v>2690</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Букет Белый шоколад из белых роз</t>
+          <t>Коробка с кустовыми розами</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C317" t="n">
-        <v>5900</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
+          <t>https://static.tildacdn.com/stor6561-6635-4566-b836-393737636261/47533235.jpg</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Ажурные розы в коробке</t>
+          <t>Дивная Орхидея</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>3800</v>
+        <v>5600</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3638-6166-4062-a634-363361633538/95787248.jpg</t>
+          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-706637499731-azhurnie-rozi-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Комплимент ВАНИЛЬ с ромашками</t>
+          <t>Коробка "Орхидея "</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>2690</v>
+        <v>5700</v>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Коробка с кустовыми розами</t>
+          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>3500</v>
+        <v>6999</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6561-6635-4566-b836-393737636261/47533235.jpg</t>
+          <t>https://static.tildacdn.com/stor3366-3065-4265-b239-376235653964/39754072.jpg</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Дивная Орхидея</t>
+          <t>Розовый дым</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>5600</v>
+        <v>13500</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Коробка "Орхидея "</t>
+          <t>Букет Комплимент ПУШ с хризантемами - M</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>5700</v>
+        <v>1800</v>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
+          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
+          <t>Букет Комплимент ПУШ с хризантемами - L</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>6999</v>
+        <v>2150</v>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3366-3065-4265-b239-376235653964/39754072.jpg</t>
+          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Розовый дым</t>
+          <t>Букет Комплимент МАРМЕЛАД</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>13500</v>
+        <v>2650</v>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - M</t>
+          <t>Коробка с цветами ЛЮКС</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>1800</v>
+        <v>9990</v>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-3036-4663-b030-666130666261/13712242.jpg</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-146373087581-korobka-s-tsvetami-lyuks</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - L</t>
+          <t>Шикарная корзина с кустовыми розами</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>2150</v>
-      </c>
-      <c r="C326" t="inlineStr"/>
+        <v>18990</v>
+      </c>
+      <c r="C326" t="n">
+        <v>21500</v>
+      </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
+          <t>https://static.tildacdn.com/stor3938-6432-4138-a266-633765366335/95496298.jpg</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Букет Комплимент МАРМЕЛАД</t>
+          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>2650</v>
+        <v>2350</v>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Коробка с цветами ЛЮКС</t>
+          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>9990</v>
+        <v>3850</v>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-3036-4663-b030-666130666261/13712242.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-146373087581-korobka-s-tsvetami-lyuks</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Шикарная корзина с кустовыми розами</t>
+          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>18990</v>
-      </c>
-      <c r="C329" t="n">
-        <v>21500</v>
-      </c>
+        <v>5350</v>
+      </c>
+      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3938-6432-4138-a266-633765366335/95496298.jpg</t>
+          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>2350</v>
+        <v>2550</v>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
+          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>3850</v>
+        <v>4250</v>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>5350</v>
+        <v>5900</v>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
+          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>2550</v>
+        <v>8600</v>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
+          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>4250</v>
+        <v>8990</v>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>5900</v>
+        <v>11990</v>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
+          <t>Букет МЕЧТА с кустовыми розами и розами крем</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>8600</v>
-      </c>
-      <c r="C336" t="inlineStr"/>
+        <v>6500</v>
+      </c>
+      <c r="C336" t="n">
+        <v>6500</v>
+      </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
+          <t>https://static.tildacdn.com/stor6538-3533-4866-b134-646334653462/14245314.jpg</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-mechta-s-kustovimi-rozami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
+          <t>Корзина кустовых роз 1</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>8990</v>
-      </c>
-      <c r="C337" t="inlineStr"/>
+        <v>13990</v>
+      </c>
+      <c r="C337" t="n">
+        <v>14990</v>
+      </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
+          <t>Ажурные французские розы - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>11990</v>
+        <v>3250</v>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Букет МЕЧТА с кустовыми розами и розами крем</t>
+          <t>Ажурные французские розы - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>6500</v>
-      </c>
-      <c r="C339" t="n">
-        <v>6500</v>
-      </c>
+        <v>3950</v>
+      </c>
+      <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6538-3533-4866-b134-646334653462/14245314.jpg</t>
+          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-mechta-s-kustovimi-rozami-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Корзина кустовых роз 1</t>
+          <t>Ажурные французские розы - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>13990</v>
-      </c>
-      <c r="C340" t="n">
-        <v>14990</v>
-      </c>
+        <v>5350</v>
+      </c>
+      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Атласная лента</t>
+          <t>Ажурные французские розы - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>3250</v>
+        <v>8850</v>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
+          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Атласная лента</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>3950</v>
+        <v>12350</v>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 15 - Атласная лента</t>
+          <t>Ажурные французские розы - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>5350</v>
+        <v>16990</v>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Атласная лента</t>
+          <t>Ажурные французские розы - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>8850</v>
+        <v>9100</v>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
+          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
         </is>
       </c>
     </row>
@@ -7941,28 +7939,28 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>12350</v>
+        <v>12650</v>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Атласная лента</t>
+          <t>Ажурные французские розы - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>16990</v>
+        <v>17500</v>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
@@ -7972,123 +7970,123 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Матовая бумага</t>
+          <t>Ажурные французские розы - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>9100</v>
+        <v>3500</v>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>Ажурные французские розы - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>12650</v>
+        <v>4200</v>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Матовая бумага</t>
+          <t>Букет пионовидных роз с эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>17500</v>
+        <v>6400</v>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Матовая бумага</t>
+          <t>Букет пионовидных роз с эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>3500</v>
+        <v>10800</v>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Матовая бумага</t>
+          <t>Букет пионовидных роз с эвкалиптом - 35</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>4200</v>
+        <v>16500</v>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 15</t>
+          <t>Букет пионовидных роз с эвкалиптом - 11</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
@@ -8098,18 +8096,18 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 25</t>
+          <t>Букет пионовидных роз с эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>10800</v>
+        <v>4400</v>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
@@ -8119,1620 +8117,1616 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 35</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>16500</v>
-      </c>
-      <c r="C354" t="inlineStr"/>
+        <v>5050</v>
+      </c>
+      <c r="C354" t="n">
+        <v>5500</v>
+      </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 11</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>5200</v>
-      </c>
-      <c r="C355" t="inlineStr"/>
+        <v>8250</v>
+      </c>
+      <c r="C355" t="n">
+        <v>9500</v>
+      </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 9</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>4400</v>
-      </c>
-      <c r="C356" t="inlineStr"/>
+        <v>11250</v>
+      </c>
+      <c r="C356" t="n">
+        <v>15500</v>
+      </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>5050</v>
+        <v>15550</v>
       </c>
       <c r="C357" t="n">
-        <v>5500</v>
+        <v>18200</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>8250</v>
+        <v>27999</v>
       </c>
       <c r="C358" t="n">
-        <v>9500</v>
+        <v>35500</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
+          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>11250</v>
+        <v>3250</v>
       </c>
       <c r="C359" t="n">
-        <v>15500</v>
+        <v>3500</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
+          <t>Вау-букет 151 роза и Большой медведь</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>15550</v>
+        <v>39990</v>
       </c>
       <c r="C360" t="n">
-        <v>18200</v>
+        <v>49999</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
+          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>27999</v>
-      </c>
-      <c r="C361" t="n">
-        <v>35500</v>
-      </c>
+        <v>3650</v>
+      </c>
+      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>3250</v>
-      </c>
-      <c r="C362" t="n">
-        <v>3500</v>
-      </c>
+        <v>4100</v>
+      </c>
+      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Вау-букет 151 роза и Большой медведь</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>39990</v>
-      </c>
-      <c r="C363" t="n">
-        <v>49999</v>
-      </c>
+        <v>9100</v>
+      </c>
+      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>3650</v>
+        <v>14900</v>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>4100</v>
+        <v>23990</v>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>9100</v>
+        <v>5750</v>
       </c>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
+          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>14900</v>
+        <v>4450</v>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
+          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>23990</v>
-      </c>
-      <c r="C368" t="inlineStr"/>
+        <v>6250</v>
+      </c>
+      <c r="C368" t="n">
+        <v>7500</v>
+      </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
+          <t>Букет "Милашка"</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>5750</v>
-      </c>
-      <c r="C369" t="inlineStr"/>
+        <v>8950</v>
+      </c>
+      <c r="C369" t="n">
+        <v>9990</v>
+      </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
+          <t>https://static.tildacdn.com/stor3033-6433-4637-b666-346533306135/93848240.jpg</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-milashka</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Корзина люкс</t>
+          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>39000</v>
+        <v>12999</v>
       </c>
       <c r="C370" t="n">
-        <v>49990</v>
+        <v>15590</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3665-3335-4462-b738-363535393066/72943061.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-832446607671-korzina-lyuks</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
+          <t>Букет Комплимент "НЕЖНОСТЬ" с хризантемами и белыми розами</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>4450</v>
+        <v>3650</v>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
+          <t>https://static.tildacdn.com/stor3639-3537-4637-b334-343835343030/44921274.jpg</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-hrizantemami</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
+          <t>Букет Комплимент "Дюшес" с альстромериями</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>6250</v>
+        <v>2450</v>
       </c>
       <c r="C372" t="n">
-        <v>7500</v>
+        <v>2600</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
+          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Букет "Милашка"</t>
+          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Нет</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>8950</v>
-      </c>
-      <c r="C373" t="n">
-        <v>9990</v>
-      </c>
+        <v>3300</v>
+      </c>
+      <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3033-6433-4637-b666-346533306135/93848240.jpg</t>
+          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=223863406172</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
+          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Да</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>12999</v>
-      </c>
-      <c r="C374" t="n">
-        <v>15590</v>
-      </c>
+        <v>3550</v>
+      </c>
+      <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=119690417772</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Букет Комплимент "НЕЖНОСТЬ" с хризантемами и белыми розами</t>
+          <t>Букет ПЛОМБИР</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>3650</v>
+        <v>4100</v>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3639-3537-4637-b334-343835343030/44921274.jpg</t>
+          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-hrizantemami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Букет Комплимент "Дюшес" с альстромериями</t>
+          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>2450</v>
-      </c>
-      <c r="C376" t="n">
-        <v>2600</v>
-      </c>
+        <v>3650</v>
+      </c>
+      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Нет</t>
+          <t>Игрушка Мишка-плюш с бантом "M"</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>3300</v>
+        <v>1850</v>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=223863406172</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Да</t>
+          <t>Игрушкп Медведь большой Ягодка</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>3550</v>
+        <v>5500</v>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=119690417772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Букет ПЛОМБИР</t>
+          <t>Игрушка Мишка-плюш "S" беж.</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>4100</v>
+        <v>1300</v>
       </c>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
+          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
+          <t>Игрушка Мишка-плюш "S" белый</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>3650</v>
+        <v>1300</v>
       </c>
       <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш с бантом "M"</t>
+          <t>Букет ГИПНОЗ с лилиями и розами</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C381" t="inlineStr"/>
+        <v>6700</v>
+      </c>
+      <c r="C381" t="n">
+        <v>7200</v>
+      </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
+          <t>https://static.tildacdn.com/stor3763-3431-4736-b439-363632386633/37134397.jpg</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Игрушкп Медведь большой Ягодка</t>
+          <t>Коробка "Ангажемент Лайт"</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
+          <t>https://static.tildacdn.com/stor6537-6664-4833-b033-343662313561/26722422.jpg</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522766706011-korobka-angazhement-lait</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" беж.</t>
+          <t>51 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C383" t="inlineStr"/>
+        <v>15750</v>
+      </c>
+      <c r="C383" t="n">
+        <v>18990</v>
+      </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" белый</t>
+          <t>Микс "Нежный "в шляпной коробке</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C384" t="inlineStr"/>
+        <v>4500</v>
+      </c>
+      <c r="C384" t="n">
+        <v>4600</v>
+      </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
+          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Букет ГИПНОЗ с лилиями и розами</t>
+          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>6700</v>
+        <v>3890</v>
       </c>
       <c r="C385" t="n">
-        <v>7200</v>
+        <v>4500</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3763-3431-4736-b439-363632386633/37134397.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Коробка "Ангажемент Лайт"</t>
+          <t>"Ванильное небо "в шляпной коробке</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>4500</v>
+        <v>4999</v>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6537-6664-4833-b033-343662313561/26722422.jpg</t>
+          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522766706011-korobka-angazhement-lait</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>51 роза нежный микс в корзине</t>
+          <t>"Мерилин "</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>15750</v>
+        <v>3650</v>
       </c>
       <c r="C387" t="n">
-        <v>18990</v>
+        <v>3999</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
+          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Микс "Нежный "в шляпной коробке</t>
+          <t>Мон Амур - 25</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C388" t="n">
-        <v>4600</v>
-      </c>
+        <v>6800</v>
+      </c>
+      <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
+          <t>Мон Амур - 35</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>3890</v>
-      </c>
-      <c r="C389" t="n">
-        <v>4500</v>
-      </c>
+        <v>9300</v>
+      </c>
+      <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке</t>
+          <t>Мон Амур - 51</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>4999</v>
-      </c>
-      <c r="C390" t="inlineStr"/>
+        <v>12990</v>
+      </c>
+      <c r="C390" t="n">
+        <v>17750</v>
+      </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>"Мерилин "</t>
+          <t>Мон Амур - 101</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>3650</v>
+        <v>24990</v>
       </c>
       <c r="C391" t="n">
-        <v>3999</v>
+        <v>35600</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Мон Амур - 25</t>
+          <t>Коробка L с радужной гипсофилой для мамы</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>6800</v>
+        <v>3799</v>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Мон Амур - 35</t>
+          <t>Коробка для мамы с гипсофилой M</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>9300</v>
+        <v>2999</v>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Мон Амур - 51</t>
+          <t>101 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>12990</v>
+        <v>27990</v>
       </c>
       <c r="C394" t="n">
-        <v>17750</v>
+        <v>33500</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Мон Амур - 101</t>
+          <t>Букет ЛЕТО с хризантемами и ромашками</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>24990</v>
-      </c>
-      <c r="C395" t="n">
-        <v>35600</v>
-      </c>
+        <v>3100</v>
+      </c>
+      <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Коробка L с радужной гипсофилой для мамы</t>
+          <t>Букет АРОМАТ с диантусами</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>3799</v>
+        <v>2700</v>
       </c>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
+          <t>https://static.tildacdn.com/stor3837-6639-4439-b637-613064363466/87696411.jpg</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-aromat-s-diantusami</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Коробка для мамы с гипсофилой M</t>
+          <t>Вставка сердце в букет</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>2999</v>
+        <v>250</v>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>101 роза нежный микс в корзине</t>
+          <t>Букет "Стильный микс" с орхидеями</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>27990</v>
+        <v>5300</v>
       </c>
       <c r="C398" t="n">
-        <v>33500</v>
+        <v>5900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
+          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-704877065131-buket-stilnii-miks-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Букет ЛЕТО с хризантемами и ромашками</t>
+          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>3100</v>
+        <v>7200</v>
       </c>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-6636-4435-b631-343863306433/59411787.jpg</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Букет АРОМАТ с диантусами</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>2700</v>
+        <v>4690</v>
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3837-6639-4439-b637-613064363466/87696411.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-aromat-s-diantusami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Вставка сердце в букет</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>250</v>
+        <v>3500</v>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
+          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
+          <t>Букет БОМБИТА</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>3890</v>
+        <v>4050</v>
       </c>
       <c r="C402" t="n">
-        <v>4000</v>
+        <v>5400</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-6363-4130-a535-336236616236/99256221.jpg</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-bombita</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Букет "Стильный микс" с орхидеями</t>
+          <t>Букет из пионовидных роз в оформлении - 7</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>5300</v>
-      </c>
-      <c r="C403" t="n">
-        <v>5900</v>
-      </c>
+        <v>2650</v>
+      </c>
+      <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
+          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-704877065131-buket-stilnii-miks-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
+          <t>Букет из пионовидных роз в оформлении - 9</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>7200</v>
+        <v>3250</v>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-6636-4435-b631-343863306433/59411787.jpg</t>
+          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
+          <t>Букет из пионовидных роз в оформлении - 11</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>4690</v>
+        <v>3850</v>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
+          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>3500</v>
+        <v>3590</v>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Букет БОМБИТА</t>
+          <t>Ромашкина любовь</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>4050</v>
-      </c>
-      <c r="C407" t="n">
-        <v>5400</v>
-      </c>
+        <v>10990</v>
+      </c>
+      <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-6363-4130-a535-336236616236/99256221.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-bombita</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 7</t>
+          <t>ВАУ КОРЗИНА ОРХИДЕЙ</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>2650</v>
+        <v>32990</v>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
+          <t>https://static.tildacdn.com/stor6232-6239-4333-b864-323133363433/21466466.jpg</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-orhidei</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 9</t>
+          <t>Букет "НЕЖЕНКА" с гортензией</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>3250</v>
+        <v>2200</v>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
+          <t>https://static.tildacdn.com/stor6532-3462-4639-b135-666433323866/31702549.jpg</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 11</t>
+          <t>Букет РАДУЖНЫЙ с альстромериями</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>3850</v>
-      </c>
-      <c r="C410" t="inlineStr"/>
+        <v>2700</v>
+      </c>
+      <c r="C410" t="n">
+        <v>3450</v>
+      </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
+          <t>Гипсофила от всего сердца</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>3590</v>
+        <v>3200</v>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6530-4836-a565-643263303762/33953573.jpg</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-398838219472-gipsofila-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Ромашкина любовь</t>
+          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>10990</v>
+        <v>3600</v>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
+          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>ВАУ КОРЗИНА ОРХИДЕЙ</t>
+          <t>Букет МАЛИНОВОЕ СУФЛЕ с кустовыми розами</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>32990</v>
+        <v>3600</v>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6232-6239-4333-b864-323133363433/21466466.jpg</t>
+          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-orhidei</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-910512563562-buket-malinovoe-sufle-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Букет "НЕЖЕНКА" с гортензией</t>
+          <t>51 пионовидная кустовая роза в нежном оформлении</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>2200</v>
-      </c>
-      <c r="C414" t="inlineStr"/>
+        <v>15500</v>
+      </c>
+      <c r="C414" t="n">
+        <v>18000</v>
+      </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6532-3462-4639-b135-666433323866/31702549.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Букет РАДУЖНЫЙ с альстромериями</t>
+          <t>Букет РОМАНТИКА</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>2700</v>
+        <v>4150</v>
       </c>
       <c r="C415" t="n">
-        <v>3450</v>
+        <v>5790</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
+          <t>https://static.tildacdn.com/stor6236-3638-4164-b265-643862396434/56613877.jpg</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-359890420482-buket-romantika</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Гипсофила от всего сердца</t>
+          <t>Букет Комплимент с маттиолой</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>3200</v>
+        <v>1800</v>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6530-4836-a565-643263303762/33953573.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-398838219472-gipsofila-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
+          <t>Пионовидные кустовые розы в оформлении - 9</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>3600</v>
+        <v>3650</v>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
+          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Букет МАЛИНОВОЕ СУФЛЕ с кустовыми розами</t>
+          <t>Пионовидные кустовые розы в оформлении - 11</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>3600</v>
+        <v>4400</v>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-910512563562-buket-malinovoe-sufle-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
+          <t>Пионовидные кустовые розы в оформлении - 15</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>5650</v>
+        <v>5500</v>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-3435-4736-b964-373535626539/31455574.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>51 пионовидная кустовая роза в нежном оформлении</t>
+          <t>Пионовидные кустовые розы в оформлении - 25</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>15500</v>
-      </c>
-      <c r="C420" t="n">
-        <v>18000</v>
-      </c>
+        <v>9500</v>
+      </c>
+      <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Букет РОМАНТИКА</t>
+          <t>Пионовидные кустовые розы в оформлении - 35</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>4150</v>
-      </c>
-      <c r="C421" t="n">
-        <v>5790</v>
-      </c>
+        <v>12900</v>
+      </c>
+      <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6236-3638-4164-b265-643862396434/56613877.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-359890420482-buket-romantika</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Букет Комплимент с маттиолой</t>
+          <t>Пионовидные кустовые розы в оформлении - 51</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>1800</v>
+        <v>15900</v>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 9</t>
+          <t>Пионовидные кустовые розы в оформлении - 101</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>3650</v>
+        <v>31100</v>
       </c>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 11</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>4400</v>
+        <v>2800</v>
       </c>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 15</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>5500</v>
+        <v>3500</v>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 25</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>9500</v>
+        <v>5500</v>
       </c>
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 35</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>12900</v>
+        <v>8700</v>
       </c>
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 51</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -9741,388 +9735,283 @@
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 101</t>
+          <t>Подарочный набор для мамы 1</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>31100</v>
+        <v>3990</v>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
+          <t>Подарок для мамы 2</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>2800</v>
+        <v>4990</v>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
+          <t>Подарок для мамы 3 селебрити</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>3500</v>
+        <v>5199</v>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
+          <t>Букет ЛЕДИ РЕД с пион розами</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>5500</v>
+        <v>2450</v>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-6634-4338-a635-316164643339/52783953.jpg</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-341373252172-buket-ledi-red-s-pion-rozami</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
+          <t>Подарочный бокс Рафаэлло</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>8700</v>
+        <v>2300</v>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor3132-3163-4362-b936-303066363765/67414703.jpg</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-291016517802-podarochnii-boks-rafaello</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
+          <t>Игрушка Мишка "Валентин"</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>15900</v>
+        <v>1300</v>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Подарочный набор для мамы 1</t>
+          <t>Игрушка Котик - 25см</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>3990</v>
+        <v>1200</v>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Подарок для мамы 2</t>
+          <t>Игрушка Котик - 35см</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>4990</v>
+        <v>1850</v>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Подарок для мамы 3 селебрити</t>
+          <t>Игрушка Мишка Милые глазки - 25см</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>5199</v>
+        <v>1100</v>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Букет ЛЕДИ РЕД с пион розами</t>
+          <t>Игрушка Мишка Милые глазки - 35см</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>2450</v>
+        <v>1850</v>
       </c>
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-6634-4338-a635-316164643339/52783953.jpg</t>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-341373252172-buket-ledi-red-s-pion-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Подарочный бокс Рафаэлло</t>
+          <t>Гипсофила от всего сердца</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>2300</v>
+        <v>4550</v>
       </c>
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3132-3163-4362-b936-303066363765/67414703.jpg</t>
+          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-291016517802-podarochnii-boks-rafaello</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Игрушка Мишка "Валентин"</t>
+          <t>Букет РУСАЛОЧКА</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>1300</v>
+        <v>4050</v>
       </c>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-6432-4761-b936-656137636438/83917609.jpg</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-195551843462-buket-rusalochka</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 25см</t>
+          <t>Букет ЭКСЛЮЗИВ с ажурными розами</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>1200</v>
+        <v>7200</v>
       </c>
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+          <t>https://static.tildacdn.com/stor3465-6139-4161-b636-326631643031/80766082.jpg</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>Игрушка Котик - 35см</t>
-        </is>
-      </c>
-      <c r="B442" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C442" t="inlineStr"/>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>Игрушка Мишка Милые глазки - 25см</t>
-        </is>
-      </c>
-      <c r="B443" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C443" t="inlineStr"/>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>Игрушка Мишка Милые глазки - 35см</t>
-        </is>
-      </c>
-      <c r="B444" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C444" t="inlineStr"/>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>Гипсофила от всего сердца</t>
-        </is>
-      </c>
-      <c r="B445" t="n">
-        <v>4550</v>
-      </c>
-      <c r="C445" t="inlineStr"/>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>Букет ЭКСЛЮЗИВ с ажурными розами</t>
-        </is>
-      </c>
-      <c r="B446" t="n">
-        <v>7200</v>
-      </c>
-      <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3465-6139-4161-b636-326631643031/80766082.jpg</t>
-        </is>
-      </c>
-      <c r="E446" t="inlineStr">
         <is>
           <t>https://ohapka-flowers.ru/tproduct/802241395-655606921272-buket-ekslyuziv-s-azhurnimi-rozami</t>
         </is>

--- a/feed_converted.xlsx
+++ b/feed_converted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E441"/>
+  <dimension ref="A1:E426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=498825305721</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=498825305721</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=265791107231</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=265791107231</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=719462284671</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=719462284671</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=858082546771</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=858082546771</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=572499562021</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=572499562021</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=937626279691</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=937626279691</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=882067735871</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=882067735871</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=295802016471</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=295802016471</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=813510992361</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=813510992361</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=918865638511</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=918865638511</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=245383163781</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=245383163781</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=172227793941</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=172227793941</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=671948342101</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=671948342101</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=147847713571</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=147847713571</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=233459302551</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=233459302551</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=769759070961</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=769759070961</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=650628430631</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=650628430631</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=381529129841</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=381529129841</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=200484781031</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=200484781031</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=521071854132</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=521071854132</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=726825371832</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=726825371832</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=468737439372</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=468737439372</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=240310577222</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=240310577222</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=629430115312</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=629430115312</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=365793161732</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=365793161732</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=194812772742</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=194812772742</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=326294220232</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=326294220232</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=383398298482</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=383398298482</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=334614005102</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=334614005102</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=338415573182</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=338415573182</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=882511537061</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=882511537061</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=365883848281</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=365883848281</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=218046257281</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=218046257281</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=888310918641</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=888310918641</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=253996242131</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=253996242131</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=524625626631</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=524625626631</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=708312676961</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=708312676961</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=890184912241</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=890184912241</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=641366797711</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=641366797711</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=286704753391</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=286704753391</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=154015712401</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=154015712401</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=755598860411</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=755598860411</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=856822328931</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=856822328931</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=343053884581</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=343053884581</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=474876597751</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=474876597751</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=715815864171</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=715815864171</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=737906730171</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=737906730171</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=131777960061</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=131777960061</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=424640009971</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=424640009971</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=792474985941</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=792474985941</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=971600188781</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=971600188781</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=849411123101</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=849411123101</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=906749549891</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=906749549891</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=232300719541</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=232300719541</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=178446277531</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=178446277531</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=339170286781</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=339170286781</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=334033959351</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=334033959351</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=648372891461</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=648372891461</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=460563284101</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=460563284101</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=812574642211</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=812574642211</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=942778462231</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=942778462231</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=933284228141</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=933284228141</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=239595825971</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=239595825971</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=622935246391</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=622935246391</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=572824907311</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=572824907311</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=376897062281</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=376897062281</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=778000219301</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=778000219301</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=749920803381</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=749920803381</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=186946957581</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=186946957581</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=245561125991</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=245561125991</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=887024486291</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=887024486291</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=698009287281</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=698009287281</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=641939630461</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=641939630461</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=251643663741</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=251643663741</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=575659429381</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=575659429381</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=746547712011</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=746547712011</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=245992221991</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=245992221991</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=732282555201</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=732282555201</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=762275033411</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=762275033411</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=869360911121</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=869360911121</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=406896937861</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=406896937861</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=911510230531</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=911510230531</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=824822713061</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=824822713061</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=575566972011</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=575566972011</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=288245960112</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=288245960112</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=904434342552</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=904434342552</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=972723029352</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=972723029352</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=345687277251</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=345687277251</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=110596316751</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=110596316751</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=834468360661</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=834468360661</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=591924431631</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=591924431631</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=809069964721</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=809069964721</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=639403969201</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=639403969201</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=437799346701</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=437799346701</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-993169958291-korobochka-s-gipsofiloi?editionuid=156969419741</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-993169958291-korobochka-s-gipsofiloi?editionuid=156969419741</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-993169958291-korobochka-s-gipsofiloi?editionuid=922840956671</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-993169958291-korobochka-s-gipsofiloi?editionuid=922840956671</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-993169958291-korobochka-s-gipsofiloi?editionuid=898673811441</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-993169958291-korobochka-s-gipsofiloi?editionuid=898673811441</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-993169958291-korobochka-s-gipsofiloi?editionuid=219581966181</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-993169958291-korobochka-s-gipsofiloi?editionuid=219581966181</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-903251068361-korobochka-s-hrizantemami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-903251068361-korobochka-s-hrizantemami</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=148944289651</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=148944289651</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=109365076101</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=109365076101</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=376488675211</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=376488675211</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=725631168041</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=725631168041</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=129706362731</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=129706362731</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=566490772771</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=566490772771</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=777289682021</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=777289682021</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=428597863731</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=428597863731</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=576429505171</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=576429505171</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=791959204501</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=791959204501</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=586956459451</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=586956459451</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=617614243671</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=617614243671</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=208995532381</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=208995532381</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=237012589071</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=237012589071</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=906221431041</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=906221431041</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=276160309481</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=276160309481</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=199090330951</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=199090330951</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=693313247081</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=693313247081</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=852958282431</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=852958282431</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=792324955791</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=792324955791</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=538009046131</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=538009046131</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=633884612171</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=633884612171</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=904023676271</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=904023676271</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=961460791401</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=961460791401</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=399118071021</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=399118071021</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=226542346681</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=226542346681</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=645786940181</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=645786940181</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=780430162101</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=780430162101</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=684771627931</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=684771627931</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=109555802941</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=109555802941</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=776811032031</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=776811032031</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=481223248931</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=481223248931</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=336239074871</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=336239074871</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=216056374821</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=216056374821</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=563951015001</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=563951015001</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=516430509881</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=516430509881</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=830975922891</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=830975922891</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=922435599331</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=922435599331</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=779667105481</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=779667105481</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=758031717621</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=758031717621</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=514142055381</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=514142055381</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=224906756131</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=224906756131</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=790412251771</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=790412251771</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=824594865831</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=824594865831</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=249527607241</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=249527607241</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=852846598511</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=852846598511</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=463498073821</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=463498073821</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=994973672881</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=994973672881</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-456677254991-51-kremovaya-roza?editionuid=470986963941</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-456677254991-51-kremovaya-roza?editionuid=470986963941</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-456677254991-51-kremovaya-roza?editionuid=756066172161</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-456677254991-51-kremovaya-roza?editionuid=756066172161</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke?editionuid=677875507802</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-128828996681-101-krasnaya-roza-v-korobke?editionuid=677875507802</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke?editionuid=414704203762</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-128828996681-101-krasnaya-roza-v-korobke?editionuid=414704203762</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=626304677871</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-848543105701-15kremovih-roz?editionuid=626304677871</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=757701389531</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-848543105701-15kremovih-roz?editionuid=757701389531</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=931089475821</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-354737980041-51-krasnaya-roza?editionuid=931089475821</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=692401540222</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-354737980041-51-krasnaya-roza?editionuid=692401540222</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-168896456031-51-roza-serdtse-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-168896456031-51-roza-serdtse-v-korobke</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-511125332671-25-rozovih-roz-premium-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-511125332671-25-rozovih-roz-premium-v-korobke</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=769434790781</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-602559582111-15-krasnih-roz?editionuid=769434790781</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=205666183652</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-602559582111-15-krasnih-roz?editionuid=205666183652</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-542827273651-51-krasno-belaya-roza-v-oformlenii?editionuid=516167563281</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-542827273651-51-krasno-belaya-roza-v-oformlenii?editionuid=516167563281</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-511893198801-51-belaya-roza?editionuid=631123744291</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-511893198801-51-belaya-roza?editionuid=631123744291</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=478488702861</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-461595881361-101-krasno-belaya-roza?editionuid=478488702861</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=658675482971</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-461595881361-101-krasno-belaya-roza?editionuid=658675482971</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-472980179331-25-roz-premium-v-oformlenii?editionuid=120293941621</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-472980179331-25-roz-premium-v-oformlenii?editionuid=120293941621</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-710052950101-25-krasno-belih-roz-v-oformlenii?editionuid=111716594231</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-710052950101-25-krasno-belih-roz-v-oformlenii?editionuid=111716594231</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=679979674191</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-264521907571-21-krasnaya-roza?editionuid=679979674191</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=688291434032</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-264521907571-21-krasnaya-roza?editionuid=688291434032</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-289807833441-51-rozovaya-roza?editionuid=895253955391</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-289807833441-51-rozovaya-roza?editionuid=895253955391</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=502662350182</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-445760300561-151-roza-v-korzine?editionuid=502662350182</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-887039306391-21-krasnaya-roza-v-tsvetnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-887039306391-21-krasnaya-roza-v-tsvetnoi-korobke</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-218567021051-15-krasno-belih-roz-v-oformlenii</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-608860089361-raffaello</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="C237" t="n">
         <v>4500</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>5600</v>
+        <v>6100</v>
       </c>
       <c r="C238" t="n">
         <v>6100</v>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>7700</v>
+        <v>8500</v>
       </c>
       <c r="C239" t="n">
         <v>8500</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>9100</v>
+        <v>10100</v>
       </c>
       <c r="C240" t="n">
         <v>10100</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>12600</v>
+        <v>14100</v>
       </c>
       <c r="C241" t="n">
         <v>14100</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>17690</v>
+        <v>17950</v>
       </c>
       <c r="C244" t="n">
         <v>18690</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>34690</v>
+        <v>35450</v>
       </c>
       <c r="C245" t="n">
         <v>38690</v>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-441113290851-dorogusha-iz-krasnih-roz-s-orhideyami</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
         </is>
       </c>
     </row>
@@ -6535,58 +6535,56 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
+          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>3690</v>
+        <v>3000</v>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
+          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Зефирный - Белые</t>
+          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C281" t="n">
-        <v>3500</v>
-      </c>
+        <v>3690</v>
+      </c>
+      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Зефирный - Микс</t>
+          <t>Зефирный - Белые</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -6597,249 +6595,249 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-997928842911-zefirnii?editionuid=323569405822</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Нежный</t>
+          <t>Зефирный - Микс</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>3450</v>
+        <v>3500</v>
       </c>
       <c r="C283" t="n">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3061-4535-b035-306430303965/35298752.jpg</t>
+          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=430145379292</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-997928842911-zefirnii?editionuid=978085575362</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Яркие</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>3550</v>
-      </c>
-      <c r="C284" t="n">
-        <v>3900</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-3031-4331-b733-356664626131/31576954.jpg</t>
+          <t>https://static.tildacdn.com/stor3037-3037-4331-b032-653532393265/10296532.jpg</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=628386621972</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>3500</v>
+        <v>5800</v>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3037-3037-4331-b032-653532393265/10296532.jpg</t>
+          <t>https://static.tildacdn.com/stor6630-3762-4363-b331-323964366539/21633765.jpg</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
+          <t>КРЕМ ДЖЕМ С ЭВКАЛИПТОМ из кустовых роз</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>5800</v>
+        <v>3950</v>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6630-3762-4363-b331-323964366539/21633765.jpg</t>
+          <t>https://static.tildacdn.com/stor6637-6164-4634-b466-333164313039/56875072.jpg</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-766984785531-krem-dzhem-s-evkaliptom-iz-kustovih-roz</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>КРЕМ ДЖЕМ С ЭВКАЛИПТОМ из кустовых роз</t>
+          <t>Игрушка Летающий Единорожка</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>3950</v>
+        <v>1400</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6637-6164-4634-b466-333164313039/56875072.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-3961-4366-b766-326639646432/18447615.jpg</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-krem-dzhem-s-evkaliptom-iz-kustovih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-721499980101-igrushka-letayuschii-edinorozhka</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Игрушка Летающий Единорожка</t>
+          <t>Игрушка Мякий медведь Мишаня</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>1400</v>
+        <v>3500</v>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-3961-4366-b766-326639646432/18447615.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-letayuschii-edinorozhka</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-778767705501-igrushka-myakii-medved-mishanya</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Игрушка Мякий медведь Мишаня</t>
+          <t>Игрушкп Зайка милашка</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>3500</v>
+        <v>1100</v>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-594044496021-igrushkp-zaika-milashka</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Игрушкп Зайка милашка</t>
+          <t>Букет Солнечный из хризантем</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>1100</v>
+        <v>2800</v>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
+          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-638070352371-buket-solnechnii-iz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Букет Солнечный из хризантем</t>
+          <t>LOVE IS....из кустовых роз с ромашками</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>2800</v>
+        <v>10990</v>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
+          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>LOVE IS....из кустовых роз с ромашками</t>
+          <t>БУКЕТ ПРОВАНС с хризантемамми и розами</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>10990</v>
-      </c>
-      <c r="C292" t="inlineStr"/>
+        <v>4990</v>
+      </c>
+      <c r="C292" t="n">
+        <v>5500</v>
+      </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
+          <t>https://static.tildacdn.com/stor6331-3465-4438-a461-636562623633/78518381.jpg</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-728832612721-buket-provans-s-hrizantemammi-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>БУКЕТ ПРОВАНС с хризантемамми и розами</t>
+          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>4990</v>
+        <v>16290</v>
       </c>
       <c r="C293" t="n">
-        <v>5500</v>
+        <v>175550</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6331-3465-4438-a461-636562623633/78518381.jpg</t>
+          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-provans-s-hrizantemammi-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
         </is>
       </c>
     </row>
@@ -6850,10 +6848,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>16290</v>
+        <v>8500</v>
       </c>
       <c r="C294" t="n">
-        <v>175550</v>
+        <v>9200</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -6862,257 +6860,255 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
+          <t>25 белых роз с эвкалиптом</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>8500</v>
+        <v>7800</v>
       </c>
       <c r="C295" t="n">
-        <v>9200</v>
+        <v>9750</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-624506536881-25-belih-roz-s-evkaliptom</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>25 белых роз с эвкалиптом</t>
+          <t>Букет орхидей БАБОЧКА</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>7800</v>
+        <v>3750</v>
       </c>
       <c r="C296" t="n">
-        <v>9750</v>
+        <v>4300</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
+          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-229561542201-buket-orhidei-babochka</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Букет орхидей БАБОЧКА</t>
+          <t>Букет ромашек "Модный"</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>3750</v>
+        <v>2800</v>
       </c>
       <c r="C297" t="n">
-        <v>4300</v>
+        <v>3200</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-966890057501-buket-romashek-modnii</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Букет ромашек "Модный"</t>
+          <t>Букет ЛАЙК с красными розами</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C298" t="n">
-        <v>3200</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
+          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-271548446971-buket-laik-s-krasnimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Букет ЛАЙК с красными розами</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
+          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>3000</v>
+        <v>3700</v>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>3700</v>
+        <v>4400</v>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
+          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>4400</v>
+        <v>5800</v>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>5800</v>
+        <v>9300</v>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>9300</v>
+        <v>11250</v>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>11250</v>
+        <v>15990</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>15990</v>
+        <v>29990</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
@@ -7122,589 +7118,589 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>29990</v>
+        <v>6700</v>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>6700</v>
+        <v>9300</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>9300</v>
+        <v>12300</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>12300</v>
+        <v>22999</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>22999</v>
+        <v>3300</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>3300</v>
+        <v>4100</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
+          <t>Букет Белый шоколад из белых роз</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C313" t="inlineStr"/>
+        <v>5800</v>
+      </c>
+      <c r="C313" t="n">
+        <v>5900</v>
+      </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-604610293441-buket-belii-shokolad-iz-belih-roz</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Букет Белый шоколад из белых роз</t>
+          <t>Ажурные розы в коробке</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C314" t="n">
-        <v>5900</v>
-      </c>
+        <v>3800</v>
+      </c>
+      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
+          <t>https://static.tildacdn.com/stor3638-6166-4062-a634-363361633538/95787248.jpg</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-706637499731-azhurnie-rozi-v-korobke</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Ажурные розы в коробке</t>
+          <t>Комплимент ВАНИЛЬ с ромашками</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>3800</v>
+        <v>2690</v>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3638-6166-4062-a634-363361633538/95787248.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-706637499731-azhurnie-rozi-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-355408923071-kompliment-vanil-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Комплимент ВАНИЛЬ с ромашками</t>
+          <t>Коробка с кустовыми розами</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>2690</v>
+        <v>3500</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
+          <t>https://static.tildacdn.com/stor6561-6635-4566-b836-393737636261/47533235.jpg</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-190380899281-korobka-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Коробка с кустовыми розами</t>
+          <t>Дивная Орхидея</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>3500</v>
+        <v>5600</v>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6561-6635-4566-b836-393737636261/47533235.jpg</t>
+          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-399495570211-divnaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Дивная Орхидея</t>
+          <t>Коробка "Орхидея "</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-909950155641-korobka-orhideya-</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Коробка "Орхидея "</t>
+          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>5700</v>
+        <v>6999</v>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
+          <t>https://static.tildacdn.com/stor3366-3065-4265-b239-376235653964/39754072.jpg</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
+          <t>Розовый дым</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>6999</v>
+        <v>13500</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3366-3065-4265-b239-376235653964/39754072.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-802553109081-rozovii-dim</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Розовый дым</t>
+          <t>Букет Комплимент ПУШ с хризантемами - M</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>13500</v>
+        <v>1800</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
+          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - M</t>
+          <t>Букет Комплимент ПУШ с хризантемами - L</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>1800</v>
+        <v>2150</v>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
+          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - L</t>
+          <t>Букет Комплимент МАРМЕЛАД</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>2150</v>
+        <v>2650</v>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-322995211141-buket-kompliment-marmelad</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Букет Комплимент МАРМЕЛАД</t>
+          <t>Коробка с цветами ЛЮКС</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>2650</v>
+        <v>9990</v>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-3036-4663-b030-666130666261/13712242.jpg</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-146373087581-korobka-s-tsvetami-lyuks</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Коробка с цветами ЛЮКС</t>
+          <t>Шикарная корзина с кустовыми розами</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>9990</v>
-      </c>
-      <c r="C325" t="inlineStr"/>
+        <v>18990</v>
+      </c>
+      <c r="C325" t="n">
+        <v>21500</v>
+      </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-3036-4663-b030-666130666261/13712242.jpg</t>
+          <t>https://static.tildacdn.com/stor3938-6432-4138-a266-633765366335/95496298.jpg</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-146373087581-korobka-s-tsvetami-lyuks</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Шикарная корзина с кустовыми розами</t>
+          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>18990</v>
-      </c>
-      <c r="C326" t="n">
-        <v>21500</v>
-      </c>
+        <v>2350</v>
+      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3938-6432-4138-a266-633765366335/95496298.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>2350</v>
+        <v>3850</v>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>3850</v>
+        <v>5350</v>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
+          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>5350</v>
+        <v>2550</v>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
+          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>2550</v>
+        <v>4250</v>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>4250</v>
+        <v>5900</v>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
+          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>5900</v>
+        <v>8600</v>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
+          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>8600</v>
+        <v>8990</v>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>8990</v>
+        <v>11990</v>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
@@ -7714,2306 +7710,1981 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
+          <t>Букет МЕЧТА с кустовыми розами и розами крем</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>11990</v>
-      </c>
-      <c r="C335" t="inlineStr"/>
+        <v>6500</v>
+      </c>
+      <c r="C335" t="n">
+        <v>6500</v>
+      </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor6538-3533-4866-b134-646334653462/14245314.jpg</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-831554304821-buket-mechta-s-kustovimi-rozami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Букет МЕЧТА с кустовыми розами и розами крем</t>
+          <t>Корзина кустовых роз 1</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>6500</v>
+        <v>13990</v>
       </c>
       <c r="C336" t="n">
-        <v>6500</v>
+        <v>14990</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6538-3533-4866-b134-646334653462/14245314.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-mechta-s-kustovimi-rozami-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-626227787071-korzina-kustovih-roz-1</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Корзина кустовых роз 1</t>
+          <t>Букет пионовидных роз с эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>13990</v>
-      </c>
-      <c r="C337" t="n">
-        <v>14990</v>
-      </c>
+        <v>6400</v>
+      </c>
+      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Атласная лента</t>
+          <t>Букет пионовидных роз с эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>3250</v>
+        <v>10800</v>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Атласная лента</t>
+          <t>Букет пионовидных роз с эвкалиптом - 35</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>3950</v>
+        <v>16500</v>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 15 - Атласная лента</t>
+          <t>Букет пионовидных роз с эвкалиптом - 11</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>5350</v>
+        <v>5200</v>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Атласная лента</t>
+          <t>Букет пионовидных роз с эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>8850</v>
+        <v>4400</v>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>Вау-букет 151 роза и Большой медведь</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>12350</v>
-      </c>
-      <c r="C342" t="inlineStr"/>
+        <v>39990</v>
+      </c>
+      <c r="C342" t="n">
+        <v>49999</v>
+      </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Атласная лента</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>16990</v>
+        <v>3650</v>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Матовая бумага</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>9100</v>
+        <v>4100</v>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>12650</v>
+        <v>9100</v>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Матовая бумага</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>17500</v>
+        <v>14900</v>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Матовая бумага</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>3500</v>
+        <v>23990</v>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Матовая бумага</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>4200</v>
+        <v>5750</v>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 15</t>
+          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>6400</v>
+        <v>4450</v>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 25</t>
+          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>10800</v>
-      </c>
-      <c r="C350" t="inlineStr"/>
+        <v>6250</v>
+      </c>
+      <c r="C350" t="n">
+        <v>7500</v>
+      </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 35</t>
+          <t>Букет "Милашка"</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>16500</v>
-      </c>
-      <c r="C351" t="inlineStr"/>
+        <v>8950</v>
+      </c>
+      <c r="C351" t="n">
+        <v>9990</v>
+      </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3033-6433-4637-b666-346533306135/93848240.jpg</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-103213775721-buket-milashka</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 11</t>
+          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>5200</v>
-      </c>
-      <c r="C352" t="inlineStr"/>
+        <v>12999</v>
+      </c>
+      <c r="C352" t="n">
+        <v>15590</v>
+      </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-337767923621-korzina-alstromerii</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 9</t>
+          <t>Букет Комплимент "НЕЖНОСТЬ" с хризантемами и белыми розами</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>4400</v>
+        <v>3650</v>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3639-3537-4637-b334-343835343030/44921274.jpg</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-559524591171-buket-kompliment-nezhnost-s-hrizantemami</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
+          <t>Букет Комплимент "Дюшес" с альстромериями</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>5050</v>
+        <v>2450</v>
       </c>
       <c r="C354" t="n">
-        <v>5500</v>
+        <v>2600</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
+          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
+          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Нет</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>8250</v>
-      </c>
-      <c r="C355" t="n">
-        <v>9500</v>
-      </c>
+        <v>3300</v>
+      </c>
+      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
+          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=223863406172</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
+          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Да</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>11250</v>
-      </c>
-      <c r="C356" t="n">
-        <v>15500</v>
-      </c>
+        <v>3550</v>
+      </c>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=119690417772</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
+          <t>Букет ПЛОМБИР</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>15550</v>
-      </c>
-      <c r="C357" t="n">
-        <v>18200</v>
-      </c>
+        <v>4100</v>
+      </c>
+      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
+          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-437576209011-buket-plombir</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
+          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>27999</v>
-      </c>
-      <c r="C358" t="n">
-        <v>35500</v>
-      </c>
+        <v>3650</v>
+      </c>
+      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-391414887741-buket-kompliment-krem-s-rozamm</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
+          <t>Игрушка Мишка-плюш с бантом "M"</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>3250</v>
-      </c>
-      <c r="C359" t="n">
-        <v>3500</v>
-      </c>
+        <v>1850</v>
+      </c>
+      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Вау-букет 151 роза и Большой медведь</t>
+          <t>Игрушкп Медведь большой Ягодка</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>39990</v>
-      </c>
-      <c r="C360" t="n">
-        <v>49999</v>
-      </c>
+        <v>5500</v>
+      </c>
+      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-551329556541-igrushkp-medved-bolshoi-yagodka</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
+          <t>Игрушка Мишка-плюш "S" беж.</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>3650</v>
+        <v>1300</v>
       </c>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
+          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-554350694011-igrushka-mishka-plyush-s-bezh</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
+          <t>Игрушка Мишка-плюш "S" белый</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>4100</v>
+        <v>1300</v>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-292174636271-igrushka-mishka-plyush-s-belii</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
+          <t>Букет ГИПНОЗ с лилиями и розами</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>9100</v>
-      </c>
-      <c r="C363" t="inlineStr"/>
+        <v>6700</v>
+      </c>
+      <c r="C363" t="n">
+        <v>7200</v>
+      </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3763-3431-4736-b439-363632386633/37134397.jpg</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
+          <t>Коробка "Ангажемент Лайт"</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>14900</v>
+        <v>4500</v>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor6537-6664-4833-b033-343662313561/26722422.jpg</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-522766706011-korobka-angazhement-lait</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
+          <t>51 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>23990</v>
-      </c>
-      <c r="C365" t="inlineStr"/>
+        <v>15750</v>
+      </c>
+      <c r="C365" t="n">
+        <v>18990</v>
+      </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-987092854851-51-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
+          <t>Микс "Нежный "в шляпной коробке</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>5750</v>
-      </c>
-      <c r="C366" t="inlineStr"/>
+        <v>4500</v>
+      </c>
+      <c r="C366" t="n">
+        <v>4600</v>
+      </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
+          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
+          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>4450</v>
-      </c>
-      <c r="C367" t="inlineStr"/>
+        <v>3890</v>
+      </c>
+      <c r="C367" t="n">
+        <v>4500</v>
+      </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
+          <t>"Ванильное небо "в шляпной коробке</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>6250</v>
-      </c>
-      <c r="C368" t="n">
-        <v>7500</v>
-      </c>
+        <v>4999</v>
+      </c>
+      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
+          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Букет "Милашка"</t>
+          <t>"Мерилин "</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>8950</v>
+        <v>3650</v>
       </c>
       <c r="C369" t="n">
-        <v>9990</v>
+        <v>3999</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3033-6433-4637-b666-346533306135/93848240.jpg</t>
+          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-570756966211-merilin-</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
+          <t>Мон Амур - 25</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>12999</v>
-      </c>
-      <c r="C370" t="n">
-        <v>15590</v>
-      </c>
+        <v>6800</v>
+      </c>
+      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-488774775451-mon-amur?editionuid=330327920391</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Букет Комплимент "НЕЖНОСТЬ" с хризантемами и белыми розами</t>
+          <t>Мон Амур - 35</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>3650</v>
+        <v>9300</v>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3639-3537-4637-b334-343835343030/44921274.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-hrizantemami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-488774775451-mon-amur?editionuid=460518387891</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Букет Комплимент "Дюшес" с альстромериями</t>
+          <t>Мон Амур - 51</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>2450</v>
+        <v>12990</v>
       </c>
       <c r="C372" t="n">
-        <v>2600</v>
+        <v>17750</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-488774775451-mon-amur?editionuid=548699367961</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Нет</t>
+          <t>Мон Амур - 101</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C373" t="inlineStr"/>
+        <v>24990</v>
+      </c>
+      <c r="C373" t="n">
+        <v>35600</v>
+      </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=223863406172</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-488774775451-mon-amur?editionuid=769488407402</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Да</t>
+          <t>Коробка L с радужной гипсофилой для мамы</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>3550</v>
+        <v>3799</v>
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=119690417772</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Букет ПЛОМБИР</t>
+          <t>Коробка для мамы с гипсофилой M</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>4100</v>
+        <v>2999</v>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
+          <t>101 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C376" t="inlineStr"/>
+        <v>27990</v>
+      </c>
+      <c r="C376" t="n">
+        <v>33500</v>
+      </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
+          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-251477018101-101-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш с бантом "M"</t>
+          <t>Букет ЛЕТО с хризантемами и ромашками</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>1850</v>
+        <v>3100</v>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
+          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Игрушкп Медведь большой Ягодка</t>
+          <t>Букет АРОМАТ с диантусами</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
+          <t>https://static.tildacdn.com/stor3837-6639-4439-b637-613064363466/87696411.jpg</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-489100649391-buket-aromat-s-diantusami</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" беж.</t>
+          <t>Вставка сердце в букет</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>1300</v>
+        <v>250</v>
       </c>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-974556600091-vstavka-serdtse-v-buket</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" белый</t>
+          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C380" t="inlineStr"/>
+        <v>3890</v>
+      </c>
+      <c r="C380" t="n">
+        <v>4000</v>
+      </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
+          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Букет ГИПНОЗ с лилиями и розами</t>
+          <t>Букет "Стильный микс" с орхидеями</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>6700</v>
+        <v>5300</v>
       </c>
       <c r="C381" t="n">
-        <v>7200</v>
+        <v>5900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3763-3431-4736-b439-363632386633/37134397.jpg</t>
+          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-704877065131-buket-stilnii-miks-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Коробка "Ангажемент Лайт"</t>
+          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>4500</v>
+        <v>7200</v>
       </c>
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6537-6664-4833-b033-343662313561/26722422.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-6636-4435-b631-343863306433/59411787.jpg</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522766706011-korobka-angazhement-lait</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>51 роза нежный микс в корзине</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>15750</v>
-      </c>
-      <c r="C383" t="n">
-        <v>18990</v>
-      </c>
+        <v>4690</v>
+      </c>
+      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Микс "Нежный "в шляпной коробке</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C384" t="n">
-        <v>4600</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
+          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
+          <t>Букет БОМБИТА</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>3890</v>
+        <v>4050</v>
       </c>
       <c r="C385" t="n">
-        <v>4500</v>
+        <v>5400</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-6363-4130-a535-336236616236/99256221.jpg</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-148743167681-buket-bombita</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке</t>
+          <t>Букет из пионовидных роз в оформлении - 7</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>4999</v>
+        <v>2900</v>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
+          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>"Мерилин "</t>
+          <t>Букет из пионовидных роз в оформлении - 9</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C387" t="n">
-        <v>3999</v>
-      </c>
+        <v>3450</v>
+      </c>
+      <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
+          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Мон Амур - 25</t>
+          <t>Букет из пионовидных роз в оформлении - 11</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>6800</v>
+        <v>4150</v>
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Мон Амур - 35</t>
+          <t>Букет из пионовидных роз в оформлении - 15</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>9300</v>
+        <v>5550</v>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=541061184792</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Мон Амур - 51</t>
+          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>12990</v>
-      </c>
-      <c r="C390" t="n">
-        <v>17750</v>
-      </c>
+        <v>3590</v>
+      </c>
+      <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Мон Амур - 101</t>
+          <t>Ромашкина любовь</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>24990</v>
-      </c>
-      <c r="C391" t="n">
-        <v>35600</v>
-      </c>
+        <v>10990</v>
+      </c>
+      <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-950411727471-romashkina-lyubov</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Коробка L с радужной гипсофилой для мамы</t>
+          <t>ВАУ КОРЗИНА ОРХИДЕЙ</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>3799</v>
+        <v>32990</v>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
+          <t>https://static.tildacdn.com/stor6232-6239-4333-b864-323133363433/21466466.jpg</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-522713984731-vau-korzina-orhidei</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Коробка для мамы с гипсофилой M</t>
+          <t>Букет "НЕЖЕНКА" с гортензией</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>2999</v>
+        <v>2200</v>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
+          <t>https://static.tildacdn.com/stor6532-3462-4639-b135-666433323866/31702549.jpg</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-500037248201-buket-nezhenka-s-gortenziei</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>101 роза нежный микс в корзине</t>
+          <t>Букет РАДУЖНЫЙ с альстромериями</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>27990</v>
+        <v>2700</v>
       </c>
       <c r="C394" t="n">
-        <v>33500</v>
+        <v>3450</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-290729033721-buket-raduzhnii-s-alstromeriyami</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Букет ЛЕТО с хризантемами и ромашками</t>
+          <t>Гипсофила от всего сердца</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6530-4836-a565-643263303762/33953573.jpg</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-398838219472-gipsofila-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Букет АРОМАТ с диантусами</t>
+          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>2700</v>
+        <v>3600</v>
       </c>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3837-6639-4439-b637-613064363466/87696411.jpg</t>
+          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-aromat-s-diantusami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-843977882512-buket-tebe-konfetka</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Вставка сердце в букет</t>
+          <t>Букет МАЛИНОВОЕ СУФЛЕ с кустовыми розами</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>250</v>
+        <v>3600</v>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
+          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-910512563562-buket-malinovoe-sufle-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Букет "Стильный микс" с орхидеями</t>
+          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>5300</v>
-      </c>
-      <c r="C398" t="n">
-        <v>5900</v>
-      </c>
+        <v>5650</v>
+      </c>
+      <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-3435-4736-b964-373535626539/31455574.jpg</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-704877065131-buket-stilnii-miks-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-907367951302-buket-sinyaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
+          <t>51 пионовидная кустовая роза в нежном оформлении</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>7200</v>
-      </c>
-      <c r="C399" t="inlineStr"/>
+        <v>15500</v>
+      </c>
+      <c r="C399" t="n">
+        <v>18000</v>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-6636-4435-b631-343863306433/59411787.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
+          <t>Букет РОМАНТИКА</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>4690</v>
-      </c>
-      <c r="C400" t="inlineStr"/>
+        <v>4150</v>
+      </c>
+      <c r="C400" t="n">
+        <v>5790</v>
+      </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
+          <t>https://static.tildacdn.com/stor6236-3638-4164-b265-643862396434/56613877.jpg</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-359890420482-buket-romantika</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
+          <t>Букет Комплимент с маттиолой</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>3500</v>
+        <v>1800</v>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-232892230242-buket-kompliment-s-mattioloi</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Букет БОМБИТА</t>
+          <t>Пионовидные кустовые розы в оформлении - 9</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>4050</v>
-      </c>
-      <c r="C402" t="n">
-        <v>5400</v>
-      </c>
+        <v>3650</v>
+      </c>
+      <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-6363-4130-a535-336236616236/99256221.jpg</t>
+          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-bombita</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 7</t>
+          <t>Пионовидные кустовые розы в оформлении - 11</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>2650</v>
+        <v>4400</v>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 9</t>
+          <t>Пионовидные кустовые розы в оформлении - 15</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>3250</v>
+        <v>5500</v>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 11</t>
+          <t>Пионовидные кустовые розы в оформлении - 25</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>3850</v>
+        <v>9500</v>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
+          <t>Пионовидные кустовые розы в оформлении - 35</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>3590</v>
+        <v>12900</v>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Ромашкина любовь</t>
+          <t>Пионовидные кустовые розы в оформлении - 51</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>10990</v>
+        <v>15900</v>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>ВАУ КОРЗИНА ОРХИДЕЙ</t>
+          <t>Пионовидные кустовые розы в оформлении - 101</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>32990</v>
+        <v>31100</v>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6232-6239-4333-b864-323133363433/21466466.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-orhidei</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Букет "НЕЖЕНКА" с гортензией</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>2200</v>
+        <v>2800</v>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6532-3462-4639-b135-666433323866/31702549.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Букет РАДУЖНЫЙ с альстромериями</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>2700</v>
-      </c>
-      <c r="C410" t="n">
-        <v>3450</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Гипсофила от всего сердца</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>3200</v>
+        <v>5500</v>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6530-4836-a565-643263303762/33953573.jpg</t>
+          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-398838219472-gipsofila-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>3600</v>
+        <v>8700</v>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Букет МАЛИНОВОЕ СУФЛЕ с кустовыми розами</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>3600</v>
+        <v>15900</v>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-910512563562-buket-malinovoe-sufle-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>51 пионовидная кустовая роза в нежном оформлении</t>
+          <t>Подарочный набор для мамы 1</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>15500</v>
-      </c>
-      <c r="C414" t="n">
-        <v>18000</v>
-      </c>
+        <v>3990</v>
+      </c>
+      <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-786253932122-podarochnii-nabor-dlya-mami-1</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Букет РОМАНТИКА</t>
+          <t>Подарок для мамы 2</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>4150</v>
-      </c>
-      <c r="C415" t="n">
-        <v>5790</v>
-      </c>
+        <v>4990</v>
+      </c>
+      <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6236-3638-4164-b265-643862396434/56613877.jpg</t>
+          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-359890420482-buket-romantika</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-738379822212-podarok-dlya-mami-2</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Букет Комплимент с маттиолой</t>
+          <t>Подарок для мамы 3 селебрити</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>1800</v>
+        <v>5199</v>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-307373021402-podarok-dlya-mami-3-selebriti</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 9</t>
+          <t>Букет ЛЕДИ РЕД с пион розами</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>3650</v>
+        <v>2450</v>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-6634-4338-a635-316164643339/52783953.jpg</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-341373252172-buket-ledi-red-s-pion-rozami</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 11</t>
+          <t>Подарочный бокс Рафаэлло</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>4400</v>
+        <v>2300</v>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
+          <t>https://static.tildacdn.com/stor3132-3163-4362-b936-303066363765/67414703.jpg</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-291016517802-podarochnii-boks-rafaello</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 15</t>
+          <t>Игрушка Мишка "Валентин"</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>5500</v>
+        <v>1300</v>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
+          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-630681598512-igrushka-mishka-valentin</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 25</t>
+          <t>Игрушка Котик - 25см</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>9500</v>
+        <v>1200</v>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-863762674412-igrushka-kotik?editionuid=707456987082</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 35</t>
+          <t>Игрушка Котик - 35см</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>12900</v>
+        <v>1850</v>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-863762674412-igrushka-kotik?editionuid=932117895852</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 51</t>
+          <t>Игрушка Мишка Милые глазки - 25см</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>15900</v>
+        <v>1100</v>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 101</t>
+          <t>Игрушка Мишка Милые глазки - 35см</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>31100</v>
+        <v>1850</v>
       </c>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
+          <t>Гипсофила от всего сердца</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>2800</v>
+        <v>4550</v>
       </c>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-745191202102-gipsofila-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
+          <t>Букет РУСАЛОЧКА</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>3500</v>
+        <v>4050</v>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-6432-4761-b936-656137636438/83917609.jpg</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-195551843462-buket-rusalochka</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
+          <t>Букет ЭКСЛЮЗИВ с ажурными розами</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>5500</v>
+        <v>7200</v>
       </c>
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
+          <t>https://static.tildacdn.com/stor3465-6139-4161-b636-326631643031/80766082.jpg</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
-        </is>
-      </c>
-      <c r="B427" t="n">
-        <v>8700</v>
-      </c>
-      <c r="C427" t="inlineStr"/>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
-        </is>
-      </c>
-      <c r="B428" t="n">
-        <v>15900</v>
-      </c>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>Подарочный набор для мамы 1</t>
-        </is>
-      </c>
-      <c r="B429" t="n">
-        <v>3990</v>
-      </c>
-      <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>Подарок для мамы 2</t>
-        </is>
-      </c>
-      <c r="B430" t="n">
-        <v>4990</v>
-      </c>
-      <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>Подарок для мамы 3 селебрити</t>
-        </is>
-      </c>
-      <c r="B431" t="n">
-        <v>5199</v>
-      </c>
-      <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>Букет ЛЕДИ РЕД с пион розами</t>
-        </is>
-      </c>
-      <c r="B432" t="n">
-        <v>2450</v>
-      </c>
-      <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor6430-6634-4338-a635-316164643339/52783953.jpg</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-341373252172-buket-ledi-red-s-pion-rozami</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>Подарочный бокс Рафаэлло</t>
-        </is>
-      </c>
-      <c r="B433" t="n">
-        <v>2300</v>
-      </c>
-      <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3132-3163-4362-b936-303066363765/67414703.jpg</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-291016517802-podarochnii-boks-rafaello</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>Игрушка Мишка "Валентин"</t>
-        </is>
-      </c>
-      <c r="B434" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>Игрушка Котик - 25см</t>
-        </is>
-      </c>
-      <c r="B435" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>Игрушка Котик - 35см</t>
-        </is>
-      </c>
-      <c r="B436" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>Игрушка Мишка Милые глазки - 25см</t>
-        </is>
-      </c>
-      <c r="B437" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>Игрушка Мишка Милые глазки - 35см</t>
-        </is>
-      </c>
-      <c r="B438" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C438" t="inlineStr"/>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>Гипсофила от всего сердца</t>
-        </is>
-      </c>
-      <c r="B439" t="n">
-        <v>4550</v>
-      </c>
-      <c r="C439" t="inlineStr"/>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>Букет РУСАЛОЧКА</t>
-        </is>
-      </c>
-      <c r="B440" t="n">
-        <v>4050</v>
-      </c>
-      <c r="C440" t="inlineStr"/>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3462-6432-4761-b936-656137636438/83917609.jpg</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-195551843462-buket-rusalochka</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>Букет ЭКСЛЮЗИВ с ажурными розами</t>
-        </is>
-      </c>
-      <c r="B441" t="n">
-        <v>7200</v>
-      </c>
-      <c r="C441" t="inlineStr"/>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>https://static.tildacdn.com/stor3465-6139-4161-b636-326631643031/80766082.jpg</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-655606921272-buket-ekslyuziv-s-azhurnimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/519013662-655606921272-buket-ekslyuziv-s-azhurnimi-rozami</t>
         </is>
       </c>
     </row>

--- a/feed_converted.xlsx
+++ b/feed_converted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E426"/>
+  <dimension ref="A1:E441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=498825305721</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=498825305721</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=265791107231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=265791107231</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=719462284671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=719462284671</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=858082546771</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=858082546771</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=572499562021</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=572499562021</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=937626279691</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=937626279691</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=882067735871</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=882067735871</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=295802016471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=295802016471</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=813510992361</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=813510992361</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=918865638511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=918865638511</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=245383163781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=245383163781</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=172227793941</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=172227793941</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=671948342101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=671948342101</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=147847713571</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=147847713571</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=233459302551</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=233459302551</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=769759070961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=769759070961</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=650628430631</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=650628430631</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=381529129841</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=381529129841</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=200484781031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=200484781031</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=521071854132</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=521071854132</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=726825371832</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=726825371832</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=468737439372</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=468737439372</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=240310577222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=240310577222</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=629430115312</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=629430115312</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=365793161732</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=365793161732</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=194812772742</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=194812772742</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=326294220232</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=326294220232</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=383398298482</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=383398298482</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=334614005102</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=334614005102</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-564054127501-ekvadorskie-krasnie-rozi?editionuid=338415573182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-564054127501-ekvadorskie-krasnie-rozi?editionuid=338415573182</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=882511537061</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=882511537061</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=365883848281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=365883848281</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=218046257281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=218046257281</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=888310918641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=888310918641</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=253996242131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=253996242131</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=524625626631</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=524625626631</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=708312676961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=708312676961</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=890184912241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=890184912241</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=641366797711</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=641366797711</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=286704753391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=286704753391</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=154015712401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=154015712401</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=755598860411</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=755598860411</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=856822328931</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=856822328931</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=343053884581</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=343053884581</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-300174588241-ekvadorskie-belie-rozi?editionuid=474876597751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-300174588241-ekvadorskie-belie-rozi?editionuid=474876597751</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=715815864171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=715815864171</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=737906730171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=737906730171</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=131777960061</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=131777960061</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=424640009971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=424640009971</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=792474985941</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=792474985941</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=971600188781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=971600188781</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=849411123101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=849411123101</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=906749549891</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=906749549891</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=232300719541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=232300719541</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=178446277531</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=178446277531</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=339170286781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=339170286781</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=334033959351</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=334033959351</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=648372891461</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=648372891461</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=460563284101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=460563284101</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-546026643601-ekvadorskie-malinovie-rozi?editionuid=812574642211</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-546026643601-ekvadorskie-malinovie-rozi?editionuid=812574642211</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=942778462231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=942778462231</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=933284228141</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=933284228141</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=239595825971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=239595825971</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=622935246391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=622935246391</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=572824907311</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=572824907311</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=376897062281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=376897062281</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=778000219301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=778000219301</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=749920803381</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=749920803381</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=186946957581</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=186946957581</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=245561125991</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=245561125991</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=887024486291</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=887024486291</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=698009287281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=698009287281</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=641939630461</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=641939630461</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=251643663741</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=251643663741</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=575659429381</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=575659429381</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=746547712011</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=746547712011</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=245992221991</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=245992221991</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=732282555201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=732282555201</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=762275033411</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=762275033411</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-185905359921-ekvadorskie-kremovie-rozi?editionuid=869360911121</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-185905359921-ekvadorskie-kremovie-rozi?editionuid=869360911121</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=406896937861</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=406896937861</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=911510230531</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=911510230531</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=824822713061</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=824822713061</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=575566972011</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=575566972011</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=288245960112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=288245960112</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=904434342552</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=904434342552</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-272533176471-101-roza-ekvador?editionuid=972723029352</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-272533176471-101-roza-ekvador?editionuid=972723029352</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=345687277251</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=345687277251</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=110596316751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=110596316751</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=834468360661</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=834468360661</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=591924431631</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=591924431631</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=809069964721</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=809069964721</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=639403969201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=639403969201</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=437799346701</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-126730218061-buket-iz-raduzhnih-gipsofil?editionuid=437799346701</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-993169958291-korobochka-s-gipsofiloi?editionuid=156969419741</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-993169958291-korobochka-s-gipsofiloi?editionuid=156969419741</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-993169958291-korobochka-s-gipsofiloi?editionuid=922840956671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-993169958291-korobochka-s-gipsofiloi?editionuid=922840956671</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-993169958291-korobochka-s-gipsofiloi?editionuid=898673811441</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-993169958291-korobochka-s-gipsofiloi?editionuid=898673811441</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-993169958291-korobochka-s-gipsofiloi?editionuid=219581966181</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-993169958291-korobochka-s-gipsofiloi?editionuid=219581966181</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-903251068361-korobochka-s-hrizantemami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-903251068361-korobochka-s-hrizantemami</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=148944289651</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=148944289651</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=109365076101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=109365076101</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=376488675211</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=376488675211</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=725631168041</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=725631168041</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=129706362731</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=129706362731</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=566490772771</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=566490772771</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=777289682021</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=777289682021</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=428597863731</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=428597863731</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=576429505171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=576429505171</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=791959204501</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=791959204501</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=586956459451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=586956459451</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=617614243671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=617614243671</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=208995532381</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=208995532381</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=237012589071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=237012589071</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=906221431041</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=906221431041</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=276160309481</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=276160309481</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=199090330951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=199090330951</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=693313247081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=693313247081</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=852958282431</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=852958282431</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=792324955791</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=792324955791</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=538009046131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=538009046131</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=633884612171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=633884612171</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=904023676271</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=904023676271</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=961460791401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=961460791401</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-303761457701-buket-iz-hrizantem?editionuid=399118071021</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-303761457701-buket-iz-hrizantem?editionuid=399118071021</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=226542346681</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=226542346681</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=645786940181</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=645786940181</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=780430162101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=780430162101</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=684771627931</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=684771627931</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=109555802941</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=109555802941</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=776811032031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=776811032031</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=481223248931</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=481223248931</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=336239074871</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=336239074871</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=216056374821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=216056374821</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=563951015001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=563951015001</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=516430509881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=516430509881</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=830975922891</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=830975922891</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=922435599331</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=922435599331</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=779667105481</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=779667105481</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=758031717621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=758031717621</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=514142055381</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=514142055381</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=224906756131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=224906756131</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=790412251771</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=790412251771</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=824594865831</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=824594865831</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=249527607241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=249527607241</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=852846598511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=852846598511</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=463498073821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=463498073821</t>
         </is>
       </c>
     </row>
@@ -3684,1330 +3684,1330 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720597145011-buket-iz-alstromerii?editionuid=994973672881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720597145011-buket-iz-alstromerii?editionuid=994973672881</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>51 кремовая роза - 60 см - Атласная лента</t>
+          <t>101 красная роза в коробке - Бутон М</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>12590</v>
-      </c>
-      <c r="C149" t="inlineStr"/>
+        <v>13690</v>
+      </c>
+      <c r="C149" t="n">
+        <v>19000</v>
+      </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3364-3835-4261-b566-613837353837/3D266CF4-F3BF-4F31-9.JPG</t>
+          <t>https://static.tildacdn.com/stor6638-3161-4662-b537-343962666666/45960822.jpg</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-456677254991-51-kremovaya-roza?editionuid=470986963941</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke?editionuid=677875507802</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>51 кремовая роза - 60 см - Матовая бумага</t>
+          <t>101 красная роза в коробке - Бутон L</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>12990</v>
-      </c>
-      <c r="C150" t="inlineStr"/>
+        <v>29990</v>
+      </c>
+      <c r="C150" t="n">
+        <v>35000</v>
+      </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3834-3339-4764-b435-613261353636/90006182.jpg</t>
+          <t>https://static.tildacdn.com/stor3035-6333-4266-b131-356161303438/80710840.jpg</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-456677254991-51-kremovaya-roza?editionuid=756066172161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke?editionuid=414704203762</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>101 красная роза в коробке - Бутон М</t>
+          <t>15кремовых роз - Атласная лента</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>13690</v>
-      </c>
-      <c r="C151" t="n">
-        <v>19000</v>
-      </c>
+        <v>4100</v>
+      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6638-3161-4662-b537-343962666666/45960822.jpg</t>
+          <t>https://static.tildacdn.com/stor3937-3639-4962-b732-366632653839/89646755.jpg</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-128828996681-101-krasnaya-roza-v-korobke?editionuid=677875507802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=626304677871</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>101 красная роза в коробке - Бутон L</t>
+          <t>15кремовых роз - Матовая бумага</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>29990</v>
-      </c>
-      <c r="C152" t="n">
-        <v>35000</v>
-      </c>
+        <v>4300</v>
+      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3035-6333-4266-b131-356161303438/80710840.jpg</t>
+          <t>https://static.tildacdn.com/stor3961-3330-4861-a331-393039383239/50564437.jpg</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-128828996681-101-krasnaya-roza-v-korobke?editionuid=414704203762</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=757701389531</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>15кремовых роз - Атласная лента</t>
+          <t>51 красная роза - 60 см</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>4100</v>
+        <v>14600</v>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3937-3639-4962-b732-366632653839/89646755.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-848543105701-15kremovih-roz?editionuid=626304677871</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=931089475821</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>15кремовых роз - Матовая бумага</t>
+          <t>51 красная роза - 45 см</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>4300</v>
+        <v>6650</v>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3961-3330-4861-a331-393039383239/50564437.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-848543105701-15kremovih-roz?editionuid=757701389531</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=692401540222</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>51 красная роза - 60 см</t>
+          <t>51 роза "Сердце "в коробке</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>14600</v>
-      </c>
-      <c r="C155" t="inlineStr"/>
+        <v>14500</v>
+      </c>
+      <c r="C155" t="n">
+        <v>19500</v>
+      </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
+          <t>https://static.tildacdn.com/stor3966-3065-4365-a431-663862633665/46922404.jpg</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-354737980041-51-krasnaya-roza?editionuid=931089475821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-168896456031-51-roza-serdtse-v-korobke</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>51 красная роза - 45 см</t>
+          <t>25 розовых роз премиум в коробке</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>6650</v>
-      </c>
-      <c r="C156" t="inlineStr"/>
+        <v>7500</v>
+      </c>
+      <c r="C156" t="n">
+        <v>10500</v>
+      </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
+          <t>https://static.tildacdn.com/tild6539-6137-4637-b936-623137333530/20220228_175635.jpg</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-354737980041-51-krasnaya-roza?editionuid=692401540222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-511125332671-25-rozovih-roz-premium-v-korobke</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>51 роза "Сердце "в коробке</t>
+          <t>15 красных роз - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>14500</v>
+        <v>4800</v>
       </c>
       <c r="C157" t="n">
-        <v>19500</v>
+        <v>5500</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3966-3065-4365-a431-663862633665/46922404.jpg</t>
+          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-168896456031-51-roza-serdtse-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=769434790781</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>25 розовых роз премиум в коробке</t>
+          <t>15 красных роз - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C158" t="n">
-        <v>10500</v>
-      </c>
+        <v>2600</v>
+      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6539-6137-4637-b936-623137333530/20220228_175635.jpg</t>
+          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-511125332671-25-rozovih-roz-premium-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=205666183652</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>15 красных роз - 60 см - Атласная лента</t>
+          <t>51 красно-белая роза в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>4800</v>
-      </c>
-      <c r="C159" t="n">
-        <v>5500</v>
-      </c>
+        <v>12990</v>
+      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
+          <t>https://static.tildacdn.com/stor6534-3435-4432-a332-373732306661/48855206.jpg</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-602559582111-15-krasnih-roz?editionuid=769434790781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-542827273651-51-krasno-belaya-roza-v-oformlenii?editionuid=516167563281</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>15 красных роз - 45 см - Атласная лента</t>
+          <t>51 Белая роза - 60 см</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2600</v>
-      </c>
-      <c r="C160" t="inlineStr"/>
+        <v>12590</v>
+      </c>
+      <c r="C160" t="n">
+        <v>15000</v>
+      </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
+          <t>https://static.tildacdn.com/stor3064-6130-4531-a664-653536653139/42234229.jpg</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-602559582111-15-krasnih-roz?editionuid=205666183652</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-511893198801-51-belaya-roza?editionuid=631123744291</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>51 красно-белая роза в оформлении - 60 см</t>
+          <t>101 красно-белая роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>12990</v>
+        <v>24590</v>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3435-4432-a332-373732306661/48855206.jpg</t>
+          <t>https://static.tildacdn.com/stor3831-3066-4439-b961-663663623165/29975434.jpg</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-542827273651-51-krasno-belaya-roza-v-oformlenii?editionuid=516167563281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=478488702861</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>51 Белая роза - 60 см</t>
+          <t>101 красно-белая роза - 60 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>12590</v>
-      </c>
-      <c r="C162" t="n">
-        <v>15000</v>
-      </c>
+        <v>24990</v>
+      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6130-4531-a664-653536653139/42234229.jpg</t>
+          <t>https://static.tildacdn.com/stor6362-3662-4063-a164-636263353730/41852469.jpg</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-511893198801-51-belaya-roza?editionuid=631123744291</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=658675482971</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>101 красно-белая роза - 60 см - Атласная лента</t>
+          <t>25 Роз Премиум в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>24590</v>
-      </c>
-      <c r="C163" t="inlineStr"/>
+        <v>6800</v>
+      </c>
+      <c r="C163" t="n">
+        <v>7800</v>
+      </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3831-3066-4439-b961-663663623165/29975434.jpg</t>
+          <t>https://static.tildacdn.com/stor3736-6232-4930-b438-303165643933/38373375.jpg</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-461595881361-101-krasno-belaya-roza?editionuid=478488702861</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-472980179331-25-roz-premium-v-oformlenii?editionuid=120293941621</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>101 красно-белая роза - 60 см - Матовая бумага</t>
+          <t>25 красно-белых роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>24990</v>
-      </c>
-      <c r="C164" t="inlineStr"/>
+        <v>6800</v>
+      </c>
+      <c r="C164" t="n">
+        <v>7800</v>
+      </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6362-3662-4063-a164-636263353730/41852469.jpg</t>
+          <t>https://static.tildacdn.com/stor3964-6438-4238-a635-313134306536/28552846.jpg</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-461595881361-101-krasno-belaya-roza?editionuid=658675482971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-710052950101-25-krasno-belih-roz-v-oformlenii?editionuid=111716594231</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>25 Роз Премиум в оформлении - 60 см</t>
+          <t>21 красная роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>6800</v>
+        <v>5600</v>
       </c>
       <c r="C165" t="n">
         <v>7800</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3736-6232-4930-b438-303165643933/38373375.jpg</t>
+          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-472980179331-25-roz-premium-v-oformlenii?editionuid=120293941621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=679979674191</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>25 красно-белых роз в оформлении - 60 см</t>
+          <t>21 красная роза - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>6800</v>
+        <v>3500</v>
       </c>
       <c r="C166" t="n">
-        <v>7800</v>
+        <v>6300</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3964-6438-4238-a635-313134306536/28552846.jpg</t>
+          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-710052950101-25-krasno-belih-roz-v-oformlenii?editionuid=111716594231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=688291434032</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>21 красная роза - 60 см - Атласная лента</t>
+          <t>51 розовая роза - 60 см</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>5600</v>
+        <v>12590</v>
       </c>
       <c r="C167" t="n">
-        <v>7800</v>
+        <v>16500</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
+          <t>https://static.tildacdn.com/tild3434-6137-4538-b861-386430633162/A14C231B-75DB-4B7B-B.JPG</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-264521907571-21-krasnaya-roza?editionuid=679979674191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-289807833441-51-rozovaya-roza?editionuid=895253955391</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>21 красная роза - 45 см - Атласная лента</t>
+          <t>15 Розовых роз Премиум в упаковке - 60 см</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>3500</v>
+        <v>4300</v>
       </c>
       <c r="C168" t="n">
-        <v>6300</v>
+        <v>5700</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
+          <t>https://static.tildacdn.com/stor3562-6666-4866-a631-386530363233/69119634.jpg</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-264521907571-21-krasnaya-roza?editionuid=688291434032</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>51 розовая роза - 60 см</t>
+          <t>151 роза в корзине - 60 см</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>12590</v>
+        <v>45500</v>
       </c>
       <c r="C169" t="n">
-        <v>16500</v>
+        <v>49000</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3434-6137-4538-b861-386430633162/A14C231B-75DB-4B7B-B.JPG</t>
+          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-289807833441-51-rozovaya-roza?editionuid=895253955391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>15 Розовых роз Премиум в упаковке - 60 см</t>
+          <t>151 роза в корзине - 45 см</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>4300</v>
+        <v>18990</v>
       </c>
       <c r="C170" t="n">
-        <v>5700</v>
+        <v>39000</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3562-6666-4866-a631-386530363233/69119634.jpg</t>
+          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=502662350182</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>151 роза в корзине - 60 см</t>
+          <t>51 роза микс в крафте - 60 см</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>45500</v>
-      </c>
-      <c r="C171" t="n">
-        <v>49000</v>
-      </c>
+        <v>12990</v>
+      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
+          <t>https://static.tildacdn.com/tild6136-3162-4138-b562-653731633664/FullSizeRender_4.jpg</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>151 роза в корзине - 45 см</t>
+          <t>25 красных роз с оформлением - 45 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>18990</v>
-      </c>
-      <c r="C172" t="n">
-        <v>39000</v>
-      </c>
+        <v>4300</v>
+      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
+          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-445760300561-151-roza-v-korzine?editionuid=502662350182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>51 роза микс в крафте - 60 см</t>
+          <t>25 красных роз с оформлением - 60 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>12990</v>
+        <v>7800</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6136-3162-4138-b562-653731633664/FullSizeRender_4.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>25 красных роз с оформлением - 45 см - Матовая бумага</t>
+          <t>301 роза в корзине - 60 см</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>4300</v>
+        <v>65500</v>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
+          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>25 красных роз с оформлением - 60 см - Матовая бумага</t>
+          <t>301 роза в корзине - 45 см</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>7800</v>
+        <v>32500</v>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
+          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>301 роза в корзине - 60 см</t>
+          <t>11 красных роз в крафте - 60 см</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>65500</v>
+        <v>3600</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>301 роза в корзине - 45 см</t>
+          <t>11 красных роз в крафте - 45 см</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>32500</v>
+        <v>2200</v>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>11 красных роз в крафте - 60 см</t>
+          <t>15 красных роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C178" t="inlineStr"/>
+        <v>4800</v>
+      </c>
+      <c r="C178" t="n">
+        <v>5900</v>
+      </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>11 красных роз в крафте - 45 см</t>
+          <t>15 красных роз в оформлении - 45 см</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2200</v>
-      </c>
-      <c r="C179" t="inlineStr"/>
+        <v>2350</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3500</v>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>15 красных роз в оформлении - 60 см</t>
+          <t>25 кремовых роз в упаковке - 60 см</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>4800</v>
-      </c>
-      <c r="C180" t="n">
-        <v>5900</v>
-      </c>
+        <v>6800</v>
+      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3437-4165-b166-393339663536/27441782.jpg</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>15 красных роз в оформлении - 45 см</t>
+          <t>Букет КЛАССИКА с красными розами и хризантемами</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2350</v>
-      </c>
-      <c r="C181" t="n">
         <v>3500</v>
       </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
+          <t>https://static.tildacdn.com/stor6362-3466-4262-b537-646161643436/11667921.jpg</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>25 кремовых роз в упаковке - 60 см</t>
+          <t>25 красных роз в крафте - 60 см</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>6800</v>
+        <v>7800</v>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3437-4165-b166-393339663536/27441782.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Букет КЛАССИКА с красными розами и хризантемами</t>
+          <t>25 красных роз в крафте - 45 см</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>3500</v>
+        <v>4300</v>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6362-3466-4262-b537-646161643436/11667921.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>25 красных роз в крафте - 60 см</t>
+          <t>21 красная роза в цветной коробке</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C184" t="inlineStr"/>
+        <v>7300</v>
+      </c>
+      <c r="C184" t="n">
+        <v>8700</v>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
+          <t>https://static.tildacdn.com/tild6661-3763-4866-a530-333563333863/60558C1C-4284-4D41-A.JPG</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-887039306391-21-krasnaya-roza-v-tsvetnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>25 красных роз в крафте - 45 см</t>
+          <t>101 красная роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C185" t="inlineStr"/>
+        <v>28590</v>
+      </c>
+      <c r="C185" t="n">
+        <v>35500</v>
+      </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
+          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>21 красная роза в цветной коробке</t>
+          <t>101 красная роза - 60 см - Матова бумага</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>7300</v>
+        <v>28990</v>
       </c>
       <c r="C186" t="n">
-        <v>8700</v>
+        <v>35500</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6661-3763-4866-a530-333563333863/60558C1C-4284-4D41-A.JPG</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-887039306391-21-krasnaya-roza-v-tsvetnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Атласная лента</t>
+          <t>101 красная роза - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>28590</v>
+        <v>12250</v>
       </c>
       <c r="C187" t="n">
-        <v>35500</v>
+        <v>15300</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Матова бумага</t>
+          <t>101 красная роза - 45 см - Матова бумага</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>28990</v>
+        <v>12550</v>
       </c>
       <c r="C188" t="n">
-        <v>35500</v>
+        <v>15500</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Атласная лента</t>
+          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>12250</v>
+        <v>3850</v>
       </c>
       <c r="C189" t="n">
-        <v>15300</v>
+        <v>4200</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Матова бумага</t>
+          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>12550</v>
+        <v>3850</v>
       </c>
       <c r="C190" t="n">
-        <v>15500</v>
+        <v>4200</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
+          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>3850</v>
+        <v>5100</v>
       </c>
       <c r="C191" t="n">
-        <v>4200</v>
+        <v>6900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>3850</v>
-      </c>
-      <c r="C192" t="n">
-        <v>4200</v>
-      </c>
+        <v>5100</v>
+      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>5100</v>
-      </c>
-      <c r="C193" t="n">
-        <v>6900</v>
-      </c>
+        <v>6950</v>
+      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>5100</v>
+        <v>6950</v>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>6950</v>
+        <v>8150</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>6950</v>
+        <v>8150</v>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>8150</v>
+        <v>9950</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>8150</v>
+        <v>9950</v>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>9950</v>
+        <v>11150</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>9950</v>
-      </c>
-      <c r="C200" t="inlineStr"/>
+        <v>11150</v>
+      </c>
+      <c r="C200" t="n">
+        <v>11300</v>
+      </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>11150</v>
+        <v>15990</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>11150</v>
-      </c>
-      <c r="C202" t="n">
-        <v>11300</v>
-      </c>
+        <v>15990</v>
+      </c>
+      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>15990</v>
+        <v>2900</v>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>15990</v>
+        <v>3700</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6562-3433-4430-a461-373464323365/33695018.jpg</t>
+          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
+          <t>15 красно белых роз в оформлении</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C205" t="inlineStr"/>
+        <v>4300</v>
+      </c>
+      <c r="C205" t="n">
+        <v>6800</v>
+      </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3036-6330-4837-a665-343235393661/51200796.jpg</t>
+          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
+          <t>Raffaello</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>3700</v>
+        <v>690</v>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
+          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>15 красно белых роз в оформлении</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C207" t="n">
-        <v>6800</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-218567021051-15-krasno-belih-roz-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Raffaello</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>690</v>
+        <v>3800</v>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-608860089361-raffaello</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
@@ -5017,18 +5017,18 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>3800</v>
+        <v>1800</v>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
@@ -5038,18 +5038,18 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
@@ -5059,18 +5059,18 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
@@ -5080,60 +5080,60 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>1400</v>
+        <v>3000</v>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1000</v>
+        <v>3800</v>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
@@ -5143,18 +5143,18 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>3800</v>
+        <v>6200</v>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
@@ -5164,18 +5164,18 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
@@ -5185,18 +5185,18 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>6200</v>
+        <v>1800</v>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
@@ -5206,18 +5206,18 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>7000</v>
+        <v>1400</v>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
@@ -5227,18 +5227,18 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
@@ -5248,60 +5248,60 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
+          <t>Набор из гелиевых шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>1400</v>
+        <v>3750</v>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
+          <t>Набор из гелиевых шаров "Сердце" - 19</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1000</v>
+        <v>4750</v>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 15</t>
+          <t>Набор из гелиевых шаров "Сердце" - 25</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>3750</v>
+        <v>6350</v>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
@@ -5311,18 +5311,18 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 19</t>
+          <t>Набор из гелиевых шаров "Сердце" - 31</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>4750</v>
+        <v>7750</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
@@ -5332,18 +5332,18 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 25</t>
+          <t>Набор из гелиевых шаров "Сердце" - 35</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>6350</v>
+        <v>8750</v>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
@@ -5353,18 +5353,18 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 31</t>
+          <t>Набор из гелиевых шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>7750</v>
+        <v>2250</v>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
@@ -5374,18 +5374,18 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 35</t>
+          <t>Набор из гелиевых шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>8750</v>
+        <v>1750</v>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
@@ -5395,18 +5395,18 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 9</t>
+          <t>Набор из гелиевых шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>2250</v>
+        <v>1250</v>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
@@ -5416,18 +5416,18 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 7</t>
+          <t>Набор из гелиевых шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1750</v>
+        <v>2750</v>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
@@ -5437,60 +5437,60 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 5</t>
+          <t>Набор из фольгированных шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1250</v>
+        <v>6750</v>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 11</t>
+          <t>Набор из фольгированных шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2750</v>
+        <v>4950</v>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 15</t>
+          <t>Набор из фольгированных шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>6750</v>
+        <v>4050</v>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
@@ -5500,18 +5500,18 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 11</t>
+          <t>Набор из фольгированных шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>4950</v>
+        <v>3150</v>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
@@ -5521,18 +5521,18 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 9</t>
+          <t>Набор из фольгированных шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>4050</v>
+        <v>2250</v>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
@@ -5542,63 +5542,67 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 7</t>
+          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>3150</v>
-      </c>
-      <c r="C235" t="inlineStr"/>
+        <v>4500</v>
+      </c>
+      <c r="C235" t="n">
+        <v>4500</v>
+      </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 5</t>
+          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>2250</v>
-      </c>
-      <c r="C236" t="inlineStr"/>
+        <v>6100</v>
+      </c>
+      <c r="C236" t="n">
+        <v>6100</v>
+      </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>4500</v>
+        <v>8500</v>
       </c>
       <c r="C237" t="n">
-        <v>4500</v>
+        <v>8500</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -5607,21 +5611,21 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>6100</v>
+        <v>10100</v>
       </c>
       <c r="C238" t="n">
-        <v>6100</v>
+        <v>10100</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -5630,21 +5634,21 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>8500</v>
+        <v>14100</v>
       </c>
       <c r="C239" t="n">
-        <v>8500</v>
+        <v>14100</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -5653,22 +5657,20 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>10100</v>
-      </c>
-      <c r="C240" t="n">
-        <v>10100</v>
-      </c>
+        <v>3700</v>
+      </c>
+      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5676,22 +5678,20 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>14100</v>
-      </c>
-      <c r="C241" t="n">
-        <v>14100</v>
-      </c>
+        <v>2900</v>
+      </c>
+      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5699,20 +5699,22 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>3700</v>
-      </c>
-      <c r="C242" t="inlineStr"/>
+        <v>17950</v>
+      </c>
+      <c r="C242" t="n">
+        <v>18690</v>
+      </c>
       <c r="D242" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5720,20 +5722,22 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C243" t="inlineStr"/>
+        <v>35450</v>
+      </c>
+      <c r="C243" t="n">
+        <v>38690</v>
+      </c>
       <c r="D243" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5741,87 +5745,83 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
+          <t>Стильный букет в крафтовой сумочке</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>17950</v>
+        <v>4200</v>
       </c>
       <c r="C244" t="n">
-        <v>18690</v>
+        <v>5200</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>35450</v>
-      </c>
-      <c r="C245" t="n">
-        <v>38690</v>
-      </c>
+        <v>4990</v>
+      </c>
+      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Стильный букет в крафтовой сумочке</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C246" t="n">
-        <v>5200</v>
-      </c>
+        <v>5680</v>
+      </c>
+      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>4990</v>
+        <v>5990</v>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
@@ -5831,18 +5831,18 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>5680</v>
+        <v>5990</v>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
@@ -5852,18 +5852,18 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>5990</v>
+        <v>6240</v>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
@@ -5873,18 +5873,18 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>5990</v>
+        <v>6290</v>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
@@ -5894,18 +5894,18 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>6240</v>
+        <v>10490</v>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
@@ -5915,106 +5915,110 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
+          <t>ДОРОГУША из красных роз с орхидеями</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>6290</v>
-      </c>
-      <c r="C252" t="inlineStr"/>
+        <v>7500</v>
+      </c>
+      <c r="C252" t="n">
+        <v>8500</v>
+      </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
+          <t>Коробка гигант с радужной гипсофилой</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>10490</v>
-      </c>
-      <c r="C253" t="inlineStr"/>
+        <v>9999</v>
+      </c>
+      <c r="C253" t="n">
+        <v>10990</v>
+      </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ДОРОГУША из красных роз с орхидеями</t>
+          <t>Букет Малиновое вино - Посмотреть...</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>7500</v>
+        <v>4650</v>
       </c>
       <c r="C254" t="n">
-        <v>8500</v>
+        <v>5200</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-441113290851-dorogusha-iz-krasnih-roz-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Коробка гигант с радужной гипсофилой</t>
+          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>9999</v>
+        <v>5340</v>
       </c>
       <c r="C255" t="n">
-        <v>10990</v>
+        <v>5200</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Посмотреть...</t>
+          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>4650</v>
+        <v>5650</v>
       </c>
       <c r="C256" t="n">
         <v>5200</v>
@@ -6026,18 +6030,18 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
+          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>5340</v>
+        <v>5650</v>
       </c>
       <c r="C257" t="n">
         <v>5200</v>
@@ -6049,18 +6053,18 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
+          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>5650</v>
+        <v>5900</v>
       </c>
       <c r="C258" t="n">
         <v>5200</v>
@@ -6072,18 +6076,18 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>5650</v>
+        <v>5950</v>
       </c>
       <c r="C259" t="n">
         <v>5200</v>
@@ -6095,18 +6099,18 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>5900</v>
+        <v>10150</v>
       </c>
       <c r="C260" t="n">
         <v>5200</v>
@@ -6118,64 +6122,64 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
+          <t>11альстромерий в оформлении - Посмотреть...</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>5950</v>
+        <v>2500</v>
       </c>
       <c r="C261" t="n">
-        <v>5200</v>
+        <v>2380</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
+          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>10150</v>
+        <v>3190</v>
       </c>
       <c r="C262" t="n">
-        <v>5200</v>
+        <v>2380</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Посмотреть...</t>
+          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="C263" t="n">
         <v>2380</v>
@@ -6187,18 +6191,18 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>3190</v>
+        <v>3500</v>
       </c>
       <c r="C264" t="n">
         <v>2380</v>
@@ -6210,18 +6214,18 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>3500</v>
+        <v>3750</v>
       </c>
       <c r="C265" t="n">
         <v>2380</v>
@@ -6233,18 +6237,18 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
+          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="C266" t="n">
         <v>2380</v>
@@ -6256,18 +6260,18 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>3750</v>
+        <v>8000</v>
       </c>
       <c r="C267" t="n">
         <v>2380</v>
@@ -6279,53 +6283,49 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>3800</v>
-      </c>
-      <c r="C268" t="n">
-        <v>2380</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C269" t="n">
-        <v>2380</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
         </is>
       </c>
     </row>
@@ -6362,12 +6362,12 @@
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
         </is>
       </c>
     </row>
@@ -6383,12 +6383,12 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6446,12 @@
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
         </is>
       </c>
     </row>
@@ -6467,12 +6467,12 @@
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
         </is>
       </c>
     </row>
@@ -6488,142 +6488,146 @@
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>900</v>
+        <v>3000</v>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>900</v>
+        <v>3690</v>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
+          <t>Зефирный - Белые</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C280" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="C280" t="n">
+        <v>3500</v>
+      </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
+          <t>Зефирный - Микс</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>3690</v>
-      </c>
-      <c r="C281" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="C281" t="n">
+        <v>3500</v>
+      </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
+          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Зефирный - Белые</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Нежный</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="C282" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3061-4535-b035-306430303965/35298752.jpg</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-997928842911-zefirnii?editionuid=323569405822</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=430145379292</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Зефирный - Микс</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Яркие</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>3500</v>
+        <v>3550</v>
       </c>
       <c r="C283" t="n">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-3031-4331-b733-356664626131/31576954.jpg</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-997928842911-zefirnii?editionuid=978085575362</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=628386621972</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6648,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6669,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
         </is>
       </c>
     </row>
@@ -6686,28 +6690,28 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-766984785531-krem-dzhem-s-evkaliptom-iz-kustovih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-krem-dzhem-s-evkaliptom-iz-kustovih-roz</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Игрушка Летающий Единорожка</t>
+          <t>Игрушка МИШАНЯ</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>1400</v>
+        <v>4500</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-3961-4366-b766-326639646432/18447615.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6436-4538-b130-383238323638/76577859.jpg</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-721499980101-igrushka-letayuschii-edinorozhka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-mishanya</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6732,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-778767705501-igrushka-myakii-medved-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6753,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-594044496021-igrushkp-zaika-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6774,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-638070352371-buket-solnechnii-iz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
         </is>
       </c>
     </row>
@@ -6791,30 +6795,30 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>БУКЕТ ПРОВАНС с хризантемамми и розами</t>
+          <t>Букет РАДУЖНЫЙ ЛАЙФ</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>4990</v>
+        <v>3450</v>
       </c>
       <c r="C292" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6331-3465-4438-a461-636562623633/78518381.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-3530-4432-b861-626238636636/49194836.jpg</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-728832612721-buket-provans-s-hrizantemammi-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-raduzhnii-laif</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6841,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
         </is>
       </c>
     </row>
@@ -6860,339 +6864,339 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>25 белых роз с эвкалиптом</t>
+          <t>Букет Красотуля с орхидеями</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C295" t="n">
-        <v>9750</v>
-      </c>
+        <v>3300</v>
+      </c>
+      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-3531-4231-b735-333535643938/12128252.jpg</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-624506536881-25-belih-roz-s-evkaliptom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Букет орхидей БАБОЧКА</t>
+          <t>25 белых роз с эвкалиптом</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>3750</v>
+        <v>7800</v>
       </c>
       <c r="C296" t="n">
-        <v>4300</v>
+        <v>9750</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-229561542201-buket-orhidei-babochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Букет ромашек "Модный"</t>
+          <t>Букет орхидей БАБОЧКА</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>2800</v>
+        <v>3750</v>
       </c>
       <c r="C297" t="n">
-        <v>3200</v>
+        <v>4300</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
+          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-966890057501-buket-romashek-modnii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Букет ЛАЙК с красными розами</t>
+          <t>Букет КОМПЛИМЕНТ АССОРТИ</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>3500</v>
+        <v>2400</v>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
+          <t>https://static.tildacdn.com/stor3765-3434-4365-b737-666431333536/57090603.jpg</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-271548446971-buket-laik-s-krasnimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-169103768201-buket-kompliment-assorti</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
+          <t>Букет ромашек "Модный"</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C299" t="inlineStr"/>
+        <v>2800</v>
+      </c>
+      <c r="C299" t="n">
+        <v>3200</v>
+      </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
+          <t>Букет ЛАЙК с красными розами</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
+          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>4400</v>
+        <v>3000</v>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
+          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>5800</v>
+        <v>3700</v>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>9300</v>
+        <v>4400</v>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
+          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>11250</v>
+        <v>5800</v>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>15990</v>
+        <v>9300</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>29990</v>
+        <v>11250</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>6700</v>
+        <v>15990</v>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>9300</v>
+        <v>29990</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>12300</v>
+        <v>6700</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>22999</v>
+        <v>9300</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
@@ -7202,303 +7206,303 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>3300</v>
+        <v>12300</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>4100</v>
+        <v>22999</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Букет Белый шоколад из белых роз</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C313" t="n">
-        <v>5900</v>
-      </c>
+        <v>3300</v>
+      </c>
+      <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
+          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-604610293441-buket-belii-shokolad-iz-belih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Ажурные розы в коробке</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>3800</v>
+        <v>4100</v>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3638-6166-4062-a634-363361633538/95787248.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-706637499731-azhurnie-rozi-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Комплимент ВАНИЛЬ с ромашками</t>
+          <t>Букет Белый шоколад из белых роз</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>2690</v>
-      </c>
-      <c r="C315" t="inlineStr"/>
+        <v>5800</v>
+      </c>
+      <c r="C315" t="n">
+        <v>5900</v>
+      </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-355408923071-kompliment-vanil-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Коробка с кустовыми розами</t>
+          <t>Комплимент ВАНИЛЬ с ромашками</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>3500</v>
+        <v>2690</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6561-6635-4566-b836-393737636261/47533235.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-190380899281-korobka-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Дивная Орхидея</t>
+          <t>Коробка с кустовыми розами</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
+          <t>https://static.tildacdn.com/stor3461-3061-4533-a361-306563366164/19857974.jpg</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-399495570211-divnaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Коробка "Орхидея "</t>
+          <t>Дивная Орхидея</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
+          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-909950155641-korobka-orhideya-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
+          <t>Коробка "Орхидея "</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>6999</v>
+        <v>5700</v>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3366-3065-4265-b239-376235653964/39754072.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Розовый дым</t>
+          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>13500</v>
+        <v>6999</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
+          <t>https://static.tildacdn.com/stor3366-3065-4265-b239-376235653964/39754072.jpg</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-802553109081-rozovii-dim</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - M</t>
+          <t>Розовый дым</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>1800</v>
+        <v>13500</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - L</t>
+          <t>Букет Комплимент ПУШ с хризантемами - M</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>2150</v>
+        <v>1800</v>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
+          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Букет Комплимент МАРМЕЛАД</t>
+          <t>Букет Комплимент ПУШ с хризантемами - L</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>2650</v>
+        <v>2150</v>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
+          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-322995211141-buket-kompliment-marmelad</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Коробка с цветами ЛЮКС</t>
+          <t>Букет Комплимент МАРМЕЛАД</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>9990</v>
+        <v>2650</v>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-3036-4663-b030-666130666261/13712242.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-146373087581-korobka-s-tsvetami-lyuks</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
         </is>
       </c>
     </row>
@@ -7516,12 +7520,12 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3938-6432-4138-a266-633765366335/95496298.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-3135-4165-b161-393937653763/76895073.jpg</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7546,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7567,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7588,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7609,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7630,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7651,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7672,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7693,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
         </is>
       </c>
     </row>
@@ -7710,30 +7714,28 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Букет МЕЧТА с кустовыми розами и розами крем</t>
+          <t>Букет МИЛАШКА</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>6500</v>
-      </c>
-      <c r="C335" t="n">
-        <v>6500</v>
-      </c>
+        <v>3150</v>
+      </c>
+      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6538-3533-4866-b134-646334653462/14245314.jpg</t>
+          <t>https://static.tildacdn.com/stor6134-3038-4436-a435-613839666164/76918896.jpg</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-831554304821-buket-mechta-s-kustovimi-rozami-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-milashka</t>
         </is>
       </c>
     </row>
@@ -7756,1935 +7758,2252 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-626227787071-korzina-kustovih-roz-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 15</t>
+          <t>Ажурные французские розы - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>6400</v>
+        <v>3250</v>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 25</t>
+          <t>Ажурные французские розы - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>10800</v>
+        <v>3950</v>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 35</t>
+          <t>Ажурные французские розы - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>16500</v>
+        <v>5350</v>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 11</t>
+          <t>Ажурные французские розы - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>5200</v>
+        <v>8850</v>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 9</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>4400</v>
+        <v>12350</v>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Вау-букет 151 роза и Большой медведь</t>
+          <t>Ажурные французские розы - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>39990</v>
-      </c>
-      <c r="C342" t="n">
-        <v>49999</v>
-      </c>
+        <v>16990</v>
+      </c>
+      <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
+          <t>Ажурные французские розы - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>3650</v>
+        <v>9100</v>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
+          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>4100</v>
+        <v>12650</v>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
+          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
+          <t>Ажурные французские розы - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>9100</v>
+        <v>17500</v>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
+          <t>Ажурные французские розы - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>14900</v>
+        <v>3500</v>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
+          <t>Ажурные французские розы - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>23990</v>
+        <v>4200</v>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
+          <t>Букет пионовидных роз с эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>5750</v>
+        <v>6400</v>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
+          <t>Букет пионовидных роз с эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>4450</v>
+        <v>10800</v>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
+          <t>Букет пионовидных роз с эвкалиптом - 35</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>6250</v>
-      </c>
-      <c r="C350" t="n">
-        <v>7500</v>
-      </c>
+        <v>16500</v>
+      </c>
+      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Букет "Милашка"</t>
+          <t>Букет пионовидных роз с эвкалиптом - 11</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>8950</v>
-      </c>
-      <c r="C351" t="n">
-        <v>9990</v>
-      </c>
+        <v>5200</v>
+      </c>
+      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3033-6433-4637-b666-346533306135/93848240.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-103213775721-buket-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
+          <t>Букет пионовидных роз с эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>12999</v>
-      </c>
-      <c r="C352" t="n">
-        <v>15590</v>
-      </c>
+        <v>4400</v>
+      </c>
+      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-337767923621-korzina-alstromerii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Букет Комплимент "НЕЖНОСТЬ" с хризантемами и белыми розами</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C353" t="inlineStr"/>
+        <v>5050</v>
+      </c>
+      <c r="C353" t="n">
+        <v>5500</v>
+      </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3639-3537-4637-b334-343835343030/44921274.jpg</t>
+          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-559524591171-buket-kompliment-nezhnost-s-hrizantemami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Букет Комплимент "Дюшес" с альстромериями</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>2450</v>
+        <v>8250</v>
       </c>
       <c r="C354" t="n">
-        <v>2600</v>
+        <v>9500</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
+          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Нет</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C355" t="inlineStr"/>
+        <v>11250</v>
+      </c>
+      <c r="C355" t="n">
+        <v>15500</v>
+      </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=223863406172</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Да</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>3550</v>
-      </c>
-      <c r="C356" t="inlineStr"/>
+        <v>15550</v>
+      </c>
+      <c r="C356" t="n">
+        <v>18200</v>
+      </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=119690417772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Букет ПЛОМБИР</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C357" t="inlineStr"/>
+        <v>27999</v>
+      </c>
+      <c r="C357" t="n">
+        <v>35500</v>
+      </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
+          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-437576209011-buket-plombir</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C358" t="inlineStr"/>
+        <v>3250</v>
+      </c>
+      <c r="C358" t="n">
+        <v>3500</v>
+      </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-391414887741-buket-kompliment-krem-s-rozamm</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш с бантом "M"</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>1850</v>
+        <v>3650</v>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Игрушкп Медведь большой Ягодка</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>5500</v>
+        <v>4100</v>
       </c>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-551329556541-igrushkp-medved-bolshoi-yagodka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" беж.</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>1300</v>
+        <v>9100</v>
       </c>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-554350694011-igrushka-mishka-plyush-s-bezh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" белый</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>1300</v>
+        <v>14900</v>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-292174636271-igrushka-mishka-plyush-s-belii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Букет ГИПНОЗ с лилиями и розами</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>6700</v>
-      </c>
-      <c r="C363" t="n">
-        <v>7200</v>
-      </c>
+        <v>23990</v>
+      </c>
+      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3763-3431-4736-b439-363632386633/37134397.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Коробка "Ангажемент Лайт"</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>4500</v>
+        <v>5750</v>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6537-6664-4833-b033-343662313561/26722422.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-522766706011-korobka-angazhement-lait</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>51 роза нежный микс в корзине</t>
+          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>15750</v>
-      </c>
-      <c r="C365" t="n">
-        <v>18990</v>
-      </c>
+        <v>4450</v>
+      </c>
+      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
+          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-987092854851-51-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Микс "Нежный "в шляпной коробке</t>
+          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>4500</v>
+        <v>6250</v>
       </c>
       <c r="C366" t="n">
-        <v>4600</v>
+        <v>7500</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
+          <t>БУКЕТ КРЕМ ЛАВ</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>3890</v>
-      </c>
-      <c r="C367" t="n">
-        <v>4500</v>
-      </c>
+        <v>5650</v>
+      </c>
+      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
+          <t>https://static.tildacdn.com/stor3835-6431-4237-a663-343437613231/32984901.jpg</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-krem-lav</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке</t>
+          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>4999</v>
-      </c>
-      <c r="C368" t="inlineStr"/>
+        <v>12999</v>
+      </c>
+      <c r="C368" t="n">
+        <v>15590</v>
+      </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>"Мерилин "</t>
+          <t>Букет Комплимент "НЕЖНОСТЬ" с белыми альстромериями</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C369" t="n">
-        <v>3999</v>
-      </c>
+        <v>2890</v>
+      </c>
+      <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
+          <t>https://static.tildacdn.com/stor6132-3736-4930-b031-323732633532/31889130.jpg</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-570756966211-merilin-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-belimi-alstr</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Мон Амур - 25</t>
+          <t>Букет Комплимент "Дюшес" с альстромериями</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C370" t="inlineStr"/>
+        <v>2450</v>
+      </c>
+      <c r="C370" t="n">
+        <v>2600</v>
+      </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
+          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-488774775451-mon-amur?editionuid=330327920391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Мон Амур - 35</t>
+          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Нет</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>9300</v>
+        <v>3300</v>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-488774775451-mon-amur?editionuid=460518387891</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=223863406172</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Мон Амур - 51</t>
+          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Да</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>12990</v>
-      </c>
-      <c r="C372" t="n">
-        <v>17750</v>
-      </c>
+        <v>3550</v>
+      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-488774775451-mon-amur?editionuid=548699367961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=119690417772</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Мон Амур - 101</t>
+          <t>Букет ПЛОМБИР</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>24990</v>
-      </c>
-      <c r="C373" t="n">
-        <v>35600</v>
-      </c>
+        <v>4100</v>
+      </c>
+      <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-488774775451-mon-amur?editionuid=769488407402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Коробка L с радужной гипсофилой для мамы</t>
+          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>3799</v>
+        <v>3950</v>
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Коробка для мамы с гипсофилой M</t>
+          <t>Игрушка Мишка-плюш с бантом "M"</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>2999</v>
+        <v>1850</v>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>101 роза нежный микс в корзине</t>
+          <t>Игрушкп Медведь большой Ягодка</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>27990</v>
-      </c>
-      <c r="C376" t="n">
-        <v>33500</v>
-      </c>
+        <v>5500</v>
+      </c>
+      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-251477018101-101-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Букет ЛЕТО с хризантемами и ромашками</t>
+          <t>Игрушка Мишка-плюш "S" беж.</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>3100</v>
+        <v>1300</v>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
+          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Букет АРОМАТ с диантусами</t>
+          <t>Игрушка Мишка-плюш "S" белый</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>2700</v>
+        <v>1300</v>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3837-6639-4439-b637-613064363466/87696411.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-489100649391-buket-aromat-s-diantusami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Вставка сердце в букет</t>
+          <t>Букет ГИПНОЗ с лилиями и розами</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>250</v>
-      </c>
-      <c r="C379" t="inlineStr"/>
+        <v>6700</v>
+      </c>
+      <c r="C379" t="n">
+        <v>7200</v>
+      </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
+          <t>https://static.tildacdn.com/stor3763-3431-4736-b439-363632386633/37134397.jpg</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-974556600091-vstavka-serdtse-v-buket</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
+          <t>51 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>3890</v>
+        <v>15750</v>
       </c>
       <c r="C380" t="n">
-        <v>4000</v>
+        <v>18990</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Букет "Стильный микс" с орхидеями</t>
+          <t>Микс "Нежный "в шляпной коробке</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>5300</v>
+        <v>4500</v>
       </c>
       <c r="C381" t="n">
-        <v>5900</v>
+        <v>4600</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
+          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-704877065131-buket-stilnii-miks-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
+          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>7200</v>
-      </c>
-      <c r="C382" t="inlineStr"/>
+        <v>3890</v>
+      </c>
+      <c r="C382" t="n">
+        <v>4500</v>
+      </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-6636-4435-b631-343863306433/59411787.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
+          <t>"Ванильное небо "в шляпной коробке</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>4690</v>
+        <v>4999</v>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
+          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
+          <t>"Мерилин "</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C384" t="inlineStr"/>
+        <v>3650</v>
+      </c>
+      <c r="C384" t="n">
+        <v>3999</v>
+      </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
+          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Букет БОМБИТА</t>
+          <t>Мон Амур - 25</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>4050</v>
-      </c>
-      <c r="C385" t="n">
-        <v>5400</v>
-      </c>
+        <v>6800</v>
+      </c>
+      <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-6363-4130-a535-336236616236/99256221.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-148743167681-buket-bombita</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 7</t>
+          <t>Мон Амур - 35</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>2900</v>
+        <v>9300</v>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 9</t>
+          <t>Мон Амур - 51</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>3450</v>
-      </c>
-      <c r="C387" t="inlineStr"/>
+        <v>12990</v>
+      </c>
+      <c r="C387" t="n">
+        <v>17750</v>
+      </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 11</t>
+          <t>Мон Амур - 101</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>4150</v>
-      </c>
-      <c r="C388" t="inlineStr"/>
+        <v>24990</v>
+      </c>
+      <c r="C388" t="n">
+        <v>35600</v>
+      </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 15</t>
+          <t>Коробка L с радужной гипсофилой для мамы</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>5550</v>
+        <v>3799</v>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=541061184792</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
+          <t>Коробка для мамы с гипсофилой M</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>3590</v>
+        <v>2999</v>
       </c>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Ромашкина любовь</t>
+          <t>101 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>10990</v>
-      </c>
-      <c r="C391" t="inlineStr"/>
+        <v>27990</v>
+      </c>
+      <c r="C391" t="n">
+        <v>33500</v>
+      </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
+          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-950411727471-romashkina-lyubov</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>ВАУ КОРЗИНА ОРХИДЕЙ</t>
+          <t>Букет ЛЕТО с хризантемами и ромашками</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>32990</v>
+        <v>3100</v>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6232-6239-4333-b864-323133363433/21466466.jpg</t>
+          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-522713984731-vau-korzina-orhidei</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Букет "НЕЖЕНКА" с гортензией</t>
+          <t>Букет ЛАПОЧКА белыми розами и диантусами</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>2200</v>
+        <v>2650</v>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6532-3462-4639-b135-666433323866/31702549.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-6265-4162-b135-653333373065/49653431.jpg</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-500037248201-buket-nezhenka-s-gortenziei</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-lapochka-belimi-rozami-i-diantusam</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Букет РАДУЖНЫЙ с альстромериями</t>
+          <t>Вставка сердце в букет</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>2700</v>
-      </c>
-      <c r="C394" t="n">
-        <v>3450</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-290729033721-buket-raduzhnii-s-alstromeriyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Гипсофила от всего сердца</t>
+          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C395" t="inlineStr"/>
+        <v>3890</v>
+      </c>
+      <c r="C395" t="n">
+        <v>4000</v>
+      </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6530-4836-a565-643263303762/33953573.jpg</t>
+          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-398838219472-gipsofila-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
+          <t>Букет "Стильный микс" с орхидеями</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
+          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-843977882512-buket-tebe-konfetka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-704877065131-buket-stilnii-miks-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Букет МАЛИНОВОЕ СУФЛЕ с кустовыми розами</t>
+          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-6636-4435-b631-343863306433/59411787.jpg</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-910512563562-buket-malinovoe-sufle-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>5650</v>
+        <v>4690</v>
       </c>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-3435-4736-b964-373535626539/31455574.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-907367951302-buket-sinyaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>51 пионовидная кустовая роза в нежном оформлении</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>15500</v>
-      </c>
-      <c r="C399" t="n">
-        <v>18000</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
+          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Букет РОМАНТИКА</t>
+          <t>БУКЕТ ПРЕСТИЖ М</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>4150</v>
-      </c>
-      <c r="C400" t="n">
-        <v>5790</v>
-      </c>
+        <v>3590</v>
+      </c>
+      <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6236-3638-4164-b265-643862396434/56613877.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-6536-4134-b762-353165623733/99395624.jpg</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-359890420482-buket-romantika</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-prestizh-m</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Букет Комплимент с маттиолой</t>
+          <t>Букет из пионовидных роз в оформлении - 7</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>1800</v>
+        <v>2900</v>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
+          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-232892230242-buket-kompliment-s-mattioloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 9</t>
+          <t>Букет из пионовидных роз в оформлении - 9</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>3650</v>
+        <v>3450</v>
       </c>
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
+          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 11</t>
+          <t>Букет из пионовидных роз в оформлении - 11</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>4400</v>
+        <v>4150</v>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 15</t>
+          <t>Букет из пионовидных роз в оформлении - 15</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>5500</v>
+        <v>5550</v>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=541061184792</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 25</t>
+          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>9500</v>
+        <v>3590</v>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 35</t>
+          <t>Ромашкина любовь</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>12900</v>
+        <v>10990</v>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 51</t>
+          <t>ВАУ КОРЗИНА ИЗ ГИПСОФИЛ</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>15900</v>
+        <v>14999</v>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor6466-3031-4535-a431-633237363865/12981366.jpg</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-iz-gipsofil</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 101</t>
+          <t>Букет "НЕЖЕНКА" с гортензией</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>31100</v>
+        <v>3450</v>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor6238-3964-4531-b231-323161623038/90169769.jpg</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
+          <t>Букет РАДУЖНЫЙ с альстромериями</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C409" t="inlineStr"/>
+        <v>2700</v>
+      </c>
+      <c r="C409" t="n">
+        <v>3450</v>
+      </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
+          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
+          <t>Букет МАЛИНОВОЕ СУФЛЕ с кустовыми розами</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>5500</v>
+        <v>3600</v>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
+          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-910512563562-buket-malinovoe-sufle-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
+          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>8700</v>
+        <v>5650</v>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-3435-4736-b964-373535626539/31455574.jpg</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
+          <t>51 пионовидная кустовая роза в нежном оформлении</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>15900</v>
-      </c>
-      <c r="C413" t="inlineStr"/>
+        <v>15500</v>
+      </c>
+      <c r="C413" t="n">
+        <v>18000</v>
+      </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Подарочный набор для мамы 1</t>
+          <t>Букет Комплимент с маттиолой</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>3990</v>
+        <v>1800</v>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-786253932122-podarochnii-nabor-dlya-mami-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Подарок для мамы 2</t>
+          <t>Пионовидные кустовые розы в оформлении - 9</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>4990</v>
+        <v>3650</v>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
+          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-738379822212-podarok-dlya-mami-2</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Подарок для мамы 3 селебрити</t>
+          <t>Пионовидные кустовые розы в оформлении - 11</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>5199</v>
+        <v>4400</v>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-307373021402-podarok-dlya-mami-3-selebriti</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Букет ЛЕДИ РЕД с пион розами</t>
+          <t>Пионовидные кустовые розы в оформлении - 15</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>2450</v>
+        <v>5500</v>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-6634-4338-a635-316164643339/52783953.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-341373252172-buket-ledi-red-s-pion-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Подарочный бокс Рафаэлло</t>
+          <t>Пионовидные кустовые розы в оформлении - 25</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>2300</v>
+        <v>9500</v>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3132-3163-4362-b936-303066363765/67414703.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-291016517802-podarochnii-boks-rafaello</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Игрушка Мишка "Валентин"</t>
+          <t>Пионовидные кустовые розы в оформлении - 35</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>1300</v>
+        <v>12900</v>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-630681598512-igrushka-mishka-valentin</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 25см</t>
+          <t>Пионовидные кустовые розы в оформлении - 51</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>1200</v>
+        <v>15900</v>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-863762674412-igrushka-kotik?editionuid=707456987082</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 35см</t>
+          <t>Пионовидные кустовые розы в оформлении - 101</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>1850</v>
+        <v>31100</v>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-863762674412-igrushka-kotik?editionuid=932117895852</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Игрушка Мишка Милые глазки - 25см</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>1100</v>
+        <v>2800</v>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Игрушка Мишка Милые глазки - 35см</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>1850</v>
+        <v>3500</v>
       </c>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Гипсофила от всего сердца</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>4550</v>
+        <v>5500</v>
       </c>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
+          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-745191202102-gipsofila-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Букет РУСАЛОЧКА</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>4050</v>
+        <v>8700</v>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-6432-4761-b936-656137636438/83917609.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-195551843462-buket-rusalochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Букет ЭКСЛЮЗИВ с ажурными розами</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>7200</v>
+        <v>15900</v>
       </c>
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3465-6139-4161-b636-326631643031/80766082.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/519013662-655606921272-buket-ekslyuziv-s-azhurnimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Подарочный набор для мамы 1</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>3990</v>
+      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Подарок для мамы 2</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>4990</v>
+      </c>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Подарок для мамы 3 селебрити</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>5199</v>
+      </c>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Игрушка Мишка "Валентин"</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Игрушка Котик - 25см</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Игрушка Котик - 35см</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Игрушка Мишка Милые глазки - 25см</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Игрушка Мишка Милые глазки - 35см</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Гипсофила от всего сердца</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>4550</v>
+      </c>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Букет РУСАЛОЧКА</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>4050</v>
+      </c>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3462-6432-4761-b936-656137636438/83917609.jpg</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-195551843462-buket-rusalochka</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Сладкий подарок "СЕРДЕЧКО"</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>1790</v>
+      </c>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3135-6532-4334-a366-383338326235/55599791.jpg</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-548040342792-sladkii-podarok-serdechko</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Сладкий сюрприз ДЛЯ МОЕЙ МАЛЫШКИ</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>2300</v>
+      </c>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3163-6664-4637-b630-386361646534/95823135.jpg</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-157699878712-sladkii-syurpriz-dlya-moei-malishki</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Набор косметики для девушки</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6165-3033-4239-a633-333863366236/47266730.jpg</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-896299306932-nabor-kosmetiki-dlya-devushki</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Автобус сладостей для девушки с конфетами и шоколадом</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3963-3839-4266-a466-343732346365/79416309.jpg</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-814276260342-avtobus-sladostei-dlya-devushki-s-konfet</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Подарочный набор ДЛЯ МУЖЧИНЫ</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>3900</v>
+      </c>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6135-6563-4262-a539-626130313439/32687838.jpg</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-693724502742-podarochnii-nabor-dlya-muzhchini</t>
         </is>
       </c>
     </row>

--- a/feed_converted.xlsx
+++ b/feed_converted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E441"/>
+  <dimension ref="A1:E445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3691,942 +3691,938 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>101 красная роза в коробке - Бутон М</t>
+          <t>51 кремовая роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>13690</v>
-      </c>
-      <c r="C149" t="n">
-        <v>19000</v>
-      </c>
+        <v>12590</v>
+      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6638-3161-4662-b537-343962666666/45960822.jpg</t>
+          <t>https://static.tildacdn.com/tild3364-3835-4261-b566-613837353837/3D266CF4-F3BF-4F31-9.JPG</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke?editionuid=677875507802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-456677254991-51-kremovaya-roza?editionuid=470986963941</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>101 красная роза в коробке - Бутон L</t>
+          <t>51 кремовая роза - 60 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>29990</v>
-      </c>
-      <c r="C150" t="n">
-        <v>35000</v>
-      </c>
+        <v>12990</v>
+      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3035-6333-4266-b131-356161303438/80710840.jpg</t>
+          <t>https://static.tildacdn.com/stor3834-3339-4764-b435-613261353636/90006182.jpg</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke?editionuid=414704203762</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-456677254991-51-kremovaya-roza?editionuid=756066172161</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>15кремовых роз - Атласная лента</t>
+          <t>101 красная роза в коробке - Бутон М</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C151" t="inlineStr"/>
+        <v>13690</v>
+      </c>
+      <c r="C151" t="n">
+        <v>19000</v>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3937-3639-4962-b732-366632653839/89646755.jpg</t>
+          <t>https://static.tildacdn.com/stor6638-3161-4662-b537-343962666666/45960822.jpg</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=626304677871</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke?editionuid=677875507802</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>15кремовых роз - Матовая бумага</t>
+          <t>101 красная роза в коробке - Бутон L</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C152" t="inlineStr"/>
+        <v>29990</v>
+      </c>
+      <c r="C152" t="n">
+        <v>35000</v>
+      </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3961-3330-4861-a331-393039383239/50564437.jpg</t>
+          <t>https://static.tildacdn.com/stor3035-6333-4266-b131-356161303438/80710840.jpg</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=757701389531</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke?editionuid=414704203762</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>51 красная роза - 60 см</t>
+          <t>15кремовых роз - Атласная лента</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>14600</v>
+        <v>4100</v>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
+          <t>https://static.tildacdn.com/stor3937-3639-4962-b732-366632653839/89646755.jpg</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=931089475821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=626304677871</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>51 красная роза - 45 см</t>
+          <t>15кремовых роз - Матовая бумага</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>6650</v>
+        <v>4300</v>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
+          <t>https://static.tildacdn.com/stor3961-3330-4861-a331-393039383239/50564437.jpg</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=692401540222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=757701389531</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>51 роза "Сердце "в коробке</t>
+          <t>51 красная роза - 60 см</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>14500</v>
-      </c>
-      <c r="C155" t="n">
-        <v>19500</v>
-      </c>
+        <v>14600</v>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3966-3065-4365-a431-663862633665/46922404.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-168896456031-51-roza-serdtse-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=931089475821</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>25 розовых роз премиум в коробке</t>
+          <t>51 красная роза - 45 см</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C156" t="n">
-        <v>10500</v>
-      </c>
+        <v>6650</v>
+      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6539-6137-4637-b936-623137333530/20220228_175635.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-511125332671-25-rozovih-roz-premium-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=692401540222</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>15 красных роз - 60 см - Атласная лента</t>
+          <t>51 роза "Сердце "в коробке</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>4800</v>
+        <v>14500</v>
       </c>
       <c r="C157" t="n">
-        <v>5500</v>
+        <v>19500</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
+          <t>https://static.tildacdn.com/stor3966-3065-4365-a431-663862633665/46922404.jpg</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=769434790781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-168896456031-51-roza-serdtse-v-korobke</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>15 красных роз - 45 см - Атласная лента</t>
+          <t>25 розовых роз премиум в коробке</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2600</v>
-      </c>
-      <c r="C158" t="inlineStr"/>
+        <v>7500</v>
+      </c>
+      <c r="C158" t="n">
+        <v>10500</v>
+      </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
+          <t>https://static.tildacdn.com/tild6539-6137-4637-b936-623137333530/20220228_175635.jpg</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=205666183652</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-511125332671-25-rozovih-roz-premium-v-korobke</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>51 красно-белая роза в оформлении - 60 см</t>
+          <t>15 красных роз - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>12990</v>
-      </c>
-      <c r="C159" t="inlineStr"/>
+        <v>4800</v>
+      </c>
+      <c r="C159" t="n">
+        <v>5500</v>
+      </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3435-4432-a332-373732306661/48855206.jpg</t>
+          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-542827273651-51-krasno-belaya-roza-v-oformlenii?editionuid=516167563281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=769434790781</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>51 Белая роза - 60 см</t>
+          <t>15 красных роз - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>12590</v>
-      </c>
-      <c r="C160" t="n">
-        <v>15000</v>
-      </c>
+        <v>2600</v>
+      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6130-4531-a664-653536653139/42234229.jpg</t>
+          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-511893198801-51-belaya-roza?editionuid=631123744291</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=205666183652</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>101 красно-белая роза - 60 см - Атласная лента</t>
+          <t>51 красно-белая роза в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>24590</v>
+        <v>12990</v>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3831-3066-4439-b961-663663623165/29975434.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3435-4432-a332-373732306661/48855206.jpg</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=478488702861</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-542827273651-51-krasno-belaya-roza-v-oformlenii?editionuid=516167563281</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>101 красно-белая роза - 60 см - Матовая бумага</t>
+          <t>51 Белая роза - 60 см</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>24990</v>
-      </c>
-      <c r="C162" t="inlineStr"/>
+        <v>12590</v>
+      </c>
+      <c r="C162" t="n">
+        <v>15000</v>
+      </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6362-3662-4063-a164-636263353730/41852469.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-6130-4531-a664-653536653139/42234229.jpg</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=658675482971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-511893198801-51-belaya-roza?editionuid=631123744291</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>25 Роз Премиум в оформлении - 60 см</t>
+          <t>101 красно-белая роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C163" t="n">
-        <v>7800</v>
-      </c>
+        <v>24590</v>
+      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3736-6232-4930-b438-303165643933/38373375.jpg</t>
+          <t>https://static.tildacdn.com/stor3831-3066-4439-b961-663663623165/29975434.jpg</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-472980179331-25-roz-premium-v-oformlenii?editionuid=120293941621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=478488702861</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>25 красно-белых роз в оформлении - 60 см</t>
+          <t>101 красно-белая роза - 60 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C164" t="n">
-        <v>7800</v>
-      </c>
+        <v>24990</v>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3964-6438-4238-a635-313134306536/28552846.jpg</t>
+          <t>https://static.tildacdn.com/stor6362-3662-4063-a164-636263353730/41852469.jpg</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-710052950101-25-krasno-belih-roz-v-oformlenii?editionuid=111716594231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=658675482971</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>21 красная роза - 60 см - Атласная лента</t>
+          <t>25 Роз Премиум в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>5600</v>
+        <v>6800</v>
       </c>
       <c r="C165" t="n">
         <v>7800</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
+          <t>https://static.tildacdn.com/stor3736-6232-4930-b438-303165643933/38373375.jpg</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=679979674191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-472980179331-25-roz-premium-v-oformlenii?editionuid=120293941621</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>21 красная роза - 45 см - Атласная лента</t>
+          <t>25 красно-белых роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>3500</v>
+        <v>6800</v>
       </c>
       <c r="C166" t="n">
-        <v>6300</v>
+        <v>7800</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
+          <t>https://static.tildacdn.com/stor3964-6438-4238-a635-313134306536/28552846.jpg</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=688291434032</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-710052950101-25-krasno-belih-roz-v-oformlenii?editionuid=111716594231</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>51 розовая роза - 60 см</t>
+          <t>21 красная роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>12590</v>
+        <v>5600</v>
       </c>
       <c r="C167" t="n">
-        <v>16500</v>
+        <v>7800</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3434-6137-4538-b861-386430633162/A14C231B-75DB-4B7B-B.JPG</t>
+          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-289807833441-51-rozovaya-roza?editionuid=895253955391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=679979674191</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>15 Розовых роз Премиум в упаковке - 60 см</t>
+          <t>21 красная роза - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>4300</v>
+        <v>3500</v>
       </c>
       <c r="C168" t="n">
-        <v>5700</v>
+        <v>6300</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3562-6666-4866-a631-386530363233/69119634.jpg</t>
+          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=688291434032</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>151 роза в корзине - 60 см</t>
+          <t>51 розовая роза - 60 см</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>45500</v>
+        <v>12590</v>
       </c>
       <c r="C169" t="n">
-        <v>49000</v>
+        <v>16500</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
+          <t>https://static.tildacdn.com/tild3434-6137-4538-b861-386430633162/A14C231B-75DB-4B7B-B.JPG</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-289807833441-51-rozovaya-roza?editionuid=895253955391</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>151 роза в корзине - 45 см</t>
+          <t>15 Розовых роз Премиум в упаковке - 60 см</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>18990</v>
+        <v>4300</v>
       </c>
       <c r="C170" t="n">
-        <v>39000</v>
+        <v>5700</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
+          <t>https://static.tildacdn.com/stor3562-6666-4866-a631-386530363233/69119634.jpg</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=502662350182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>51 роза микс в крафте - 60 см</t>
+          <t>151 роза в корзине - 60 см</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>12990</v>
-      </c>
-      <c r="C171" t="inlineStr"/>
+        <v>45500</v>
+      </c>
+      <c r="C171" t="n">
+        <v>49000</v>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6136-3162-4138-b562-653731633664/FullSizeRender_4.jpg</t>
+          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>25 красных роз с оформлением - 45 см - Матовая бумага</t>
+          <t>151 роза в корзине - 45 см</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C172" t="inlineStr"/>
+        <v>18990</v>
+      </c>
+      <c r="C172" t="n">
+        <v>39000</v>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
+          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=502662350182</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>25 красных роз с оформлением - 60 см - Матовая бумага</t>
+          <t>51 роза микс в крафте - 60 см</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>7800</v>
+        <v>12990</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
+          <t>https://static.tildacdn.com/tild6136-3162-4138-b562-653731633664/FullSizeRender_4.jpg</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>301 роза в корзине - 60 см</t>
+          <t>25 красных роз с оформлением - 45 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>65500</v>
+        <v>4300</v>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>301 роза в корзине - 45 см</t>
+          <t>25 красных роз с оформлением - 60 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>32500</v>
+        <v>7800</v>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>11 красных роз в крафте - 60 см</t>
+          <t>301 роза в корзине - 60 см</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>3600</v>
+        <v>65500</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
+          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>11 красных роз в крафте - 45 см</t>
+          <t>301 роза в корзине - 45 см</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2200</v>
+        <v>32500</v>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
+          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>15 красных роз в оформлении - 60 см</t>
+          <t>11 красных роз в крафте - 60 см</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>4800</v>
-      </c>
-      <c r="C178" t="n">
-        <v>5900</v>
-      </c>
+        <v>3600</v>
+      </c>
+      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>15 красных роз в оформлении - 45 см</t>
+          <t>11 красных роз в крафте - 45 см</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2350</v>
-      </c>
-      <c r="C179" t="n">
-        <v>3500</v>
-      </c>
+        <v>2200</v>
+      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>25 кремовых роз в упаковке - 60 см</t>
+          <t>15 красных роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C180" t="inlineStr"/>
+        <v>4800</v>
+      </c>
+      <c r="C180" t="n">
+        <v>5900</v>
+      </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3437-4165-b166-393339663536/27441782.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Букет КЛАССИКА с красными розами и хризантемами</t>
+          <t>15 красных роз в оформлении - 45 см</t>
         </is>
       </c>
       <c r="B181" t="n">
+        <v>2350</v>
+      </c>
+      <c r="C181" t="n">
         <v>3500</v>
       </c>
-      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6362-3466-4262-b537-646161643436/11667921.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>25 красных роз в крафте - 60 см</t>
+          <t>25 кремовых роз в упаковке - 60 см</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>7800</v>
+        <v>6800</v>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3437-4165-b166-393339663536/27441782.jpg</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>25 красных роз в крафте - 45 см</t>
+          <t>Букет КЛАССИКА с красными розами и хризантемами</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>4300</v>
+        <v>3500</v>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
+          <t>https://static.tildacdn.com/stor6362-3466-4262-b537-646161643436/11667921.jpg</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>21 красная роза в цветной коробке</t>
+          <t>25 красных роз в крафте - 60 см</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>7300</v>
-      </c>
-      <c r="C184" t="n">
-        <v>8700</v>
-      </c>
+        <v>7800</v>
+      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6661-3763-4866-a530-333563333863/60558C1C-4284-4D41-A.JPG</t>
+          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-887039306391-21-krasnaya-roza-v-tsvetnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Атласная лента</t>
+          <t>25 красных роз в крафте - 45 см</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>28590</v>
-      </c>
-      <c r="C185" t="n">
-        <v>35500</v>
-      </c>
+        <v>4300</v>
+      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
+          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Матова бумага</t>
+          <t>21 красная роза в цветной коробке</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>28990</v>
+        <v>7300</v>
       </c>
       <c r="C186" t="n">
-        <v>35500</v>
+        <v>8700</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/tild6661-3763-4866-a530-333563333863/60558C1C-4284-4D41-A.JPG</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-887039306391-21-krasnaya-roza-v-tsvetnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Атласная лента</t>
+          <t>101 красная роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>12250</v>
+        <v>28590</v>
       </c>
       <c r="C187" t="n">
-        <v>15300</v>
+        <v>35500</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Матова бумага</t>
+          <t>101 красная роза - 60 см - Матова бумага</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>12550</v>
+        <v>28990</v>
       </c>
       <c r="C188" t="n">
-        <v>15500</v>
+        <v>35500</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
+          <t>101 красная роза - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>3850</v>
+        <v>12250</v>
       </c>
       <c r="C189" t="n">
-        <v>4200</v>
+        <v>15300</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
+          <t>101 красная роза - 45 см - Матова бумага</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>3850</v>
+        <v>12550</v>
       </c>
       <c r="C190" t="n">
-        <v>4200</v>
+        <v>15500</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>5100</v>
+        <v>3850</v>
       </c>
       <c r="C191" t="n">
-        <v>6900</v>
+        <v>4200</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -4635,41 +4631,45 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>5100</v>
-      </c>
-      <c r="C192" t="inlineStr"/>
+        <v>3850</v>
+      </c>
+      <c r="C192" t="n">
+        <v>4200</v>
+      </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>6950</v>
-      </c>
-      <c r="C193" t="inlineStr"/>
+        <v>5100</v>
+      </c>
+      <c r="C193" t="n">
+        <v>6900</v>
+      </c>
       <c r="D193" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
@@ -4677,18 +4677,18 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>6950</v>
+        <v>5100</v>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
@@ -4698,18 +4698,18 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>8150</v>
+        <v>6950</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
@@ -4719,18 +4719,18 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>8150</v>
+        <v>6950</v>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
@@ -4740,18 +4740,18 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>9950</v>
+        <v>8150</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
@@ -4761,18 +4761,18 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>9950</v>
+        <v>8150</v>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
@@ -4782,43 +4782,41 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>11150</v>
+        <v>9950</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>11150</v>
-      </c>
-      <c r="C200" t="n">
-        <v>11300</v>
-      </c>
+        <v>9950</v>
+      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
@@ -4826,41 +4824,43 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>15990</v>
+        <v>11150</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>15990</v>
-      </c>
-      <c r="C202" t="inlineStr"/>
+        <v>11150</v>
+      </c>
+      <c r="C202" t="n">
+        <v>11300</v>
+      </c>
       <c r="D202" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
@@ -4868,18 +4868,18 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>2900</v>
+        <v>15990</v>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
@@ -4889,125 +4889,125 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>3700</v>
+        <v>15990</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>15 красно белых роз в оформлении</t>
+          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C205" t="n">
-        <v>6800</v>
-      </c>
+        <v>2900</v>
+      </c>
+      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Raffaello</t>
+          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>690</v>
+        <v>3700</v>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
+          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
+          <t>15 красно белых роз в оформлении</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C207" t="inlineStr"/>
+        <v>4300</v>
+      </c>
+      <c r="C207" t="n">
+        <v>6800</v>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
+          <t>Raffaello</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>3800</v>
+        <v>690</v>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
@@ -5017,18 +5017,18 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1800</v>
+        <v>3800</v>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
@@ -5038,18 +5038,18 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1400</v>
+        <v>5000</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
@@ -5059,18 +5059,18 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
@@ -5080,60 +5080,60 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>3800</v>
+        <v>1000</v>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
@@ -5143,18 +5143,18 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>6200</v>
+        <v>3800</v>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
@@ -5164,18 +5164,18 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
@@ -5185,18 +5185,18 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1800</v>
+        <v>6200</v>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
@@ -5206,18 +5206,18 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1400</v>
+        <v>7000</v>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
@@ -5227,18 +5227,18 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
@@ -5248,60 +5248,60 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 15</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>3750</v>
+        <v>1400</v>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 19</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>4750</v>
+        <v>1000</v>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 25</t>
+          <t>Набор из гелиевых шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>6350</v>
+        <v>3750</v>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
@@ -5311,18 +5311,18 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 31</t>
+          <t>Набор из гелиевых шаров "Сердце" - 19</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>7750</v>
+        <v>4750</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
@@ -5332,18 +5332,18 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 35</t>
+          <t>Набор из гелиевых шаров "Сердце" - 25</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>8750</v>
+        <v>6350</v>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
@@ -5353,18 +5353,18 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 9</t>
+          <t>Набор из гелиевых шаров "Сердце" - 31</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>2250</v>
+        <v>7750</v>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
@@ -5374,18 +5374,18 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 7</t>
+          <t>Набор из гелиевых шаров "Сердце" - 35</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1750</v>
+        <v>8750</v>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
@@ -5395,18 +5395,18 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 5</t>
+          <t>Набор из гелиевых шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1250</v>
+        <v>2250</v>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
@@ -5416,18 +5416,18 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 11</t>
+          <t>Набор из гелиевых шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2750</v>
+        <v>1750</v>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
@@ -5437,60 +5437,60 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 15</t>
+          <t>Набор из гелиевых шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>6750</v>
+        <v>1250</v>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 11</t>
+          <t>Набор из гелиевых шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>4950</v>
+        <v>2750</v>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 9</t>
+          <t>Набор из фольгированных шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>4050</v>
+        <v>6750</v>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
@@ -5500,18 +5500,18 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 7</t>
+          <t>Набор из фольгированных шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>3150</v>
+        <v>4950</v>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
@@ -5521,18 +5521,18 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 5</t>
+          <t>Набор из фольгированных шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2250</v>
+        <v>4050</v>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
@@ -5542,67 +5542,63 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
+          <t>Набор из фольгированных шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C235" t="n">
-        <v>4500</v>
-      </c>
+        <v>3150</v>
+      </c>
+      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
+          <t>Набор из фольгированных шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>6100</v>
-      </c>
-      <c r="C236" t="n">
-        <v>6100</v>
-      </c>
+        <v>2250</v>
+      </c>
+      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>8500</v>
+        <v>4500</v>
       </c>
       <c r="C237" t="n">
-        <v>8500</v>
+        <v>4500</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -5611,21 +5607,21 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>10100</v>
+        <v>6100</v>
       </c>
       <c r="C238" t="n">
-        <v>10100</v>
+        <v>6100</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -5634,21 +5630,21 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>14100</v>
+        <v>8500</v>
       </c>
       <c r="C239" t="n">
-        <v>14100</v>
+        <v>8500</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -5657,20 +5653,22 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>3700</v>
-      </c>
-      <c r="C240" t="inlineStr"/>
+        <v>10100</v>
+      </c>
+      <c r="C240" t="n">
+        <v>10100</v>
+      </c>
       <c r="D240" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5678,20 +5676,22 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C241" t="inlineStr"/>
+        <v>14100</v>
+      </c>
+      <c r="C241" t="n">
+        <v>14100</v>
+      </c>
       <c r="D241" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5699,22 +5699,20 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>17950</v>
-      </c>
-      <c r="C242" t="n">
-        <v>18690</v>
-      </c>
+        <v>3700</v>
+      </c>
+      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5722,22 +5720,20 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>35450</v>
-      </c>
-      <c r="C243" t="n">
-        <v>38690</v>
-      </c>
+        <v>2900</v>
+      </c>
+      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5745,83 +5741,87 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Стильный букет в крафтовой сумочке</t>
+          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>4200</v>
+        <v>17950</v>
       </c>
       <c r="C244" t="n">
-        <v>5200</v>
+        <v>18690</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
+          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>4990</v>
-      </c>
-      <c r="C245" t="inlineStr"/>
+        <v>35450</v>
+      </c>
+      <c r="C245" t="n">
+        <v>38690</v>
+      </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
+          <t>Стильный букет в крафтовой сумочке</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>5680</v>
-      </c>
-      <c r="C246" t="inlineStr"/>
+        <v>4200</v>
+      </c>
+      <c r="C246" t="n">
+        <v>5200</v>
+      </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>5990</v>
+        <v>4990</v>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
@@ -5838,11 +5838,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>5990</v>
+        <v>5680</v>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
@@ -5859,11 +5859,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>6240</v>
+        <v>5990</v>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
@@ -5880,11 +5880,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>6290</v>
+        <v>5990</v>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
@@ -5901,11 +5901,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>10490</v>
+        <v>6240</v>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
@@ -5922,103 +5922,99 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ДОРОГУША из красных роз с орхидеями</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C252" t="n">
-        <v>8500</v>
-      </c>
+        <v>6290</v>
+      </c>
+      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Коробка гигант с радужной гипсофилой</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>9999</v>
-      </c>
-      <c r="C253" t="n">
-        <v>10990</v>
-      </c>
+        <v>10490</v>
+      </c>
+      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Посмотреть...</t>
+          <t>ДОРОГУША из красных роз с ромашками</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>4650</v>
+        <v>7500</v>
       </c>
       <c r="C254" t="n">
-        <v>5200</v>
+        <v>8500</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
+          <t>Коробка гигант с радужной гипсофилой</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>5340</v>
+        <v>9999</v>
       </c>
       <c r="C255" t="n">
-        <v>5200</v>
+        <v>10990</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
+          <t>Букет Малиновое вино - Посмотреть...</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>5650</v>
+        <v>4650</v>
       </c>
       <c r="C256" t="n">
         <v>5200</v>
@@ -6037,11 +6033,11 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>5650</v>
+        <v>5340</v>
       </c>
       <c r="C257" t="n">
         <v>5200</v>
@@ -6060,11 +6056,11 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>5900</v>
+        <v>5650</v>
       </c>
       <c r="C258" t="n">
         <v>5200</v>
@@ -6083,11 +6079,11 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
+          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>5950</v>
+        <v>5650</v>
       </c>
       <c r="C259" t="n">
         <v>5200</v>
@@ -6106,11 +6102,11 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
+          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>10150</v>
+        <v>5900</v>
       </c>
       <c r="C260" t="n">
         <v>5200</v>
@@ -6129,57 +6125,57 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Посмотреть...</t>
+          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>2500</v>
+        <v>5950</v>
       </c>
       <c r="C261" t="n">
-        <v>2380</v>
+        <v>5200</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
+          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>3190</v>
+        <v>10150</v>
       </c>
       <c r="C262" t="n">
-        <v>2380</v>
+        <v>5200</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
+          <t>11альстромерий в оформлении - Посмотреть...</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="C263" t="n">
         <v>2380</v>
@@ -6198,11 +6194,11 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
+          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>3500</v>
+        <v>3190</v>
       </c>
       <c r="C264" t="n">
         <v>2380</v>
@@ -6221,11 +6217,11 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>3750</v>
+        <v>3500</v>
       </c>
       <c r="C265" t="n">
         <v>2380</v>
@@ -6244,11 +6240,11 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="C266" t="n">
         <v>2380</v>
@@ -6267,11 +6263,11 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>8000</v>
+        <v>3750</v>
       </c>
       <c r="C267" t="n">
         <v>2380</v>
@@ -6290,42 +6286,46 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>900</v>
-      </c>
-      <c r="C268" t="inlineStr"/>
+        <v>3800</v>
+      </c>
+      <c r="C268" t="n">
+        <v>2380</v>
+      </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>900</v>
-      </c>
-      <c r="C269" t="inlineStr"/>
+        <v>8000</v>
+      </c>
+      <c r="C269" t="n">
+        <v>2380</v>
+      </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
         </is>
       </c>
     </row>
@@ -6362,12 +6362,12 @@
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
         </is>
       </c>
     </row>
@@ -6383,12 +6383,12 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6446,12 @@
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
         </is>
       </c>
     </row>
@@ -6467,12 +6467,12 @@
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
         </is>
       </c>
     </row>
@@ -6488,757 +6488,757 @@
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>3000</v>
+        <v>900</v>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
+          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>3690</v>
+        <v>900</v>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
+          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Зефирный - Белые</t>
+          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C280" t="n">
-        <v>3500</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
+          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Зефирный - Микс</t>
+          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C281" t="n">
-        <v>3500</v>
-      </c>
+        <v>3690</v>
+      </c>
+      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Нежный</t>
+          <t>Зефирный - Белые</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>3450</v>
+        <v>3500</v>
       </c>
       <c r="C282" t="n">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3061-4535-b035-306430303965/35298752.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=430145379292</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Яркие</t>
+          <t>Зефирный - Микс</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>3550</v>
+        <v>3500</v>
       </c>
       <c r="C283" t="n">
-        <v>3900</v>
+        <v>3500</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-3031-4331-b733-356664626131/31576954.jpg</t>
+          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=628386621972</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Нежный</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C284" t="inlineStr"/>
+        <v>3450</v>
+      </c>
+      <c r="C284" t="n">
+        <v>3800</v>
+      </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3037-3037-4331-b032-653532393265/10296532.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3061-4535-b035-306430303965/35298752.jpg</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=430145379292</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Яркие</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C285" t="inlineStr"/>
+        <v>3550</v>
+      </c>
+      <c r="C285" t="n">
+        <v>3900</v>
+      </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6630-3762-4363-b331-323964366539/21633765.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-3031-4331-b733-356664626131/31576954.jpg</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=628386621972</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>КРЕМ ДЖЕМ С ЭВКАЛИПТОМ из кустовых роз</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>3950</v>
+        <v>3500</v>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6637-6164-4634-b466-333164313039/56875072.jpg</t>
+          <t>https://static.tildacdn.com/stor3037-3037-4331-b032-653532393265/10296532.jpg</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-krem-dzhem-s-evkaliptom-iz-kustovih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Игрушка МИШАНЯ</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>4500</v>
+        <v>5800</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6436-4538-b130-383238323638/76577859.jpg</t>
+          <t>https://static.tildacdn.com/stor6630-3762-4363-b331-323964366539/21633765.jpg</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Игрушка Мякий медведь Мишаня</t>
+          <t>КРЕМ ДЖЕМ С ЭВКАЛИПТОМ из кустовых роз</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>3500</v>
+        <v>3950</v>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
+          <t>https://static.tildacdn.com/stor6637-6164-4634-b466-333164313039/56875072.jpg</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-krem-dzhem-s-evkaliptom-iz-kustovih-roz</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Игрушкп Зайка милашка</t>
+          <t>Игрушка МИШАНЯ</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>1100</v>
+        <v>4500</v>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6436-4538-b130-383238323638/76577859.jpg</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-mishanya</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Букет Солнечный из хризантем</t>
+          <t>Игрушка Мякий медведь Мишаня</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>2800</v>
+        <v>3500</v>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>LOVE IS....из кустовых роз с ромашками</t>
+          <t>Игрушкп Зайка милашка</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>10990</v>
+        <v>1100</v>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Букет РАДУЖНЫЙ ЛАЙФ</t>
+          <t>Букет Солнечный из хризантем</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>3450</v>
-      </c>
-      <c r="C292" t="n">
-        <v>3900</v>
-      </c>
+        <v>2800</v>
+      </c>
+      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-3530-4432-b861-626238636636/49194836.jpg</t>
+          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-raduzhnii-laif</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
+          <t>LOVE IS....из кустовых роз с ромашками</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>16290</v>
-      </c>
-      <c r="C293" t="n">
-        <v>175550</v>
-      </c>
+        <v>10990</v>
+      </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
+          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
+          <t>Букет РАДУЖНЫЙ ЛАЙФ</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>8500</v>
+        <v>3450</v>
       </c>
       <c r="C294" t="n">
-        <v>9200</v>
+        <v>3900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-3530-4432-b861-626238636636/49194836.jpg</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-raduzhnii-laif</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Букет Красотуля с орхидеями</t>
+          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C295" t="inlineStr"/>
+        <v>16290</v>
+      </c>
+      <c r="C295" t="n">
+        <v>175550</v>
+      </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-3531-4231-b735-333535643938/12128252.jpg</t>
+          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>25 белых роз с эвкалиптом</t>
+          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>7800</v>
+        <v>8500</v>
       </c>
       <c r="C296" t="n">
-        <v>9750</v>
+        <v>9200</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
+          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Букет орхидей БАБОЧКА</t>
+          <t>Букет Красотуля с орхидеями</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>3750</v>
-      </c>
-      <c r="C297" t="n">
-        <v>4300</v>
-      </c>
+        <v>3300</v>
+      </c>
+      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-3531-4231-b735-333535643938/12128252.jpg</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Букет КОМПЛИМЕНТ АССОРТИ</t>
+          <t>25 белых роз с эвкалиптом</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>2400</v>
-      </c>
-      <c r="C298" t="inlineStr"/>
+        <v>7800</v>
+      </c>
+      <c r="C298" t="n">
+        <v>9750</v>
+      </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3765-3434-4365-b737-666431333536/57090603.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-169103768201-buket-kompliment-assorti</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Букет ромашек "Модный"</t>
+          <t>Букет орхидей БАБОЧКА</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>2800</v>
+        <v>3750</v>
       </c>
       <c r="C299" t="n">
-        <v>3200</v>
+        <v>4300</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
+          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Букет ЛАЙК с красными розами</t>
+          <t>Букет КОМПЛИМЕНТ АССОРТИ</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>3500</v>
+        <v>2400</v>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
+          <t>https://static.tildacdn.com/stor3765-3434-4365-b737-666431333536/57090603.jpg</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-169103768201-buket-kompliment-assorti</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
+          <t>Букет ромашек "Модный"</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C301" t="inlineStr"/>
+        <v>2800</v>
+      </c>
+      <c r="C301" t="n">
+        <v>3200</v>
+      </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
+          <t>Букет ЛАЙК с красными розами</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
+          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>4400</v>
+        <v>3000</v>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
+          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>5800</v>
+        <v>3700</v>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>9300</v>
+        <v>4400</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
+          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>11250</v>
+        <v>5800</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>15990</v>
+        <v>9300</v>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>29990</v>
+        <v>11250</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>6700</v>
+        <v>15990</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>9300</v>
+        <v>29990</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>12300</v>
+        <v>6700</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>22999</v>
+        <v>9300</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
@@ -7248,463 +7248,461 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>3300</v>
+        <v>12300</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>4100</v>
+        <v>22999</v>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Букет Белый шоколад из белых роз</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C315" t="n">
-        <v>5900</v>
-      </c>
+        <v>3300</v>
+      </c>
+      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
+          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Комплимент ВАНИЛЬ с ромашками</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>2690</v>
+        <v>4100</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Коробка с кустовыми розами</t>
+          <t>Букет Белый шоколад из белых роз</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C317" t="inlineStr"/>
+        <v>5800</v>
+      </c>
+      <c r="C317" t="n">
+        <v>5900</v>
+      </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3461-3061-4533-a361-306563366164/19857974.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Дивная Орхидея</t>
+          <t>Комплимент ВАНИЛЬ с ромашками</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>5600</v>
+        <v>2690</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Коробка "Орхидея "</t>
+          <t>Коробка с кустовыми розами</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>5700</v>
+        <v>3500</v>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
+          <t>https://static.tildacdn.com/stor3461-3061-4533-a361-306563366164/19857974.jpg</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
+          <t>Дивная Орхидея</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>6999</v>
+        <v>5600</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3366-3065-4265-b239-376235653964/39754072.jpg</t>
+          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Розовый дым</t>
+          <t>Коробка "Орхидея "</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>13500</v>
+        <v>5700</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - M</t>
+          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>1800</v>
+        <v>6999</v>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6538-4838-b665-353662303035/42686584.jpg</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - L</t>
+          <t>Розовый дым</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>2150</v>
+        <v>13500</v>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Букет Комплимент МАРМЕЛАД</t>
+          <t>Букет Комплимент ПУШ с хризантемами - M</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>2650</v>
+        <v>1800</v>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
+          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Шикарная корзина с кустовыми розами</t>
+          <t>Букет Комплимент ПУШ с хризантемами - L</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>18990</v>
-      </c>
-      <c r="C325" t="n">
-        <v>21500</v>
-      </c>
+        <v>2150</v>
+      </c>
+      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-3135-4165-b161-393937653763/76895073.jpg</t>
+          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
+          <t>Букет Комплимент МАРМЕЛАД</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>2350</v>
+        <v>2650</v>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>3850</v>
+        <v>2350</v>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>5350</v>
+        <v>3850</v>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>2550</v>
+        <v>5350</v>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
+          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>4250</v>
+        <v>2550</v>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
+          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>5900</v>
+        <v>4250</v>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>8600</v>
+        <v>5900</v>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
+          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>8990</v>
+        <v>8600</v>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>11990</v>
+        <v>8990</v>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
@@ -7714,146 +7712,146 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Букет МИЛАШКА</t>
+          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>3150</v>
+        <v>11990</v>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6134-3038-4436-a435-613839666164/76918896.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Корзина кустовых роз 1</t>
+          <t>Букет МИЛАШКА</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>13990</v>
-      </c>
-      <c r="C336" t="n">
-        <v>14990</v>
-      </c>
+        <v>3150</v>
+      </c>
+      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
+          <t>https://static.tildacdn.com/stor6134-3038-4436-a435-613839666164/76918896.jpg</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-milashka</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Атласная лента</t>
+          <t>51 кремовая роза</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>3250</v>
+        <v>12590</v>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3966-4136-b735-386133633035/40006718.jpg</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-555099133731-51-kremovaya-roza</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Атласная лента</t>
+          <t>Корзина кустовых роз 1</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>3950</v>
-      </c>
-      <c r="C338" t="inlineStr"/>
+        <v>13990</v>
+      </c>
+      <c r="C338" t="n">
+        <v>14990</v>
+      </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 15 - Атласная лента</t>
+          <t>Ажурные французские розы - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>5350</v>
+        <v>3250</v>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Атласная лента</t>
+          <t>Ажурные французские розы - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>8850</v>
+        <v>3950</v>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
+          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>Ажурные французские розы - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>12350</v>
+        <v>5350</v>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
@@ -7863,123 +7861,123 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Атласная лента</t>
+          <t>Ажурные французские розы - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>16990</v>
+        <v>8850</v>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Матовая бумага</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>9100</v>
+        <v>12350</v>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>Ажурные французские розы - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>12650</v>
+        <v>16990</v>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Матовая бумага</t>
+          <t>Ажурные французские розы - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>17500</v>
+        <v>9100</v>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Матовая бумага</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>3500</v>
+        <v>12650</v>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Матовая бумага</t>
+          <t>Ажурные французские розы - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>4200</v>
+        <v>17500</v>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
@@ -7989,60 +7987,60 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 15</t>
+          <t>Ажурные французские розы - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>6400</v>
+        <v>3500</v>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 25</t>
+          <t>Ажурные французские розы - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>10800</v>
+        <v>4200</v>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 35</t>
+          <t>Букет пионовидных роз с эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>16500</v>
+        <v>6400</v>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
@@ -8052,18 +8050,18 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 11</t>
+          <t>Букет пионовидных роз с эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>5200</v>
+        <v>10800</v>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
@@ -8073,18 +8071,18 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 9</t>
+          <t>Букет пионовидных роз с эвкалиптом - 35</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>4400</v>
+        <v>16500</v>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
@@ -8094,1914 +8092,2002 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
+          <t>Букет пионовидных роз с эвкалиптом - 11</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>5050</v>
-      </c>
-      <c r="C353" t="n">
-        <v>5500</v>
-      </c>
+        <v>5200</v>
+      </c>
+      <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
+          <t>Букет пионовидных роз с эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>8250</v>
-      </c>
-      <c r="C354" t="n">
-        <v>9500</v>
-      </c>
+        <v>4400</v>
+      </c>
+      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>11250</v>
+        <v>5050</v>
       </c>
       <c r="C355" t="n">
-        <v>15500</v>
+        <v>5500</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
+          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>15550</v>
+        <v>8250</v>
       </c>
       <c r="C356" t="n">
-        <v>18200</v>
+        <v>9500</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
+          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>27999</v>
+        <v>11250</v>
       </c>
       <c r="C357" t="n">
-        <v>35500</v>
+        <v>15500</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>3250</v>
+        <v>15550</v>
       </c>
       <c r="C358" t="n">
-        <v>3500</v>
+        <v>18200</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C359" t="inlineStr"/>
+        <v>27999</v>
+      </c>
+      <c r="C359" t="n">
+        <v>35500</v>
+      </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
+          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C360" t="inlineStr"/>
+        <v>3250</v>
+      </c>
+      <c r="C360" t="n">
+        <v>3500</v>
+      </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
+          <t>Вау-букет 151 роза и Большой медведь</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>9100</v>
-      </c>
-      <c r="C361" t="inlineStr"/>
+        <v>39990</v>
+      </c>
+      <c r="C361" t="n">
+        <v>49999</v>
+      </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>14900</v>
+        <v>3650</v>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>23990</v>
+        <v>4100</v>
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>5750</v>
+        <v>9100</v>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>4450</v>
+        <v>14900</v>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>6250</v>
-      </c>
-      <c r="C366" t="n">
-        <v>7500</v>
-      </c>
+        <v>23990</v>
+      </c>
+      <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>БУКЕТ КРЕМ ЛАВ</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>5650</v>
+        <v>5750</v>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3835-6431-4237-a663-343437613231/32984901.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-krem-lav</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
+          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>12999</v>
-      </c>
-      <c r="C368" t="n">
-        <v>15590</v>
-      </c>
+        <v>4450</v>
+      </c>
+      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
+          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Букет Комплимент "НЕЖНОСТЬ" с белыми альстромериями</t>
+          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>2890</v>
-      </c>
-      <c r="C369" t="inlineStr"/>
+        <v>6250</v>
+      </c>
+      <c r="C369" t="n">
+        <v>7500</v>
+      </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6132-3736-4930-b031-323732633532/31889130.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-belimi-alstr</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Букет Комплимент "Дюшес" с альстромериями</t>
+          <t>БУКЕТ КРЕМ ЛАВ</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>2450</v>
-      </c>
-      <c r="C370" t="n">
-        <v>2600</v>
-      </c>
+        <v>5650</v>
+      </c>
+      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
+          <t>https://static.tildacdn.com/stor3835-6431-4237-a663-343437613231/32984901.jpg</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-krem-lav</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Нет</t>
+          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C371" t="inlineStr"/>
+        <v>12999</v>
+      </c>
+      <c r="C371" t="n">
+        <v>15590</v>
+      </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=223863406172</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Да</t>
+          <t>Букет Комплимент "НЕЖНОСТЬ" с белыми альстромериями</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>3550</v>
+        <v>2890</v>
       </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
+          <t>https://static.tildacdn.com/stor6132-3736-4930-b031-323732633532/31889130.jpg</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=119690417772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-belimi-alstr</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Букет ПЛОМБИР</t>
+          <t>Букет Комплимент "Дюшес" с альстромериями</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C373" t="inlineStr"/>
+        <v>2450</v>
+      </c>
+      <c r="C373" t="n">
+        <v>2600</v>
+      </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
+          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
+          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Нет</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>3950</v>
+        <v>3300</v>
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
+          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=223863406172</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш с бантом "M"</t>
+          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Да</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>1850</v>
+        <v>3550</v>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=119690417772</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Игрушкп Медведь большой Ягодка</t>
+          <t>Букет ПЛОМБИР</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>5500</v>
+        <v>4100</v>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
+          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" беж.</t>
+          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>1300</v>
+        <v>3950</v>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" белый</t>
+          <t>Игрушка Мишка-плюш с бантом "M"</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>1300</v>
+        <v>1850</v>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Букет ГИПНОЗ с лилиями и розами</t>
+          <t>Игрушкп Медведь большой Ягодка</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>6700</v>
-      </c>
-      <c r="C379" t="n">
-        <v>7200</v>
-      </c>
+        <v>5500</v>
+      </c>
+      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3763-3431-4736-b439-363632386633/37134397.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>51 роза нежный микс в корзине</t>
+          <t>Игрушка Мишка-плюш "S" беж.</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>15750</v>
-      </c>
-      <c r="C380" t="n">
-        <v>18990</v>
-      </c>
+        <v>1300</v>
+      </c>
+      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
+          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Микс "Нежный "в шляпной коробке</t>
+          <t>Игрушка Мишка-плюш "S" белый</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C381" t="n">
-        <v>4600</v>
-      </c>
+        <v>1300</v>
+      </c>
+      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
+          <t>БУКЕТ ГИПНОЗ с лилиями и розами</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>3890</v>
+        <v>8500</v>
       </c>
       <c r="C382" t="n">
-        <v>4500</v>
+        <v>9200</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
+          <t>https://static.tildacdn.com/stor3264-3966-4536-b462-663135316366/99420913.jpg</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке</t>
+          <t>51 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>4999</v>
-      </c>
-      <c r="C383" t="inlineStr"/>
+        <v>15750</v>
+      </c>
+      <c r="C383" t="n">
+        <v>18990</v>
+      </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>"Мерилин "</t>
+          <t>От всего сердца</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>3650</v>
+        <v>27800</v>
       </c>
       <c r="C384" t="n">
-        <v>3999</v>
+        <v>29890</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
+          <t>https://static.tildacdn.com/stor6132-3266-4466-a338-636461616235/65353807.jpg</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-279941586181-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Мон Амур - 25</t>
+          <t>Микс "Нежный "в шляпной коробке</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C385" t="inlineStr"/>
+        <v>4500</v>
+      </c>
+      <c r="C385" t="n">
+        <v>4600</v>
+      </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
+          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Мон Амур - 35</t>
+          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>9300</v>
-      </c>
-      <c r="C386" t="inlineStr"/>
+        <v>3890</v>
+      </c>
+      <c r="C386" t="n">
+        <v>4500</v>
+      </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Мон Амур - 51</t>
+          <t>"Ванильное небо "в шляпной коробке</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>12990</v>
-      </c>
-      <c r="C387" t="n">
-        <v>17750</v>
-      </c>
+        <v>4999</v>
+      </c>
+      <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Мон Амур - 101</t>
+          <t>"Мерилин "</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>24990</v>
+        <v>3650</v>
       </c>
       <c r="C388" t="n">
-        <v>35600</v>
+        <v>3999</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Коробка L с радужной гипсофилой для мамы</t>
+          <t>Мон Амур - 25</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>3799</v>
+        <v>6800</v>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Коробка для мамы с гипсофилой M</t>
+          <t>Мон Амур - 35</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>2999</v>
+        <v>9300</v>
       </c>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>101 роза нежный микс в корзине</t>
+          <t>Мон Амур - 51</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>27990</v>
+        <v>12990</v>
       </c>
       <c r="C391" t="n">
-        <v>33500</v>
+        <v>17750</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Букет ЛЕТО с хризантемами и ромашками</t>
+          <t>Мон Амур - 101</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>3100</v>
-      </c>
-      <c r="C392" t="inlineStr"/>
+        <v>24990</v>
+      </c>
+      <c r="C392" t="n">
+        <v>35600</v>
+      </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Букет ЛАПОЧКА белыми розами и диантусами</t>
+          <t>Коробка L с радужной гипсофилой для мамы</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>2650</v>
+        <v>3799</v>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-6265-4162-b135-653333373065/49653431.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-lapochka-belimi-rozami-i-diantusam</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Вставка сердце в букет</t>
+          <t>Коробка для мамы с гипсофилой M</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>250</v>
+        <v>2999</v>
       </c>
       <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
+          <t>101 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>3890</v>
+        <v>27990</v>
       </c>
       <c r="C395" t="n">
-        <v>4000</v>
+        <v>33500</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
+          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Букет "Стильный микс" с орхидеями</t>
+          <t>Букет ЛЕТО с хризантемами и ромашками</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>5000</v>
+        <v>3100</v>
       </c>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
+          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-704877065131-buket-stilnii-miks-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
+          <t>Букет ЛАПОЧКА белыми розами и диантусами</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>7200</v>
+        <v>2650</v>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-6636-4435-b631-343863306433/59411787.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-6265-4162-b135-653333373065/49653431.jpg</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-lapochka-belimi-rozami-i-diantusam</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
+          <t>Вставка сердце в букет</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>4690</v>
+        <v>250</v>
       </c>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
+          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C399" t="inlineStr"/>
+        <v>3890</v>
+      </c>
+      <c r="C399" t="n">
+        <v>4000</v>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
+          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>БУКЕТ ПРЕСТИЖ М</t>
+          <t>Букет "Стильный микс" с орхидеями</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>3590</v>
+        <v>5000</v>
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-6536-4134-b762-353165623733/99395624.jpg</t>
+          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-prestizh-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-704877065131-buket-stilnii-miks-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 7</t>
+          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>2900</v>
+        <v>7200</v>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
+          <t>https://static.tildacdn.com/stor3336-3133-4237-b132-643964343939/93723355.jpg</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 9</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>3450</v>
+        <v>4690</v>
       </c>
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 11</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>4150</v>
+        <v>3500</v>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
+          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 15</t>
+          <t>БУКЕТ ПРЕСТИЖ М</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>5550</v>
+        <v>3590</v>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-6536-4134-b762-353165623733/99395624.jpg</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=541061184792</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-prestizh-m</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
+          <t>Букет из пионовидных роз в оформлении - 7</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>3590</v>
+        <v>2900</v>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
+          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Ромашкина любовь</t>
+          <t>Букет из пионовидных роз в оформлении - 9</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>10990</v>
+        <v>3450</v>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
+          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>ВАУ КОРЗИНА ИЗ ГИПСОФИЛ</t>
+          <t>Букет из пионовидных роз в оформлении - 11</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>14999</v>
+        <v>4150</v>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6466-3031-4535-a431-633237363865/12981366.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-iz-gipsofil</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Букет "НЕЖЕНКА" с гортензией</t>
+          <t>Букет из пионовидных роз в оформлении - 15</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>3450</v>
+        <v>5550</v>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6238-3964-4531-b231-323161623038/90169769.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=541061184792</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Букет РАДУЖНЫЙ с альстромериями</t>
+          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>2700</v>
-      </c>
-      <c r="C409" t="n">
-        <v>3450</v>
-      </c>
+        <v>3590</v>
+      </c>
+      <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
+          <t>Ромашкина любовь</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>3600</v>
+        <v>10990</v>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Букет МАЛИНОВОЕ СУФЛЕ с кустовыми розами</t>
+          <t>ВАУ КОРЗИНА ИЗ ГИПСОФИЛ</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>3600</v>
+        <v>14999</v>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
+          <t>https://static.tildacdn.com/stor6466-3031-4535-a431-633237363865/12981366.jpg</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-910512563562-buket-malinovoe-sufle-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-iz-gipsofil</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
+          <t>Букет "НЕЖЕНКА" с гортензией</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>5650</v>
+        <v>3450</v>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-3435-4736-b964-373535626539/31455574.jpg</t>
+          <t>https://static.tildacdn.com/stor6238-3964-4531-b231-323161623038/90169769.jpg</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>51 пионовидная кустовая роза в нежном оформлении</t>
+          <t>Букет РАДУЖНЫЙ с альстромериями</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>15500</v>
+        <v>2700</v>
       </c>
       <c r="C413" t="n">
-        <v>18000</v>
+        <v>3450</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Букет Комплимент с маттиолой</t>
+          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
+          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 9</t>
+          <t>Букет МАЛИНОВОЕ СУФЛЕ с кустовыми розами</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>3650</v>
+        <v>3600</v>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
+          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-910512563562-buket-malinovoe-sufle-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 11</t>
+          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>4400</v>
+        <v>5200</v>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3632-4566-a533-386631646134/30216142.jpg</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 15</t>
+          <t>Букет РОМАНТИКА</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>5500</v>
-      </c>
-      <c r="C417" t="inlineStr"/>
+        <v>4150</v>
+      </c>
+      <c r="C417" t="n">
+        <v>5790</v>
+      </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
+          <t>https://static.tildacdn.com/stor6236-3638-4164-b265-643862396434/56613877.jpg</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-359890420482-buket-romantika</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 25</t>
+          <t>Букет Комплимент с маттиолой</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>9500</v>
+        <v>1800</v>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 35</t>
+          <t>Пионовидные кустовые розы в оформлении - 9</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>12900</v>
+        <v>3650</v>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 51</t>
+          <t>Пионовидные кустовые розы в оформлении - 11</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>15900</v>
+        <v>4400</v>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 101</t>
+          <t>Пионовидные кустовые розы в оформлении - 15</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>31100</v>
+        <v>5500</v>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
+          <t>Пионовидные кустовые розы в оформлении - 25</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>2800</v>
+        <v>9500</v>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
+          <t>Пионовидные кустовые розы в оформлении - 35</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>3500</v>
+        <v>12900</v>
       </c>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
+          <t>Пионовидные кустовые розы в оформлении - 51</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>5500</v>
+        <v>15900</v>
       </c>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
+          <t>Пионовидные кустовые розы в оформлении - 101</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>8700</v>
+        <v>31100</v>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>15900</v>
+        <v>2800</v>
       </c>
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Подарочный набор для мамы 1</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>3990</v>
+        <v>3500</v>
       </c>
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Подарок для мамы 2</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>4990</v>
+        <v>5500</v>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
+          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Подарок для мамы 3 селебрити</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>5199</v>
+        <v>8700</v>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Игрушка Мишка "Валентин"</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>1300</v>
+        <v>15900</v>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 25см</t>
+          <t>Подарочный набор для мамы 1</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>1200</v>
+        <v>3990</v>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 35см</t>
+          <t>Подарок для мамы 2</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>1850</v>
+        <v>4990</v>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Игрушка Мишка Милые глазки - 25см</t>
+          <t>Подарок для мамы 3 селебрити</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>1100</v>
+        <v>5199</v>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Игрушка Мишка Милые глазки - 35см</t>
+          <t>Игрушка Мишка "Валентин"</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>1850</v>
+        <v>1300</v>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Гипсофила от всего сердца</t>
+          <t>Игрушка Котик - 25см</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>4550</v>
+        <v>1200</v>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Букет РУСАЛОЧКА</t>
+          <t>Игрушка Котик - 35см</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>4050</v>
+        <v>1850</v>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-6432-4761-b936-656137636438/83917609.jpg</t>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-195551843462-buket-rusalochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Сладкий подарок "СЕРДЕЧКО"</t>
+          <t>Игрушка Мишка Милые глазки - 25см</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>1790</v>
+        <v>1100</v>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3135-6532-4334-a366-383338326235/55599791.jpg</t>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-548040342792-sladkii-podarok-serdechko</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Сладкий сюрприз ДЛЯ МОЕЙ МАЛЫШКИ</t>
+          <t>Игрушка Мишка Милые глазки - 35см</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>2300</v>
+        <v>1850</v>
       </c>
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3163-6664-4637-b630-386361646534/95823135.jpg</t>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-157699878712-sladkii-syurpriz-dlya-moei-malishki</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Набор косметики для девушки</t>
+          <t>Гипсофила от всего сердца</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>2500</v>
+        <v>4550</v>
       </c>
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3033-4239-a633-333863366236/47266730.jpg</t>
+          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-896299306932-nabor-kosmetiki-dlya-devushki</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Автобус сладостей для девушки с конфетами и шоколадом</t>
+          <t>Букет РУСАЛОЧКА</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>3200</v>
+        <v>4050</v>
       </c>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3963-3839-4266-a466-343732346365/79416309.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-6432-4761-b936-656137636438/83917609.jpg</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-814276260342-avtobus-sladostei-dlya-devushki-s-konfet</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-195551843462-buket-rusalochka</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Подарочный набор ДЛЯ МУЖЧИНЫ</t>
+          <t>Сладкий подарок "СЕРДЕЧКО"</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>3900</v>
+        <v>1790</v>
       </c>
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
+          <t>https://static.tildacdn.com/stor3135-6532-4334-a366-383338326235/55599791.jpg</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-548040342792-sladkii-podarok-serdechko</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Детский сладкий сюрприз</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>2300</v>
+      </c>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3163-6664-4637-b630-386361646534/95823135.jpg</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-157699878712-detskii-sladkii-syurpriz</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Набор косметики для девушки</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6165-3033-4239-a633-333863366236/47266730.jpg</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-896299306932-nabor-kosmetiki-dlya-devushki</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Автобус сладостей для девушки с конфетами и шоколадом</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3963-3839-4266-a466-343732346365/79416309.jpg</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-814276260342-avtobus-sladostei-dlya-devushki-s-konfet</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Подарочный набор ДЛЯ МУЖЧИНЫ</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>3900</v>
+      </c>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
           <t>https://static.tildacdn.com/stor6135-6563-4262-a539-626130313439/32687838.jpg</t>
         </is>
       </c>
-      <c r="E441" t="inlineStr">
+      <c r="E445" t="inlineStr">
         <is>
           <t>https://ohapka-flowers.ru/tproduct/802241395-693724502742-podarochnii-nabor-dlya-muzhchini</t>
         </is>

--- a/feed_converted.xlsx
+++ b/feed_converted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E445"/>
+  <dimension ref="A1:E446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,7 +492,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-3366-4439-a537-343165306539/38116469.jpg</t>
+          <t>https://static.tildacdn.com/stor3938-6361-4732-a335-396636356339/53025676.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3133-6564-4632-b537-346232633564/buket-iz-25-krasnykh.png</t>
+          <t>https://static.tildacdn.com/stor3365-6137-4661-a663-323734636466/44717671.jpg</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3133-6564-4632-b537-346232633564/buket-iz-25-krasnykh.png</t>
+          <t>https://static.tildacdn.com/stor3365-6137-4661-a663-323734636466/44717671.jpg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -764,7 +764,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-6564-4237-b365-316533653730/10294322.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3532-4063-a364-323564366264/37524859.jpg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -785,7 +785,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6262-3135-4636-b135-663638353030/10739440.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3532-4063-a364-323564366264/37524859.jpg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1100,7 +1100,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6262-3135-4636-b135-663638353030/10739440.jpg</t>
+          <t>https://static.tildacdn.com/tild3133-6564-4632-b537-346232633564/buket-iz-25-krasnykh.png</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3963-6133-4334-b762-343039303230/11513252.jpg</t>
+          <t>https://static.tildacdn.com/stor3461-3233-4866-a533-646232363732/57881236.jpg</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3737,14 +3737,14 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>13690</v>
+        <v>14690</v>
       </c>
       <c r="C151" t="n">
         <v>19000</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6638-3161-4662-b537-343962666666/45960822.jpg</t>
+          <t>https://static.tildacdn.com/stor6235-6532-4661-b132-646539356231/70418960.jpg</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>29990</v>
+        <v>2999</v>
       </c>
       <c r="C152" t="n">
         <v>35000</v>
@@ -4619,11 +4619,9 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>3850</v>
-      </c>
-      <c r="C191" t="n">
-        <v>4200</v>
-      </c>
+        <v>4400</v>
+      </c>
+      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
@@ -4642,11 +4640,9 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>3850</v>
-      </c>
-      <c r="C192" t="n">
-        <v>4200</v>
-      </c>
+        <v>4400</v>
+      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
@@ -4665,11 +4661,9 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>5100</v>
-      </c>
-      <c r="C193" t="n">
-        <v>6900</v>
-      </c>
+        <v>5900</v>
+      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
@@ -4688,7 +4682,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>5100</v>
+        <v>5900</v>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
@@ -4709,7 +4703,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>6950</v>
+        <v>7990</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
@@ -4730,7 +4724,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>6950</v>
+        <v>7990</v>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
@@ -4751,7 +4745,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>8150</v>
+        <v>9400</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
@@ -4772,7 +4766,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>8150</v>
+        <v>9400</v>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
@@ -4793,7 +4787,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>9950</v>
+        <v>11500</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
@@ -4814,7 +4808,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>9950</v>
+        <v>11500</v>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
@@ -4835,7 +4829,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>11150</v>
+        <v>12900</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
@@ -4856,14 +4850,12 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>11150</v>
-      </c>
-      <c r="C202" t="n">
-        <v>11300</v>
-      </c>
+        <v>12900</v>
+      </c>
+      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor6134-6663-4264-b937-613539323531/96969308.jpg</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -4879,7 +4871,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>15990</v>
+        <v>117900</v>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
@@ -4900,7 +4892,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>15990</v>
+        <v>17900</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
@@ -4921,7 +4913,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
@@ -6563,28 +6555,30 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
+          <t>Зефирный - Белые</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>3690</v>
-      </c>
-      <c r="C281" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="C281" t="n">
+        <v>3500</v>
+      </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Зефирный - Белые</t>
+          <t>Зефирный - Микс</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -6595,650 +6589,644 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
+          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Зефирный - Микс</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C283" t="n">
-        <v>3500</v>
-      </c>
+        <v>3550</v>
+      </c>
+      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
+          <t>https://static.tildacdn.com/stor3333-6134-4931-b064-626531613738/26831923.jpg</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Нежный</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>3450</v>
-      </c>
-      <c r="C284" t="n">
-        <v>3800</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3061-4535-b035-306430303965/35298752.jpg</t>
+          <t>https://static.tildacdn.com/stor3161-3631-4130-b561-653330386363/79575723.jpg</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=430145379292</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз - Яркие</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>3550</v>
-      </c>
-      <c r="C285" t="n">
-        <v>3900</v>
-      </c>
+        <v>5800</v>
+      </c>
+      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-3031-4331-b733-356664626131/31576954.jpg</t>
+          <t>https://static.tildacdn.com/stor3161-3631-4130-b561-653330386363/79575723.jpg</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz?editionuid=628386621972</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
+          <t>Букет МАГНОЛИЯ</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>3500</v>
+        <v>5750</v>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3037-3037-4331-b032-653532393265/10296532.jpg</t>
+          <t>https://static.tildacdn.com/stor3365-6335-4433-b938-333931306239/10745399.jpg</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-buket-magnoliya</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
+          <t>Игрушка МИШАНЯ</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>5800</v>
+        <v>4500</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6630-3762-4363-b331-323964366539/21633765.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6436-4538-b130-383238323638/76577859.jpg</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-mishanya</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>КРЕМ ДЖЕМ С ЭВКАЛИПТОМ из кустовых роз</t>
+          <t>Игрушка Мякий медведь Мишаня</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>3950</v>
+        <v>3500</v>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6637-6164-4634-b466-333164313039/56875072.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-krem-dzhem-s-evkaliptom-iz-kustovih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Игрушка МИШАНЯ</t>
+          <t>Игрушкп Зайка милашка</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>4500</v>
+        <v>1100</v>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6436-4538-b130-383238323638/76577859.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Игрушка Мякий медведь Мишаня</t>
+          <t>Букет Солнечный из хризантем</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
+          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Игрушкп Зайка милашка</t>
+          <t>Букет КАПРИЗ</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>1100</v>
+        <v>3500</v>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
+          <t>https://static.tildacdn.com/stor3966-3332-4534-a338-393735383465/63784469.jpg</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-202799168931-buket-kapriz</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Букет Солнечный из хризантем</t>
+          <t>Букет РАДУЖНЫЙ ЛАЙФ</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C292" t="inlineStr"/>
+        <v>3450</v>
+      </c>
+      <c r="C292" t="n">
+        <v>3900</v>
+      </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-3530-4432-b861-626238636636/49194836.jpg</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-raduzhnii-laif</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>LOVE IS....из кустовых роз с ромашками</t>
+          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>10990</v>
-      </c>
-      <c r="C293" t="inlineStr"/>
+        <v>16290</v>
+      </c>
+      <c r="C293" t="n">
+        <v>175550</v>
+      </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
+          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Букет РАДУЖНЫЙ ЛАЙФ</t>
+          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>3450</v>
+        <v>8500</v>
       </c>
       <c r="C294" t="n">
-        <v>3900</v>
+        <v>9200</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-3530-4432-b861-626238636636/49194836.jpg</t>
+          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-raduzhnii-laif</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
+          <t>Букет Красотуля с орхидеями</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>16290</v>
-      </c>
-      <c r="C295" t="n">
-        <v>175550</v>
-      </c>
+        <v>4100</v>
+      </c>
+      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
+          <t>https://static.tildacdn.com/stor3931-3734-4437-a234-313232633735/93320832.jpg</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
+          <t>25 белых роз с эвкалиптом</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>8500</v>
+        <v>7800</v>
       </c>
       <c r="C296" t="n">
-        <v>9200</v>
+        <v>9750</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Букет Красотуля с орхидеями</t>
+          <t>Букет орхидей БАБОЧКА</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C297" t="inlineStr"/>
+        <v>3750</v>
+      </c>
+      <c r="C297" t="n">
+        <v>4300</v>
+      </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-3531-4231-b735-333535643938/12128252.jpg</t>
+          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>25 белых роз с эвкалиптом</t>
+          <t>Букет КОМПЛИМЕНТ АССОРТИ</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C298" t="n">
-        <v>9750</v>
-      </c>
+        <v>2400</v>
+      </c>
+      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
+          <t>https://static.tildacdn.com/stor3765-3434-4365-b737-666431333536/57090603.jpg</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-169103768201-buket-kompliment-assorti</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Букет орхидей БАБОЧКА</t>
+          <t>Букет ромашек "Модный"</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>3750</v>
+        <v>2800</v>
       </c>
       <c r="C299" t="n">
-        <v>4300</v>
+        <v>3200</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Букет КОМПЛИМЕНТ АССОРТИ</t>
+          <t>Букет ЛАЙК с красными розами</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>2400</v>
+        <v>3500</v>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3765-3434-4365-b737-666431333536/57090603.jpg</t>
+          <t>https://static.tildacdn.com/stor3534-3438-4762-a236-656639623635/85107167.jpg</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-169103768201-buket-kompliment-assorti</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Букет ромашек "Модный"</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C301" t="n">
-        <v>3200</v>
-      </c>
+        <v>3350</v>
+      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
+          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Букет ЛАЙК с красными розами</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>3500</v>
+        <v>4150</v>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3830-3031-4835-b835-383138636235/22989356.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>3000</v>
+        <v>4950</v>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
+          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>3700</v>
+        <v>6550</v>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>4400</v>
+        <v>9500</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>5800</v>
+        <v>12850</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>9300</v>
+        <v>17590</v>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>11250</v>
+        <v>33990</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>15990</v>
+        <v>7290</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>29990</v>
+        <v>9950</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>6700</v>
+        <v>13999</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>9300</v>
+        <v>26990</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
@@ -7248,482 +7236,486 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>12300</v>
+        <v>3650</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
+          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>22999</v>
+        <v>4990</v>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
+          <t>Букет Белый шоколад из белых роз</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C315" t="inlineStr"/>
+        <v>5800</v>
+      </c>
+      <c r="C315" t="n">
+        <v>5900</v>
+      </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
+          <t>Комплимент ВАНИЛЬ с ромашками</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>4100</v>
+        <v>2790</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Букет Белый шоколад из белых роз</t>
+          <t>Коробка с кустовыми розами</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C317" t="n">
-        <v>5900</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
+          <t>https://static.tildacdn.com/stor3461-3061-4533-a361-306563366164/19857974.jpg</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Комплимент ВАНИЛЬ с ромашками</t>
+          <t>Дивная Орхидея</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>2690</v>
+        <v>5600</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
+          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Коробка с кустовыми розами</t>
+          <t>Коробка "Орхидея "</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>3500</v>
+        <v>5700</v>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3461-3061-4533-a361-306563366164/19857974.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Дивная Орхидея</t>
+          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>5600</v>
+        <v>6999</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6538-4838-b665-353662303035/42686584.jpg</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Коробка "Орхидея "</t>
+          <t>Розовый дым</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>5700</v>
+        <v>13500</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
+          <t>Букет Комплимент ПУШ с хризантемами - M</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>6999</v>
+        <v>1800</v>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6538-4838-b665-353662303035/42686584.jpg</t>
+          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Розовый дым</t>
+          <t>Букет Комплимент ПУШ с хризантемами - L</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>13500</v>
+        <v>2150</v>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
+          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - M</t>
+          <t>Букет Комплимент МАРМЕЛАД</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>1800</v>
+        <v>2650</v>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - L</t>
+          <t>Коробка с цветами ЛЮКС</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>2150</v>
+        <v>9990</v>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-3036-4663-b030-666130666261/13712242.jpg</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-146373087581-korobka-s-tsvetami-lyuks</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Букет Комплимент МАРМЕЛАД</t>
+          <t>Шикарная корзина с кустовыми розами</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>2650</v>
-      </c>
-      <c r="C326" t="inlineStr"/>
+        <v>20990</v>
+      </c>
+      <c r="C326" t="n">
+        <v>21500</v>
+      </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-3135-4165-b161-393937653763/76895073.jpg</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
+          <t>Коробка с орхидеями и кустовыми розами</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>2350</v>
-      </c>
-      <c r="C327" t="inlineStr"/>
+        <v>4990</v>
+      </c>
+      <c r="C327" t="n">
+        <v>5900</v>
+      </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-3837-4130-b565-316434363939/31198124.jpg</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-665629263531-korobka-s-orhideyami-i-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>3850</v>
+        <v>2350</v>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>5350</v>
+        <v>3850</v>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>2550</v>
+        <v>5350</v>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
+          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>4250</v>
+        <v>2550</v>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
+          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>5900</v>
+        <v>4250</v>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
+          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>8600</v>
+        <v>5900</v>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
+          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>8990</v>
+        <v>8600</v>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
+          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>11990</v>
+        <v>8990</v>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
@@ -7733,335 +7725,335 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Букет МИЛАШКА</t>
+          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>3150</v>
+        <v>11990</v>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6134-3038-4436-a435-613839666164/76918896.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>51 кремовая роза</t>
+          <t>Букет МИЛАШКА</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>12590</v>
+        <v>3150</v>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3966-4136-b735-386133633035/40006718.jpg</t>
+          <t>https://static.tildacdn.com/stor6135-3161-4637-b761-356232373633/78238867.jpg</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-555099133731-51-kremovaya-roza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-milashka</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Корзина кустовых роз 1</t>
+          <t>51 кремовая роза</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>13990</v>
-      </c>
-      <c r="C338" t="n">
-        <v>14990</v>
-      </c>
+        <v>12590</v>
+      </c>
+      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3966-4136-b735-386133633035/40006718.jpg</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-555099133731-51-kremovaya-roza</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Атласная лента</t>
+          <t>Корзина кустовых роз 1</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>3250</v>
-      </c>
-      <c r="C339" t="inlineStr"/>
+        <v>17100</v>
+      </c>
+      <c r="C339" t="n">
+        <v>17990</v>
+      </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Атласная лента</t>
+          <t>Ажурные французские розы - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>3950</v>
+        <v>3250</v>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 15 - Атласная лента</t>
+          <t>Ажурные французские розы - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>5350</v>
+        <v>3950</v>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Атласная лента</t>
+          <t>Ажурные французские розы - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>8850</v>
+        <v>5350</v>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>Ажурные французские розы - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>12350</v>
+        <v>8850</v>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Атласная лента</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>16990</v>
+        <v>12350</v>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Матовая бумага</t>
+          <t>Ажурные французские розы - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>9100</v>
+        <v>16990</v>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>Ажурные французские розы - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>12650</v>
+        <v>9100</v>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6435-3033-4561-b562-346335303639/16590426.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Матовая бумага</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>17500</v>
+        <v>12650</v>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Матовая бумага</t>
+          <t>Ажурные французские розы - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>3500</v>
+        <v>17500</v>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Матовая бумага</t>
+          <t>Ажурные французские розы - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3432-3764-4737-a161-393436303834/88821887.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 15</t>
+          <t>Ажурные французские розы - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>6400</v>
+        <v>4200</v>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 25</t>
+          <t>Букет пионовидных роз с эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>10800</v>
+        <v>6850</v>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
@@ -8071,18 +8063,18 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 35</t>
+          <t>Букет пионовидных роз с эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>16500</v>
+        <v>10800</v>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
@@ -8092,18 +8084,18 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 11</t>
+          <t>Букет пионовидных роз с эвкалиптом - 35</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>5200</v>
+        <v>14990</v>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
@@ -8113,18 +8105,18 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 9</t>
+          <t>Букет пионовидных роз с эвкалиптом - 11</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>4400</v>
+        <v>5450</v>
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
@@ -8134,242 +8126,242 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
+          <t>Букет пионовидных роз с эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>5050</v>
-      </c>
-      <c r="C355" t="n">
-        <v>5500</v>
-      </c>
+        <v>4690</v>
+      </c>
+      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>8250</v>
+        <v>5050</v>
       </c>
       <c r="C356" t="n">
-        <v>9500</v>
+        <v>5500</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
+          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>11250</v>
+        <v>8250</v>
       </c>
       <c r="C357" t="n">
-        <v>15500</v>
+        <v>9500</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
+          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>15550</v>
+        <v>11250</v>
       </c>
       <c r="C358" t="n">
-        <v>18200</v>
+        <v>15500</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>27999</v>
+        <v>15550</v>
       </c>
       <c r="C359" t="n">
-        <v>35500</v>
+        <v>18200</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>3250</v>
+        <v>27999</v>
       </c>
       <c r="C360" t="n">
-        <v>3500</v>
+        <v>35500</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
+          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Вау-букет 151 роза и Большой медведь</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>39990</v>
+        <v>3250</v>
       </c>
       <c r="C361" t="n">
-        <v>49999</v>
+        <v>3500</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
+          <t>Вау-букет 151 роза и Большой медведь</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C362" t="inlineStr"/>
+        <v>39990</v>
+      </c>
+      <c r="C362" t="n">
+        <v>49999</v>
+      </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
+          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>4100</v>
+        <v>3650</v>
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>9100</v>
+        <v>4100</v>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>14900</v>
+        <v>9100</v>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
@@ -8379,314 +8371,316 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>23990</v>
+        <v>14900</v>
       </c>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>5750</v>
+        <v>23990</v>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>4450</v>
+        <v>5750</v>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
+          <t>Корзина люкс</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>6250</v>
+        <v>39000</v>
       </c>
       <c r="C369" t="n">
-        <v>7500</v>
+        <v>49990</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
+          <t>https://static.tildacdn.com/stor3665-3335-4462-b738-363535393066/72943061.jpg</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-832446607671-korzina-lyuks</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>БУКЕТ КРЕМ ЛАВ</t>
+          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>5650</v>
+        <v>4450</v>
       </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3835-6431-4237-a663-343437613231/32984901.jpg</t>
+          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-krem-lav</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
+          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>12999</v>
+        <v>6250</v>
       </c>
       <c r="C371" t="n">
-        <v>15590</v>
+        <v>7500</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Букет Комплимент "НЕЖНОСТЬ" с белыми альстромериями</t>
+          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>2890</v>
-      </c>
-      <c r="C372" t="inlineStr"/>
+        <v>12999</v>
+      </c>
+      <c r="C372" t="n">
+        <v>15590</v>
+      </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6132-3736-4930-b031-323732633532/31889130.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-belimi-alstr</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Букет Комплимент "Дюшес" с альстромериями</t>
+          <t>Букет Комплимент "НЕЖНОСТЬ" с белыми альстромериями</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>2450</v>
-      </c>
-      <c r="C373" t="n">
-        <v>2600</v>
-      </c>
+        <v>2890</v>
+      </c>
+      <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
+          <t>https://static.tildacdn.com/stor6132-3736-4930-b031-323732633532/31889130.jpg</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-belimi-alstr</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Нет</t>
+          <t>Букет Комплимент "Дюшес" с альстромериями</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C374" t="inlineStr"/>
+        <v>2450</v>
+      </c>
+      <c r="C374" t="n">
+        <v>2600</v>
+      </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6564-3265-4165-b836-316637653438/14104172.jpg</t>
+          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=223863406172</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>БУКЕТ ИГРУШКА) с кустовыми розами - Да</t>
+          <t>Букет ПЛОМБИР</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>3550</v>
+        <v>4100</v>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-6263-4639-b237-383237333030/83919482.jpg</t>
+          <t>https://static.tildacdn.com/stor3439-6536-4663-b263-353034613736/33171735.jpg</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-236889112951-buket-igrushka-s-kustovimi-rozami?editionuid=119690417772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Букет ПЛОМБИР</t>
+          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>4100</v>
+        <v>3950</v>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6262-6631-4563-a539-666230633333/16075438.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
+          <t>Игрушка Мишка-плюш с бантом "M"</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>3950</v>
+        <v>1850</v>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш с бантом "M"</t>
+          <t>Игрушкп Медведь большой Ягодка</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>1850</v>
+        <v>5500</v>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Игрушкп Медведь большой Ягодка</t>
+          <t>Игрушка Мишка-плюш "S" беж.</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>5500</v>
+        <v>1300</v>
       </c>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
+          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" беж.</t>
+          <t>Игрушка Мишка-плюш "S" белый</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -8695,56 +8689,56 @@
       <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" белый</t>
+          <t>БУКЕТ ГИПНОЗ с лилиями и розами</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C381" t="inlineStr"/>
+        <v>8500</v>
+      </c>
+      <c r="C381" t="n">
+        <v>9200</v>
+      </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
+          <t>https://static.tildacdn.com/stor3264-3966-4536-b462-663135316366/99420913.jpg</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>БУКЕТ ГИПНОЗ с лилиями и розами</t>
+          <t>Корзина французских роз</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>8500</v>
-      </c>
-      <c r="C382" t="n">
-        <v>9200</v>
-      </c>
+        <v>7300</v>
+      </c>
+      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3264-3966-4536-b462-663135316366/99420913.jpg</t>
+          <t>https://static.tildacdn.com/stor6563-6462-4337-a637-646433396235/18661426.jpg</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522766706011-korzina-frantsuzskih-roz</t>
         </is>
       </c>
     </row>
@@ -9147,137 +9141,137 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Букет 11 красных роз с кустовыми розами в красивом оформлении</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>7200</v>
+        <v>4690</v>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3336-3133-4237-b132-643964343939/93723355.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-11-krasnih-roz-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>4690</v>
+        <v>3500</v>
       </c>
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
+          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
+          <t>БУКЕТ ПРЕСТИЖ М</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>3500</v>
+        <v>3590</v>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-3936-4962-b964-383035613735/62450227.jpg</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-prestizh-m</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>БУКЕТ ПРЕСТИЖ М</t>
+          <t>Букет из пионовидных роз в оформлении - 7</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>3590</v>
+        <v>2900</v>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-6536-4134-b762-353165623733/99395624.jpg</t>
+          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-prestizh-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 7</t>
+          <t>Букет из пионовидных роз в оформлении - 9</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>2900</v>
+        <v>3450</v>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
+          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 9</t>
+          <t>Букет из пионовидных роз в оформлении - 11</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>3450</v>
+        <v>4150</v>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 11</t>
+          <t>Букет из пионовидных роз в оформлении - 15</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>4150</v>
+        <v>5550</v>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
@@ -9287,70 +9281,70 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=541061184792</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 15</t>
+          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>5550</v>
+        <v>3590</v>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=541061184792</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
+          <t>Ромашкина любовь - XXL</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>3590</v>
+        <v>10990</v>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov?editionuid=407344541282</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Ромашкина любовь</t>
+          <t>Ромашкина любовь - L</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>10990</v>
+        <v>3800</v>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
+          <t>https://static.tildacdn.com/stor3464-3333-4434-a531-336439396466/16521764.jpg</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov?editionuid=825207994132</t>
         </is>
       </c>
     </row>
@@ -9443,42 +9437,44 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Букет МАЛИНОВОЕ СУФЛЕ с кустовыми розами</t>
+          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>3600</v>
+        <v>5200</v>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3839-3732-4230-b263-356135623338/81392984.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3632-4566-a533-386631646134/30216142.jpg</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-910512563562-buket-malinovoe-sufle-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
+          <t>51 пионовидная кустовая роза в нежном оформлении</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>5200</v>
-      </c>
-      <c r="C416" t="inlineStr"/>
+        <v>18600</v>
+      </c>
+      <c r="C416" t="n">
+        <v>18000</v>
+      </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3632-4566-a533-386631646134/30216142.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
         </is>
       </c>
     </row>
@@ -9489,14 +9485,12 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>4150</v>
-      </c>
-      <c r="C417" t="n">
-        <v>5790</v>
-      </c>
+        <v>6250</v>
+      </c>
+      <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6236-3638-4164-b265-643862396434/56613877.jpg</t>
+          <t>https://static.tildacdn.com/stor3833-6263-4665-b264-386639363531/55310964.jpg</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -9533,7 +9527,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>3650</v>
+        <v>4150</v>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
@@ -9554,7 +9548,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>4400</v>
+        <v>4950</v>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
@@ -9575,7 +9569,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>5500</v>
+        <v>6550</v>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
@@ -9596,7 +9590,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>9500</v>
+        <v>10550</v>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
@@ -9617,7 +9611,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>12900</v>
+        <v>14550</v>
       </c>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
@@ -9638,7 +9632,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>15900</v>
+        <v>18400</v>
       </c>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
@@ -9659,7 +9653,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>31100</v>
+        <v>35900</v>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
@@ -9844,53 +9838,53 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Игрушка Мишка "Валентин"</t>
+          <t>Букет ЛЕДИ РЕД с краснымм розами</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>1300</v>
+        <v>2490</v>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-6135-4034-a139-376262616331/46580879.jpg</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-341373252172-buket-ledi-red-s-krasnimm-rozami</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 25см</t>
+          <t>Игрушка Мишка "Валентин"</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 35см</t>
+          <t>Игрушка Котик - 25см</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
@@ -9900,39 +9894,39 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Игрушка Мишка Милые глазки - 25см</t>
+          <t>Игрушка Котик - 35см</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>1100</v>
+        <v>1850</v>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Игрушка Мишка Милые глазки - 35см</t>
+          <t>Игрушка Мишка Милые глазки - 25см</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>1850</v>
+        <v>1100</v>
       </c>
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
@@ -9942,152 +9936,173 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Гипсофила от всего сердца</t>
+          <t>Игрушка Мишка Милые глазки - 35см</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>4550</v>
+        <v>1850</v>
       </c>
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Букет РУСАЛОЧКА</t>
+          <t>Гипсофила от всего сердца</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>4050</v>
+        <v>4550</v>
       </c>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-6432-4761-b936-656137636438/83917609.jpg</t>
+          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-195551843462-buket-rusalochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Сладкий подарок "СЕРДЕЧКО"</t>
+          <t>Букет РУСАЛОЧКА</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>1790</v>
+        <v>4050</v>
       </c>
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3135-6532-4334-a366-383338326235/55599791.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-6432-4761-b936-656137636438/83917609.jpg</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-548040342792-sladkii-podarok-serdechko</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-195551843462-buket-rusalochka</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Детский сладкий сюрприз</t>
+          <t>Сладкий подарок "СЕРДЕЧКО"</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>2300</v>
+        <v>1790</v>
       </c>
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3163-6664-4637-b630-386361646534/95823135.jpg</t>
+          <t>https://static.tildacdn.com/stor3135-6532-4334-a366-383338326235/55599791.jpg</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-157699878712-detskii-sladkii-syurpriz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-548040342792-sladkii-podarok-serdechko</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Набор косметики для девушки</t>
+          <t>Детский сладкий сюрприз</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3033-4239-a633-333863366236/47266730.jpg</t>
+          <t>https://static.tildacdn.com/stor3163-6664-4637-b630-386361646534/95823135.jpg</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-896299306932-nabor-kosmetiki-dlya-devushki</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-157699878712-detskii-sladkii-syurpriz</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Автобус сладостей для девушки с конфетами и шоколадом</t>
+          <t>Набор косметики для девушки</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>3200</v>
+        <v>2500</v>
       </c>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3963-3839-4266-a466-343732346365/79416309.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3033-4239-a633-333863366236/47266730.jpg</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-814276260342-avtobus-sladostei-dlya-devushki-s-konfet</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-896299306932-nabor-kosmetiki-dlya-devushki</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Подарочный набор ДЛЯ МУЖЧИНЫ</t>
+          <t>Автобус сладостей для девушки с конфетами и шоколадом</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>3900</v>
+        <v>3200</v>
       </c>
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
+          <t>https://static.tildacdn.com/stor3963-3839-4266-a466-343732346365/79416309.jpg</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-814276260342-avtobus-sladostei-dlya-devushki-s-konfet</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Подарочный набор ДЛЯ МУЖЧИНЫ</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>3900</v>
+      </c>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
           <t>https://static.tildacdn.com/stor6135-6563-4262-a539-626130313439/32687838.jpg</t>
         </is>
       </c>
-      <c r="E445" t="inlineStr">
+      <c r="E446" t="inlineStr">
         <is>
           <t>https://ohapka-flowers.ru/tproduct/802241395-693724502742-podarochnii-nabor-dlya-muzhchini</t>
         </is>

--- a/feed_converted.xlsx
+++ b/feed_converted.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/feed_converted.xlsx
+++ b/feed_converted.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E446"/>
+  <dimension ref="A1:E452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14600</v>
+        <v>12590</v>
       </c>
       <c r="C8" t="n">
         <v>15600</v>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14990</v>
+        <v>12999</v>
       </c>
       <c r="C9" t="n">
         <v>15700</v>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28400</v>
+        <v>24550</v>
       </c>
       <c r="C12" t="n">
         <v>35300</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28900</v>
+        <v>24990</v>
       </c>
       <c r="C13" t="n">
         <v>35400</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28900</v>
+        <v>24990</v>
       </c>
       <c r="C14" t="n">
         <v>35500</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3250</v>
+        <v>3850</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3550</v>
+        <v>4050</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>28990</v>
+        <v>22990</v>
       </c>
       <c r="C82" t="n">
         <v>30550</v>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>24590</v>
+        <v>22590</v>
       </c>
       <c r="C83" t="n">
         <v>30300</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>24990</v>
+        <v>22990</v>
       </c>
       <c r="C84" t="n">
         <v>30400</v>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>24990</v>
+        <v>22990</v>
       </c>
       <c r="C85" t="n">
         <v>30500</v>
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>24990</v>
+        <v>22990</v>
       </c>
       <c r="C86" t="n">
         <v>30500</v>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24990</v>
+        <v>22990</v>
       </c>
       <c r="C87" t="n">
         <v>30500</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="C89" t="n">
         <v>3800</v>
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4300</v>
+        <v>4500</v>
       </c>
       <c r="C90" t="n">
         <v>4800</v>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6162-3462-4665-a666-383535306666/20220813_083506.jpg</t>
+          <t>https://static.tildacdn.com/stor6562-6362-4462-a136-356462343333/53746350.jpg</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2454,11 +2454,9 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C94" t="n">
         <v>3000</v>
       </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3961-6264-4337-b137-623930663066/20220811_150234.jpg</t>
@@ -2477,11 +2475,9 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2300</v>
-      </c>
-      <c r="C95" t="n">
         <v>2500</v>
       </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor6266-6230-4532-a438-663132306564/43045113.jpg</t>
@@ -2584,11 +2580,9 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C100" t="n">
-        <v>5000</v>
-      </c>
+        <v>3150</v>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor3064-3233-4834-a430-616534346663/33071370.jpg</t>
@@ -3825,9 +3819,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>14600</v>
-      </c>
-      <c r="C155" t="inlineStr"/>
+        <v>11990</v>
+      </c>
+      <c r="C155" t="n">
+        <v>12590</v>
+      </c>
       <c r="D155" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
@@ -3886,7 +3882,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>25 розовых роз премиум в коробке</t>
+          <t>25 малиновых роз в шляной коробке</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -3902,7 +3898,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-511125332671-25-rozovih-roz-premium-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-511125332671-25-malinovih-roz-v-shlyanoi-korobke</t>
         </is>
       </c>
     </row>
@@ -3957,9 +3953,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>12990</v>
-      </c>
-      <c r="C161" t="inlineStr"/>
+        <v>11990</v>
+      </c>
+      <c r="C161" t="n">
+        <v>12999</v>
+      </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/stor6534-3435-4432-a332-373732306661/48855206.jpg</t>
@@ -3978,7 +3976,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>12590</v>
+        <v>11990</v>
       </c>
       <c r="C162" t="n">
         <v>15000</v>
@@ -4039,7 +4037,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>25 Роз Премиум в оформлении - 60 см</t>
+          <t>25 малиновых роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4055,7 +4053,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-472980179331-25-roz-premium-v-oformlenii?editionuid=120293941621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-472980179331-25-malinovih-roz-v-oformlenii?editionuid=120293941621</t>
         </is>
       </c>
     </row>
@@ -4131,60 +4129,60 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>51 розовая роза - 60 см</t>
+          <t>15 Розовых роз Премиум в упаковке - 60 см</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>12590</v>
+        <v>4300</v>
       </c>
       <c r="C169" t="n">
-        <v>16500</v>
+        <v>5700</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3434-6137-4538-b861-386430633162/A14C231B-75DB-4B7B-B.JPG</t>
+          <t>https://static.tildacdn.com/stor3562-6666-4866-a631-386530363233/69119634.jpg</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-289807833441-51-rozovaya-roza?editionuid=895253955391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>15 Розовых роз Премиум в упаковке - 60 см</t>
+          <t>151 роза в корзине - 60 см</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>4300</v>
+        <v>45500</v>
       </c>
       <c r="C170" t="n">
-        <v>5700</v>
+        <v>49000</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3562-6666-4866-a631-386530363233/69119634.jpg</t>
+          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>151 роза в корзине - 60 см</t>
+          <t>151 роза в корзине - 45 см</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>45500</v>
+        <v>18990</v>
       </c>
       <c r="C171" t="n">
-        <v>49000</v>
+        <v>39000</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -4193,62 +4191,60 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=502662350182</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>151 роза в корзине - 45 см</t>
+          <t>51 роза микс в крафте - 60 см</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>18990</v>
-      </c>
-      <c r="C172" t="n">
-        <v>39000</v>
-      </c>
+        <v>12990</v>
+      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
+          <t>https://static.tildacdn.com/tild6136-3162-4138-b562-653731633664/FullSizeRender_4.jpg</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=502662350182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>51 роза микс в крафте - 60 см</t>
+          <t>25 красных роз с оформлением - 45 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>12990</v>
+        <v>4300</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6136-3162-4138-b562-653731633664/FullSizeRender_4.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>25 красных роз с оформлением - 45 см - Матовая бумага</t>
+          <t>25 красных роз с оформлением - 60 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>4300</v>
+        <v>7800</v>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
@@ -4258,39 +4254,41 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>25 красных роз с оформлением - 60 см - Матовая бумага</t>
+          <t>301 роза в корзине - 60 см</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C175" t="inlineStr"/>
+        <v>60900</v>
+      </c>
+      <c r="C175" t="n">
+        <v>65500</v>
+      </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
+          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>301 роза в корзине - 60 см</t>
+          <t>301 роза в корзине - 45 см</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>65500</v>
+        <v>32500</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
@@ -4300,39 +4298,39 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>301 роза в корзине - 45 см</t>
+          <t>11 красных роз в крафте - 60 см</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>32500</v>
+        <v>3600</v>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>11 красных роз в крафте - 60 см</t>
+          <t>11 красных роз в крафте - 45 см</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3600</v>
+        <v>2200</v>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
@@ -4342,42 +4340,44 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>11 красных роз в крафте - 45 см</t>
+          <t>15 красных роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2200</v>
-      </c>
-      <c r="C179" t="inlineStr"/>
+        <v>4800</v>
+      </c>
+      <c r="C179" t="n">
+        <v>5900</v>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>15 красных роз в оформлении - 60 см</t>
+          <t>15 красных роз в оформлении - 45 см</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>4800</v>
+        <v>2350</v>
       </c>
       <c r="C180" t="n">
-        <v>5900</v>
+        <v>3500</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -4386,83 +4386,81 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>15 красных роз в оформлении - 45 см</t>
+          <t>25 кремовых роз в упаковке - 60 см</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2350</v>
-      </c>
-      <c r="C181" t="n">
-        <v>3500</v>
-      </c>
+        <v>6800</v>
+      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3437-4165-b166-393339663536/27441782.jpg</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>25 кремовых роз в упаковке - 60 см</t>
+          <t>Букет КЛАССИКА с красными розами и хризантемами</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>6800</v>
+        <v>3350</v>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3437-4165-b166-393339663536/27441782.jpg</t>
+          <t>https://static.tildacdn.com/stor6362-3466-4262-b537-646161643436/11667921.jpg</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Букет КЛАССИКА с красными розами и хризантемами</t>
+          <t>25 красных роз в крафте - 60 см</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>3500</v>
+        <v>7800</v>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6362-3466-4262-b537-646161643436/11667921.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>25 красных роз в крафте - 60 см</t>
+          <t>25 красных роз в крафте - 45 см</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>7800</v>
+        <v>4300</v>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
@@ -4472,196 +4470,194 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>25 красных роз в крафте - 45 см</t>
+          <t>101 красная роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C185" t="inlineStr"/>
+        <v>24590</v>
+      </c>
+      <c r="C185" t="n">
+        <v>35500</v>
+      </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
+          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>21 красная роза в цветной коробке</t>
+          <t>101 красная роза - 60 см - Матова бумага</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>7300</v>
+        <v>24990</v>
       </c>
       <c r="C186" t="n">
-        <v>8700</v>
+        <v>35500</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6661-3763-4866-a530-333563333863/60558C1C-4284-4D41-A.JPG</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-887039306391-21-krasnaya-roza-v-tsvetnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Атласная лента</t>
+          <t>101 красная роза - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>28590</v>
+        <v>12250</v>
       </c>
       <c r="C187" t="n">
-        <v>35500</v>
+        <v>15300</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Матова бумага</t>
+          <t>101 красная роза - 45 см - Матова бумага</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>28990</v>
+        <v>12550</v>
       </c>
       <c r="C188" t="n">
-        <v>35500</v>
+        <v>15500</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Атласная лента</t>
+          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>12250</v>
-      </c>
-      <c r="C189" t="n">
-        <v>15300</v>
-      </c>
+        <v>4600</v>
+      </c>
+      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Матова бумага</t>
+          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>12550</v>
-      </c>
-      <c r="C190" t="n">
-        <v>15500</v>
-      </c>
+        <v>4600</v>
+      </c>
+      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
+          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>4400</v>
+        <v>6000</v>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor3465-6137-4339-a635-626237396331/61031457.jpg</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>4400</v>
+        <v>6000</v>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
+          <t>https://static.tildacdn.com/stor3465-6137-4339-a635-626237396331/61031457.jpg</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>5900</v>
+        <v>8100</v>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
@@ -4671,18 +4667,18 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>5900</v>
+        <v>8100</v>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
@@ -4692,18 +4688,18 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7990</v>
+        <v>9500</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
@@ -4713,39 +4709,39 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>7990</v>
+        <v>9500</v>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor6134-6663-4264-b937-613539323531/96969308.jpg</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>9400</v>
+        <v>11600</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
@@ -4755,18 +4751,18 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>9400</v>
+        <v>11600</v>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
@@ -4776,102 +4772,102 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>11500</v>
+        <v>12300</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>11500</v>
+        <v>12300</v>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor6134-6663-4264-b937-613539323531/96969308.jpg</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>12900</v>
+        <v>18600</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>12900</v>
+        <v>18600</v>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6134-6663-4264-b937-613539323531/96969308.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>117900</v>
+        <v>3200</v>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
@@ -4881,125 +4877,125 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>17900</v>
+        <v>3900</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
+          <t>15 красно белых роз в оформлении</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C205" t="inlineStr"/>
+        <v>4300</v>
+      </c>
+      <c r="C205" t="n">
+        <v>6800</v>
+      </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
+          <t>Raffaello</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>3700</v>
+        <v>690</v>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
+          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>15 красно белых роз в оформлении</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C207" t="n">
-        <v>6800</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Raffaello</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>690</v>
+        <v>3800</v>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
@@ -5009,18 +5005,18 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>3800</v>
+        <v>1800</v>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
@@ -5030,18 +5026,18 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
@@ -5051,18 +5047,18 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
@@ -5072,60 +5068,60 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>1400</v>
+        <v>3000</v>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1000</v>
+        <v>3800</v>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
@@ -5135,18 +5131,18 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>3800</v>
+        <v>6200</v>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
@@ -5156,18 +5152,18 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
@@ -5177,18 +5173,18 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>6200</v>
+        <v>1800</v>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
@@ -5198,18 +5194,18 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>7000</v>
+        <v>1400</v>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
@@ -5219,18 +5215,18 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
@@ -5240,60 +5236,60 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
+          <t>Набор из гелиевых шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>1400</v>
+        <v>3750</v>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
+          <t>Набор из гелиевых шаров "Сердце" - 19</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1000</v>
+        <v>4750</v>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 15</t>
+          <t>Набор из гелиевых шаров "Сердце" - 25</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>3750</v>
+        <v>6350</v>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
@@ -5303,18 +5299,18 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 19</t>
+          <t>Набор из гелиевых шаров "Сердце" - 31</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>4750</v>
+        <v>7750</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
@@ -5324,18 +5320,18 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 25</t>
+          <t>Набор из гелиевых шаров "Сердце" - 35</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>6350</v>
+        <v>8750</v>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
@@ -5345,18 +5341,18 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 31</t>
+          <t>Набор из гелиевых шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>7750</v>
+        <v>2250</v>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
@@ -5366,18 +5362,18 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 35</t>
+          <t>Набор из гелиевых шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>8750</v>
+        <v>1750</v>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
@@ -5387,18 +5383,18 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 9</t>
+          <t>Набор из гелиевых шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>2250</v>
+        <v>1250</v>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
@@ -5408,18 +5404,18 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 7</t>
+          <t>Набор из гелиевых шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1750</v>
+        <v>2750</v>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
@@ -5429,60 +5425,60 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 5</t>
+          <t>Набор из фольгированных шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1250</v>
+        <v>6750</v>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 11</t>
+          <t>Набор из фольгированных шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2750</v>
+        <v>4950</v>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 15</t>
+          <t>Набор из фольгированных шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>6750</v>
+        <v>4050</v>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
@@ -5492,18 +5488,18 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 11</t>
+          <t>Набор из фольгированных шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>4950</v>
+        <v>3150</v>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
@@ -5513,18 +5509,18 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 9</t>
+          <t>Набор из фольгированных шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>4050</v>
+        <v>2250</v>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
@@ -5534,63 +5530,67 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 7</t>
+          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>3150</v>
-      </c>
-      <c r="C235" t="inlineStr"/>
+        <v>4500</v>
+      </c>
+      <c r="C235" t="n">
+        <v>4500</v>
+      </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 5</t>
+          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>2250</v>
-      </c>
-      <c r="C236" t="inlineStr"/>
+        <v>6100</v>
+      </c>
+      <c r="C236" t="n">
+        <v>6100</v>
+      </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>4500</v>
+        <v>8500</v>
       </c>
       <c r="C237" t="n">
-        <v>4500</v>
+        <v>8500</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>6100</v>
+        <v>10100</v>
       </c>
       <c r="C238" t="n">
-        <v>6100</v>
+        <v>10100</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -5622,21 +5622,21 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>8500</v>
+        <v>14100</v>
       </c>
       <c r="C239" t="n">
-        <v>8500</v>
+        <v>14100</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -5645,22 +5645,20 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>10100</v>
-      </c>
-      <c r="C240" t="n">
-        <v>10100</v>
-      </c>
+        <v>3700</v>
+      </c>
+      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5668,22 +5666,20 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>14100</v>
-      </c>
-      <c r="C241" t="n">
-        <v>14100</v>
-      </c>
+        <v>2900</v>
+      </c>
+      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5691,20 +5687,22 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>3700</v>
-      </c>
-      <c r="C242" t="inlineStr"/>
+        <v>17950</v>
+      </c>
+      <c r="C242" t="n">
+        <v>18690</v>
+      </c>
       <c r="D242" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5712,20 +5710,22 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C243" t="inlineStr"/>
+        <v>35450</v>
+      </c>
+      <c r="C243" t="n">
+        <v>38690</v>
+      </c>
       <c r="D243" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5733,87 +5733,83 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
+          <t>Стильный букет в крафтовой сумочке</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>17950</v>
+        <v>4200</v>
       </c>
       <c r="C244" t="n">
-        <v>18690</v>
+        <v>5200</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>35450</v>
-      </c>
-      <c r="C245" t="n">
-        <v>38690</v>
-      </c>
+        <v>5040</v>
+      </c>
+      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Стильный букет в крафтовой сумочке</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C246" t="n">
-        <v>5200</v>
-      </c>
+        <v>5730</v>
+      </c>
+      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>4990</v>
+        <v>6040</v>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
@@ -5830,11 +5826,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>5680</v>
+        <v>6040</v>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
@@ -5851,11 +5847,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>5990</v>
+        <v>6290</v>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
@@ -5872,11 +5868,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>5990</v>
+        <v>6340</v>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
@@ -5893,11 +5889,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>6240</v>
+        <v>10540</v>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
@@ -5914,99 +5910,103 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
+          <t>ДОРОГУША из красных роз с ромашками</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>6290</v>
-      </c>
-      <c r="C252" t="inlineStr"/>
+        <v>8450</v>
+      </c>
+      <c r="C252" t="n">
+        <v>8500</v>
+      </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
+          <t>Коробка гигант с радужной гипсофилой</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>10490</v>
-      </c>
-      <c r="C253" t="inlineStr"/>
+        <v>9999</v>
+      </c>
+      <c r="C253" t="n">
+        <v>10990</v>
+      </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ДОРОГУША из красных роз с ромашками</t>
+          <t>Букет Малиновое вино - Посмотреть...</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>7500</v>
+        <v>4920</v>
       </c>
       <c r="C254" t="n">
-        <v>8500</v>
+        <v>5200</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Коробка гигант с радужной гипсофилой</t>
+          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>9999</v>
+        <v>5610</v>
       </c>
       <c r="C255" t="n">
-        <v>10990</v>
+        <v>5200</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Посмотреть...</t>
+          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>4650</v>
+        <v>5920</v>
       </c>
       <c r="C256" t="n">
         <v>5200</v>
@@ -6025,11 +6025,11 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
+          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>5340</v>
+        <v>5920</v>
       </c>
       <c r="C257" t="n">
         <v>5200</v>
@@ -6048,11 +6048,11 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
+          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>5650</v>
+        <v>6170</v>
       </c>
       <c r="C258" t="n">
         <v>5200</v>
@@ -6071,11 +6071,11 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>5650</v>
+        <v>6220</v>
       </c>
       <c r="C259" t="n">
         <v>5200</v>
@@ -6094,11 +6094,11 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>5900</v>
+        <v>10420</v>
       </c>
       <c r="C260" t="n">
         <v>5200</v>
@@ -6117,57 +6117,57 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
+          <t>11альстромерий в оформлении - Посмотреть...</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>5950</v>
+        <v>2500</v>
       </c>
       <c r="C261" t="n">
-        <v>5200</v>
+        <v>2380</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
+          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>10150</v>
+        <v>3190</v>
       </c>
       <c r="C262" t="n">
-        <v>5200</v>
+        <v>2380</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Посмотреть...</t>
+          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="C263" t="n">
         <v>2380</v>
@@ -6186,11 +6186,11 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>3190</v>
+        <v>3500</v>
       </c>
       <c r="C264" t="n">
         <v>2380</v>
@@ -6209,11 +6209,11 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>3500</v>
+        <v>3750</v>
       </c>
       <c r="C265" t="n">
         <v>2380</v>
@@ -6232,11 +6232,11 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
+          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="C266" t="n">
         <v>2380</v>
@@ -6255,11 +6255,11 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>3750</v>
+        <v>8000</v>
       </c>
       <c r="C267" t="n">
         <v>2380</v>
@@ -6278,46 +6278,42 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>3800</v>
-      </c>
-      <c r="C268" t="n">
-        <v>2380</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C269" t="n">
-        <v>2380</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
         </is>
       </c>
     </row>
@@ -6333,12 +6329,12 @@
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
         </is>
       </c>
     </row>
@@ -6354,12 +6350,12 @@
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
         </is>
       </c>
     </row>
@@ -6375,12 +6371,12 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6392,12 @@
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6413,12 @@
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6434,12 @@
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6455,12 @@
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
         </is>
       </c>
     </row>
@@ -6480,82 +6476,84 @@
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>900</v>
+        <v>3000</v>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>900</v>
+        <v>3560</v>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
+          <t>Зефирный - Белые</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C280" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="C280" t="n">
+        <v>3500</v>
+      </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Зефирный - Белые</t>
+          <t>Зефирный - Микс</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -6566,67 +6564,65 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
+          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Зефирный - Микс</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C282" t="n">
-        <v>3500</v>
-      </c>
+        <v>3700</v>
+      </c>
+      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
+          <t>https://static.tildacdn.com/stor3333-6134-4931-b064-626531613738/26831923.jpg</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>3550</v>
+        <v>3700</v>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3333-6134-4931-b064-626531613738/26831923.jpg</t>
+          <t>https://static.tildacdn.com/stor3161-3631-4130-b561-653330386363/79575723.jpg</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>3500</v>
+        <v>6050</v>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
@@ -6636,133 +6632,133 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
+          <t>Букет МАГНОЛИЯ</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>5800</v>
+        <v>5420</v>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3161-3631-4130-b561-653330386363/79575723.jpg</t>
+          <t>https://static.tildacdn.com/stor3365-6335-4433-b938-333931306239/10745399.jpg</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-buket-magnoliya</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Букет МАГНОЛИЯ</t>
+          <t>Игрушка МИШАНЯ</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>5750</v>
+        <v>4500</v>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3365-6335-4433-b938-333931306239/10745399.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6436-4538-b130-383238323638/76577859.jpg</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-buket-magnoliya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-mishanya</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Игрушка МИШАНЯ</t>
+          <t>Игрушка Мякий медведь Мишаня</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6436-4538-b130-383238323638/76577859.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Игрушка Мякий медведь Мишаня</t>
+          <t>Игрушкп Зайка милашка</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>3500</v>
+        <v>1100</v>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Игрушкп Зайка милашка</t>
+          <t>Букет Солнечный из хризантем</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>1100</v>
+        <v>3250</v>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
+          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Букет Солнечный из хризантем</t>
+          <t>LOVE IS....из кустовых роз с ромашками</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>2800</v>
+        <v>10990</v>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
+          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6769,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>3500</v>
+        <v>3540</v>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
@@ -6817,7 +6813,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>16290</v>
+        <v>15950</v>
       </c>
       <c r="C293" t="n">
         <v>175550</v>
@@ -6836,1203 +6832,1207 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
+          <t>Букет Красотуля с орхидеями</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>8500</v>
-      </c>
-      <c r="C294" t="n">
-        <v>9200</v>
-      </c>
+        <v>4250</v>
+      </c>
+      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
+          <t>https://static.tildacdn.com/stor3931-3734-4437-a234-313232633735/93320832.jpg</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=736484317922</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Букет Красотуля с орхидеями</t>
+          <t>25 белых роз с эвкалиптом</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C295" t="inlineStr"/>
+        <v>7800</v>
+      </c>
+      <c r="C295" t="n">
+        <v>9750</v>
+      </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3734-4437-a234-313232633735/93320832.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>25 белых роз с эвкалиптом</t>
+          <t>Букет орхидей БАБОЧКА</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>7800</v>
+        <v>4200</v>
       </c>
       <c r="C296" t="n">
-        <v>9750</v>
+        <v>4300</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
+          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Букет орхидей БАБОЧКА</t>
+          <t>Букет "Сердце" из роз - 51 - Красный</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>3750</v>
-      </c>
-      <c r="C297" t="n">
-        <v>4300</v>
-      </c>
+        <v>13200</v>
+      </c>
+      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
+          <t>https://static.tildacdn.com/stor3265-6563-4066-b333-623131303566/86344649.jpg</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=596862368331</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Букет КОМПЛИМЕНТ АССОРТИ</t>
+          <t>Букет "Сердце" из роз - 35 - Красный</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>2400</v>
+        <v>9300</v>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3765-3434-4365-b737-666431333536/57090603.jpg</t>
+          <t>https://static.tildacdn.com/stor3730-3736-4134-a134-623235356232/75639760.jpg</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-169103768201-buket-kompliment-assorti</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=420576792261</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Букет ромашек "Модный"</t>
+          <t>Букет "Сердце" из роз - 51 - Белые</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C299" t="n">
-        <v>3200</v>
-      </c>
+        <v>13200</v>
+      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
+          <t>https://static.tildacdn.com/stor6332-3761-4964-b337-633939613039/40797598.jpg</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=384773199531</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Букет ЛАЙК с красными розами</t>
+          <t>Букет "Сердце" из роз - 35 - Белые</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C300" t="inlineStr"/>
+        <v>9300</v>
+      </c>
+      <c r="C300" t="n">
+        <v>11500</v>
+      </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3534-3438-4762-a236-656639623635/85107167.jpg</t>
+          <t>https://static.tildacdn.com/stor6332-3761-4964-b337-633939613039/40797598.jpg</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=310959153071</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
+          <t>Букет "Сердце" из роз - 51 - Пионовидные крем</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>3350</v>
-      </c>
-      <c r="C301" t="inlineStr"/>
+        <v>15500</v>
+      </c>
+      <c r="C301" t="n">
+        <v>16500</v>
+      </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
+          <t>https://static.tildacdn.com/stor6135-3363-4562-b462-396239336435/10956098.jpg</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=419923721431</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
+          <t>Букет "Сердце" из роз - 51 - Нежные</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>4150</v>
+        <v>13200</v>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3433-4738-b166-646364353731/26315844.jpg</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=131250231871</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
+          <t>Букет "Сердце" из роз - 51 - Микс</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>4950</v>
-      </c>
-      <c r="C303" t="inlineStr"/>
+        <v>13200</v>
+      </c>
+      <c r="C303" t="n">
+        <v>14500</v>
+      </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-3936-4262-b064-303838613332/48226272.jpg</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=197174543341</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
+          <t>Букет "Сердце" из роз - 35 - Микс</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>6550</v>
+        <v>9300</v>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-3936-4262-b064-303838613332/48226272.jpg</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=168510316671</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
+          <t>Букет "Сердце" из роз - 35 - Нежные</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>9500</v>
+        <v>9200</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
+          <t>https://static.tildacdn.com/stor3730-3532-4662-b161-323433393562/67841903.jpg</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=356370001431</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
+          <t>Букет КОМПЛИМЕНТ АССОРТИ</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>12850</v>
+        <v>2600</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
+          <t>https://static.tildacdn.com/stor3765-3434-4365-b737-666431333536/57090603.jpg</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-169103768201-buket-kompliment-assorti</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
+          <t>Букет ромашек "Модный"</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>17590</v>
-      </c>
-      <c r="C307" t="inlineStr"/>
+        <v>2700</v>
+      </c>
+      <c r="C307" t="n">
+        <v>3200</v>
+      </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
+          <t>Букет ЛАЙК с красными розами</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>33990</v>
+        <v>3500</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor3534-3438-4762-a236-656639623635/85107167.jpg</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>7290</v>
+        <v>3350</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
+          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>9950</v>
+        <v>4150</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>13999</v>
+        <v>4950</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
+          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>26990</v>
+        <v>6550</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>3650</v>
+        <v>9500</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>4990</v>
+        <v>12850</v>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Букет Белый шоколад из белых роз</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C315" t="n">
-        <v>5900</v>
-      </c>
+        <v>17590</v>
+      </c>
+      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Комплимент ВАНИЛЬ с ромашками</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>2790</v>
+        <v>33990</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Коробка с кустовыми розами</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>3500</v>
+        <v>7290</v>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3461-3061-4533-a361-306563366164/19857974.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Дивная Орхидея</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>5600</v>
+        <v>9940</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Коробка "Орхидея "</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>5700</v>
+        <v>14180</v>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>6999</v>
+        <v>27430</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6538-4838-b665-353662303035/42686584.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Розовый дым</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>13500</v>
+        <v>3580</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
+          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - M</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>1800</v>
+        <v>4640</v>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - L</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>2150</v>
+        <v>3050</v>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=972782492442</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Букет Комплимент МАРМЕЛАД</t>
+          <t>Букет Белый шоколад из белых роз</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>2650</v>
-      </c>
-      <c r="C324" t="inlineStr"/>
+        <v>5900</v>
+      </c>
+      <c r="C324" t="n">
+        <v>5900</v>
+      </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Коробка с цветами ЛЮКС</t>
+          <t>Комплимент ВАНИЛЬ с ромашками</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>9990</v>
+        <v>2900</v>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-3036-4663-b030-666130666261/13712242.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-146373087581-korobka-s-tsvetami-lyuks</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Шикарная корзина с кустовыми розами</t>
+          <t>Коробка с кустовыми розами</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>20990</v>
-      </c>
-      <c r="C326" t="n">
-        <v>21500</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-3135-4165-b161-393937653763/76895073.jpg</t>
+          <t>https://static.tildacdn.com/stor3461-3061-4533-a361-306563366164/19857974.jpg</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Коробка с орхидеями и кустовыми розами</t>
+          <t>Дивная Орхидея</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>4990</v>
-      </c>
-      <c r="C327" t="n">
-        <v>5900</v>
-      </c>
+        <v>5450</v>
+      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-3837-4130-b565-316434363939/31198124.jpg</t>
+          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-665629263531-korobka-s-orhideyami-i-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Атласная лента</t>
+          <t>Коробка "Орхидея "</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>2350</v>
+        <v>5700</v>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=807760891511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Атласная лента</t>
+          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>3850</v>
+        <v>7320</v>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6538-4838-b665-353662303035/42686584.jpg</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=935605880011</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Атласная лента</t>
+          <t>Розовый дым</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>5350</v>
+        <v>13500</v>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=621399533081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 3 - Матовая бумага</t>
+          <t>Букет Комплимент ПУШ с хризантемами - M</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>2550</v>
+        <v>1950</v>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
+          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=428830803781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 5 - Матовая бумага</t>
+          <t>Букет Комплимент ПУШ с хризантемами - L</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>4250</v>
+        <v>2450</v>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
+          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=507029921911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 7 - Матовая бумага</t>
+          <t>Букет Комплимент МАРМЕЛАД</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>5900</v>
+        <v>2680</v>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=330876877451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Атласная лента</t>
+          <t>Шикарная корзина с кустовыми розами</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>8600</v>
-      </c>
-      <c r="C334" t="inlineStr"/>
+        <v>20990</v>
+      </c>
+      <c r="C334" t="n">
+        <v>21500</v>
+      </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-3135-4165-b161-393937653763/76895073.jpg</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=352141135642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 11 - Матовая бумага</t>
+          <t>Коробка с орхидеями и кустовыми розами</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>8990</v>
-      </c>
-      <c r="C335" t="inlineStr"/>
+        <v>4990</v>
+      </c>
+      <c r="C335" t="n">
+        <v>5900</v>
+      </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-3837-4130-b565-316434363939/31198124.jpg</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=444544724772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-665629263531-korobka-s-orhideyami-i-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Букет ароматных лилии в ленту - 15 - Матовая бумага</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 3 - Атласная лента</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>11990</v>
+        <v>2450</v>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii-v-lentu?editionuid=810198608332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=807760891511</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Букет МИЛАШКА</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 5 - Атласная лента</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>3150</v>
+        <v>3850</v>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6135-3161-4637-b761-356232373633/78238867.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=935605880011</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>51 кремовая роза</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>12590</v>
+        <v>5350</v>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3966-4136-b735-386133633035/40006718.jpg</t>
+          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-555099133731-51-kremovaya-roza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=621399533081</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Корзина кустовых роз 1</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 3 - Матовая бумага</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>17100</v>
-      </c>
-      <c r="C339" t="n">
-        <v>17990</v>
-      </c>
+        <v>2850</v>
+      </c>
+      <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
+          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=428830803781</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Атласная лента</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 5 - Матовая бумага</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>3250</v>
+        <v>4250</v>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=507029921911</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Атласная лента</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>3950</v>
+        <v>5650</v>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
+          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=330876877451</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 15 - Атласная лента</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>5350</v>
+        <v>8050</v>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=352141135642</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Атласная лента</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>8850</v>
+        <v>8450</v>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=444544724772</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>12350</v>
+        <v>11550</v>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=810198608332</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Атласная лента</t>
+          <t>Букет МИЛАШКА</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>16990</v>
+        <v>3160</v>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor6135-3161-4637-b761-356232373633/78238867.jpg</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-milashka</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Матовая бумага</t>
+          <t>51 кремовая роза</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>9100</v>
+        <v>11590</v>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3966-4136-b735-386133633035/40006718.jpg</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-555099133731-51-kremovaya-roza</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>Корзина кустовых роз 1</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>12650</v>
-      </c>
-      <c r="C347" t="inlineStr"/>
+        <v>17100</v>
+      </c>
+      <c r="C347" t="n">
+        <v>17990</v>
+      </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Матовая бумага</t>
+          <t>Ажурные французские розы - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>17500</v>
+        <v>3250</v>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Матовая бумага</t>
+          <t>Ажурные французские розы - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>3500</v>
+        <v>3950</v>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Матовая бумага</t>
+          <t>Ажурные французские розы - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>4200</v>
+        <v>5350</v>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
@@ -8042,1639 +8042,1641 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 15</t>
+          <t>Ажурные французские розы - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>6850</v>
+        <v>8850</v>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=708375581471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 25</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>10800</v>
+        <v>12350</v>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=997102028441</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 35</t>
+          <t>Ажурные французские розы - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>14990</v>
+        <v>16990</v>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=585625855371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 11</t>
+          <t>Ажурные французские розы - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>5450</v>
+        <v>9100</v>
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=976684960222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Букет пионовидных роз с эвкалиптом - 9</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>4690</v>
+        <v>12650</v>
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pionovidnih-roz-s-evkaliptom?editionuid=285996858812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
+          <t>Ажурные французские розы - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>5050</v>
-      </c>
-      <c r="C356" t="n">
-        <v>5500</v>
-      </c>
+        <v>17500</v>
+      </c>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
+          <t>Ажурные французские розы - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>8250</v>
-      </c>
-      <c r="C357" t="n">
-        <v>9500</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
+          <t>Ажурные французские розы - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>11250</v>
-      </c>
-      <c r="C358" t="n">
-        <v>15500</v>
-      </c>
+        <v>4200</v>
+      </c>
+      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>15550</v>
-      </c>
-      <c r="C359" t="n">
-        <v>18200</v>
-      </c>
+        <v>6759</v>
+      </c>
+      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=708375581471</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>27999</v>
-      </c>
-      <c r="C360" t="n">
-        <v>35500</v>
-      </c>
+        <v>10500</v>
+      </c>
+      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=997102028441</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 35</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>3250</v>
-      </c>
-      <c r="C361" t="n">
-        <v>3500</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=585625855371</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Вау-букет 151 роза и Большой медведь</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 11</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>39990</v>
-      </c>
-      <c r="C362" t="n">
-        <v>49999</v>
-      </c>
+        <v>5350</v>
+      </c>
+      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=976684960222</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>3650</v>
+        <v>4400</v>
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=285996858812</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 51</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>4100</v>
+        <v>20600</v>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=627988456352</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>9100</v>
-      </c>
-      <c r="C365" t="inlineStr"/>
+        <v>5050</v>
+      </c>
+      <c r="C365" t="n">
+        <v>5500</v>
+      </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>14900</v>
-      </c>
-      <c r="C366" t="inlineStr"/>
+        <v>8250</v>
+      </c>
+      <c r="C366" t="n">
+        <v>9500</v>
+      </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>23990</v>
-      </c>
-      <c r="C367" t="inlineStr"/>
+        <v>11250</v>
+      </c>
+      <c r="C367" t="n">
+        <v>15500</v>
+      </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>5750</v>
-      </c>
-      <c r="C368" t="inlineStr"/>
+        <v>15550</v>
+      </c>
+      <c r="C368" t="n">
+        <v>18200</v>
+      </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Корзина люкс</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>39000</v>
+        <v>27999</v>
       </c>
       <c r="C369" t="n">
-        <v>49990</v>
+        <v>35500</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3665-3335-4462-b738-363535393066/72943061.jpg</t>
+          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-832446607671-korzina-lyuks</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>4450</v>
-      </c>
-      <c r="C370" t="inlineStr"/>
+        <v>3250</v>
+      </c>
+      <c r="C370" t="n">
+        <v>3500</v>
+      </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
+          <t>Вау-букет 151 роза и Большой медведь</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>6250</v>
+        <v>35950</v>
       </c>
       <c r="C371" t="n">
-        <v>7500</v>
+        <v>49999</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
+          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>12999</v>
-      </c>
-      <c r="C372" t="n">
-        <v>15590</v>
-      </c>
+        <v>3650</v>
+      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Букет Комплимент "НЕЖНОСТЬ" с белыми альстромериями</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>2890</v>
+        <v>4100</v>
       </c>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6132-3736-4930-b031-323732633532/31889130.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-belimi-alstr</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Букет Комплимент "Дюшес" с альстромериями</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>2450</v>
-      </c>
-      <c r="C374" t="n">
-        <v>2600</v>
-      </c>
+        <v>9100</v>
+      </c>
+      <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Букет ПЛОМБИР</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>4100</v>
+        <v>14900</v>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3439-6536-4663-b263-353034613736/33171735.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>3950</v>
+        <v>23990</v>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш с бантом "M"</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>1850</v>
+        <v>5750</v>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Игрушкп Медведь большой Ягодка</t>
+          <t>КОРЗИНА ЛЮКС</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>5500</v>
-      </c>
-      <c r="C378" t="inlineStr"/>
+        <v>39000</v>
+      </c>
+      <c r="C378" t="n">
+        <v>49990</v>
+      </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
+          <t>https://static.tildacdn.com/stor6336-3363-4361-b966-623065383162/15116412.jpg</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-832446607671-korzina-lyuks</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" беж.</t>
+          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>1300</v>
+        <v>5850</v>
       </c>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
+          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" белый</t>
+          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C380" t="inlineStr"/>
+        <v>6550</v>
+      </c>
+      <c r="C380" t="n">
+        <v>7500</v>
+      </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>БУКЕТ ГИПНОЗ с лилиями и розами</t>
+          <t>БУКЕТ КРЕМ ЛАВ</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>8500</v>
-      </c>
-      <c r="C381" t="n">
-        <v>9200</v>
-      </c>
+        <v>5500</v>
+      </c>
+      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3264-3966-4536-b462-663135316366/99420913.jpg</t>
+          <t>https://static.tildacdn.com/stor3835-6431-4237-a663-343437613231/32984901.jpg</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-krem-lav</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Корзина французских роз</t>
+          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>7300</v>
-      </c>
-      <c r="C382" t="inlineStr"/>
+        <v>12999</v>
+      </c>
+      <c r="C382" t="n">
+        <v>15590</v>
+      </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6563-6462-4337-a637-646433396235/18661426.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522766706011-korzina-frantsuzskih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>51 роза нежный микс в корзине</t>
+          <t>Букет Комплимент "НЕЖНОСТЬ" с белыми альстромериями</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>15750</v>
-      </c>
-      <c r="C383" t="n">
-        <v>18990</v>
-      </c>
+        <v>3120</v>
+      </c>
+      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
+          <t>https://static.tildacdn.com/stor6132-3736-4930-b031-323732633532/31889130.jpg</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-belimi-alstr</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>От всего сердца</t>
+          <t>Букет Комплимент "Дюшес" с альстромериями</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>27800</v>
+        <v>2510</v>
       </c>
       <c r="C384" t="n">
-        <v>29890</v>
+        <v>2600</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6132-3266-4466-a338-636461616235/65353807.jpg</t>
+          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-279941586181-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Микс "Нежный "в шляпной коробке</t>
+          <t>Букет ПЛОМБИР</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C385" t="n">
-        <v>4600</v>
-      </c>
+        <v>4150</v>
+      </c>
+      <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
+          <t>https://static.tildacdn.com/stor3439-6536-4663-b263-353034613736/33171735.jpg</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
+          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>3890</v>
-      </c>
-      <c r="C386" t="n">
-        <v>4500</v>
-      </c>
+        <v>4260</v>
+      </c>
+      <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке</t>
+          <t>Игрушка Мишка-плюш с бантом "M"</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>4999</v>
+        <v>1850</v>
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>"Мерилин "</t>
+          <t>Игрушкп Медведь большой Ягодка</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C388" t="n">
-        <v>3999</v>
-      </c>
+        <v>5500</v>
+      </c>
+      <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Мон Амур - 25</t>
+          <t>Игрушка Мишка-плюш "S" беж.</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>6800</v>
+        <v>1300</v>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
+          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Мон Амур - 35</t>
+          <t>Игрушка Мишка-плюш "S" белый</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>9300</v>
+        <v>1300</v>
       </c>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Мон Амур - 51</t>
+          <t>БУКЕТ ГИПНОЗ с лилиями и розами</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>12990</v>
+        <v>8200</v>
       </c>
       <c r="C391" t="n">
-        <v>17750</v>
+        <v>9200</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3264-3966-4536-b462-663135316366/99420913.jpg</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Мон Амур - 101</t>
+          <t>Корзина французских роз</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>24990</v>
-      </c>
-      <c r="C392" t="n">
-        <v>35600</v>
-      </c>
+        <v>7300</v>
+      </c>
+      <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor6563-6462-4337-a637-646433396235/18661426.jpg</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522766706011-korzina-frantsuzskih-roz</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Коробка L с радужной гипсофилой для мамы</t>
+          <t>51 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>3799</v>
-      </c>
-      <c r="C393" t="inlineStr"/>
+        <v>15750</v>
+      </c>
+      <c r="C393" t="n">
+        <v>18990</v>
+      </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Коробка для мамы с гипсофилой M</t>
+          <t>От всего сердца</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>2999</v>
-      </c>
-      <c r="C394" t="inlineStr"/>
+        <v>26800</v>
+      </c>
+      <c r="C394" t="n">
+        <v>29890</v>
+      </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
+          <t>https://static.tildacdn.com/stor6132-3266-4466-a338-636461616235/65353807.jpg</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-279941586181-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>101 роза нежный микс в корзине</t>
+          <t>Микс "Нежный "в шляпной коробке</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>27990</v>
+        <v>4500</v>
       </c>
       <c r="C395" t="n">
-        <v>33500</v>
+        <v>4600</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
+          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Букет ЛЕТО с хризантемами и ромашками</t>
+          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>3100</v>
-      </c>
-      <c r="C396" t="inlineStr"/>
+        <v>3890</v>
+      </c>
+      <c r="C396" t="n">
+        <v>4500</v>
+      </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Букет ЛАПОЧКА белыми розами и диантусами</t>
+          <t>"Ванильное небо "в шляпной коробке</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>2650</v>
+        <v>4999</v>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-6265-4162-b135-653333373065/49653431.jpg</t>
+          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-lapochka-belimi-rozami-i-diantusam</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Вставка сердце в букет</t>
+          <t>"Мерилин "</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>250</v>
-      </c>
-      <c r="C398" t="inlineStr"/>
+        <v>3650</v>
+      </c>
+      <c r="C398" t="n">
+        <v>3999</v>
+      </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
+          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
+          <t>Мон Амур - 25</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>3890</v>
-      </c>
-      <c r="C399" t="n">
-        <v>4000</v>
-      </c>
+        <v>6800</v>
+      </c>
+      <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Букет "Стильный микс" с орхидеями</t>
+          <t>Мон Амур - 35</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>5000</v>
+        <v>9300</v>
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3438-3261-4464-a639-333432623737/58155197.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-704877065131-buket-stilnii-miks-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
+          <t>Мон Амур - 51</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>4690</v>
-      </c>
-      <c r="C401" t="inlineStr"/>
+        <v>12990</v>
+      </c>
+      <c r="C401" t="n">
+        <v>17750</v>
+      </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
+          <t>Мон Амур - 101</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C402" t="inlineStr"/>
+        <v>22990</v>
+      </c>
+      <c r="C402" t="n">
+        <v>35600</v>
+      </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>БУКЕТ ПРЕСТИЖ М</t>
+          <t>Коробка L с радужной гипсофилой для мамы</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>3590</v>
+        <v>3799</v>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3434-3936-4962-b964-383035613735/62450227.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-prestizh-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 7</t>
+          <t>Коробка для мамы с гипсофилой M</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>2900</v>
+        <v>2999</v>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3437-6163-4565-a262-326664653130/42939189.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=308194824921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 9</t>
+          <t>101 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>3450</v>
-      </c>
-      <c r="C405" t="inlineStr"/>
+        <v>27990</v>
+      </c>
+      <c r="C405" t="n">
+        <v>33500</v>
+      </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3730-6336-4237-a665-313838623331/13509496.jpg</t>
+          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=302968644811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 11</t>
+          <t>Букет ЛЕТО с хризантемами и ромашками</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>4150</v>
+        <v>3060</v>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
+          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=266242456331</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Букет из пионовидных роз в оформлении - 15</t>
+          <t>Букет ЛАПОЧКА белыми розами и диантусами</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>5550</v>
+        <v>2550</v>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3561-4438-b732-376434653936/64677586.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-6265-4162-b135-653333373065/49653431.jpg</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-597405396191-buket-iz-pionovidnih-roz-v-oformlenii?editionuid=541061184792</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-lapochka-belimi-rozami-i-diantusam</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
+          <t>Вставка сердце в букет</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>3590</v>
+        <v>250</v>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Ромашкина любовь - XXL</t>
+          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>10990</v>
-      </c>
-      <c r="C409" t="inlineStr"/>
+        <v>4230</v>
+      </c>
+      <c r="C409" t="n">
+        <v>4000</v>
+      </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
+          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov?editionuid=407344541282</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Ромашкина любовь - L</t>
+          <t>Букет 15 НЕЖНЫХ ПИОН КУСТОВЫХ РОЗ</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>3800</v>
+        <v>6950</v>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3464-3333-4434-a531-336439396466/16521764.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-6536-4463-b165-383562363338/84502320.jpg</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov?editionuid=825207994132</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-15-nezhnih-pion-kustovih-roz</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ВАУ КОРЗИНА ИЗ ГИПСОФИЛ</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>14999</v>
+        <v>4700</v>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6466-3031-4535-a431-633237363865/12981366.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-iz-gipsofil</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Букет "НЕЖЕНКА" с гортензией</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>3450</v>
+        <v>3500</v>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6238-3964-4531-b231-323161623038/90169769.jpg</t>
+          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Букет РАДУЖНЫЙ с альстромериями</t>
+          <t>БУКЕТ ПРЕСТИЖ М</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>2700</v>
-      </c>
-      <c r="C413" t="n">
-        <v>3450</v>
-      </c>
+        <v>3900</v>
+      </c>
+      <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-3936-4962-b964-383035613735/62450227.jpg</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-prestizh-m</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
+          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
+          <t>Ромашкина любовь - XXL</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>5200</v>
-      </c>
-      <c r="C415" t="inlineStr"/>
+        <v>10600</v>
+      </c>
+      <c r="C415" t="n">
+        <v>10990</v>
+      </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3632-4566-a533-386631646134/30216142.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov?editionuid=407344541282</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>51 пионовидная кустовая роза в нежном оформлении</t>
+          <t>Ромашкина любовь - L</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>18600</v>
-      </c>
-      <c r="C416" t="n">
-        <v>18000</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
+          <t>https://static.tildacdn.com/stor3464-3333-4434-a531-336439396466/16521764.jpg</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov?editionuid=825207994132</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Букет РОМАНТИКА</t>
+          <t>ВАУ КОРЗИНА ИЗ ГИПСОФИЛ</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>6250</v>
+        <v>14999</v>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3833-6263-4665-b264-386639363531/55310964.jpg</t>
+          <t>https://static.tildacdn.com/stor6466-3031-4535-a431-633237363865/12981366.jpg</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-359890420482-buket-romantika</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-iz-gipsofil</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Букет Комплимент с маттиолой</t>
+          <t>Букет "НЕЖЕНКА" с гортензией</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>1800</v>
+        <v>2900</v>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
+          <t>https://static.tildacdn.com/stor6238-3964-4531-b231-323161623038/90169769.jpg</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 9</t>
+          <t>Букет РАДУЖНЫЙ с альстромериями</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>4150</v>
-      </c>
-      <c r="C419" t="inlineStr"/>
+        <v>2890</v>
+      </c>
+      <c r="C419" t="n">
+        <v>3450</v>
+      </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3364-3334-4339-b730-653536623666/41200469.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=762768049002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 11</t>
+          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>4950</v>
+        <v>3600</v>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6135-4630-b531-356538373065/45691131.jpg</t>
+          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=231966809752</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 15</t>
+          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>6550</v>
+        <v>5200</v>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3165-4131-b634-353939346238/45754421.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3632-4566-a533-386631646134/30216142.jpg</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=197416122812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 25</t>
+          <t>51 пионовидная кустовая роза в нежном оформлении</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>10550</v>
-      </c>
-      <c r="C422" t="inlineStr"/>
+        <v>18600</v>
+      </c>
+      <c r="C422" t="n">
+        <v>18000</v>
+      </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=531645917332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 35</t>
+          <t>Букет РОМАНТИКА</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>14550</v>
+        <v>6190</v>
       </c>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3833-6263-4665-b264-386639363531/55310964.jpg</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=172751700112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-359890420482-buket-romantika</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 51</t>
+          <t>Букет Комплимент с маттиолой</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>18400</v>
+        <v>1910</v>
       </c>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=261066938402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Пионовидные кустовые розы в оформлении - 101</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>35900</v>
+        <v>2800</v>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-6339-4931-a536-383533343232/59431960.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-883743434962-pionovidnie-kustovie-rozi-v-oformlenii?editionuid=818806872532</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>2800</v>
+        <v>3500</v>
       </c>
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
@@ -9684,60 +9686,60 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>3500</v>
+        <v>5500</v>
       </c>
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>5500</v>
+        <v>8700</v>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>8700</v>
+        <v>15900</v>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
@@ -9747,144 +9749,144 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
+          <t>Подарочный набор для мамы 1</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>15900</v>
+        <v>3990</v>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Подарочный набор для мамы 1</t>
+          <t>Подарок для мамы 2</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>3990</v>
+        <v>4990</v>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Подарок для мамы 2</t>
+          <t>Подарок для мамы 3 селебрити</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>4990</v>
+        <v>5199</v>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Подарок для мамы 3 селебрити</t>
+          <t>Букет ЛЕДИ РЕД с краснымм розами</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>5199</v>
+        <v>2650</v>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-6135-4034-a139-376262616331/46580879.jpg</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-341373252172-buket-ledi-red-s-krasnimm-rozami</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Букет ЛЕДИ РЕД с краснымм розами</t>
+          <t>Игрушка Мишка "Валентин"</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>2490</v>
+        <v>1300</v>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-6135-4034-a139-376262616331/46580879.jpg</t>
+          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-341373252172-buket-ledi-red-s-krasnimm-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Игрушка Мишка "Валентин"</t>
+          <t>Игрушка Котик - 25см</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 25см</t>
+          <t>Игрушка Котик - 35см</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
@@ -9894,39 +9896,39 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 35см</t>
+          <t>Игрушка Мишка Милые глазки - 25см</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>1850</v>
+        <v>1100</v>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Игрушка Мишка Милые глазки - 25см</t>
+          <t>Игрушка Мишка Милые глазки - 35см</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>1100</v>
+        <v>1850</v>
       </c>
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
@@ -9936,175 +9938,301 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Игрушка Мишка Милые глазки - 35см</t>
+          <t>Гипсофила от всего сердца</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>1850</v>
+        <v>4650</v>
       </c>
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Гипсофила от всего сердца</t>
+          <t>Сладкий подарок "ПРЕСТИЖ"</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>4550</v>
+        <v>1690</v>
       </c>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
+          <t>https://static.tildacdn.com/stor3135-6532-4334-a366-383338326235/55599791.jpg</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-548040342792-sladkii-podarok-prestizh</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Букет РУСАЛОЧКА</t>
+          <t>Детский сладкий сюрприз</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>4050</v>
+        <v>2300</v>
       </c>
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-6432-4761-b936-656137636438/83917609.jpg</t>
+          <t>https://static.tildacdn.com/stor3163-6664-4637-b630-386361646534/95823135.jpg</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-195551843462-buket-rusalochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-157699878712-detskii-sladkii-syurpriz</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Сладкий подарок "СЕРДЕЧКО"</t>
+          <t>Набор косметики для девушки</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>1790</v>
+        <v>2500</v>
       </c>
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3135-6532-4334-a366-383338326235/55599791.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3033-4239-a633-333863366236/47266730.jpg</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-548040342792-sladkii-podarok-serdechko</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-896299306932-nabor-kosmetiki-dlya-devushki</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Детский сладкий сюрприз</t>
+          <t>Автобус сладостей для девушки с конфетами и шоколадом</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>2300</v>
+        <v>3200</v>
       </c>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3163-6664-4637-b630-386361646534/95823135.jpg</t>
+          <t>https://static.tildacdn.com/stor3963-3839-4266-a466-343732346365/79416309.jpg</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-157699878712-detskii-sladkii-syurpriz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-814276260342-avtobus-sladostei-dlya-devushki-s-konfet</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Набор косметики для девушки</t>
+          <t>Подарочный набор ДЛЯ МУЖЧИНЫ</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3033-4239-a633-333863366236/47266730.jpg</t>
+          <t>https://static.tildacdn.com/stor6135-6563-4262-a539-626130313439/32687838.jpg</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-896299306932-nabor-kosmetiki-dlya-devushki</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-693724502742-podarochnii-nabor-dlya-muzhchini</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Автобус сладостей для девушки с конфетами и шоколадом</t>
+          <t>Пионы Сара Бернар - 5</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>3200</v>
+        <v>3050</v>
       </c>
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3963-3839-4266-a466-343732346365/79416309.jpg</t>
+          <t>https://static.tildacdn.com/stor3364-3834-4631-a139-336434323835/67477016.jpg</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-814276260342-avtobus-sladostei-dlya-devushki-s-konfet</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=817212322182</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Подарочный набор ДЛЯ МУЖЧИНЫ</t>
+          <t>Пионы Сара Бернар - 7</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>3900</v>
+        <v>4050</v>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6135-6563-4262-a539-626130313439/32687838.jpg</t>
+          <t>https://static.tildacdn.com/stor3364-3834-4631-a139-336434323835/67477016.jpg</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-693724502742-podarochnii-nabor-dlya-muzhchini</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=672137873212</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Пионы Сара Бернар - 9</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>5050</v>
+      </c>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3732-6531-4139-b439-356330303866/21328489.jpg</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=573374811462</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Пионы Сара Бернар - 11</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>6050</v>
+      </c>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3732-6531-4139-b439-356330303866/21328489.jpg</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=199245635062</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Пионы Сара Бернар - 15</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>8050</v>
+      </c>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3361-3661-4533-a631-316539363130/40788019.jpg</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=553932304422</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Пионы Сара Бернар - 17</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>9050</v>
+      </c>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3064-3261-4861-b930-333738353538/14995848.jpg</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=312411207952</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Пионы Сара Бернар - 19</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor3064-3261-4861-b930-333738353538/14995848.jpg</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=611416781092</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Пионы Сара Бернар - 25</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>13050</v>
+      </c>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>https://static.tildacdn.com/stor6465-6537-4635-b233-643661663663/11224874.jpg</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=190345697122</t>
         </is>
       </c>
     </row>

--- a/feed_converted.xlsx
+++ b/feed_converted.xlsx
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6232-6535-4165-a330-356664653439/72802638.jpg</t>
+          <t>https://static.tildacdn.com/tild6430-6438-4461-a235-366433323731/101.jpg</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1301,7 +1301,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3837-4332-a236-616635353939/50561648.jpg</t>
+          <t>https://static.tildacdn.com/tild6430-6438-4461-a235-366433323731/101.jpg</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1322,7 +1322,7 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3336-3935-4166-a438-323436363835/74111806.jpg</t>
+          <t>https://static.tildacdn.com/tild6430-6438-4461-a235-366433323731/101.jpg</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1343,7 +1343,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3336-3935-4166-a438-323436363835/74111806.jpg</t>
+          <t>https://static.tildacdn.com/tild6430-6438-4461-a235-366433323731/101.jpg</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1364,7 +1364,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3336-3935-4166-a438-323436363835/74111806.jpg</t>
+          <t>https://static.tildacdn.com/tild6430-6438-4461-a235-366433323731/101.jpg</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1385,7 +1385,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3336-3935-4166-a438-323436363835/74111806.jpg</t>
+          <t>https://static.tildacdn.com/tild6430-6438-4461-a235-366433323731/101.jpg</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2999</v>
+        <v>2600</v>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3999</v>
+        <v>3750</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>4990</v>
+        <v>4900</v>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
@@ -3727,11 +3727,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>101 красная роза в коробке - Бутон М</t>
+          <t>101 красная роза в коробке</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>14690</v>
+        <v>14670</v>
       </c>
       <c r="C151" t="n">
         <v>19000</v>
@@ -3743,87 +3743,85 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke?editionuid=677875507802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>101 красная роза в коробке - Бутон L</t>
+          <t>15кремовых роз - Атласная лента</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2999</v>
-      </c>
-      <c r="C152" t="n">
-        <v>35000</v>
-      </c>
+        <v>4100</v>
+      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3035-6333-4266-b131-356161303438/80710840.jpg</t>
+          <t>https://static.tildacdn.com/stor3937-3639-4962-b732-366632653839/89646755.jpg</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-128828996681-101-krasnaya-roza-v-korobke?editionuid=414704203762</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=626304677871</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>15кремовых роз - Атласная лента</t>
+          <t>15кремовых роз - Матовая бумага</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>4100</v>
+        <v>4300</v>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3937-3639-4962-b732-366632653839/89646755.jpg</t>
+          <t>https://static.tildacdn.com/stor3961-3330-4861-a331-393039383239/50564437.jpg</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=626304677871</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=757701389531</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>15кремовых роз - Матовая бумага</t>
+          <t>51 красная роза - 60 см</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C154" t="inlineStr"/>
+        <v>11990</v>
+      </c>
+      <c r="C154" t="n">
+        <v>12590</v>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3961-3330-4861-a331-393039383239/50564437.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-848543105701-15kremovih-roz?editionuid=757701389531</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=931089475821</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>51 красная роза - 60 см</t>
+          <t>51 красная роза - 45 см</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>11990</v>
-      </c>
-      <c r="C155" t="n">
-        <v>12590</v>
-      </c>
+        <v>6650</v>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
@@ -3831,749 +3829,743 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=931089475821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=692401540222</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>51 красная роза - 45 см</t>
+          <t>51 роза "Сердце "в коробке</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>6650</v>
-      </c>
-      <c r="C156" t="inlineStr"/>
+        <v>14590</v>
+      </c>
+      <c r="C156" t="n">
+        <v>19500</v>
+      </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-3764-4565-b465-313430646236/7E9B89E4-EB09-4184-9.JPG</t>
+          <t>https://static.tildacdn.com/stor3966-3065-4365-a431-663862633665/46922404.jpg</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-354737980041-51-krasnaya-roza?editionuid=692401540222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-168896456031-51-roza-serdtse-v-korobke</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>51 роза "Сердце "в коробке</t>
+          <t>15 красных роз - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>14500</v>
+        <v>4800</v>
       </c>
       <c r="C157" t="n">
-        <v>19500</v>
+        <v>5500</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3966-3065-4365-a431-663862633665/46922404.jpg</t>
+          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-168896456031-51-roza-serdtse-v-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=769434790781</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>25 малиновых роз в шляной коробке</t>
+          <t>15 красных роз - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C158" t="n">
-        <v>10500</v>
-      </c>
+        <v>2600</v>
+      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6539-6137-4637-b936-623137333530/20220228_175635.jpg</t>
+          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-511125332671-25-malinovih-roz-v-shlyanoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=205666183652</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>15 красных роз - 60 см - Атласная лента</t>
+          <t>51 красно-белая роза в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>4800</v>
+        <v>11990</v>
       </c>
       <c r="C159" t="n">
-        <v>5500</v>
+        <v>12999</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
+          <t>https://static.tildacdn.com/stor6534-3435-4432-a332-373732306661/48855206.jpg</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=769434790781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-542827273651-51-krasno-belaya-roza-v-oformlenii?editionuid=516167563281</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>15 красных роз - 45 см - Атласная лента</t>
+          <t>51 Белая роза - 60 см</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2600</v>
-      </c>
-      <c r="C160" t="inlineStr"/>
+        <v>11990</v>
+      </c>
+      <c r="C160" t="n">
+        <v>15000</v>
+      </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3139-3366-4939-b436-663865363839/29E30EE9-B8EB-4CCD-8.JPG</t>
+          <t>https://static.tildacdn.com/stor3064-6130-4531-a664-653536653139/42234229.jpg</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-602559582111-15-krasnih-roz?editionuid=205666183652</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-511893198801-51-belaya-roza?editionuid=631123744291</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>51 красно-белая роза в оформлении - 60 см</t>
+          <t>101 красно-белая роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>11990</v>
-      </c>
-      <c r="C161" t="n">
-        <v>12999</v>
-      </c>
+        <v>24590</v>
+      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3435-4432-a332-373732306661/48855206.jpg</t>
+          <t>https://static.tildacdn.com/stor3831-3066-4439-b961-663663623165/29975434.jpg</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-542827273651-51-krasno-belaya-roza-v-oformlenii?editionuid=516167563281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=478488702861</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>51 Белая роза - 60 см</t>
+          <t>101 красно-белая роза - 60 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>11990</v>
-      </c>
-      <c r="C162" t="n">
-        <v>15000</v>
-      </c>
+        <v>24990</v>
+      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6130-4531-a664-653536653139/42234229.jpg</t>
+          <t>https://static.tildacdn.com/stor6362-3662-4063-a164-636263353730/41852469.jpg</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-511893198801-51-belaya-roza?editionuid=631123744291</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=658675482971</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>101 красно-белая роза - 60 см - Атласная лента</t>
+          <t>25 малиновых роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>24590</v>
-      </c>
-      <c r="C163" t="inlineStr"/>
+        <v>6800</v>
+      </c>
+      <c r="C163" t="n">
+        <v>7800</v>
+      </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3831-3066-4439-b961-663663623165/29975434.jpg</t>
+          <t>https://static.tildacdn.com/stor3736-6232-4930-b438-303165643933/38373375.jpg</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=478488702861</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-472980179331-25-malinovih-roz-v-oformlenii?editionuid=120293941621</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>101 красно-белая роза - 60 см - Матовая бумага</t>
+          <t>25 красно-белых роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>24990</v>
-      </c>
-      <c r="C164" t="inlineStr"/>
+        <v>6800</v>
+      </c>
+      <c r="C164" t="n">
+        <v>7800</v>
+      </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6362-3662-4063-a164-636263353730/41852469.jpg</t>
+          <t>https://static.tildacdn.com/stor3964-6438-4238-a635-313134306536/28552846.jpg</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-461595881361-101-krasno-belaya-roza?editionuid=658675482971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-710052950101-25-krasno-belih-roz-v-oformlenii?editionuid=111716594231</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>25 малиновых роз в оформлении - 60 см</t>
+          <t>21 красная роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>6800</v>
+        <v>5600</v>
       </c>
       <c r="C165" t="n">
         <v>7800</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3736-6232-4930-b438-303165643933/38373375.jpg</t>
+          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-472980179331-25-malinovih-roz-v-oformlenii?editionuid=120293941621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=679979674191</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>25 красно-белых роз в оформлении - 60 см</t>
+          <t>21 красная роза - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>6800</v>
+        <v>3500</v>
       </c>
       <c r="C166" t="n">
-        <v>7800</v>
+        <v>6300</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3964-6438-4238-a635-313134306536/28552846.jpg</t>
+          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-710052950101-25-krasno-belih-roz-v-oformlenii?editionuid=111716594231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=688291434032</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>21 красная роза - 60 см - Атласная лента</t>
+          <t>15 Розовых роз Премиум в упаковке - 60 см</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>5600</v>
+        <v>4300</v>
       </c>
       <c r="C167" t="n">
-        <v>7800</v>
+        <v>5700</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
+          <t>https://static.tildacdn.com/stor3562-6666-4866-a631-386530363233/69119634.jpg</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=679979674191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>21 красная роза - 45 см - Атласная лента</t>
+          <t>151 роза в корзине - 60 см</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>3500</v>
+        <v>33540</v>
       </c>
       <c r="C168" t="n">
-        <v>6300</v>
+        <v>49000</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3436-6234-4437-b364-656135353762/9186860A-309D-45B2-A.JPG</t>
+          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-264521907571-21-krasnaya-roza?editionuid=688291434032</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>15 Розовых роз Премиум в упаковке - 60 см</t>
+          <t>51 роза микс в крафте - 60 см</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C169" t="n">
-        <v>5700</v>
-      </c>
+        <v>12990</v>
+      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3562-6666-4866-a631-386530363233/69119634.jpg</t>
+          <t>https://static.tildacdn.com/tild6136-3162-4138-b562-653731633664/FullSizeRender_4.jpg</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-873229231971-15-rozovih-roz-premium-v-upakovke?editionuid=530062772641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>151 роза в корзине - 60 см</t>
+          <t>25 красных роз с оформлением - 45 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>45500</v>
-      </c>
-      <c r="C170" t="n">
-        <v>49000</v>
-      </c>
+        <v>4300</v>
+      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
+          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=488917405081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>151 роза в корзине - 45 см</t>
+          <t>25 красных роз с оформлением - 60 см - Матовая бумага</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>18990</v>
-      </c>
-      <c r="C171" t="n">
-        <v>39000</v>
-      </c>
+        <v>7800</v>
+      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6165-3739-4434-a665-333030326661/FB82831F-C808-44E7-9.JPG</t>
+          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-445760300561-151-roza-v-korzine?editionuid=502662350182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>51 роза микс в крафте - 60 см</t>
+          <t>301 роза в корзине</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>12990</v>
+        <v>34890</v>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6136-3162-4138-b562-653731633664/FullSizeRender_4.jpg</t>
+          <t>https://static.tildacdn.com/stor3264-6537-4661-a466-656139376438/97863263.jpg</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-967517048271-51-roza-miks-v-krafte?editionuid=514113565101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>25 красных роз с оформлением - 45 см - Матовая бумага</t>
+          <t>11 красных роз в крафте - 60 см</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>4300</v>
+        <v>3600</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=337910530012</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>25 красных роз с оформлением - 60 см - Матовая бумага</t>
+          <t>11 красных роз в крафте - 45 см</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7800</v>
+        <v>2200</v>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-3630-4532-b162-663934303666/14539145.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408230011221-25-krasnih-roz-s-oformleniem?editionuid=487855233192</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>301 роза в корзине - 60 см</t>
+          <t>15 красных роз в оформлении - 60 см</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>60900</v>
+        <v>4800</v>
       </c>
       <c r="C175" t="n">
-        <v>65500</v>
+        <v>5900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=223226228751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>301 роза в корзине - 45 см</t>
+          <t>15 красных роз в оформлении - 45 см</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>32500</v>
-      </c>
-      <c r="C176" t="inlineStr"/>
+        <v>2350</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3500</v>
+      </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6264-3131-4432-b439-646133646133/FullSizeRender_15.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-497806958801-301-roza-v-korzine?editionuid=629056511182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>11 красных роз в крафте - 60 см</t>
+          <t>25 кремовых роз в упаковке - 60 см</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>3600</v>
+        <v>6800</v>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3437-4165-b166-393339663536/27441782.jpg</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=402736727631</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>11 красных роз в крафте - 45 см</t>
+          <t>Букет КЛАССИКА с красными розами и хризантемами</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2200</v>
+        <v>3350</v>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3131-4534-b835-626436616161/69433641.jpg</t>
+          <t>https://static.tildacdn.com/stor6362-3466-4262-b537-646161643436/11667921.jpg</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759057751351-11-krasnih-roz-v-krafte?editionuid=249699223652</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>15 красных роз в оформлении - 60 см</t>
+          <t>25 красных роз в крафте - 60 см</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>4800</v>
-      </c>
-      <c r="C179" t="n">
-        <v>5900</v>
-      </c>
+        <v>7800</v>
+      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=535172836301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>15 красных роз в оформлении - 45 см</t>
+          <t>25 красных роз в крафте - 45 см</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>2350</v>
-      </c>
-      <c r="C180" t="n">
-        <v>3500</v>
-      </c>
+        <v>4300</v>
+      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-6136-4337-b266-643035643563/47190425.jpg</t>
+          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-714746659301-15-krasnih-roz-v-oformlenii?editionuid=807893800812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>25 кремовых роз в упаковке - 60 см</t>
+          <t>101 красная роза - 60 см - Атласная лента</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C181" t="inlineStr"/>
+        <v>24590</v>
+      </c>
+      <c r="C181" t="n">
+        <v>35500</v>
+      </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3437-4165-b166-393339663536/27441782.jpg</t>
+          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-633761680771-25-kremovih-roz-v-upakovke?editionuid=166403618581</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Букет КЛАССИКА с красными розами и хризантемами</t>
+          <t>101 красная роза - 60 см - Матова бумага</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>3350</v>
-      </c>
-      <c r="C182" t="inlineStr"/>
+        <v>24990</v>
+      </c>
+      <c r="C182" t="n">
+        <v>35500</v>
+      </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6362-3466-4262-b537-646161643436/11667921.jpg</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-759586080041-buket-klassika-s-krasnimi-rozami-i-hriza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>25 красных роз в крафте - 60 см</t>
+          <t>101 красная роза - 45 см - Атласная лента</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C183" t="inlineStr"/>
+        <v>12250</v>
+      </c>
+      <c r="C183" t="n">
+        <v>15300</v>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
+          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=757664759951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>25 красных роз в крафте - 45 см</t>
+          <t>101 красная роза - 45 см - Матова бумага</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C184" t="inlineStr"/>
+        <v>12550</v>
+      </c>
+      <c r="C184" t="n">
+        <v>15500</v>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3237-6636-4231-b662-303234643233/FullSizeRender.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-273635666921-25-krasnih-roz-v-krafte?editionuid=654345431912</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Атласная лента</t>
+          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>24590</v>
-      </c>
-      <c r="C185" t="n">
-        <v>35500</v>
-      </c>
+        <v>4600</v>
+      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6361-6636-4266-b062-353966373435/4BC02103-219A-4F95-B.JPG</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=394239337111</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>101 красная роза - 60 см - Матова бумага</t>
+          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>24990</v>
-      </c>
-      <c r="C186" t="n">
-        <v>35500</v>
-      </c>
+        <v>4600</v>
+      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=427549884841</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Атласная лента</t>
+          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>12250</v>
-      </c>
-      <c r="C187" t="n">
-        <v>15300</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3865-3331-4230-b632-303034313365/14531374.jpg</t>
+          <t>https://static.tildacdn.com/stor3465-6137-4339-a635-626237396331/61031457.jpg</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=969262113402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>101 красная роза - 45 см - Матова бумага</t>
+          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>12550</v>
-      </c>
-      <c r="C188" t="n">
-        <v>15500</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3162-4833-b438-613736306365/81439031.jpg</t>
+          <t>https://static.tildacdn.com/stor3465-6137-4339-a635-626237396331/61031457.jpg</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-424784503001-101-krasnaya-roza?editionuid=904803933062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>4600</v>
+        <v>8100</v>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
@@ -4583,81 +4575,81 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=948128002611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 11 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>4600</v>
+        <v>8100</v>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3565-3661-4465-b530-353638393762/21409363.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=786174189071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>6000</v>
+        <v>9500</v>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3465-6137-4339-a635-626237396331/61031457.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=187164980561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 15 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>6000</v>
+        <v>9500</v>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3465-6137-4339-a635-626237396331/61031457.jpg</t>
+          <t>https://static.tildacdn.com/stor6134-6663-4264-b937-613539323531/96969308.jpg</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=764558635881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>8100</v>
+        <v>11600</v>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
@@ -4667,18 +4659,18 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=750789294071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 21 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>8100</v>
+        <v>11600</v>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
@@ -4688,39 +4680,39 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=620664939261</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>9500</v>
+        <v>12300</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=755779056751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 25 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>9500</v>
+        <v>12300</v>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
@@ -4730,18 +4722,18 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=246611373241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>11600</v>
+        <v>18600</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
@@ -4751,18 +4743,18 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=739836024611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 31 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>11600</v>
+        <v>18600</v>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
@@ -4772,188 +4764,188 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=743147164201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Крафт-бумага</t>
+          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>12300</v>
+        <v>3200</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3761-3762-4064-b230-666433636133/68638297.jpg</t>
+          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=498886075481</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 35 - Матовая бумага</t>
+          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>12300</v>
+        <v>3900</v>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6134-6663-4264-b937-613539323531/96969308.jpg</t>
+          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=463622792911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Крафт-бумага</t>
+          <t>15 красно белых роз в оформлении</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>18600</v>
-      </c>
-      <c r="C201" t="inlineStr"/>
+        <v>4300</v>
+      </c>
+      <c r="C201" t="n">
+        <v>6800</v>
+      </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=984611990561</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 51 - Матовая бумага</t>
+          <t>Raffaello</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>18600</v>
+        <v>690</v>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=909075165191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 7 - Матовая бумага</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3633-3137-4561-b762-356630333665/15001281.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=470941710541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Охапка кустовых роз - 9 - Матовая бумага</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3736-6561-4338-a665-666566623439/43052787.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-677638530321-ohapka-kustovih-roz?editionuid=856962373961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>15 красно белых роз в оформлении</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C205" t="n">
-        <v>6800</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3066-6233-4161-b631-633830386163/28152392.jpg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-218567021051-15-krasno-belih-roz-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Raffaello</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>690</v>
+        <v>1800</v>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3639-3232-4663-a539-333335383439/aba7d219_0f07_11e6_9.jpeg</t>
+          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-608860089361-raffaello</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 15</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
@@ -4963,18 +4955,18 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=236585268671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 19</t>
+          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>3800</v>
+        <v>1000</v>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
@@ -4984,102 +4976,102 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=258112848201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 25</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=865174930451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 9</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1800</v>
+        <v>3800</v>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=639207534271</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 7</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1400</v>
+        <v>5000</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=772143984511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров микс (12 дюймов) - 5</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1000</v>
+        <v>6200</v>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3238-6338-4631-b665-356537616432/6057122972.jpg</t>
+          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-970929032081-nabor-iz-gelievih-sharov-miks-12-dyuimov?editionuid=955820451821</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 15</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
@@ -5089,18 +5081,18 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=639540432131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 19</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>3800</v>
+        <v>1800</v>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
@@ -5110,18 +5102,18 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=419475097251</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 25</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
@@ -5131,18 +5123,18 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=822323827341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 31</t>
+          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>6200</v>
+        <v>1000</v>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
@@ -5152,102 +5144,102 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=502425687241</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 35</t>
+          <t>Набор из гелиевых шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>7000</v>
+        <v>3750</v>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=930713156991</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 9</t>
+          <t>Набор из гелиевых шаров "Сердце" - 19</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1800</v>
+        <v>4750</v>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=303371552921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 7</t>
+          <t>Набор из гелиевых шаров "Сердце" - 25</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1400</v>
+        <v>6350</v>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=577795209061</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "С днем рождения" - 5</t>
+          <t>Набор из гелиевых шаров "Сердце" - 31</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1000</v>
+        <v>7750</v>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6266-3132-4632-b235-333537353730/81400.jpg</t>
+          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926611977411-nabor-iz-gelievih-sharov-s-dnem-rozhdeni?editionuid=345438213191</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 15</t>
+          <t>Набор из гелиевых шаров "Сердце" - 35</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>3750</v>
+        <v>8750</v>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
@@ -5257,18 +5249,18 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=619806166751</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 19</t>
+          <t>Набор из гелиевых шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>4750</v>
+        <v>2250</v>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
@@ -5278,18 +5270,18 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=586128610851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 25</t>
+          <t>Набор из гелиевых шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>6350</v>
+        <v>1750</v>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
@@ -5299,18 +5291,18 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=161077505461</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 31</t>
+          <t>Набор из гелиевых шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>7750</v>
+        <v>1250</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
@@ -5320,18 +5312,18 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=792649891401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 35</t>
+          <t>Набор из гелиевых шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>8750</v>
+        <v>2750</v>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
@@ -5341,102 +5333,102 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=453147256301</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 9</t>
+          <t>Набор из фольгированных шаров "Сердце" - 15</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>2250</v>
+        <v>6750</v>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=877347966041</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 7</t>
+          <t>Набор из фольгированных шаров "Сердце" - 11</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1750</v>
+        <v>4950</v>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=278948808541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 5</t>
+          <t>Набор из фольгированных шаров "Сердце" - 9</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1250</v>
+        <v>4050</v>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=718188030721</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Набор из гелиевых шаров "Сердце" - 11</t>
+          <t>Набор из фольгированных шаров "Сердце" - 7</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2750</v>
+        <v>3150</v>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6665-3432-4339-a462-366437636230/15-serd.jpg</t>
+          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-926561766701-nabor-iz-gelievih-sharov-serdtse?editionuid=427414692941</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 15</t>
+          <t>Набор из фольгированных шаров "Сердце" - 5</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>6750</v>
+        <v>2250</v>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
@@ -5446,105 +5438,113 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=302095014001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 11</t>
+          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>4950</v>
-      </c>
-      <c r="C231" t="inlineStr"/>
+        <v>4500</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4500</v>
+      </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=609360827851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 9</t>
+          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>4050</v>
-      </c>
-      <c r="C232" t="inlineStr"/>
+        <v>6100</v>
+      </c>
+      <c r="C232" t="n">
+        <v>6100</v>
+      </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=339334493231</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 7</t>
+          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>3150</v>
-      </c>
-      <c r="C233" t="inlineStr"/>
+        <v>8500</v>
+      </c>
+      <c r="C233" t="n">
+        <v>8500</v>
+      </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=760697469671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Набор из фольгированных шаров "Сердце" - 5</t>
+          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2250</v>
-      </c>
-      <c r="C234" t="inlineStr"/>
+        <v>10100</v>
+      </c>
+      <c r="C234" t="n">
+        <v>10100</v>
+      </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6231-6564-4361-a166-333639636632/5cf673570fff81aae50b.jpg</t>
+          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-717193108191-nabor-iz-folgirovannih-sharov-serdtse?editionuid=312398033811</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 11 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>4500</v>
+        <v>14100</v>
       </c>
       <c r="C235" t="n">
-        <v>4500</v>
+        <v>14100</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -5553,22 +5553,20 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=173933309341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 15 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>6100</v>
-      </c>
-      <c r="C236" t="n">
-        <v>6100</v>
-      </c>
+        <v>3700</v>
+      </c>
+      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5576,22 +5574,20 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=716637850171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 21 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>8500</v>
-      </c>
-      <c r="C237" t="n">
-        <v>8500</v>
-      </c>
+        <v>2900</v>
+      </c>
+      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
@@ -5599,21 +5595,21 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=924932493761</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 25 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>10100</v>
+        <v>17950</v>
       </c>
       <c r="C238" t="n">
-        <v>10100</v>
+        <v>18690</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -5622,21 +5618,21 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=491246820001</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 35 - Атласная лента</t>
+          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>14100</v>
+        <v>35450</v>
       </c>
       <c r="C239" t="n">
-        <v>14100</v>
+        <v>38690</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -5645,129 +5641,125 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=295847790471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 9 - Атласная лента</t>
+          <t>Стильный букет в крафтовой сумочке</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>3700</v>
-      </c>
-      <c r="C240" t="inlineStr"/>
+        <v>5150</v>
+      </c>
+      <c r="C240" t="n">
+        <v>5200</v>
+      </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=651331422171</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 7 - Атласная лента</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>2900</v>
+        <v>5040</v>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=111618763131</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 51 - Атласная лента</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>17950</v>
-      </c>
-      <c r="C242" t="n">
-        <v>18690</v>
-      </c>
+        <v>5730</v>
+      </c>
+      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=932669717562</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Метровые розы-гиганты - 101 - Атласная лента</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>35450</v>
-      </c>
-      <c r="C243" t="n">
-        <v>38690</v>
-      </c>
+        <v>6040</v>
+      </c>
+      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3064-3430-4363-b638-393836633966/666.JPG</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-716338094361-metrovie-rozi-giganti?editionuid=920280704782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Стильный букет в крафтовой сумочке</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C244" t="n">
-        <v>5200</v>
-      </c>
+        <v>6040</v>
+      </c>
+      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3031-6134-4631-b837-323638663231/Screenshot_20211203-.jpg</t>
+          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-957375155621-stilnii-buket-v-kraftovoi-sumochke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Посмотреть...</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>5040</v>
+        <v>6290</v>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
@@ -5784,11 +5776,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Raffaello (+690 руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>5730</v>
+        <v>6340</v>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
@@ -5805,11 +5797,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров микс (+1000руб)</t>
+          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>6040</v>
+        <v>10540</v>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
@@ -5826,141 +5818,149 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "ДР" (+1000 руб)</t>
+          <t>ДОРОГУША из красных роз с ромашками</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>6040</v>
-      </c>
-      <c r="C248" t="inlineStr"/>
+        <v>8450</v>
+      </c>
+      <c r="C248" t="n">
+        <v>8500</v>
+      </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Коробка гигант с радужной гипсофилой</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>6290</v>
-      </c>
-      <c r="C249" t="inlineStr"/>
+        <v>8800</v>
+      </c>
+      <c r="C249" t="n">
+        <v>10990</v>
+      </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка-медведь (+1300 руб)</t>
+          <t>Букет Малиновое вино - Посмотреть...</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>6340</v>
-      </c>
-      <c r="C250" t="inlineStr"/>
+        <v>4920</v>
+      </c>
+      <c r="C250" t="n">
+        <v>5200</v>
+      </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЕДИ из хризантем и орхидей - Игрушка мишка 110см (+5500руб)</t>
+          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>10540</v>
-      </c>
-      <c r="C251" t="inlineStr"/>
+        <v>5610</v>
+      </c>
+      <c r="C251" t="n">
+        <v>5200</v>
+      </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3533-3366-4163-b764-333731313433/21856218.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-647668517821-buket-pervaya-ledi-iz-hrizantem-i-orhide</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ДОРОГУША из красных роз с ромашками</t>
+          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>8450</v>
+        <v>5920</v>
       </c>
       <c r="C252" t="n">
-        <v>8500</v>
+        <v>5200</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6333-3666-4836-a665-383364326136/22998316.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-441113290851-dorogusha-iz-krasnih-roz-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Коробка гигант с радужной гипсофилой</t>
+          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>9999</v>
+        <v>5920</v>
       </c>
       <c r="C253" t="n">
-        <v>10990</v>
+        <v>5200</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3833-6237-4338-a666-383235363466/62993953.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-142634004681-korobka-gigant-s-raduzhnoi-gipsofiloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Посмотреть...</t>
+          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>4920</v>
+        <v>6170</v>
       </c>
       <c r="C254" t="n">
         <v>5200</v>
@@ -5979,11 +5979,11 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Raffaello (+690 руб)</t>
+          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>5610</v>
+        <v>6220</v>
       </c>
       <c r="C255" t="n">
         <v>5200</v>
@@ -6002,11 +6002,11 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров микс (+1000руб)</t>
+          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>5920</v>
+        <v>10420</v>
       </c>
       <c r="C256" t="n">
         <v>5200</v>
@@ -6025,103 +6025,103 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "ДР" (+1000 руб)</t>
+          <t>11альстромерий в оформлении - Посмотреть...</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>5920</v>
+        <v>2500</v>
       </c>
       <c r="C257" t="n">
-        <v>5200</v>
+        <v>2380</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>6170</v>
+        <v>3190</v>
       </c>
       <c r="C258" t="n">
-        <v>5200</v>
+        <v>2380</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка-медведь (+1300 руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>6220</v>
+        <v>3500</v>
       </c>
       <c r="C259" t="n">
-        <v>5200</v>
+        <v>2380</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Букет Малиновое вино - Игрушка мишка 110см (+5500руб)</t>
+          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>10420</v>
+        <v>3500</v>
       </c>
       <c r="C260" t="n">
-        <v>5200</v>
+        <v>2380</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3133-4539-a666-346234366262/58274540.jpg</t>
+          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-242751418301-buket-malinovoe-vino</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Посмотреть...</t>
+          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>2500</v>
+        <v>3750</v>
       </c>
       <c r="C261" t="n">
         <v>2380</v>
@@ -6140,11 +6140,11 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Raffaello (+690 руб)</t>
+          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>3190</v>
+        <v>3800</v>
       </c>
       <c r="C262" t="n">
         <v>2380</v>
@@ -6163,11 +6163,11 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров микс (+1000руб)</t>
+          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>3500</v>
+        <v>8000</v>
       </c>
       <c r="C263" t="n">
         <v>2380</v>
@@ -6186,92 +6186,84 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "ДР" (+1000 руб)</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C264" t="n">
-        <v>2380</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - 5 шаров "сердце" (+ 1250руб)</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>3750</v>
-      </c>
-      <c r="C265" t="n">
-        <v>2380</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка-медведь (+1300 руб)</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>3800</v>
-      </c>
-      <c r="C266" t="n">
-        <v>2380</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>11альстромерий в оформлении - Игрушка мишка 110см (+5500руб)</t>
+          <t>Шары цифры 100см - 1</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C267" t="n">
-        <v>2380</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6533-6233-4338-b066-333864666262/59764787.jpg</t>
+          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-302423702051-11alstromerii-v-oformlenii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
         </is>
       </c>
     </row>
@@ -6287,12 +6279,12 @@
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3632-3736-4335-a239-383462336437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=513414707421</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
         </is>
       </c>
     </row>
@@ -6308,12 +6300,12 @@
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3935-6530-4935-b033-653438643437/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=245989871161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6321,12 @@
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6433-3662-4432-b566-386563373461/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=926150789031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6342,12 @@
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild6632-3338-4032-b065-343265343134/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=204966492501</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
         </is>
       </c>
     </row>
@@ -6371,12 +6363,12 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3338-3134-4333-b166-383833666533/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=541092160971</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
         </is>
       </c>
     </row>
@@ -6392,514 +6384,512 @@
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3432-3532-4537-b466-636238353865/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=151286241621</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>900</v>
+        <v>3000</v>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3835-3162-4338-b762-626436663661/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=931128225951</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>900</v>
+        <v>3560</v>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3563-6461-4264-a533-653264663135/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=505146431881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>Зефирный - Белые</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>900</v>
+        <v>3300</v>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3862-3836-4164-a161-386166303965/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=693004566791</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Шары цифры 100см - 1</t>
+          <t>Зефирный - Микс</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>900</v>
+        <v>3300</v>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3063-3339-4236-b838-323432633335/Screenshot_20220524-.jpg</t>
+          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-483408073161-shari-tsifri-100sm?editionuid=212065177451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "Куколка" из хризантем с орхидеей</t>
+          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>3000</v>
+        <v>3700</v>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6330-3763-4539-b363-343632303661/20514984.jpg</t>
+          <t>https://static.tildacdn.com/stor3333-6134-4931-b064-626531613738/26831923.jpg</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-332537387381-buket-kompliment-kukolka-iz-hrizantem-s</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Букет НАСТРОЕНИЕ с кустовыми розами и альстромериями</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>3560</v>
+        <v>3700</v>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-3534-4462-b933-376264343737/19089090.jpg</t>
+          <t>https://static.tildacdn.com/stor3161-3631-4130-b561-653330386363/79575723.jpg</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-380119168961-buket-nastroenie-s-kustovimi-rozami-i-al</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Зефирный - Белые</t>
+          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C280" t="n">
-        <v>3500</v>
-      </c>
+        <v>6050</v>
+      </c>
+      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3865-4065-b832-666132396634/62621178.jpg</t>
+          <t>https://static.tildacdn.com/stor3161-3631-4130-b561-653330386363/79575723.jpg</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=323569405822</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Зефирный - Микс</t>
+          <t>Букет МАГНОЛИЯ</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C281" t="n">
-        <v>3500</v>
-      </c>
+        <v>5420</v>
+      </c>
+      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3265-6265-4531-a138-356639393637/87868104.jpg</t>
+          <t>https://static.tildacdn.com/stor3365-6335-4433-b938-333931306239/10745399.jpg</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-997928842911-zefirnii?editionuid=978085575362</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-buket-magnoliya</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ФРАНЦУЗСКИЙ ХИТ из ажурных роз</t>
+          <t>Игрушка МИШАНЯ</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>3700</v>
+        <v>4500</v>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3333-6134-4931-b064-626531613738/26831923.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6436-4538-b130-383238323638/76577859.jpg</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-283093013351-frantsuzskii-hit-iz-azhurnih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-mishanya</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - M</t>
+          <t>Игрушка Мякий медведь Мишаня</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3161-3631-4130-b561-653330386363/79575723.jpg</t>
+          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=767108929642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Комплимент "ГЛАМУР " из маттиолы - L</t>
+          <t>Игрушкп Зайка милашка</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>6050</v>
+        <v>1100</v>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3161-3631-4130-b561-653330386363/79575723.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-955871926561-kompliment-glamur-iz-mattioli?editionuid=754884276952</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Букет МАГНОЛИЯ</t>
+          <t>Букет Солнечный из хризантем</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>5420</v>
+        <v>3250</v>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3365-6335-4433-b938-333931306239/10745399.jpg</t>
+          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-766984785531-buket-magnoliya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Игрушка МИШАНЯ</t>
+          <t>LOVE IS....из кустовых роз с ромашками</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>4500</v>
+        <v>10990</v>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6436-4538-b130-383238323638/76577859.jpg</t>
+          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-721499980101-igrushka-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Игрушка Мякий медведь Мишаня</t>
+          <t>Букет КАПРИЗ</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>3500</v>
+        <v>3540</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3039-6138-4161-b666-373034636636/35372297.jpg</t>
+          <t>https://static.tildacdn.com/stor3966-3332-4534-a338-393735383465/63784469.jpg</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-778767705501-igrushka-myakii-medved-mishanya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-202799168931-buket-kapriz</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Игрушкп Зайка милашка</t>
+          <t>Букет РАДУЖНЫЙ ЛАЙФ</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C288" t="inlineStr"/>
+        <v>3450</v>
+      </c>
+      <c r="C288" t="n">
+        <v>3900</v>
+      </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-3132-4531-b365-363630366634/25068525.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-3530-4432-b861-626238636636/49194836.jpg</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594044496021-igrushkp-zaika-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-raduzhnii-laif</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Букет Солнечный из хризантем</t>
+          <t>Букет Красотуля с орхидеями</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>3250</v>
+        <v>4250</v>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3939-6135-4863-b537-333262333264/16847685.jpg</t>
+          <t>https://static.tildacdn.com/stor3931-3734-4437-a234-313232633735/93320832.jpg</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-638070352371-buket-solnechnii-iz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>LOVE IS....из кустовых роз с ромашками</t>
+          <t>25 белых роз с эвкалиптом</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>10990</v>
-      </c>
-      <c r="C290" t="inlineStr"/>
+        <v>8500</v>
+      </c>
+      <c r="C290" t="n">
+        <v>9750</v>
+      </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6334-3962-4663-b339-356435346562/91779203.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-499203730941-love-isiz-kustovih-roz-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Букет КАПРИЗ</t>
+          <t>Букет орхидей БАБОЧКА</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>3540</v>
-      </c>
-      <c r="C291" t="inlineStr"/>
+        <v>4200</v>
+      </c>
+      <c r="C291" t="n">
+        <v>4300</v>
+      </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3966-3332-4534-a338-393735383465/63784469.jpg</t>
+          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-202799168931-buket-kapriz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Букет РАДУЖНЫЙ ЛАЙФ</t>
+          <t>Букет "Сердце" из роз - 51 - Красный</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>3450</v>
-      </c>
-      <c r="C292" t="n">
-        <v>3900</v>
-      </c>
+        <v>13200</v>
+      </c>
+      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-3530-4432-b861-626238636636/49194836.jpg</t>
+          <t>https://static.tildacdn.com/stor3265-6563-4066-b333-623131303566/86344649.jpg</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-728832612721-buket-raduzhnii-laif</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=596862368331</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>БУКЕТ "ЛЮБЛЮ" из пион роз с ромашками -</t>
+          <t>Букет "Сердце" из роз - 35 - Красный</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>15950</v>
-      </c>
-      <c r="C293" t="n">
-        <v>175550</v>
-      </c>
+        <v>9300</v>
+      </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6536-3637-4863-a130-623137613739/27964095.jpg</t>
+          <t>https://static.tildacdn.com/stor3730-3736-4134-a134-623235356232/75639760.jpg</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-594449693621-buket-lyublyu-iz-pion-roz-s-romashkami?editionuid=990271714812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=420576792261</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Букет Красотуля с орхидеями</t>
+          <t>Букет "Сердце" из роз - 51 - Белые</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>4250</v>
+        <v>13200</v>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3734-4437-a234-313232633735/93320832.jpg</t>
+          <t>https://static.tildacdn.com/stor6332-3761-4964-b337-633939613039/40797598.jpg</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-619538785821-buket-krasotulya-s-orhideyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=384773199531</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>25 белых роз с эвкалиптом</t>
+          <t>Букет "Сердце" из роз - 35 - Белые</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>7800</v>
+        <v>9300</v>
       </c>
       <c r="C295" t="n">
-        <v>9750</v>
+        <v>11500</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-6132-4064-a332-316230306131/91575755.jpg</t>
+          <t>https://static.tildacdn.com/stor6332-3761-4964-b337-633939613039/40797598.jpg</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-624506536881-25-belih-roz-s-evkaliptom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=310959153071</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Букет орхидей БАБОЧКА</t>
+          <t>Букет "Сердце" из роз - 51 - Пионовидные крем</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>4200</v>
+        <v>15500</v>
       </c>
       <c r="C296" t="n">
-        <v>4300</v>
+        <v>16500</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3834-6334-4363-b333-613363393661/14233072.jpg</t>
+          <t>https://static.tildacdn.com/stor6135-3363-4562-b462-396239336435/10956098.jpg</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-229561542201-buket-orhidei-babochka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=419923721431</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Букет "Сердце" из роз - 51 - Красный</t>
+          <t>Букет "Сердце" из роз - 51 - Нежные</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -6908,1131 +6898,1127 @@
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3265-6563-4066-b333-623131303566/86344649.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3433-4738-b166-646364353731/26315844.jpg</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=596862368331</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=131250231871</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Букет "Сердце" из роз - 35 - Красный</t>
+          <t>Букет "Сердце" из роз - 51 - Микс</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>9300</v>
-      </c>
-      <c r="C298" t="inlineStr"/>
+        <v>13200</v>
+      </c>
+      <c r="C298" t="n">
+        <v>14500</v>
+      </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3730-3736-4134-a134-623235356232/75639760.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-3936-4262-b064-303838613332/48226272.jpg</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=420576792261</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=197174543341</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Букет "Сердце" из роз - 51 - Белые</t>
+          <t>Букет "Сердце" из роз - 35 - Микс</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>13200</v>
+        <v>9300</v>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6332-3761-4964-b337-633939613039/40797598.jpg</t>
+          <t>https://static.tildacdn.com/stor6166-3936-4262-b064-303838613332/48226272.jpg</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=384773199531</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=168510316671</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Букет "Сердце" из роз - 35 - Белые</t>
+          <t>Букет "Сердце" из роз - 35 - Нежные</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>9300</v>
-      </c>
-      <c r="C300" t="n">
-        <v>11500</v>
-      </c>
+        <v>9200</v>
+      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6332-3761-4964-b337-633939613039/40797598.jpg</t>
+          <t>https://static.tildacdn.com/stor3730-3532-4662-b161-323433393562/67841903.jpg</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=310959153071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=356370001431</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Букет "Сердце" из роз - 51 - Пионовидные крем</t>
+          <t>Букет КОМПЛИМЕНТ АССОРТИ</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>15500</v>
-      </c>
-      <c r="C301" t="n">
-        <v>16500</v>
-      </c>
+        <v>2600</v>
+      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6135-3363-4562-b462-396239336435/10956098.jpg</t>
+          <t>https://static.tildacdn.com/stor3765-3434-4365-b737-666431333536/57090603.jpg</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=419923721431</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-169103768201-buket-kompliment-assorti</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Букет "Сердце" из роз - 51 - Нежные</t>
+          <t>Букет ромашек "Модный"</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>13200</v>
-      </c>
-      <c r="C302" t="inlineStr"/>
+        <v>2700</v>
+      </c>
+      <c r="C302" t="n">
+        <v>3200</v>
+      </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3433-4738-b166-646364353731/26315844.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=131250231871</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Букет "Сердце" из роз - 51 - Микс</t>
+          <t>Букет ЛАЙК с красными розами</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>13200</v>
-      </c>
-      <c r="C303" t="n">
-        <v>14500</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-3936-4262-b064-303838613332/48226272.jpg</t>
+          <t>https://static.tildacdn.com/stor3534-3438-4762-a236-656639623635/85107167.jpg</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=197174543341</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Букет "Сердце" из роз - 35 - Микс</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>9300</v>
+        <v>3350</v>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6166-3936-4262-b064-303838613332/48226272.jpg</t>
+          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=168510316671</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Букет "Сердце" из роз - 35 - Нежные</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>9200</v>
+        <v>4150</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3730-3532-4662-b161-323433393562/67841903.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-476287490581-buket-serdtse-iz-roz?editionuid=356370001431</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Букет КОМПЛИМЕНТ АССОРТИ</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>2600</v>
+        <v>4950</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3765-3434-4365-b737-666431333536/57090603.jpg</t>
+          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-169103768201-buket-kompliment-assorti</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Букет ромашек "Модный"</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>2700</v>
-      </c>
-      <c r="C307" t="n">
-        <v>3200</v>
-      </c>
+        <v>6550</v>
+      </c>
+      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3832-4565-b737-636232616363/96239568.jpg</t>
+          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-966890057501-buket-romashek-modnii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Букет ЛАЙК с красными розами</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>3500</v>
+        <v>9500</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3534-3438-4762-a236-656639623635/85107167.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-271548446971-buket-laik-s-krasnimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 7 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>3350</v>
+        <v>12850</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6431-3361-4431-b434-346262633764/67610820.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=685412047851</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 9 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>4150</v>
+        <v>17590</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3261-4731-b234-386337616532/43856125.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=747300906151</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 11 - Матовая бумага</t>
+          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>4950</v>
+        <v>33990</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6436-3239-4132-b137-306231333036/58018420.jpg</t>
+          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=112918374101</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 15 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>6550</v>
+        <v>7290</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3764-3935-4162-b661-326239363839/24782806.jpg</t>
+          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=584191326611</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 25 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>9500</v>
+        <v>9940</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3430-4766-b836-313464656162/12162191.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=409857313401</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 35 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>12850</v>
+        <v>14180</v>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6633-4938-b362-393762646662/67653659.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=447172835881</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 51 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>17590</v>
+        <v>27430</v>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=499742739092</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ПИОН РОЗЫ КЕНДИЛАЙТ с роскошным бутоном - 101 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>33990</v>
+        <v>3580</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3065-3436-4637-a539-326138303462/27922432.jpg</t>
+          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-408842247631-pion-rozi-kendilait-s-roskoshnim-butonom?editionuid=490529641782</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 25 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>7290</v>
+        <v>4640</v>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3235-6463-4134-b838-643065393437/42874590.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=144808655921</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 35 - Матовая бумага</t>
+          <t>Микс "Нежный " из кустовых роз с альстромериями - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>9940</v>
+        <v>3050</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=682095661901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=972782492442</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 51 - Матовая бумага</t>
+          <t>Букет Белый шоколад из белых роз</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>14180</v>
-      </c>
-      <c r="C319" t="inlineStr"/>
+        <v>5900</v>
+      </c>
+      <c r="C319" t="n">
+        <v>5900</v>
+      </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-3565-4330-a533-343835336231/19693626.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=818421126901</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 101 - Матовая бумага</t>
+          <t>Комплимент ВАНИЛЬ с ромашками</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>27430</v>
+        <v>2900</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3537-6464-4265-a237-376565623661/67652712.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=339758706201</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 11 - Матовая бумага</t>
+          <t>Коробка с кустовыми розами микс</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>3580</v>
+        <v>4100</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6230-3539-4562-b538-353434303535/33043186.jpg</t>
+          <t>https://static.tildacdn.com/stor3461-3061-4533-a361-306563366164/19857974.jpg</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=231105875691</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami-miks</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 15 - Матовая бумага</t>
+          <t>Дивная Орхидея</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>4640</v>
+        <v>5450</v>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
+          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=759439311541</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Микс "Нежный " из кустовых роз с альстромериями - 9 - Матовая бумага</t>
+          <t>Коробка "Орхидея "</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>3050</v>
+        <v>5160</v>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6162-6638-4265-a134-666564346264/85360901.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-969675948161-miks-nezhnii-iz-kustovih-roz-s-alstromer?editionuid=972782492442</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Букет Белый шоколад из белых роз</t>
+          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>5900</v>
-      </c>
-      <c r="C324" t="n">
-        <v>5900</v>
-      </c>
+        <v>7320</v>
+      </c>
+      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6333-4436-b830-636438386630/21485586.jpg</t>
+          <t>https://static.tildacdn.com/stor3531-6538-4838-b665-353662303035/42686584.jpg</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-604610293441-buket-belii-shokolad-iz-belih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Комплимент ВАНИЛЬ с ромашками</t>
+          <t>Розовый дым</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>2900</v>
+        <v>13090</v>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3566-4639-b964-323030333165/90202533.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-355408923071-kompliment-vanil-s-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Коробка с кустовыми розами</t>
+          <t>Букет Комплимент ПУШ с хризантемами - M</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>3500</v>
+        <v>1950</v>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3461-3061-4533-a361-306563366164/19857974.jpg</t>
+          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-190380899281-korobka-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Дивная Орхидея</t>
+          <t>Букет Комплимент ПУШ с хризантемами - L</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>5450</v>
+        <v>2450</v>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6631-3961-4166-a236-343666333130/79650328.jpg</t>
+          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-399495570211-divnaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Коробка "Орхидея "</t>
+          <t>Букет Комплимент МАРМЕЛАД</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>5700</v>
+        <v>2680</v>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3062-4739-a365-633930663962/93446831.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-909950155641-korobka-orhideya-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Букет КРИСТАЛЛ из красных роз и белых орхидей</t>
+          <t>Шикарная корзина с кустовыми розами</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>7320</v>
-      </c>
-      <c r="C329" t="inlineStr"/>
+        <v>21100</v>
+      </c>
+      <c r="C329" t="n">
+        <v>21500</v>
+      </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3531-6538-4838-b665-353662303035/42686584.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-3135-4165-b161-393937653763/76895073.jpg</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-516964640791-buket-kristall-iz-krasnih-roz-i-belih-or</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Розовый дым</t>
+          <t>Коробка с орхидеями и кустовыми розами</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>13500</v>
-      </c>
-      <c r="C330" t="inlineStr"/>
+        <v>6350</v>
+      </c>
+      <c r="C330" t="n">
+        <v>6900</v>
+      </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6139-4462-b233-336561353864/89607982.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-3837-4130-b565-316434363939/31198124.jpg</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-802553109081-rozovii-dim</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-665629263531-korobka-s-orhideyami-i-kustovimi-rozami</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - M</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 3 - Атласная лента</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>1950</v>
+        <v>2450</v>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6130-3238-4262-a461-356438363462/10580626.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=217256802002</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=807760891511</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Букет Комплимент ПУШ с хризантемами - L</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 5 - Атласная лента</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>2450</v>
+        <v>3850</v>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3166-3461-4061-b836-613539313633/10742640.jpg</t>
+          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-339880785851-buket-kompliment-push-s-hrizantemami?editionuid=989656423962</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=935605880011</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Букет Комплимент МАРМЕЛАД</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 7 - Атласная лента</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>2680</v>
+        <v>5350</v>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3439-4462-b735-636564646463/91567819.jpg</t>
+          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-322995211141-buket-kompliment-marmelad</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=621399533081</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Шикарная корзина с кустовыми розами</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 3 - Матовая бумага</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>20990</v>
-      </c>
-      <c r="C334" t="n">
-        <v>21500</v>
-      </c>
+        <v>2850</v>
+      </c>
+      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-3135-4165-b161-393937653763/76895073.jpg</t>
+          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-329147948761-shikarnaya-korzina-s-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=428830803781</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Коробка с орхидеями и кустовыми розами</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 5 - Матовая бумага</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>4990</v>
-      </c>
-      <c r="C335" t="n">
-        <v>5900</v>
-      </c>
+        <v>4250</v>
+      </c>
+      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-3837-4130-b565-316434363939/31198124.jpg</t>
+          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-665629263531-korobka-s-orhideyami-i-kustovimi-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=507029921911</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 3 - Атласная лента</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 7 - Матовая бумага</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>2450</v>
+        <v>5650</v>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-3863-4464-b164-376561333937/27613053.jpg</t>
+          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=807760891511</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=330876877451</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 5 - Атласная лента</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>3850</v>
+        <v>8050</v>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3232-3234-4665-b932-346439353435/70920808.jpg</t>
+          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=935605880011</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=352141135642</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 7 - Атласная лента</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>5350</v>
+        <v>8450</v>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3266-3865-4235-a261-383438323636/78878017.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=621399533081</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=444544724772</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 3 - Матовая бумага</t>
+          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 15 - Матовая бумага</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>2850</v>
+        <v>11550</v>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3433-3933-4632-b430-363235313034/58463971.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=428830803781</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=810198608332</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 5 - Матовая бумага</t>
+          <t>Букет МИЛАШКА</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>4250</v>
+        <v>3340</v>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6364-6334-4261-a634-336263636434/83026114.jpg</t>
+          <t>https://static.tildacdn.com/stor6135-3161-4637-b761-356232373633/78238867.jpg</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=507029921911</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-milashka</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 7 - Матовая бумага</t>
+          <t>51 кремовая роза</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>5650</v>
+        <v>11590</v>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3534-6531-4138-a363-356333643062/85735675.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3966-4136-b735-386133633035/40006718.jpg</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=330876877451</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-555099133731-51-kremovaya-roza</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 11 - Атласная лента</t>
+          <t>Корзина кустовых роз 1</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>8050</v>
-      </c>
-      <c r="C342" t="inlineStr"/>
+        <v>17050</v>
+      </c>
+      <c r="C342" t="n">
+        <v>17990</v>
+      </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6231-6132-4133-b632-656636393735/40808809.jpg</t>
+          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=352141135642</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 11 - Матовая бумага</t>
+          <t>Ажурные французские розы - 9 - Атласная лента</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>8450</v>
+        <v>3250</v>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=444544724772</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>БУКЕТ АРОМАТНЫХ ЛИЛИЙ - 15 - Матовая бумага</t>
+          <t>Ажурные французские розы - 11 - Атласная лента</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>11550</v>
+        <v>3950</v>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-6236-4438-b538-633738336135/85330738.jpg</t>
+          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-854974054121-buket-aromatnih-lilii?editionuid=810198608332</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Букет МИЛАШКА</t>
+          <t>Ажурные французские розы - 15 - Атласная лента</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>3160</v>
+        <v>5350</v>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6135-3161-4637-b761-356232373633/78238867.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-831554304821-buket-milashka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>51 кремовая роза</t>
+          <t>Ажурные французские розы - 25 - Атласная лента</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>11590</v>
+        <v>8850</v>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3966-4136-b735-386133633035/40006718.jpg</t>
+          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-555099133731-51-kremovaya-roza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Корзина кустовых роз 1</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>17100</v>
-      </c>
-      <c r="C347" t="n">
-        <v>17990</v>
-      </c>
+        <v>12350</v>
+      </c>
+      <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3661-3663-4137-a566-393037623464/36437121.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-626227787071-korzina-kustovih-roz-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Атласная лента</t>
+          <t>Ажурные французские розы - 51 - Атласная лента</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>3250</v>
+        <v>16990</v>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-6461-4233-b234-333431646332/10018467.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=479860460281</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Атласная лента</t>
+          <t>Ажурные французские розы - 25 - Матовая бумага</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>3950</v>
+        <v>9100</v>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3862-3665-4631-b838-363039313734/65474535.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=817416543161</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 15 - Атласная лента</t>
+          <t>Ажурные французские розы - 35 - Атласная лента</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>5350</v>
+        <v>12650</v>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
@@ -8042,39 +8028,39 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=113980163861</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Атласная лента</t>
+          <t>Ажурные французские розы - 51 - Матовая бумага</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>8850</v>
+        <v>17500</v>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3163-3837-4832-b062-363336666632/14683462.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=162556953471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>Ажурные французские розы - 9 - Матовая бумага</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>12350</v>
+        <v>3500</v>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
@@ -8084,18 +8070,18 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=650704204641</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Атласная лента</t>
+          <t>Ажурные французские розы - 11 - Матовая бумага</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>16990</v>
+        <v>4200</v>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
@@ -8105,123 +8091,123 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=488272316371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 25 - Матовая бумага</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>9100</v>
+        <v>6759</v>
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=915258588842</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=708375581471</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 35 - Атласная лента</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>12650</v>
+        <v>10500</v>
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=562197366242</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=997102028441</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 51 - Матовая бумага</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 35</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>17500</v>
+        <v>14000</v>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=812920415532</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=585625855371</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 9 - Матовая бумага</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 11</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>3500</v>
+        <v>5350</v>
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=237078662282</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=976684960222</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Ажурные французские розы - 11 - Матовая бумага</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-3566-4863-b163-383365353130/33191387.jpg</t>
+          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-315826494761-azhurnie-frantsuzskie-rozi?editionuid=397736131802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=285996858812</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Букет пион роз кендилайт с эвкалиптом - 15</t>
+          <t>Букет пион роз кендилайт с эвкалиптом - 51</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>6759</v>
+        <v>20600</v>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
@@ -8231,1536 +8217,1536 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=708375581471</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=627988456352</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Букет пион роз кендилайт с эвкалиптом - 25</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>10500</v>
-      </c>
-      <c r="C360" t="inlineStr"/>
+        <v>5050</v>
+      </c>
+      <c r="C360" t="n">
+        <v>5500</v>
+      </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=997102028441</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Букет пион роз кендилайт с эвкалиптом - 35</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>14000</v>
-      </c>
-      <c r="C361" t="inlineStr"/>
+        <v>8250</v>
+      </c>
+      <c r="C361" t="n">
+        <v>9500</v>
+      </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=585625855371</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Букет пион роз кендилайт с эвкалиптом - 11</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>5350</v>
-      </c>
-      <c r="C362" t="inlineStr"/>
+        <v>11250</v>
+      </c>
+      <c r="C362" t="n">
+        <v>15500</v>
+      </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=976684960222</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Букет пион роз кендилайт с эвкалиптом - 9</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>4400</v>
-      </c>
-      <c r="C363" t="inlineStr"/>
+        <v>15550</v>
+      </c>
+      <c r="C363" t="n">
+        <v>18200</v>
+      </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=285996858812</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Букет пион роз кендилайт с эвкалиптом - 51</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>20600</v>
-      </c>
-      <c r="C364" t="inlineStr"/>
+        <v>27999</v>
+      </c>
+      <c r="C364" t="n">
+        <v>35500</v>
+      </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3062-6363-4933-b066-333439363166/16107521.jpg</t>
+          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-779240055231-buket-pion-roz-kendilait-s-evkaliptom?editionuid=627988456352</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 15</t>
+          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>5050</v>
+        <v>3250</v>
       </c>
       <c r="C365" t="n">
-        <v>5500</v>
+        <v>3500</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3165-3932-4861-a531-323836623735/37479800.jpg</t>
+          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=996141501582</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 25</t>
+          <t>Вау-букет 151 роза и Большой медведь</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>8250</v>
+        <v>36850</v>
       </c>
       <c r="C366" t="n">
-        <v>9500</v>
+        <v>49999</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3136-6364-4463-b436-653834326437/18587012.jpg</t>
+          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=204989056352</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 35</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>11250</v>
-      </c>
-      <c r="C367" t="n">
-        <v>15500</v>
-      </c>
+        <v>3650</v>
+      </c>
+      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6635-3139-4339-a461-326665396331/67564859.jpg</t>
+          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=958352563632</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 51</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>15550</v>
-      </c>
-      <c r="C368" t="n">
-        <v>18200</v>
-      </c>
+        <v>4150</v>
+      </c>
+      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3337-3966-4535-a635-373930393161/67450178.jpg</t>
+          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=211503308152</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 101</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>27999</v>
-      </c>
-      <c r="C369" t="n">
-        <v>35500</v>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6263-3536-4263-a631-653462343963/77678309.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=807594863492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ПИОНОВИДНЫЕ РОЗЫ ЭСПЕРАНС в оформлении - 9</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>3250</v>
-      </c>
-      <c r="C370" t="n">
-        <v>3500</v>
-      </c>
+        <v>16250</v>
+      </c>
+      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3533-4134-b562-623233306363/74005429.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630572230861-pionovidnie-rozi-esperans-v-oformlenii?editionuid=672364840112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Вау-букет 151 роза и Большой медведь</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>35950</v>
-      </c>
-      <c r="C371" t="n">
-        <v>49999</v>
-      </c>
+        <v>28440</v>
+      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3031-3464-4438-a530-343839366363/74084416.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-694865027691-vau-buket-151-roza-i-bolshoi-medved</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 9</t>
+          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>3650</v>
+        <v>7000</v>
       </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6462-6261-4231-b161-623838343362/35127181.jpg</t>
+          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=456287886831</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 11</t>
+          <t>25 белых роз в оформлении</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C373" t="inlineStr"/>
+        <v>6800</v>
+      </c>
+      <c r="C373" t="n">
+        <v>8500</v>
+      </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3663-6331-4837-a661-626362363061/94340912.jpg</t>
+          <t>https://static.tildacdn.com/stor3838-6538-4261-b337-306161613838/51749167.jpg</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=845116940031</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-602395216981-25-belih-roz-v-oformlenii</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 25</t>
+          <t>КОРЗИНА ЛЮКС</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>9100</v>
-      </c>
-      <c r="C374" t="inlineStr"/>
+        <v>50100</v>
+      </c>
+      <c r="C374" t="n">
+        <v>69990</v>
+      </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor6336-3363-4361-b966-623065383162/15116412.jpg</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=862089508361</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-832446607671-korzina-lyuks</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 51</t>
+          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>14900</v>
+        <v>5850</v>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-3038-4363-a130-353261333636/29689047.jpg</t>
+          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=295574500062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 101</t>
+          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>23990</v>
-      </c>
-      <c r="C376" t="inlineStr"/>
+        <v>6550</v>
+      </c>
+      <c r="C376" t="n">
+        <v>7500</v>
+      </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3363-4864-b836-663831653462/25298990.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=167066001212</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>КОРЗИНА РОМАШЕК из хризантем - 15</t>
+          <t>БУКЕТ КРЕМ ЛАВ</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>5750</v>
+        <v>5500</v>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3462-3837-4339-b136-373366663565/97529689.jpg</t>
+          <t>https://static.tildacdn.com/stor3031-6462-4033-b534-333166323132/98788350.jpg</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-174679188781-korzina-romashek-iz-hrizantem?editionuid=854699513312</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-krem-lav</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>КОРЗИНА ЛЮКС</t>
+          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>39000</v>
+        <v>12520</v>
       </c>
       <c r="C378" t="n">
-        <v>49990</v>
+        <v>15590</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6336-3363-4361-b966-623065383162/15116412.jpg</t>
+          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-832446607671-korzina-lyuks</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Букет "Улыбка " с лилиями и кустовыми розами</t>
+          <t>Букет Комплимент "НЕЖНОСТЬ" с белыми альстромериями</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>5850</v>
+        <v>3120</v>
       </c>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3061-3038-4737-a139-323338396665/77387930.jpg</t>
+          <t>https://static.tildacdn.com/stor6132-3736-4930-b031-323732633532/31889130.jpg</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-639588006771-buket-ulibka-s-liliyami-i-kustovimi-roza</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-belimi-alstr</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Букет "Свидание" из кустовых роз ,хризантем и орхидей</t>
+          <t>Букет Комплимент "Дюшес"</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>6550</v>
+        <v>2940</v>
       </c>
       <c r="C380" t="n">
-        <v>7500</v>
+        <v>3200</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-6532-4265-a430-643866626163/43983847.jpg</t>
+          <t>https://static.tildacdn.com/stor6661-6235-4135-b763-306665373633/14529900.jpg</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-719554914021-buket-svidanie-iz-kustovih-roz-hrizantem</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>БУКЕТ КРЕМ ЛАВ</t>
+          <t>Букет ПЛОМБИР</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>5500</v>
+        <v>4150</v>
       </c>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3835-6431-4237-a663-343437613231/32984901.jpg</t>
+          <t>https://static.tildacdn.com/stor3439-6536-4663-b263-353034613736/33171735.jpg</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-103213775721-buket-krem-lav</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>КОРЗИНА АЛЬСТРОМЕРИИ</t>
+          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>12999</v>
-      </c>
-      <c r="C382" t="n">
-        <v>15590</v>
-      </c>
+        <v>4260</v>
+      </c>
+      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3063-3261-4239-b065-376335323134/13594109.jpg</t>
+          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-337767923621-korzina-alstromerii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Букет Комплимент "НЕЖНОСТЬ" с белыми альстромериями</t>
+          <t>Игрушка Мишка-плюш с бантом "M"</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>3120</v>
+        <v>1850</v>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6132-3736-4930-b031-323732633532/31889130.jpg</t>
+          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-559524591171-buket-kompliment-nezhnost-s-belimi-alstr</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Букет Комплимент "Дюшес" с альстромериями</t>
+          <t>Игрушкп Медведь большой Ягодка</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>2510</v>
-      </c>
-      <c r="C384" t="n">
-        <v>2600</v>
-      </c>
+        <v>5500</v>
+      </c>
+      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3931-3233-4435-a435-613230333733/29080419.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-660527432041-buket-kompliment-dyushes-s-alstromeriyam</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Букет ПЛОМБИР</t>
+          <t>Игрушка Мишка-плюш "S" беж.</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>4150</v>
+        <v>1300</v>
       </c>
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3439-6536-4663-b263-353034613736/33171735.jpg</t>
+          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-437576209011-buket-plombir</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>БУКЕТ Комплимент "КРЕМ" с розамм</t>
+          <t>Игрушка Мишка-плюш "S" белый</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>4260</v>
+        <v>1300</v>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6430-3531-4135-a633-303931373131/16463170.jpg</t>
+          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-391414887741-buket-kompliment-krem-s-rozamm</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш с бантом "M"</t>
+          <t>БУКЕТ ГИПНОЗ с лилиями и розами</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C387" t="inlineStr"/>
+        <v>8200</v>
+      </c>
+      <c r="C387" t="n">
+        <v>9200</v>
+      </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3861-3531-4361-b737-646332333164/65839106.jpg</t>
+          <t>https://static.tildacdn.com/stor3264-3966-4536-b462-663135316366/99420913.jpg</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-763780152561-igrushka-mishka-plyush-s-bantom-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Игрушкп Медведь большой Ягодка</t>
+          <t>Коробка "Ангажемент "</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>5500</v>
+        <v>5780</v>
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3432-4163-b165-616433306430/44526455.jpg</t>
+          <t>https://static.tildacdn.com/stor6363-3963-4364-a238-633236333363/13028423.jpg</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-551329556541-igrushkp-medved-bolshoi-yagodka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-359890373941-korobka-angazhement-</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" беж.</t>
+          <t>Корзина французских роз</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>1300</v>
+        <v>8700</v>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3735-3232-4230-b363-303739646231/14667432.jpg</t>
+          <t>https://static.tildacdn.com/stor6563-6462-4337-a637-646433396235/18661426.jpg</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-554350694011-igrushka-mishka-plyush-s-bezh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522766706011-korzina-frantsuzskih-roz</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Игрушка Мишка-плюш "S" белый</t>
+          <t>51 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C390" t="inlineStr"/>
+        <v>16090</v>
+      </c>
+      <c r="C390" t="n">
+        <v>18990</v>
+      </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6261-6461-4639-b830-623535303032/54965825.jpg</t>
+          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-292174636271-igrushka-mishka-plyush-s-belii</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>БУКЕТ ГИПНОЗ с лилиями и розами</t>
+          <t>От всего сердца</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>8200</v>
+        <v>26800</v>
       </c>
       <c r="C391" t="n">
-        <v>9200</v>
+        <v>29890</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3264-3966-4536-b462-663135316366/99420913.jpg</t>
+          <t>https://static.tildacdn.com/stor6132-3266-4466-a338-636461616235/65353807.jpg</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-362023850031-buket-gipnoz-s-liliyami-i-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-279941586181-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Корзина французских роз</t>
+          <t>Микс "Нежный "в шляпной коробке</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>7300</v>
+        <v>4920</v>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6563-6462-4337-a637-646433396235/18661426.jpg</t>
+          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522766706011-korzina-frantsuzskih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>51 роза нежный микс в корзине</t>
+          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>15750</v>
+        <v>3890</v>
       </c>
       <c r="C393" t="n">
-        <v>18990</v>
+        <v>4500</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3733-3265-4436-a539-626133653530/77569907.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-987092854851-51-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>От всего сердца</t>
+          <t>"Ванильное небо "в шляпной коробке</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>26800</v>
-      </c>
-      <c r="C394" t="n">
-        <v>29890</v>
-      </c>
+        <v>5580</v>
+      </c>
+      <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6132-3266-4466-a338-636461616235/65353807.jpg</t>
+          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-279941586181-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Микс "Нежный "в шляпной коробке</t>
+          <t>"Мерилин "</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="C395" t="n">
-        <v>4600</v>
+        <v>3999</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3962-3266-4430-b762-613863326537/35194428.jpg</t>
+          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-940945779031-miks-nezhnii-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке лучшей маме на свете</t>
+          <t>Мон Амур - 25</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>3890</v>
-      </c>
-      <c r="C396" t="n">
-        <v>4500</v>
-      </c>
+        <v>7100</v>
+      </c>
+      <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-3138-4664-a365-636461383061/29872873.jpg</t>
+          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-654674837331-vanilnoe-nebo-v-shlyapnoi-korobke-luchsh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>"Ванильное небо "в шляпной коробке</t>
+          <t>Мон Амур - 35</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>4999</v>
+        <v>9600</v>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6338-3661-4264-a238-663161626462/86539497.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-192732519511-vanilnoe-nebo-v-shlyapnoi-korobke</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>"Мерилин "</t>
+          <t>Мон Амур - 51</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>3650</v>
+        <v>13099</v>
       </c>
       <c r="C398" t="n">
-        <v>3999</v>
+        <v>17750</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6437-3261-4836-b665-353037326231/74437439.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-570756966211-merilin-</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Мон Амур - 25</t>
+          <t>Мон Амур - 101</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C399" t="inlineStr"/>
+        <v>25090</v>
+      </c>
+      <c r="C399" t="n">
+        <v>35600</v>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3564-6238-4537-b331-393231666534/39451674.jpg</t>
+          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=330327920391</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Мон Амур - 35</t>
+          <t>Коробка с радужной гипсофилой для мамы</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>9300</v>
+        <v>3700</v>
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=460518387891</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-s-raduzhnoi-gipsofiloi-dlya-mami</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Мон Амур - 51</t>
+          <t>101 роза нежный микс в корзине</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>12990</v>
+        <v>27890</v>
       </c>
       <c r="C401" t="n">
-        <v>17750</v>
+        <v>33500</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=548699367961</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Мон Амур - 101</t>
+          <t>Букет ЛЕТО с хризантемами и ромашками</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>22990</v>
-      </c>
-      <c r="C402" t="n">
-        <v>35600</v>
-      </c>
+        <v>3060</v>
+      </c>
+      <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6530-3135-4634-a435-303833653537/62658586.jpg</t>
+          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-488774775451-mon-amur?editionuid=769488407402</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Коробка L с радужной гипсофилой для мамы</t>
+          <t>Букет ЛАПОЧКА белыми розами и диантусами</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>3799</v>
+        <v>2550</v>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-6566-4338-b733-663135306263/58897006.jpg</t>
+          <t>https://static.tildacdn.com/stor6433-6265-4162-b135-653333373065/49653431.jpg</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-600666953471-korobka-l-s-raduzhnoi-gipsofiloi-dlya-ma</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-lapochka-belimi-rozami-i-diantusam</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Коробка для мамы с гипсофилой M</t>
+          <t>Вставка сердце в букет</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>2999</v>
+        <v>250</v>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6534-3033-4361-a336-343962343961/44420144.jpg</t>
+          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-582942710541-korobka-dlya-mami-s-gipsofiloi-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>101 роза нежный микс в корзине</t>
+          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>27990</v>
+        <v>4230</v>
       </c>
       <c r="C405" t="n">
-        <v>33500</v>
+        <v>4000</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6439-3961-4033-a239-613063663235/53251246.jpg</t>
+          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-251477018101-101-roza-nezhnii-miks-v-korzine</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Букет ЛЕТО с хризантемами и ромашками</t>
+          <t>Букет 15 НЕЖНЫХ ПИОН КУСТОВЫХ РОЗ</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>3060</v>
+        <v>6950</v>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3134-6132-4238-b161-343433346231/88471835.jpg</t>
+          <t>https://static.tildacdn.com/stor3530-6536-4463-b165-383562363338/84502320.jpg</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-821180964631-buket-leto-s-hrizantemami-i-romashkami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-15-nezhnih-pion-kustovih-roz</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Букет ЛАПОЧКА белыми розами и диантусами</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>2550</v>
+        <v>4700</v>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6433-6265-4162-b135-653333373065/49653431.jpg</t>
+          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-489100649391-buket-lapochka-belimi-rozami-i-diantusam</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Вставка сердце в букет</t>
+          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>250</v>
+        <v>3500</v>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3230-6663-4066-b534-643662323937/62263476.jpg</t>
+          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-974556600091-vstavka-serdtse-v-buket</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Букет ФЕЯ с кустовыми розами и орхидеями</t>
+          <t>БУКЕТ ПРЕСТИЖ М</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>4230</v>
-      </c>
-      <c r="C409" t="n">
-        <v>4000</v>
-      </c>
+        <v>3900</v>
+      </c>
+      <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3333-6334-4865-b463-363036343536/77073318.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-3936-4962-b964-383035613735/62450227.jpg</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-720813660271-buket-feya-s-kustovimi-rozami-i-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-prestizh-m</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Букет 15 НЕЖНЫХ ПИОН КУСТОВЫХ РОЗ</t>
+          <t>Пионовидные розы в стильном конусе</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>6950</v>
+        <v>5390</v>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3530-6536-4463-b165-383562363338/84502320.jpg</t>
+          <t>https://static.tildacdn.com/stor3830-6237-4833-b633-373332376339/52184635.jpg</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-335025577601-buket-15-nezhnih-pion-kustovih-roz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-153496331021-pionovidnie-rozi-v-stilnom-konuse</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - Xl</t>
+          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>4700</v>
+        <v>3500</v>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3239-3737-4435-a633-613836386633/51111587.jpg</t>
+          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=958551503321</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Букет ПЕРВАЯ ЛЮБОВЬ с хризантемами - L</t>
+          <t>Ромашкина любовь - XXL</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C412" t="inlineStr"/>
+        <v>10600</v>
+      </c>
+      <c r="C412" t="n">
+        <v>10990</v>
+      </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6666-6663-4466-b936-653534393765/80171896.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-659712674101-buket-pervaya-lyubov-s-hrizantemami?editionuid=138048727071</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov?editionuid=407344541282</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>БУКЕТ ПРЕСТИЖ М</t>
+          <t>Ромашкина любовь - L</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3434-3936-4962-b964-383035613735/62450227.jpg</t>
+          <t>https://static.tildacdn.com/stor3464-3333-4434-a531-336439396466/16521764.jpg</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-148743167681-buket-prestizh-m</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov?editionuid=825207994132</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Букет ТВОЙ ДЕНЬ с красными розами и ромашками</t>
+          <t>ВАУ КОРЗИНА ИЗ ГИПСОФИЛ</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>3500</v>
+        <v>16540</v>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3434-6538-4239-b135-306430353463/13446289.jpg</t>
+          <t>https://static.tildacdn.com/stor6466-3031-4535-a431-633237363865/12981366.jpg</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-845612782351-buket-tvoi-den-s-krasnimi-rozami-i-romas</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-iz-gipsofil</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Ромашкина любовь - XXL</t>
+          <t>Букет "НЕЖЕНКА" с гортензией</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>10600</v>
-      </c>
-      <c r="C415" t="n">
-        <v>10990</v>
-      </c>
+        <v>3400</v>
+      </c>
+      <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3562-4761-b936-303433316233/50013829.jpg</t>
+          <t>https://static.tildacdn.com/stor6238-3964-4531-b231-323161623038/90169769.jpg</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov?editionuid=407344541282</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Ромашкина любовь - L</t>
+          <t>Букет РАДУЖНЫЙ с альстромериями</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C416" t="inlineStr"/>
+        <v>2890</v>
+      </c>
+      <c r="C416" t="n">
+        <v>3450</v>
+      </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3464-3333-4434-a531-336439396466/16521764.jpg</t>
+          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-950411727471-romashkina-lyubov?editionuid=825207994132</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>ВАУ КОРЗИНА ИЗ ГИПСОФИЛ</t>
+          <t>Букет АРОМАТ</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>14999</v>
+        <v>2880</v>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6466-3031-4535-a431-633237363865/12981366.jpg</t>
+          <t>https://static.tildacdn.com/stor6234-6430-4566-a262-386231326666/37052586.jpg</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-522713984731-vau-korzina-iz-gipsofil</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-398838219472-buket-aromat</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Букет "НЕЖЕНКА" с гортензией</t>
+          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>2900</v>
+        <v>3400</v>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6238-3964-4531-b231-323161623038/90169769.jpg</t>
+          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-500037248201-buket-nezhenka-s-gortenziei</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Букет РАДУЖНЫЙ с альстромериями</t>
+          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>2890</v>
-      </c>
-      <c r="C419" t="n">
-        <v>3450</v>
-      </c>
+        <v>5200</v>
+      </c>
+      <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6464-6336-4230-b836-643663653338/18214303.jpg</t>
+          <t>https://static.tildacdn.com/stor6531-3632-4566-a533-386631646134/30216142.jpg</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-290729033721-buket-raduzhnii-s-alstromeriyami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Букет " ТЕБЕ КОНФЕТКА"</t>
+          <t>51 пионовидная кустовая роза в нежном оформлении</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C420" t="inlineStr"/>
+        <v>18800</v>
+      </c>
+      <c r="C420" t="n">
+        <v>19800</v>
+      </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3863-3438-4534-a566-343962323762/19778219.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-843977882512-buket-tebe-konfetka</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Букет СИНЯЯ ОРХИДЕЯ</t>
+          <t>Букет РОМАНТИКА</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>5200</v>
+        <v>6190</v>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6531-3632-4566-a533-386631646134/30216142.jpg</t>
+          <t>https://static.tildacdn.com/stor3833-6263-4665-b264-386639363531/55310964.jpg</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-907367951302-buket-sinyaya-orhideya</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-359890420482-buket-romantika</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>51 пионовидная кустовая роза в нежном оформлении</t>
+          <t>Букет Комплимент с маттиолой</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>18600</v>
-      </c>
-      <c r="C422" t="n">
-        <v>18000</v>
-      </c>
+        <v>1910</v>
+      </c>
+      <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3734-4461-b561-613532326164/47005492.jpg</t>
+          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-420829464592-51-pionovidnaya-kustovaya-roza-v-nezhnom</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Букет РОМАНТИКА</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>6190</v>
+        <v>3000</v>
       </c>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3833-6263-4665-b264-386639363531/55310964.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-359890420482-buket-romantika</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Букет Комплимент с маттиолой</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>1910</v>
+        <v>3500</v>
       </c>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3634-3738-4766-b239-623731653165/17661798.jpg</t>
+          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-232892230242-buket-kompliment-s-mattioloi</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 7</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>2800</v>
+        <v>5500</v>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=567905219022</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 9</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>3500</v>
+        <v>8000</v>
       </c>
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6161-6130-4532-b930-666332343033/85650724.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=644036935612</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 15</t>
+          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>5500</v>
+        <v>15550</v>
       </c>
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3532-3633-4461-b437-343834656232/90309562.jpg</t>
+          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=726938892802</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 25</t>
+          <t>Подарочный набор для мамы 1</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>8700</v>
+        <v>3990</v>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=114889111492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ХРИЗАНТЕМНЫЙ ХИТ с ароматным эвкалиптом - 51</t>
+          <t>Подарок для мамы 2</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>15900</v>
+        <v>4990</v>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3430-3636-4034-b134-346533313532/67329986.jpg</t>
+          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-115432094412-hrizantemnii-hit-s-aromatnim-evkaliptom?editionuid=505843168492</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Подарочный набор для мамы 1</t>
+          <t>Подарок для мамы 3 селебрити</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>3990</v>
+        <v>5199</v>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
@@ -9770,102 +9756,102 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-786253932122-podarochnii-nabor-dlya-mami-1</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Подарок для мамы 2</t>
+          <t>Букет ЛЕДИ РЕД с краснымм розами</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>4990</v>
+        <v>2650</v>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6463-3033-4463-b465-336631396138/43923411.jpg</t>
+          <t>https://static.tildacdn.com/stor3965-6135-4034-a139-376262616331/46580879.jpg</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-738379822212-podarok-dlya-mami-2</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-341373252172-buket-ledi-red-s-krasnimm-rozami</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Подарок для мамы 3 селебрити</t>
+          <t>Подарочный бокс Рафаэлло</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>5199</v>
+        <v>2500</v>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3034-6266-4430-a335-333262613362/59813076.jpg</t>
+          <t>https://static.tildacdn.com/stor3132-3163-4362-b936-303066363765/67414703.jpg</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-307373021402-podarok-dlya-mami-3-selebriti</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-291016517802-podarochnii-boks-rafaello</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Букет ЛЕДИ РЕД с краснымм розами</t>
+          <t>Игрушка Мишка "Валентин"</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>2650</v>
+        <v>1300</v>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3965-6135-4034-a139-376262616331/46580879.jpg</t>
+          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-341373252172-buket-ledi-red-s-krasnimm-rozami</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Игрушка Мишка "Валентин"</t>
+          <t>Игрушка Котик - 25см</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6237-3065-4533-a239-366234626365/19817249.jpg</t>
+          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-630681598512-igrushka-mishka-valentin</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 25см</t>
+          <t>Игрушка Котик - 35см</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
@@ -9875,39 +9861,39 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=707456987082</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Игрушка Котик - 35см</t>
+          <t>Игрушка Мишка Милые глазки - 25см</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>1850</v>
+        <v>1100</v>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3737-6166-4664-a139-353931396239/38823458.jpg</t>
+          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-863762674412-igrushka-kotik?editionuid=932117895852</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Игрушка Мишка Милые глазки - 25см</t>
+          <t>Игрушка Мишка Милые глазки - 35см</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>1100</v>
+        <v>1850</v>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
@@ -9917,165 +9903,165 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=689680733112</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Игрушка Мишка Милые глазки - 35см</t>
+          <t>Гипсофила от всего сердца</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>1850</v>
+        <v>4650</v>
       </c>
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3738-6530-4433-b733-383763306638/66223016.jpg</t>
+          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-138877637952-igrushka-mishka-milie-glazki?editionuid=511053776132</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Гипсофила от всего сердца</t>
+          <t>Сладкий подарок "ПРЕСТИЖ"</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>4650</v>
+        <v>1690</v>
       </c>
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6565-3231-4933-b332-373334633831/91612642.jpg</t>
+          <t>https://static.tildacdn.com/stor3135-6532-4334-a366-383338326235/55599791.jpg</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-745191202102-gipsofila-ot-vsego-serdtsa</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-548040342792-sladkii-podarok-prestizh</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Сладкий подарок "ПРЕСТИЖ"</t>
+          <t>Детский сладкий сюрприз</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>1690</v>
+        <v>2300</v>
       </c>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3135-6532-4334-a366-383338326235/55599791.jpg</t>
+          <t>https://static.tildacdn.com/stor3163-6664-4637-b630-386361646534/95823135.jpg</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-548040342792-sladkii-podarok-prestizh</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-157699878712-detskii-sladkii-syurpriz</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Детский сладкий сюрприз</t>
+          <t>Набор косметики для девушки</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3163-6664-4637-b630-386361646534/95823135.jpg</t>
+          <t>https://static.tildacdn.com/stor6165-3033-4239-a633-333863366236/47266730.jpg</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-157699878712-detskii-sladkii-syurpriz</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-896299306932-nabor-kosmetiki-dlya-devushki</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Набор косметики для девушки</t>
+          <t>Автобус сладостей для девушки с конфетами и шоколадом</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6165-3033-4239-a633-333863366236/47266730.jpg</t>
+          <t>https://static.tildacdn.com/stor3963-3839-4266-a466-343732346365/79416309.jpg</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-896299306932-nabor-kosmetiki-dlya-devushki</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-814276260342-avtobus-sladostei-dlya-devushki-s-konfet</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Автобус сладостей для девушки с конфетами и шоколадом</t>
+          <t>Подарочный набор ДЛЯ МУЖЧИНЫ</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>3200</v>
+        <v>3900</v>
       </c>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3963-3839-4266-a466-343732346365/79416309.jpg</t>
+          <t>https://static.tildacdn.com/stor6135-6563-4262-a539-626130313439/32687838.jpg</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-814276260342-avtobus-sladostei-dlya-devushki-s-konfet</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-693724502742-podarochnii-nabor-dlya-muzhchini</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Подарочный набор ДЛЯ МУЖЧИНЫ</t>
+          <t>Пионы Сара Бернар - 5</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>3900</v>
+        <v>3150</v>
       </c>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6135-6563-4262-a539-626130313439/32687838.jpg</t>
+          <t>https://static.tildacdn.com/stor3364-3834-4631-a139-336434323835/67477016.jpg</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-693724502742-podarochnii-nabor-dlya-muzhchini</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=817212322182</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Пионы Сара Бернар - 5</t>
+          <t>Пионы Сара Бернар - 7</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>3050</v>
+        <v>4150</v>
       </c>
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
@@ -10085,39 +10071,39 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=817212322182</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=672137873212</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Пионы Сара Бернар - 7</t>
+          <t>Пионы Сара Бернар - 9</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>4050</v>
+        <v>5150</v>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3364-3834-4631-a139-336434323835/67477016.jpg</t>
+          <t>https://static.tildacdn.com/stor3732-6531-4139-b439-356330303866/21328489.jpg</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=672137873212</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=573374811462</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Пионы Сара Бернар - 9</t>
+          <t>Пионы Сара Бернар - 11</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>5050</v>
+        <v>6150</v>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
@@ -10127,60 +10113,60 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=573374811462</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=199245635062</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Пионы Сара Бернар - 11</t>
+          <t>Пионы Сара Бернар - 15</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>6050</v>
+        <v>8150</v>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3732-6531-4139-b439-356330303866/21328489.jpg</t>
+          <t>https://static.tildacdn.com/stor3361-3661-4533-a631-316539363130/40788019.jpg</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=199245635062</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=553932304422</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Пионы Сара Бернар - 15</t>
+          <t>Пионы Сара Бернар - 17</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>8050</v>
+        <v>9250</v>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3361-3661-4533-a631-316539363130/40788019.jpg</t>
+          <t>https://static.tildacdn.com/stor3064-3261-4861-b930-333738353538/14995848.jpg</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=553932304422</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=312411207952</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Пионы Сара Бернар - 17</t>
+          <t>Пионы Сара Бернар - 19</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>9050</v>
+        <v>10150</v>
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
@@ -10190,49 +10176,49 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=312411207952</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=611416781092</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Пионы Сара Бернар - 19</t>
+          <t>Пионы Сара Бернар - 25</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>1050</v>
+        <v>13150</v>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor3064-3261-4861-b930-333738353538/14995848.jpg</t>
+          <t>https://static.tildacdn.com/stor6465-6537-4635-b233-643661663663/11224874.jpg</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=611416781092</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=190345697122</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Пионы Сара Бернар - 25</t>
+          <t>Букет АМОРЕ</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>13050</v>
+        <v>8300</v>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/stor6465-6537-4635-b233-643661663663/11224874.jpg</t>
+          <t>https://static.tildacdn.com/stor6466-6261-4936-a463-373531666264/70504367.jpg</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>https://ohapka-flowers.ru/tproduct/802241395-410889245912-pioni-sara-bernar?editionuid=190345697122</t>
+          <t>https://ohapka-flowers.ru/tproduct/802241395-256767988962-buket-amore</t>
         </is>
       </c>
     </row>
